--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-08-21 13:00:00</t>
+          <t>2026-08-21 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-08-21 13:00:00</t>
+          <t>2026-08-21 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2712,22 +2712,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G15">
@@ -2875,22 +2875,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G16">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G17">
@@ -3201,22 +3201,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G18">
@@ -3364,22 +3364,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G19">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G21">
@@ -4174,12 +4174,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G24">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>2026-08-21 13:15:00</t>
+          <t>2026-08-21 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4337,12 +4337,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G25">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-08-21 13:30:00</t>
+          <t>2026-08-21 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G26">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-08-21 13:30:00</t>
+          <t>2026-08-21 13:15:00</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G29">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G30">
@@ -5315,12 +5315,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G31">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:00</t>
+          <t>2026-08-21 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5478,27 +5478,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G32">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:00</t>
+          <t>2026-08-21 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G33">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:30:00</t>
+          <t>2026-08-21 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G34">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:30:00</t>
+          <t>2026-08-21 14:00:00</t>
         </is>
       </c>
     </row>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G35">
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G36">
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-08-21 15:00:00</t>
+          <t>2026-08-21 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G38">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-08-21 15:00:00</t>
+          <t>2026-08-21 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6624,22 +6624,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G40">
@@ -6950,22 +6950,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G41">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G43">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G45">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G50">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G52">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G54">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G55">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>2026-08-21 15:15:00</t>
+          <t>2026-08-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -9390,12 +9390,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G56">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>2026-08-21 15:15:00</t>
+          <t>2026-08-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G57">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-08-21 15:30:00</t>
+          <t>2026-08-21 15:15:00</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G58">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-08-21 15:30:00</t>
+          <t>2026-08-21 15:15:00</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G59">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-08-21 15:30:00</t>
+          <t>2026-08-21 15:15:00</t>
         </is>
       </c>
     </row>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>3.26</v>
+        <v>2.61</v>
       </c>
       <c r="O60">
         <v>3.3</v>
       </c>
       <c r="P60">
-        <v>2.04</v>
+        <v>2.59</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB60">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10210,22 +10210,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G61">
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G62">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G64">
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G65">
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-08-21 15:45:00</t>
+          <t>2026-08-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G66">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-08-21 15:45:00</t>
+          <t>2026-08-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11183,12 +11183,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="N67">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="P67">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q67">
         <v>0</v>
@@ -11275,10 +11275,10 @@
         <v>0</v>
       </c>
       <c r="AC67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD67">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE67">
         <v>0</v>
@@ -11334,7 +11334,7 @@
       </c>
       <c r="AU67" t="inlineStr">
         <is>
-          <t>2026-08-21 15:45:00</t>
+          <t>2026-08-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11351,22 +11351,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P68">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11432,10 +11432,10 @@
         <v>0</v>
       </c>
       <c r="AA68">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB68">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC68">
         <v>0</v>
@@ -11514,22 +11514,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,13 +11556,13 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P69">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="Q69">
         <v>0</v>
@@ -11595,10 +11595,10 @@
         <v>0</v>
       </c>
       <c r="AA69">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB69">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC69">
         <v>0</v>
@@ -11677,22 +11677,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="O70">
-        <v>3.92</v>
+        <v>4.52</v>
       </c>
       <c r="P70">
-        <v>4.36</v>
+        <v>4.57</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11764,10 +11764,10 @@
         <v>0</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE70">
         <v>0</v>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12247,10 +12247,10 @@
         <v>0</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC73">
         <v>0</v>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G74">
@@ -12492,22 +12492,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G75">
@@ -12650,27 +12650,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G76">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>2026-08-21 16:00:00</t>
+          <t>2026-08-21 15:45:00</t>
         </is>
       </c>
     </row>
@@ -12813,27 +12813,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="O77">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="P77">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12905,10 +12905,10 @@
         <v>0</v>
       </c>
       <c r="AC77">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD77">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE77">
         <v>0</v>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-08-21 16:00:00</t>
+          <t>2026-08-21 15:45:00</t>
         </is>
       </c>
     </row>
@@ -12976,27 +12976,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O78">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P78">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13127,7 +13127,7 @@
       </c>
       <c r="AU78" t="inlineStr">
         <is>
-          <t>2026-08-21 16:00:00</t>
+          <t>2026-08-21 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13144,22 +13144,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P79">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB79">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13307,7 +13307,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AC80">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD80">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE80">
         <v>0</v>
@@ -13470,22 +13470,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13633,22 +13633,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC82">
         <v>0</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G83">
@@ -13959,7 +13959,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G84">
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G85">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G86">
@@ -14443,12 +14443,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G87">
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>2026-08-21 16:15:00</t>
+          <t>2026-08-21 16:00:00</t>
         </is>
       </c>
     </row>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G88">
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-08-21 16:30:00</t>
+          <t>2026-08-21 16:00:00</t>
         </is>
       </c>
     </row>
@@ -14769,27 +14769,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G89">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>2026-08-21 19:00:00</t>
+          <t>2026-08-21 16:00:00</t>
         </is>
       </c>
     </row>
@@ -14932,27 +14932,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G90">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-08-21 19:30:00</t>
+          <t>2026-08-21 16:15:00</t>
         </is>
       </c>
     </row>
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 16:30:00</t>
         </is>
       </c>
     </row>
@@ -15258,27 +15258,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 19:00:00</t>
         </is>
       </c>
     </row>
@@ -15421,27 +15421,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 19:30:00</t>
         </is>
       </c>
     </row>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G96">
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G97">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G100">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G103">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G115">
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G127">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G130">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G134">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G139">
@@ -23087,7 +23087,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G140">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G146">

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU150"/>
+  <dimension ref="A1:AU151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1897,22 +1897,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G10">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G11">
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-08-21 12:30:00</t>
+          <t>2026-08-21 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G13">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G14">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-08-21 13:00:00</t>
+          <t>2026-08-21 12:30:00</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G16">
@@ -3038,22 +3038,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G17">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G18">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G19">
@@ -3527,22 +3527,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G20">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G25">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G26">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-08-21 13:15:00</t>
+          <t>2026-08-21 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-08-21 13:30:00</t>
+          <t>2026-08-21 13:15:00</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G31">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G32">
@@ -5641,12 +5641,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G33">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:00</t>
+          <t>2026-08-21 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5809,22 +5809,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G34">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G35">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:30:00</t>
+          <t>2026-08-21 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G36">
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:30:00</t>
+          <t>2026-08-21 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G37">
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G38">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G39">
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-08-21 15:00:00</t>
+          <t>2026-08-21 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G40">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>2026-08-21 15:00:00</t>
+          <t>2026-08-21 14:30:00</t>
         </is>
       </c>
     </row>
@@ -6945,27 +6945,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G41">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="AU41" t="inlineStr">
         <is>
-          <t>2026-08-21 15:00:00</t>
+          <t>2026-08-21 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G42">
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G43">
@@ -7439,22 +7439,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G44">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G46">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G47">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G48">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G49">
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="G51">
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G52">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G53">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G54">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G56">
@@ -9553,12 +9553,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G57">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>2026-08-21 15:15:00</t>
+          <t>2026-08-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -9716,12 +9716,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G58">
@@ -9867,7 +9867,7 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>2026-08-21 15:15:00</t>
+          <t>2026-08-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -9879,12 +9879,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G59">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>2026-08-21 15:15:00</t>
+          <t>2026-08-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -10128,10 +10128,10 @@
         <v>0</v>
       </c>
       <c r="AA60">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB60">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC60">
         <v>0</v>
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-08-21 15:30:00</t>
+          <t>2026-08-21 15:15:00</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G61">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-08-21 15:30:00</t>
+          <t>2026-08-21 15:15:00</t>
         </is>
       </c>
     </row>
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G62">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-08-21 15:30:00</t>
+          <t>2026-08-21 15:15:00</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.26</v>
+        <v>2.61</v>
       </c>
       <c r="O63">
         <v>3.3</v>
       </c>
       <c r="P63">
-        <v>2.04</v>
+        <v>2.59</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AB63">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10699,22 +10699,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G64">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G65">
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11106,10 +11106,10 @@
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC66">
         <v>0</v>
@@ -11188,22 +11188,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G67">
@@ -11346,12 +11346,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G68">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="AU68" t="inlineStr">
         <is>
-          <t>2026-08-21 15:45:00</t>
+          <t>2026-08-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G69">
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-08-21 15:45:00</t>
+          <t>2026-08-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11672,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="P70">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11764,10 +11764,10 @@
         <v>0</v>
       </c>
       <c r="AC70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD70">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE70">
         <v>0</v>
@@ -11823,7 +11823,7 @@
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>2026-08-21 15:45:00</t>
+          <t>2026-08-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11840,22 +11840,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P71">
-        <v>3.97</v>
+        <v>0</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -11921,10 +11921,10 @@
         <v>0</v>
       </c>
       <c r="AA71">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB71">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC71">
         <v>0</v>
@@ -12003,22 +12003,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="P72">
-        <v>4.36</v>
+        <v>0</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>5.08</v>
+        <v>1.74</v>
       </c>
       <c r="O73">
-        <v>3.74</v>
+        <v>4.52</v>
       </c>
       <c r="P73">
-        <v>1.66</v>
+        <v>4.57</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12247,16 +12247,16 @@
         <v>0</v>
       </c>
       <c r="AA73">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB73">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE73">
         <v>0</v>
@@ -12329,7 +12329,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="O74">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P74">
-        <v>0</v>
+        <v>3.97</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="P75">
-        <v>0</v>
+        <v>4.36</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G77">
@@ -12981,22 +12981,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G78">
@@ -13139,27 +13139,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G79">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="AU79" t="inlineStr">
         <is>
-          <t>2026-08-21 16:00:00</t>
+          <t>2026-08-21 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13302,27 +13302,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="P80">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13394,10 +13394,10 @@
         <v>0</v>
       </c>
       <c r="AC80">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD80">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE80">
         <v>0</v>
@@ -13453,7 +13453,7 @@
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>2026-08-21 16:00:00</t>
+          <t>2026-08-21 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13465,27 +13465,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P81">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13616,7 +13616,7 @@
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>2026-08-21 16:00:00</t>
+          <t>2026-08-21 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13633,22 +13633,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="O82">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P82">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13714,10 +13714,10 @@
         <v>0</v>
       </c>
       <c r="AA82">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB82">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC82">
         <v>0</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13883,10 +13883,10 @@
         <v>0</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE83">
         <v>0</v>
@@ -13959,22 +13959,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O84">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P84">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14122,22 +14122,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,13 +14164,13 @@
         </is>
       </c>
       <c r="N85">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O85">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P85">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q85">
         <v>0</v>
@@ -14203,10 +14203,10 @@
         <v>0</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC85">
         <v>0</v>
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G86">
@@ -14448,7 +14448,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G87">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G88">
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G89">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G90">
@@ -15083,7 +15083,7 @@
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>2026-08-21 16:15:00</t>
+          <t>2026-08-21 16:00:00</t>
         </is>
       </c>
     </row>
@@ -15095,12 +15095,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G91">
@@ -15246,7 +15246,7 @@
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>2026-08-21 16:30:00</t>
+          <t>2026-08-21 16:00:00</t>
         </is>
       </c>
     </row>
@@ -15258,27 +15258,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G92">
@@ -15409,7 +15409,7 @@
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>2026-08-21 19:00:00</t>
+          <t>2026-08-21 16:00:00</t>
         </is>
       </c>
     </row>
@@ -15421,27 +15421,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G93">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-08-21 19:30:00</t>
+          <t>2026-08-21 16:15:00</t>
         </is>
       </c>
     </row>
@@ -15584,12 +15584,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G94">
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 16:30:00</t>
         </is>
       </c>
     </row>
@@ -15747,27 +15747,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G95">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 19:00:00</t>
         </is>
       </c>
     </row>
@@ -15910,27 +15910,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G96">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 19:30:00</t>
         </is>
       </c>
     </row>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G98">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G99">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G100">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G101">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G104">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G105">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Shkëndija Haraçinë</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Aresimi</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Maccabi Haifa</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G129">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G130">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Corvinul Hunedoara</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G133">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G135">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="G136">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G137">
@@ -22771,12 +22771,12 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G138">
@@ -22934,12 +22934,12 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Segesta Sisak</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kustošija</t>
+          <t>Orijent 1919</t>
         </is>
       </c>
       <c r="G139">
@@ -23097,12 +23097,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Jadran LP</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Kustošija</t>
         </is>
       </c>
       <c r="G140">
@@ -23250,7 +23250,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -23260,12 +23260,12 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Jadran LP</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G141">
@@ -23423,12 +23423,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G142">
@@ -23586,12 +23586,12 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G143">
@@ -23749,12 +23749,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G144">
@@ -23912,12 +23912,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G145">
@@ -24075,12 +24075,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G146">
@@ -24223,27 +24223,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G147">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>2026-08-21 21:30:00</t>
+          <t>2026-08-21 21:00:00</t>
         </is>
       </c>
     </row>
@@ -24391,7 +24391,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -24401,12 +24401,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G148">
@@ -24554,7 +24554,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -24564,12 +24564,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G149">
@@ -24712,156 +24712,319 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N150">
+        <v>0</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <v>0</v>
+      </c>
+      <c r="Q150">
+        <v>0</v>
+      </c>
+      <c r="R150">
+        <v>0</v>
+      </c>
+      <c r="S150">
+        <v>0</v>
+      </c>
+      <c r="T150">
+        <v>0</v>
+      </c>
+      <c r="U150">
+        <v>0</v>
+      </c>
+      <c r="V150">
+        <v>0</v>
+      </c>
+      <c r="W150">
+        <v>0</v>
+      </c>
+      <c r="X150">
+        <v>0</v>
+      </c>
+      <c r="Y150">
+        <v>0</v>
+      </c>
+      <c r="Z150">
+        <v>0</v>
+      </c>
+      <c r="AA150">
+        <v>0</v>
+      </c>
+      <c r="AB150">
+        <v>0</v>
+      </c>
+      <c r="AC150">
+        <v>0</v>
+      </c>
+      <c r="AD150">
+        <v>0</v>
+      </c>
+      <c r="AE150">
+        <v>0</v>
+      </c>
+      <c r="AF150">
+        <v>0</v>
+      </c>
+      <c r="AG150">
+        <v>0</v>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ150">
+        <v>0</v>
+      </c>
+      <c r="AK150">
+        <v>0</v>
+      </c>
+      <c r="AL150">
+        <v>0</v>
+      </c>
+      <c r="AM150">
+        <v>-1</v>
+      </c>
+      <c r="AN150">
+        <v>-1</v>
+      </c>
+      <c r="AO150">
+        <v>-1</v>
+      </c>
+      <c r="AP150">
+        <v>-1</v>
+      </c>
+      <c r="AQ150">
+        <v>0</v>
+      </c>
+      <c r="AR150">
+        <v>0</v>
+      </c>
+      <c r="AS150">
+        <v>0</v>
+      </c>
+      <c r="AT150">
+        <v>0</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>2026-08-21 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C150" t="inlineStr">
+      <c r="C151" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
+      <c r="D151" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
+      <c r="E151" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>Utah Royals</t>
         </is>
       </c>
-      <c r="G150">
-        <v>0</v>
-      </c>
-      <c r="H150">
-        <v>0</v>
-      </c>
-      <c r="I150">
-        <v>0</v>
-      </c>
-      <c r="J150">
-        <v>0</v>
-      </c>
-      <c r="K150">
-        <v>0</v>
-      </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-      <c r="M150" t="inlineStr">
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N150">
-        <v>0</v>
-      </c>
-      <c r="O150">
-        <v>0</v>
-      </c>
-      <c r="P150">
-        <v>0</v>
-      </c>
-      <c r="Q150">
-        <v>0</v>
-      </c>
-      <c r="R150">
-        <v>0</v>
-      </c>
-      <c r="S150">
-        <v>0</v>
-      </c>
-      <c r="T150">
-        <v>0</v>
-      </c>
-      <c r="U150">
-        <v>0</v>
-      </c>
-      <c r="V150">
-        <v>0</v>
-      </c>
-      <c r="W150">
-        <v>0</v>
-      </c>
-      <c r="X150">
-        <v>0</v>
-      </c>
-      <c r="Y150">
-        <v>0</v>
-      </c>
-      <c r="Z150">
-        <v>0</v>
-      </c>
-      <c r="AA150">
-        <v>0</v>
-      </c>
-      <c r="AB150">
-        <v>0</v>
-      </c>
-      <c r="AC150">
-        <v>0</v>
-      </c>
-      <c r="AD150">
-        <v>0</v>
-      </c>
-      <c r="AE150">
-        <v>0</v>
-      </c>
-      <c r="AF150">
-        <v>0</v>
-      </c>
-      <c r="AG150">
-        <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ150">
-        <v>0</v>
-      </c>
-      <c r="AK150">
-        <v>0</v>
-      </c>
-      <c r="AL150">
-        <v>0</v>
-      </c>
-      <c r="AM150">
-        <v>-1</v>
-      </c>
-      <c r="AN150">
-        <v>-1</v>
-      </c>
-      <c r="AO150">
-        <v>-1</v>
-      </c>
-      <c r="AP150">
-        <v>-1</v>
-      </c>
-      <c r="AQ150">
-        <v>0</v>
-      </c>
-      <c r="AR150">
-        <v>0</v>
-      </c>
-      <c r="AS150">
-        <v>0</v>
-      </c>
-      <c r="AT150">
-        <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
+      <c r="N151">
+        <v>0</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <v>0</v>
+      </c>
+      <c r="Q151">
+        <v>0</v>
+      </c>
+      <c r="R151">
+        <v>0</v>
+      </c>
+      <c r="S151">
+        <v>0</v>
+      </c>
+      <c r="T151">
+        <v>0</v>
+      </c>
+      <c r="U151">
+        <v>0</v>
+      </c>
+      <c r="V151">
+        <v>0</v>
+      </c>
+      <c r="W151">
+        <v>0</v>
+      </c>
+      <c r="X151">
+        <v>0</v>
+      </c>
+      <c r="Y151">
+        <v>0</v>
+      </c>
+      <c r="Z151">
+        <v>0</v>
+      </c>
+      <c r="AA151">
+        <v>0</v>
+      </c>
+      <c r="AB151">
+        <v>0</v>
+      </c>
+      <c r="AC151">
+        <v>0</v>
+      </c>
+      <c r="AD151">
+        <v>0</v>
+      </c>
+      <c r="AE151">
+        <v>0</v>
+      </c>
+      <c r="AF151">
+        <v>0</v>
+      </c>
+      <c r="AG151">
+        <v>0</v>
+      </c>
+      <c r="AH151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ151">
+        <v>0</v>
+      </c>
+      <c r="AK151">
+        <v>0</v>
+      </c>
+      <c r="AL151">
+        <v>0</v>
+      </c>
+      <c r="AM151">
+        <v>-1</v>
+      </c>
+      <c r="AN151">
+        <v>-1</v>
+      </c>
+      <c r="AO151">
+        <v>-1</v>
+      </c>
+      <c r="AP151">
+        <v>-1</v>
+      </c>
+      <c r="AQ151">
+        <v>0</v>
+      </c>
+      <c r="AR151">
+        <v>0</v>
+      </c>
+      <c r="AS151">
+        <v>0</v>
+      </c>
+      <c r="AT151">
+        <v>0</v>
+      </c>
+      <c r="AU151" t="inlineStr">
         <is>
           <t>2026-08-21 23:00:00</t>
         </is>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G79">
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G80">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G106">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G107">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G109">

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.72</v>
+        <v>5.08</v>
       </c>
       <c r="O75">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="P75">
-        <v>4.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>5.08</v>
+        <v>1.72</v>
       </c>
       <c r="O76">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="P76">
-        <v>1.66</v>
+        <v>4.36</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB76">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC76">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G42">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G43">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O78">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P78">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="O79">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P79">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O80">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P80">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O92">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P92">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q92">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G90">

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU151"/>
+  <dimension ref="A1:AU139"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G45">
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G46">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G47">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G48">
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G49">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G51">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="G52">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G57">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G59">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>5.08</v>
+        <v>1.72</v>
       </c>
       <c r="O75">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="P75">
-        <v>1.66</v>
+        <v>4.36</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12573,10 +12573,10 @@
         <v>0</v>
       </c>
       <c r="AA75">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB75">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.72</v>
+        <v>5.08</v>
       </c>
       <c r="O76">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="P76">
-        <v>4.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G90">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shkëndija Haraçinë</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Aresimi</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G117">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G119">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,22 +19990,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Maccabi Haifa</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G123">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G126">
@@ -20968,7 +20968,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G128">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Corvinul Hunedoara</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G131">
@@ -21783,7 +21783,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G132">
@@ -21946,7 +21946,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G133">
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -22119,12 +22119,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G134">
@@ -22272,7 +22272,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -22282,12 +22282,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G135">
@@ -22430,27 +22430,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G136">
@@ -22581,7 +22581,7 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -22593,27 +22593,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G137">
@@ -22744,7 +22744,7 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -22756,27 +22756,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G138">
@@ -22907,7 +22907,7 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -22919,27 +22919,27 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Segesta Sisak</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Orijent 1919</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G139">
@@ -23069,1962 +23069,6 @@
         <v>0</v>
       </c>
       <c r="AU139" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Croatia Druga HNL</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Dugopolje</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Kustošija</t>
-        </is>
-      </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-      <c r="H140">
-        <v>0</v>
-      </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
-      <c r="K140">
-        <v>0</v>
-      </c>
-      <c r="L140">
-        <v>0</v>
-      </c>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N140">
-        <v>0</v>
-      </c>
-      <c r="O140">
-        <v>0</v>
-      </c>
-      <c r="P140">
-        <v>0</v>
-      </c>
-      <c r="Q140">
-        <v>0</v>
-      </c>
-      <c r="R140">
-        <v>0</v>
-      </c>
-      <c r="S140">
-        <v>0</v>
-      </c>
-      <c r="T140">
-        <v>0</v>
-      </c>
-      <c r="U140">
-        <v>0</v>
-      </c>
-      <c r="V140">
-        <v>0</v>
-      </c>
-      <c r="W140">
-        <v>0</v>
-      </c>
-      <c r="X140">
-        <v>0</v>
-      </c>
-      <c r="Y140">
-        <v>0</v>
-      </c>
-      <c r="Z140">
-        <v>0</v>
-      </c>
-      <c r="AA140">
-        <v>0</v>
-      </c>
-      <c r="AB140">
-        <v>0</v>
-      </c>
-      <c r="AC140">
-        <v>0</v>
-      </c>
-      <c r="AD140">
-        <v>0</v>
-      </c>
-      <c r="AE140">
-        <v>0</v>
-      </c>
-      <c r="AF140">
-        <v>0</v>
-      </c>
-      <c r="AG140">
-        <v>0</v>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ140">
-        <v>0</v>
-      </c>
-      <c r="AK140">
-        <v>0</v>
-      </c>
-      <c r="AL140">
-        <v>0</v>
-      </c>
-      <c r="AM140">
-        <v>-1</v>
-      </c>
-      <c r="AN140">
-        <v>-1</v>
-      </c>
-      <c r="AO140">
-        <v>-1</v>
-      </c>
-      <c r="AP140">
-        <v>-1</v>
-      </c>
-      <c r="AQ140">
-        <v>0</v>
-      </c>
-      <c r="AR140">
-        <v>0</v>
-      </c>
-      <c r="AS140">
-        <v>0</v>
-      </c>
-      <c r="AT140">
-        <v>0</v>
-      </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Croatia Druga HNL</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Jadran LP</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Opatija</t>
-        </is>
-      </c>
-      <c r="G141">
-        <v>0</v>
-      </c>
-      <c r="H141">
-        <v>0</v>
-      </c>
-      <c r="I141">
-        <v>0</v>
-      </c>
-      <c r="J141">
-        <v>0</v>
-      </c>
-      <c r="K141">
-        <v>0</v>
-      </c>
-      <c r="L141">
-        <v>0</v>
-      </c>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N141">
-        <v>0</v>
-      </c>
-      <c r="O141">
-        <v>0</v>
-      </c>
-      <c r="P141">
-        <v>0</v>
-      </c>
-      <c r="Q141">
-        <v>0</v>
-      </c>
-      <c r="R141">
-        <v>0</v>
-      </c>
-      <c r="S141">
-        <v>0</v>
-      </c>
-      <c r="T141">
-        <v>0</v>
-      </c>
-      <c r="U141">
-        <v>0</v>
-      </c>
-      <c r="V141">
-        <v>0</v>
-      </c>
-      <c r="W141">
-        <v>0</v>
-      </c>
-      <c r="X141">
-        <v>0</v>
-      </c>
-      <c r="Y141">
-        <v>0</v>
-      </c>
-      <c r="Z141">
-        <v>0</v>
-      </c>
-      <c r="AA141">
-        <v>0</v>
-      </c>
-      <c r="AB141">
-        <v>0</v>
-      </c>
-      <c r="AC141">
-        <v>0</v>
-      </c>
-      <c r="AD141">
-        <v>0</v>
-      </c>
-      <c r="AE141">
-        <v>0</v>
-      </c>
-      <c r="AF141">
-        <v>0</v>
-      </c>
-      <c r="AG141">
-        <v>0</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ141">
-        <v>0</v>
-      </c>
-      <c r="AK141">
-        <v>0</v>
-      </c>
-      <c r="AL141">
-        <v>0</v>
-      </c>
-      <c r="AM141">
-        <v>-1</v>
-      </c>
-      <c r="AN141">
-        <v>-1</v>
-      </c>
-      <c r="AO141">
-        <v>-1</v>
-      </c>
-      <c r="AP141">
-        <v>-1</v>
-      </c>
-      <c r="AQ141">
-        <v>0</v>
-      </c>
-      <c r="AR141">
-        <v>0</v>
-      </c>
-      <c r="AS141">
-        <v>0</v>
-      </c>
-      <c r="AT141">
-        <v>0</v>
-      </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Bulgaria First League</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Botev Vratsa</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Botev Plovdiv</t>
-        </is>
-      </c>
-      <c r="G142">
-        <v>0</v>
-      </c>
-      <c r="H142">
-        <v>0</v>
-      </c>
-      <c r="I142">
-        <v>0</v>
-      </c>
-      <c r="J142">
-        <v>0</v>
-      </c>
-      <c r="K142">
-        <v>0</v>
-      </c>
-      <c r="L142">
-        <v>0</v>
-      </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N142">
-        <v>0</v>
-      </c>
-      <c r="O142">
-        <v>0</v>
-      </c>
-      <c r="P142">
-        <v>0</v>
-      </c>
-      <c r="Q142">
-        <v>0</v>
-      </c>
-      <c r="R142">
-        <v>0</v>
-      </c>
-      <c r="S142">
-        <v>0</v>
-      </c>
-      <c r="T142">
-        <v>0</v>
-      </c>
-      <c r="U142">
-        <v>0</v>
-      </c>
-      <c r="V142">
-        <v>0</v>
-      </c>
-      <c r="W142">
-        <v>0</v>
-      </c>
-      <c r="X142">
-        <v>0</v>
-      </c>
-      <c r="Y142">
-        <v>0</v>
-      </c>
-      <c r="Z142">
-        <v>0</v>
-      </c>
-      <c r="AA142">
-        <v>0</v>
-      </c>
-      <c r="AB142">
-        <v>0</v>
-      </c>
-      <c r="AC142">
-        <v>0</v>
-      </c>
-      <c r="AD142">
-        <v>0</v>
-      </c>
-      <c r="AE142">
-        <v>0</v>
-      </c>
-      <c r="AF142">
-        <v>0</v>
-      </c>
-      <c r="AG142">
-        <v>0</v>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ142">
-        <v>0</v>
-      </c>
-      <c r="AK142">
-        <v>0</v>
-      </c>
-      <c r="AL142">
-        <v>0</v>
-      </c>
-      <c r="AM142">
-        <v>-1</v>
-      </c>
-      <c r="AN142">
-        <v>-1</v>
-      </c>
-      <c r="AO142">
-        <v>-1</v>
-      </c>
-      <c r="AP142">
-        <v>-1</v>
-      </c>
-      <c r="AQ142">
-        <v>0</v>
-      </c>
-      <c r="AR142">
-        <v>0</v>
-      </c>
-      <c r="AS142">
-        <v>0</v>
-      </c>
-      <c r="AT142">
-        <v>0</v>
-      </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Bulgaria First League</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Septemvri Sofia</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>CSKA 1948 Sofia</t>
-        </is>
-      </c>
-      <c r="G143">
-        <v>0</v>
-      </c>
-      <c r="H143">
-        <v>0</v>
-      </c>
-      <c r="I143">
-        <v>0</v>
-      </c>
-      <c r="J143">
-        <v>0</v>
-      </c>
-      <c r="K143">
-        <v>0</v>
-      </c>
-      <c r="L143">
-        <v>0</v>
-      </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N143">
-        <v>0</v>
-      </c>
-      <c r="O143">
-        <v>0</v>
-      </c>
-      <c r="P143">
-        <v>0</v>
-      </c>
-      <c r="Q143">
-        <v>0</v>
-      </c>
-      <c r="R143">
-        <v>0</v>
-      </c>
-      <c r="S143">
-        <v>0</v>
-      </c>
-      <c r="T143">
-        <v>0</v>
-      </c>
-      <c r="U143">
-        <v>0</v>
-      </c>
-      <c r="V143">
-        <v>0</v>
-      </c>
-      <c r="W143">
-        <v>0</v>
-      </c>
-      <c r="X143">
-        <v>0</v>
-      </c>
-      <c r="Y143">
-        <v>0</v>
-      </c>
-      <c r="Z143">
-        <v>0</v>
-      </c>
-      <c r="AA143">
-        <v>0</v>
-      </c>
-      <c r="AB143">
-        <v>0</v>
-      </c>
-      <c r="AC143">
-        <v>0</v>
-      </c>
-      <c r="AD143">
-        <v>0</v>
-      </c>
-      <c r="AE143">
-        <v>0</v>
-      </c>
-      <c r="AF143">
-        <v>0</v>
-      </c>
-      <c r="AG143">
-        <v>0</v>
-      </c>
-      <c r="AH143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ143">
-        <v>0</v>
-      </c>
-      <c r="AK143">
-        <v>0</v>
-      </c>
-      <c r="AL143">
-        <v>0</v>
-      </c>
-      <c r="AM143">
-        <v>-1</v>
-      </c>
-      <c r="AN143">
-        <v>-1</v>
-      </c>
-      <c r="AO143">
-        <v>-1</v>
-      </c>
-      <c r="AP143">
-        <v>-1</v>
-      </c>
-      <c r="AQ143">
-        <v>0</v>
-      </c>
-      <c r="AR143">
-        <v>0</v>
-      </c>
-      <c r="AS143">
-        <v>0</v>
-      </c>
-      <c r="AT143">
-        <v>0</v>
-      </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Bulgaria First League</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Lokomotiv Sofia 1929</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>CSKA Sofia</t>
-        </is>
-      </c>
-      <c r="G144">
-        <v>0</v>
-      </c>
-      <c r="H144">
-        <v>0</v>
-      </c>
-      <c r="I144">
-        <v>0</v>
-      </c>
-      <c r="J144">
-        <v>0</v>
-      </c>
-      <c r="K144">
-        <v>0</v>
-      </c>
-      <c r="L144">
-        <v>0</v>
-      </c>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N144">
-        <v>0</v>
-      </c>
-      <c r="O144">
-        <v>0</v>
-      </c>
-      <c r="P144">
-        <v>0</v>
-      </c>
-      <c r="Q144">
-        <v>0</v>
-      </c>
-      <c r="R144">
-        <v>0</v>
-      </c>
-      <c r="S144">
-        <v>0</v>
-      </c>
-      <c r="T144">
-        <v>0</v>
-      </c>
-      <c r="U144">
-        <v>0</v>
-      </c>
-      <c r="V144">
-        <v>0</v>
-      </c>
-      <c r="W144">
-        <v>0</v>
-      </c>
-      <c r="X144">
-        <v>0</v>
-      </c>
-      <c r="Y144">
-        <v>0</v>
-      </c>
-      <c r="Z144">
-        <v>0</v>
-      </c>
-      <c r="AA144">
-        <v>0</v>
-      </c>
-      <c r="AB144">
-        <v>0</v>
-      </c>
-      <c r="AC144">
-        <v>0</v>
-      </c>
-      <c r="AD144">
-        <v>0</v>
-      </c>
-      <c r="AE144">
-        <v>0</v>
-      </c>
-      <c r="AF144">
-        <v>0</v>
-      </c>
-      <c r="AG144">
-        <v>0</v>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ144">
-        <v>0</v>
-      </c>
-      <c r="AK144">
-        <v>0</v>
-      </c>
-      <c r="AL144">
-        <v>0</v>
-      </c>
-      <c r="AM144">
-        <v>-1</v>
-      </c>
-      <c r="AN144">
-        <v>-1</v>
-      </c>
-      <c r="AO144">
-        <v>-1</v>
-      </c>
-      <c r="AP144">
-        <v>-1</v>
-      </c>
-      <c r="AQ144">
-        <v>0</v>
-      </c>
-      <c r="AR144">
-        <v>0</v>
-      </c>
-      <c r="AS144">
-        <v>0</v>
-      </c>
-      <c r="AT144">
-        <v>0</v>
-      </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Bulgaria First League</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Levski Sofia</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Spartak Varna</t>
-        </is>
-      </c>
-      <c r="G145">
-        <v>0</v>
-      </c>
-      <c r="H145">
-        <v>0</v>
-      </c>
-      <c r="I145">
-        <v>0</v>
-      </c>
-      <c r="J145">
-        <v>0</v>
-      </c>
-      <c r="K145">
-        <v>0</v>
-      </c>
-      <c r="L145">
-        <v>0</v>
-      </c>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N145">
-        <v>0</v>
-      </c>
-      <c r="O145">
-        <v>0</v>
-      </c>
-      <c r="P145">
-        <v>0</v>
-      </c>
-      <c r="Q145">
-        <v>0</v>
-      </c>
-      <c r="R145">
-        <v>0</v>
-      </c>
-      <c r="S145">
-        <v>0</v>
-      </c>
-      <c r="T145">
-        <v>0</v>
-      </c>
-      <c r="U145">
-        <v>0</v>
-      </c>
-      <c r="V145">
-        <v>0</v>
-      </c>
-      <c r="W145">
-        <v>0</v>
-      </c>
-      <c r="X145">
-        <v>0</v>
-      </c>
-      <c r="Y145">
-        <v>0</v>
-      </c>
-      <c r="Z145">
-        <v>0</v>
-      </c>
-      <c r="AA145">
-        <v>0</v>
-      </c>
-      <c r="AB145">
-        <v>0</v>
-      </c>
-      <c r="AC145">
-        <v>0</v>
-      </c>
-      <c r="AD145">
-        <v>0</v>
-      </c>
-      <c r="AE145">
-        <v>0</v>
-      </c>
-      <c r="AF145">
-        <v>0</v>
-      </c>
-      <c r="AG145">
-        <v>0</v>
-      </c>
-      <c r="AH145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ145">
-        <v>0</v>
-      </c>
-      <c r="AK145">
-        <v>0</v>
-      </c>
-      <c r="AL145">
-        <v>0</v>
-      </c>
-      <c r="AM145">
-        <v>-1</v>
-      </c>
-      <c r="AN145">
-        <v>-1</v>
-      </c>
-      <c r="AO145">
-        <v>-1</v>
-      </c>
-      <c r="AP145">
-        <v>-1</v>
-      </c>
-      <c r="AQ145">
-        <v>0</v>
-      </c>
-      <c r="AR145">
-        <v>0</v>
-      </c>
-      <c r="AS145">
-        <v>0</v>
-      </c>
-      <c r="AT145">
-        <v>0</v>
-      </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Bulgaria First League</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Ludogorets</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Slavia Sofia</t>
-        </is>
-      </c>
-      <c r="G146">
-        <v>0</v>
-      </c>
-      <c r="H146">
-        <v>0</v>
-      </c>
-      <c r="I146">
-        <v>0</v>
-      </c>
-      <c r="J146">
-        <v>0</v>
-      </c>
-      <c r="K146">
-        <v>0</v>
-      </c>
-      <c r="L146">
-        <v>0</v>
-      </c>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N146">
-        <v>0</v>
-      </c>
-      <c r="O146">
-        <v>0</v>
-      </c>
-      <c r="P146">
-        <v>0</v>
-      </c>
-      <c r="Q146">
-        <v>0</v>
-      </c>
-      <c r="R146">
-        <v>0</v>
-      </c>
-      <c r="S146">
-        <v>0</v>
-      </c>
-      <c r="T146">
-        <v>0</v>
-      </c>
-      <c r="U146">
-        <v>0</v>
-      </c>
-      <c r="V146">
-        <v>0</v>
-      </c>
-      <c r="W146">
-        <v>0</v>
-      </c>
-      <c r="X146">
-        <v>0</v>
-      </c>
-      <c r="Y146">
-        <v>0</v>
-      </c>
-      <c r="Z146">
-        <v>0</v>
-      </c>
-      <c r="AA146">
-        <v>0</v>
-      </c>
-      <c r="AB146">
-        <v>0</v>
-      </c>
-      <c r="AC146">
-        <v>0</v>
-      </c>
-      <c r="AD146">
-        <v>0</v>
-      </c>
-      <c r="AE146">
-        <v>0</v>
-      </c>
-      <c r="AF146">
-        <v>0</v>
-      </c>
-      <c r="AG146">
-        <v>0</v>
-      </c>
-      <c r="AH146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ146">
-        <v>0</v>
-      </c>
-      <c r="AK146">
-        <v>0</v>
-      </c>
-      <c r="AL146">
-        <v>0</v>
-      </c>
-      <c r="AM146">
-        <v>-1</v>
-      </c>
-      <c r="AN146">
-        <v>-1</v>
-      </c>
-      <c r="AO146">
-        <v>-1</v>
-      </c>
-      <c r="AP146">
-        <v>-1</v>
-      </c>
-      <c r="AQ146">
-        <v>0</v>
-      </c>
-      <c r="AR146">
-        <v>0</v>
-      </c>
-      <c r="AS146">
-        <v>0</v>
-      </c>
-      <c r="AT146">
-        <v>0</v>
-      </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Bulgaria First League</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Lokomotiv Plovdiv</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Arda</t>
-        </is>
-      </c>
-      <c r="G147">
-        <v>0</v>
-      </c>
-      <c r="H147">
-        <v>0</v>
-      </c>
-      <c r="I147">
-        <v>0</v>
-      </c>
-      <c r="J147">
-        <v>0</v>
-      </c>
-      <c r="K147">
-        <v>0</v>
-      </c>
-      <c r="L147">
-        <v>0</v>
-      </c>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N147">
-        <v>0</v>
-      </c>
-      <c r="O147">
-        <v>0</v>
-      </c>
-      <c r="P147">
-        <v>0</v>
-      </c>
-      <c r="Q147">
-        <v>0</v>
-      </c>
-      <c r="R147">
-        <v>0</v>
-      </c>
-      <c r="S147">
-        <v>0</v>
-      </c>
-      <c r="T147">
-        <v>0</v>
-      </c>
-      <c r="U147">
-        <v>0</v>
-      </c>
-      <c r="V147">
-        <v>0</v>
-      </c>
-      <c r="W147">
-        <v>0</v>
-      </c>
-      <c r="X147">
-        <v>0</v>
-      </c>
-      <c r="Y147">
-        <v>0</v>
-      </c>
-      <c r="Z147">
-        <v>0</v>
-      </c>
-      <c r="AA147">
-        <v>0</v>
-      </c>
-      <c r="AB147">
-        <v>0</v>
-      </c>
-      <c r="AC147">
-        <v>0</v>
-      </c>
-      <c r="AD147">
-        <v>0</v>
-      </c>
-      <c r="AE147">
-        <v>0</v>
-      </c>
-      <c r="AF147">
-        <v>0</v>
-      </c>
-      <c r="AG147">
-        <v>0</v>
-      </c>
-      <c r="AH147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ147">
-        <v>0</v>
-      </c>
-      <c r="AK147">
-        <v>0</v>
-      </c>
-      <c r="AL147">
-        <v>0</v>
-      </c>
-      <c r="AM147">
-        <v>-1</v>
-      </c>
-      <c r="AN147">
-        <v>-1</v>
-      </c>
-      <c r="AO147">
-        <v>-1</v>
-      </c>
-      <c r="AP147">
-        <v>-1</v>
-      </c>
-      <c r="AQ147">
-        <v>0</v>
-      </c>
-      <c r="AR147">
-        <v>0</v>
-      </c>
-      <c r="AS147">
-        <v>0</v>
-      </c>
-      <c r="AT147">
-        <v>0</v>
-      </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Rangers</t>
-        </is>
-      </c>
-      <c r="G148">
-        <v>0</v>
-      </c>
-      <c r="H148">
-        <v>0</v>
-      </c>
-      <c r="I148">
-        <v>0</v>
-      </c>
-      <c r="J148">
-        <v>0</v>
-      </c>
-      <c r="K148">
-        <v>0</v>
-      </c>
-      <c r="L148">
-        <v>0</v>
-      </c>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N148">
-        <v>0</v>
-      </c>
-      <c r="O148">
-        <v>0</v>
-      </c>
-      <c r="P148">
-        <v>0</v>
-      </c>
-      <c r="Q148">
-        <v>0</v>
-      </c>
-      <c r="R148">
-        <v>0</v>
-      </c>
-      <c r="S148">
-        <v>0</v>
-      </c>
-      <c r="T148">
-        <v>0</v>
-      </c>
-      <c r="U148">
-        <v>0</v>
-      </c>
-      <c r="V148">
-        <v>0</v>
-      </c>
-      <c r="W148">
-        <v>0</v>
-      </c>
-      <c r="X148">
-        <v>0</v>
-      </c>
-      <c r="Y148">
-        <v>0</v>
-      </c>
-      <c r="Z148">
-        <v>0</v>
-      </c>
-      <c r="AA148">
-        <v>0</v>
-      </c>
-      <c r="AB148">
-        <v>0</v>
-      </c>
-      <c r="AC148">
-        <v>0</v>
-      </c>
-      <c r="AD148">
-        <v>0</v>
-      </c>
-      <c r="AE148">
-        <v>0</v>
-      </c>
-      <c r="AF148">
-        <v>0</v>
-      </c>
-      <c r="AG148">
-        <v>0</v>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ148">
-        <v>0</v>
-      </c>
-      <c r="AK148">
-        <v>0</v>
-      </c>
-      <c r="AL148">
-        <v>0</v>
-      </c>
-      <c r="AM148">
-        <v>-1</v>
-      </c>
-      <c r="AN148">
-        <v>-1</v>
-      </c>
-      <c r="AO148">
-        <v>-1</v>
-      </c>
-      <c r="AP148">
-        <v>-1</v>
-      </c>
-      <c r="AQ148">
-        <v>0</v>
-      </c>
-      <c r="AR148">
-        <v>0</v>
-      </c>
-      <c r="AS148">
-        <v>0</v>
-      </c>
-      <c r="AT148">
-        <v>0</v>
-      </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Unión La Calera</t>
-        </is>
-      </c>
-      <c r="G149">
-        <v>0</v>
-      </c>
-      <c r="H149">
-        <v>0</v>
-      </c>
-      <c r="I149">
-        <v>0</v>
-      </c>
-      <c r="J149">
-        <v>0</v>
-      </c>
-      <c r="K149">
-        <v>0</v>
-      </c>
-      <c r="L149">
-        <v>0</v>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N149">
-        <v>0</v>
-      </c>
-      <c r="O149">
-        <v>0</v>
-      </c>
-      <c r="P149">
-        <v>0</v>
-      </c>
-      <c r="Q149">
-        <v>0</v>
-      </c>
-      <c r="R149">
-        <v>0</v>
-      </c>
-      <c r="S149">
-        <v>0</v>
-      </c>
-      <c r="T149">
-        <v>0</v>
-      </c>
-      <c r="U149">
-        <v>0</v>
-      </c>
-      <c r="V149">
-        <v>0</v>
-      </c>
-      <c r="W149">
-        <v>0</v>
-      </c>
-      <c r="X149">
-        <v>0</v>
-      </c>
-      <c r="Y149">
-        <v>0</v>
-      </c>
-      <c r="Z149">
-        <v>0</v>
-      </c>
-      <c r="AA149">
-        <v>0</v>
-      </c>
-      <c r="AB149">
-        <v>0</v>
-      </c>
-      <c r="AC149">
-        <v>0</v>
-      </c>
-      <c r="AD149">
-        <v>0</v>
-      </c>
-      <c r="AE149">
-        <v>0</v>
-      </c>
-      <c r="AF149">
-        <v>0</v>
-      </c>
-      <c r="AG149">
-        <v>0</v>
-      </c>
-      <c r="AH149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ149">
-        <v>0</v>
-      </c>
-      <c r="AK149">
-        <v>0</v>
-      </c>
-      <c r="AL149">
-        <v>0</v>
-      </c>
-      <c r="AM149">
-        <v>-1</v>
-      </c>
-      <c r="AN149">
-        <v>-1</v>
-      </c>
-      <c r="AO149">
-        <v>-1</v>
-      </c>
-      <c r="AP149">
-        <v>-1</v>
-      </c>
-      <c r="AQ149">
-        <v>0</v>
-      </c>
-      <c r="AR149">
-        <v>0</v>
-      </c>
-      <c r="AS149">
-        <v>0</v>
-      </c>
-      <c r="AT149">
-        <v>0</v>
-      </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
-      <c r="G150">
-        <v>0</v>
-      </c>
-      <c r="H150">
-        <v>0</v>
-      </c>
-      <c r="I150">
-        <v>0</v>
-      </c>
-      <c r="J150">
-        <v>0</v>
-      </c>
-      <c r="K150">
-        <v>0</v>
-      </c>
-      <c r="L150">
-        <v>0</v>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N150">
-        <v>0</v>
-      </c>
-      <c r="O150">
-        <v>0</v>
-      </c>
-      <c r="P150">
-        <v>0</v>
-      </c>
-      <c r="Q150">
-        <v>0</v>
-      </c>
-      <c r="R150">
-        <v>0</v>
-      </c>
-      <c r="S150">
-        <v>0</v>
-      </c>
-      <c r="T150">
-        <v>0</v>
-      </c>
-      <c r="U150">
-        <v>0</v>
-      </c>
-      <c r="V150">
-        <v>0</v>
-      </c>
-      <c r="W150">
-        <v>0</v>
-      </c>
-      <c r="X150">
-        <v>0</v>
-      </c>
-      <c r="Y150">
-        <v>0</v>
-      </c>
-      <c r="Z150">
-        <v>0</v>
-      </c>
-      <c r="AA150">
-        <v>0</v>
-      </c>
-      <c r="AB150">
-        <v>0</v>
-      </c>
-      <c r="AC150">
-        <v>0</v>
-      </c>
-      <c r="AD150">
-        <v>0</v>
-      </c>
-      <c r="AE150">
-        <v>0</v>
-      </c>
-      <c r="AF150">
-        <v>0</v>
-      </c>
-      <c r="AG150">
-        <v>0</v>
-      </c>
-      <c r="AH150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI150" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ150">
-        <v>0</v>
-      </c>
-      <c r="AK150">
-        <v>0</v>
-      </c>
-      <c r="AL150">
-        <v>0</v>
-      </c>
-      <c r="AM150">
-        <v>-1</v>
-      </c>
-      <c r="AN150">
-        <v>-1</v>
-      </c>
-      <c r="AO150">
-        <v>-1</v>
-      </c>
-      <c r="AP150">
-        <v>-1</v>
-      </c>
-      <c r="AQ150">
-        <v>0</v>
-      </c>
-      <c r="AR150">
-        <v>0</v>
-      </c>
-      <c r="AS150">
-        <v>0</v>
-      </c>
-      <c r="AT150">
-        <v>0</v>
-      </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="G151">
-        <v>0</v>
-      </c>
-      <c r="H151">
-        <v>0</v>
-      </c>
-      <c r="I151">
-        <v>0</v>
-      </c>
-      <c r="J151">
-        <v>0</v>
-      </c>
-      <c r="K151">
-        <v>0</v>
-      </c>
-      <c r="L151">
-        <v>0</v>
-      </c>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N151">
-        <v>0</v>
-      </c>
-      <c r="O151">
-        <v>0</v>
-      </c>
-      <c r="P151">
-        <v>0</v>
-      </c>
-      <c r="Q151">
-        <v>0</v>
-      </c>
-      <c r="R151">
-        <v>0</v>
-      </c>
-      <c r="S151">
-        <v>0</v>
-      </c>
-      <c r="T151">
-        <v>0</v>
-      </c>
-      <c r="U151">
-        <v>0</v>
-      </c>
-      <c r="V151">
-        <v>0</v>
-      </c>
-      <c r="W151">
-        <v>0</v>
-      </c>
-      <c r="X151">
-        <v>0</v>
-      </c>
-      <c r="Y151">
-        <v>0</v>
-      </c>
-      <c r="Z151">
-        <v>0</v>
-      </c>
-      <c r="AA151">
-        <v>0</v>
-      </c>
-      <c r="AB151">
-        <v>0</v>
-      </c>
-      <c r="AC151">
-        <v>0</v>
-      </c>
-      <c r="AD151">
-        <v>0</v>
-      </c>
-      <c r="AE151">
-        <v>0</v>
-      </c>
-      <c r="AF151">
-        <v>0</v>
-      </c>
-      <c r="AG151">
-        <v>0</v>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ151">
-        <v>0</v>
-      </c>
-      <c r="AK151">
-        <v>0</v>
-      </c>
-      <c r="AL151">
-        <v>0</v>
-      </c>
-      <c r="AM151">
-        <v>-1</v>
-      </c>
-      <c r="AN151">
-        <v>-1</v>
-      </c>
-      <c r="AO151">
-        <v>-1</v>
-      </c>
-      <c r="AP151">
-        <v>-1</v>
-      </c>
-      <c r="AQ151">
-        <v>0</v>
-      </c>
-      <c r="AR151">
-        <v>0</v>
-      </c>
-      <c r="AS151">
-        <v>0</v>
-      </c>
-      <c r="AT151">
-        <v>0</v>
-      </c>
-      <c r="AU151" t="inlineStr">
         <is>
           <t>2026-08-21 23:00:00</t>
         </is>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU139"/>
+  <dimension ref="A1:AU137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G49">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G59">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O82">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P82">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -14160,7 +14160,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N85">
@@ -14173,34 +14173,34 @@
         <v>4.22</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA85">
         <v>1.95</v>
@@ -14209,19 +14209,19 @@
         <v>1.85</v>
       </c>
       <c r="AC85">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD85">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -16078,22 +16078,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G97">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G98">
@@ -16893,7 +16893,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G103">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G104">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G110">
@@ -18360,7 +18360,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G111">
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G115">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,22 +19501,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,22 +19664,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,22 +19827,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G120">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G121">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Tel Aviv</t>
         </is>
       </c>
       <c r="G122">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G124">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G125">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>CS U Craiova</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Voluntari</t>
         </is>
       </c>
       <c r="G126">
@@ -20978,12 +20978,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Sepsi</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="G127">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -21141,12 +21141,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G128">
@@ -21294,7 +21294,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -21304,12 +21304,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="G129">
@@ -21457,7 +21457,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -21467,12 +21467,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G130">
@@ -21620,7 +21620,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>CSKA 1948 Sofia</t>
         </is>
       </c>
       <c r="G131">
@@ -21793,12 +21793,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G132">
@@ -21956,12 +21956,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>CSKA 1948 Sofia</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="G133">
@@ -22104,27 +22104,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G134">
@@ -22255,7 +22255,7 @@
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -22267,27 +22267,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G135">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -22435,7 +22435,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -22445,12 +22445,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G136">
@@ -22593,12 +22593,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -22608,12 +22608,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G137">
@@ -22640,13 +22640,13 @@
         </is>
       </c>
       <c r="N137">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P137">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -22679,10 +22679,10 @@
         <v>0</v>
       </c>
       <c r="AA137">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB137">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC137">
         <v>0</v>
@@ -22743,332 +22743,6 @@
         <v>0</v>
       </c>
       <c r="AU137" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
-      <c r="G138">
-        <v>0</v>
-      </c>
-      <c r="H138">
-        <v>0</v>
-      </c>
-      <c r="I138">
-        <v>0</v>
-      </c>
-      <c r="J138">
-        <v>0</v>
-      </c>
-      <c r="K138">
-        <v>0</v>
-      </c>
-      <c r="L138">
-        <v>0</v>
-      </c>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
-      <c r="O138">
-        <v>0</v>
-      </c>
-      <c r="P138">
-        <v>0</v>
-      </c>
-      <c r="Q138">
-        <v>0</v>
-      </c>
-      <c r="R138">
-        <v>0</v>
-      </c>
-      <c r="S138">
-        <v>0</v>
-      </c>
-      <c r="T138">
-        <v>0</v>
-      </c>
-      <c r="U138">
-        <v>0</v>
-      </c>
-      <c r="V138">
-        <v>0</v>
-      </c>
-      <c r="W138">
-        <v>0</v>
-      </c>
-      <c r="X138">
-        <v>0</v>
-      </c>
-      <c r="Y138">
-        <v>0</v>
-      </c>
-      <c r="Z138">
-        <v>0</v>
-      </c>
-      <c r="AA138">
-        <v>0</v>
-      </c>
-      <c r="AB138">
-        <v>0</v>
-      </c>
-      <c r="AC138">
-        <v>0</v>
-      </c>
-      <c r="AD138">
-        <v>0</v>
-      </c>
-      <c r="AE138">
-        <v>0</v>
-      </c>
-      <c r="AF138">
-        <v>0</v>
-      </c>
-      <c r="AG138">
-        <v>0</v>
-      </c>
-      <c r="AH138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ138">
-        <v>0</v>
-      </c>
-      <c r="AK138">
-        <v>0</v>
-      </c>
-      <c r="AL138">
-        <v>0</v>
-      </c>
-      <c r="AM138">
-        <v>-1</v>
-      </c>
-      <c r="AN138">
-        <v>-1</v>
-      </c>
-      <c r="AO138">
-        <v>-1</v>
-      </c>
-      <c r="AP138">
-        <v>-1</v>
-      </c>
-      <c r="AQ138">
-        <v>0</v>
-      </c>
-      <c r="AR138">
-        <v>0</v>
-      </c>
-      <c r="AS138">
-        <v>0</v>
-      </c>
-      <c r="AT138">
-        <v>0</v>
-      </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="G139">
-        <v>0</v>
-      </c>
-      <c r="H139">
-        <v>0</v>
-      </c>
-      <c r="I139">
-        <v>0</v>
-      </c>
-      <c r="J139">
-        <v>0</v>
-      </c>
-      <c r="K139">
-        <v>0</v>
-      </c>
-      <c r="L139">
-        <v>0</v>
-      </c>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
-      <c r="O139">
-        <v>0</v>
-      </c>
-      <c r="P139">
-        <v>0</v>
-      </c>
-      <c r="Q139">
-        <v>0</v>
-      </c>
-      <c r="R139">
-        <v>0</v>
-      </c>
-      <c r="S139">
-        <v>0</v>
-      </c>
-      <c r="T139">
-        <v>0</v>
-      </c>
-      <c r="U139">
-        <v>0</v>
-      </c>
-      <c r="V139">
-        <v>0</v>
-      </c>
-      <c r="W139">
-        <v>0</v>
-      </c>
-      <c r="X139">
-        <v>0</v>
-      </c>
-      <c r="Y139">
-        <v>0</v>
-      </c>
-      <c r="Z139">
-        <v>0</v>
-      </c>
-      <c r="AA139">
-        <v>0</v>
-      </c>
-      <c r="AB139">
-        <v>0</v>
-      </c>
-      <c r="AC139">
-        <v>0</v>
-      </c>
-      <c r="AD139">
-        <v>0</v>
-      </c>
-      <c r="AE139">
-        <v>0</v>
-      </c>
-      <c r="AF139">
-        <v>0</v>
-      </c>
-      <c r="AG139">
-        <v>0</v>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ139">
-        <v>0</v>
-      </c>
-      <c r="AK139">
-        <v>0</v>
-      </c>
-      <c r="AL139">
-        <v>0</v>
-      </c>
-      <c r="AM139">
-        <v>-1</v>
-      </c>
-      <c r="AN139">
-        <v>-1</v>
-      </c>
-      <c r="AO139">
-        <v>-1</v>
-      </c>
-      <c r="AP139">
-        <v>-1</v>
-      </c>
-      <c r="AQ139">
-        <v>0</v>
-      </c>
-      <c r="AR139">
-        <v>0</v>
-      </c>
-      <c r="AS139">
-        <v>0</v>
-      </c>
-      <c r="AT139">
-        <v>0</v>
-      </c>
-      <c r="AU139" t="inlineStr">
         <is>
           <t>2026-08-21 23:00:00</t>
         </is>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB48">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G59">

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G26">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O90">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P90">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q90">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>5.22</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -837,10 +837,10 @@
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G59">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="Q72">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU137"/>
+  <dimension ref="A1:AU130"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G26">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N103">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Maccabi Tel Aviv</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G122">
@@ -20326,12 +20326,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G123">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -20489,12 +20489,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G124">
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G125">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -20815,12 +20815,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>CS U Craiova</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Voluntari</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G126">
@@ -20963,27 +20963,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sepsi</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G127">
@@ -21114,7 +21114,7 @@
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -21126,27 +21126,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G128">
@@ -21277,7 +21277,7 @@
       </c>
       <c r="AU128" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -21289,27 +21289,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G129">
@@ -21440,7 +21440,7 @@
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -21452,27 +21452,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G130">
@@ -21499,13 +21499,13 @@
         </is>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O130">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P130">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q130">
         <v>0</v>
@@ -21538,10 +21538,10 @@
         <v>0</v>
       </c>
       <c r="AA130">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB130">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC130">
         <v>0</v>
@@ -21602,1147 +21602,6 @@
         <v>0</v>
       </c>
       <c r="AU130" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Bulgaria First League</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Septemvri Sofia</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>CSKA 1948 Sofia</t>
-        </is>
-      </c>
-      <c r="G131">
-        <v>0</v>
-      </c>
-      <c r="H131">
-        <v>0</v>
-      </c>
-      <c r="I131">
-        <v>0</v>
-      </c>
-      <c r="J131">
-        <v>0</v>
-      </c>
-      <c r="K131">
-        <v>0</v>
-      </c>
-      <c r="L131">
-        <v>0</v>
-      </c>
-      <c r="M131" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
-      <c r="O131">
-        <v>0</v>
-      </c>
-      <c r="P131">
-        <v>0</v>
-      </c>
-      <c r="Q131">
-        <v>0</v>
-      </c>
-      <c r="R131">
-        <v>0</v>
-      </c>
-      <c r="S131">
-        <v>0</v>
-      </c>
-      <c r="T131">
-        <v>0</v>
-      </c>
-      <c r="U131">
-        <v>0</v>
-      </c>
-      <c r="V131">
-        <v>0</v>
-      </c>
-      <c r="W131">
-        <v>0</v>
-      </c>
-      <c r="X131">
-        <v>0</v>
-      </c>
-      <c r="Y131">
-        <v>0</v>
-      </c>
-      <c r="Z131">
-        <v>0</v>
-      </c>
-      <c r="AA131">
-        <v>0</v>
-      </c>
-      <c r="AB131">
-        <v>0</v>
-      </c>
-      <c r="AC131">
-        <v>0</v>
-      </c>
-      <c r="AD131">
-        <v>0</v>
-      </c>
-      <c r="AE131">
-        <v>0</v>
-      </c>
-      <c r="AF131">
-        <v>0</v>
-      </c>
-      <c r="AG131">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ131">
-        <v>0</v>
-      </c>
-      <c r="AK131">
-        <v>0</v>
-      </c>
-      <c r="AL131">
-        <v>0</v>
-      </c>
-      <c r="AM131">
-        <v>-1</v>
-      </c>
-      <c r="AN131">
-        <v>-1</v>
-      </c>
-      <c r="AO131">
-        <v>-1</v>
-      </c>
-      <c r="AP131">
-        <v>-1</v>
-      </c>
-      <c r="AQ131">
-        <v>0</v>
-      </c>
-      <c r="AR131">
-        <v>0</v>
-      </c>
-      <c r="AS131">
-        <v>0</v>
-      </c>
-      <c r="AT131">
-        <v>0</v>
-      </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Bulgaria First League</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Lokomotiv Sofia 1929</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>CSKA Sofia</t>
-        </is>
-      </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132">
-        <v>0</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
-      </c>
-      <c r="K132">
-        <v>0</v>
-      </c>
-      <c r="L132">
-        <v>0</v>
-      </c>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
-      <c r="O132">
-        <v>0</v>
-      </c>
-      <c r="P132">
-        <v>0</v>
-      </c>
-      <c r="Q132">
-        <v>0</v>
-      </c>
-      <c r="R132">
-        <v>0</v>
-      </c>
-      <c r="S132">
-        <v>0</v>
-      </c>
-      <c r="T132">
-        <v>0</v>
-      </c>
-      <c r="U132">
-        <v>0</v>
-      </c>
-      <c r="V132">
-        <v>0</v>
-      </c>
-      <c r="W132">
-        <v>0</v>
-      </c>
-      <c r="X132">
-        <v>0</v>
-      </c>
-      <c r="Y132">
-        <v>0</v>
-      </c>
-      <c r="Z132">
-        <v>0</v>
-      </c>
-      <c r="AA132">
-        <v>0</v>
-      </c>
-      <c r="AB132">
-        <v>0</v>
-      </c>
-      <c r="AC132">
-        <v>0</v>
-      </c>
-      <c r="AD132">
-        <v>0</v>
-      </c>
-      <c r="AE132">
-        <v>0</v>
-      </c>
-      <c r="AF132">
-        <v>0</v>
-      </c>
-      <c r="AG132">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ132">
-        <v>0</v>
-      </c>
-      <c r="AK132">
-        <v>0</v>
-      </c>
-      <c r="AL132">
-        <v>0</v>
-      </c>
-      <c r="AM132">
-        <v>-1</v>
-      </c>
-      <c r="AN132">
-        <v>-1</v>
-      </c>
-      <c r="AO132">
-        <v>-1</v>
-      </c>
-      <c r="AP132">
-        <v>-1</v>
-      </c>
-      <c r="AQ132">
-        <v>0</v>
-      </c>
-      <c r="AR132">
-        <v>0</v>
-      </c>
-      <c r="AS132">
-        <v>0</v>
-      </c>
-      <c r="AT132">
-        <v>0</v>
-      </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Bulgaria First League</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Lokomotiv Plovdiv</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Arda</t>
-        </is>
-      </c>
-      <c r="G133">
-        <v>0</v>
-      </c>
-      <c r="H133">
-        <v>0</v>
-      </c>
-      <c r="I133">
-        <v>0</v>
-      </c>
-      <c r="J133">
-        <v>0</v>
-      </c>
-      <c r="K133">
-        <v>0</v>
-      </c>
-      <c r="L133">
-        <v>0</v>
-      </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
-      <c r="O133">
-        <v>0</v>
-      </c>
-      <c r="P133">
-        <v>0</v>
-      </c>
-      <c r="Q133">
-        <v>0</v>
-      </c>
-      <c r="R133">
-        <v>0</v>
-      </c>
-      <c r="S133">
-        <v>0</v>
-      </c>
-      <c r="T133">
-        <v>0</v>
-      </c>
-      <c r="U133">
-        <v>0</v>
-      </c>
-      <c r="V133">
-        <v>0</v>
-      </c>
-      <c r="W133">
-        <v>0</v>
-      </c>
-      <c r="X133">
-        <v>0</v>
-      </c>
-      <c r="Y133">
-        <v>0</v>
-      </c>
-      <c r="Z133">
-        <v>0</v>
-      </c>
-      <c r="AA133">
-        <v>0</v>
-      </c>
-      <c r="AB133">
-        <v>0</v>
-      </c>
-      <c r="AC133">
-        <v>0</v>
-      </c>
-      <c r="AD133">
-        <v>0</v>
-      </c>
-      <c r="AE133">
-        <v>0</v>
-      </c>
-      <c r="AF133">
-        <v>0</v>
-      </c>
-      <c r="AG133">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ133">
-        <v>0</v>
-      </c>
-      <c r="AK133">
-        <v>0</v>
-      </c>
-      <c r="AL133">
-        <v>0</v>
-      </c>
-      <c r="AM133">
-        <v>-1</v>
-      </c>
-      <c r="AN133">
-        <v>-1</v>
-      </c>
-      <c r="AO133">
-        <v>-1</v>
-      </c>
-      <c r="AP133">
-        <v>-1</v>
-      </c>
-      <c r="AQ133">
-        <v>0</v>
-      </c>
-      <c r="AR133">
-        <v>0</v>
-      </c>
-      <c r="AS133">
-        <v>0</v>
-      </c>
-      <c r="AT133">
-        <v>0</v>
-      </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Rangers</t>
-        </is>
-      </c>
-      <c r="G134">
-        <v>0</v>
-      </c>
-      <c r="H134">
-        <v>0</v>
-      </c>
-      <c r="I134">
-        <v>0</v>
-      </c>
-      <c r="J134">
-        <v>0</v>
-      </c>
-      <c r="K134">
-        <v>0</v>
-      </c>
-      <c r="L134">
-        <v>0</v>
-      </c>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
-      <c r="O134">
-        <v>0</v>
-      </c>
-      <c r="P134">
-        <v>0</v>
-      </c>
-      <c r="Q134">
-        <v>0</v>
-      </c>
-      <c r="R134">
-        <v>0</v>
-      </c>
-      <c r="S134">
-        <v>0</v>
-      </c>
-      <c r="T134">
-        <v>0</v>
-      </c>
-      <c r="U134">
-        <v>0</v>
-      </c>
-      <c r="V134">
-        <v>0</v>
-      </c>
-      <c r="W134">
-        <v>0</v>
-      </c>
-      <c r="X134">
-        <v>0</v>
-      </c>
-      <c r="Y134">
-        <v>0</v>
-      </c>
-      <c r="Z134">
-        <v>0</v>
-      </c>
-      <c r="AA134">
-        <v>0</v>
-      </c>
-      <c r="AB134">
-        <v>0</v>
-      </c>
-      <c r="AC134">
-        <v>0</v>
-      </c>
-      <c r="AD134">
-        <v>0</v>
-      </c>
-      <c r="AE134">
-        <v>0</v>
-      </c>
-      <c r="AF134">
-        <v>0</v>
-      </c>
-      <c r="AG134">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ134">
-        <v>0</v>
-      </c>
-      <c r="AK134">
-        <v>0</v>
-      </c>
-      <c r="AL134">
-        <v>0</v>
-      </c>
-      <c r="AM134">
-        <v>-1</v>
-      </c>
-      <c r="AN134">
-        <v>-1</v>
-      </c>
-      <c r="AO134">
-        <v>-1</v>
-      </c>
-      <c r="AP134">
-        <v>-1</v>
-      </c>
-      <c r="AQ134">
-        <v>0</v>
-      </c>
-      <c r="AR134">
-        <v>0</v>
-      </c>
-      <c r="AS134">
-        <v>0</v>
-      </c>
-      <c r="AT134">
-        <v>0</v>
-      </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Unión La Calera</t>
-        </is>
-      </c>
-      <c r="G135">
-        <v>0</v>
-      </c>
-      <c r="H135">
-        <v>0</v>
-      </c>
-      <c r="I135">
-        <v>0</v>
-      </c>
-      <c r="J135">
-        <v>0</v>
-      </c>
-      <c r="K135">
-        <v>0</v>
-      </c>
-      <c r="L135">
-        <v>0</v>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
-      <c r="O135">
-        <v>0</v>
-      </c>
-      <c r="P135">
-        <v>0</v>
-      </c>
-      <c r="Q135">
-        <v>0</v>
-      </c>
-      <c r="R135">
-        <v>0</v>
-      </c>
-      <c r="S135">
-        <v>0</v>
-      </c>
-      <c r="T135">
-        <v>0</v>
-      </c>
-      <c r="U135">
-        <v>0</v>
-      </c>
-      <c r="V135">
-        <v>0</v>
-      </c>
-      <c r="W135">
-        <v>0</v>
-      </c>
-      <c r="X135">
-        <v>0</v>
-      </c>
-      <c r="Y135">
-        <v>0</v>
-      </c>
-      <c r="Z135">
-        <v>0</v>
-      </c>
-      <c r="AA135">
-        <v>0</v>
-      </c>
-      <c r="AB135">
-        <v>0</v>
-      </c>
-      <c r="AC135">
-        <v>0</v>
-      </c>
-      <c r="AD135">
-        <v>0</v>
-      </c>
-      <c r="AE135">
-        <v>0</v>
-      </c>
-      <c r="AF135">
-        <v>0</v>
-      </c>
-      <c r="AG135">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ135">
-        <v>0</v>
-      </c>
-      <c r="AK135">
-        <v>0</v>
-      </c>
-      <c r="AL135">
-        <v>0</v>
-      </c>
-      <c r="AM135">
-        <v>-1</v>
-      </c>
-      <c r="AN135">
-        <v>-1</v>
-      </c>
-      <c r="AO135">
-        <v>-1</v>
-      </c>
-      <c r="AP135">
-        <v>-1</v>
-      </c>
-      <c r="AQ135">
-        <v>0</v>
-      </c>
-      <c r="AR135">
-        <v>0</v>
-      </c>
-      <c r="AS135">
-        <v>0</v>
-      </c>
-      <c r="AT135">
-        <v>0</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
-      <c r="G136">
-        <v>0</v>
-      </c>
-      <c r="H136">
-        <v>0</v>
-      </c>
-      <c r="I136">
-        <v>0</v>
-      </c>
-      <c r="J136">
-        <v>0</v>
-      </c>
-      <c r="K136">
-        <v>0</v>
-      </c>
-      <c r="L136">
-        <v>0</v>
-      </c>
-      <c r="M136" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
-      <c r="O136">
-        <v>0</v>
-      </c>
-      <c r="P136">
-        <v>0</v>
-      </c>
-      <c r="Q136">
-        <v>0</v>
-      </c>
-      <c r="R136">
-        <v>0</v>
-      </c>
-      <c r="S136">
-        <v>0</v>
-      </c>
-      <c r="T136">
-        <v>0</v>
-      </c>
-      <c r="U136">
-        <v>0</v>
-      </c>
-      <c r="V136">
-        <v>0</v>
-      </c>
-      <c r="W136">
-        <v>0</v>
-      </c>
-      <c r="X136">
-        <v>0</v>
-      </c>
-      <c r="Y136">
-        <v>0</v>
-      </c>
-      <c r="Z136">
-        <v>0</v>
-      </c>
-      <c r="AA136">
-        <v>0</v>
-      </c>
-      <c r="AB136">
-        <v>0</v>
-      </c>
-      <c r="AC136">
-        <v>0</v>
-      </c>
-      <c r="AD136">
-        <v>0</v>
-      </c>
-      <c r="AE136">
-        <v>0</v>
-      </c>
-      <c r="AF136">
-        <v>0</v>
-      </c>
-      <c r="AG136">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ136">
-        <v>0</v>
-      </c>
-      <c r="AK136">
-        <v>0</v>
-      </c>
-      <c r="AL136">
-        <v>0</v>
-      </c>
-      <c r="AM136">
-        <v>-1</v>
-      </c>
-      <c r="AN136">
-        <v>-1</v>
-      </c>
-      <c r="AO136">
-        <v>-1</v>
-      </c>
-      <c r="AP136">
-        <v>-1</v>
-      </c>
-      <c r="AQ136">
-        <v>0</v>
-      </c>
-      <c r="AR136">
-        <v>0</v>
-      </c>
-      <c r="AS136">
-        <v>0</v>
-      </c>
-      <c r="AT136">
-        <v>0</v>
-      </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="G137">
-        <v>0</v>
-      </c>
-      <c r="H137">
-        <v>0</v>
-      </c>
-      <c r="I137">
-        <v>0</v>
-      </c>
-      <c r="J137">
-        <v>0</v>
-      </c>
-      <c r="K137">
-        <v>0</v>
-      </c>
-      <c r="L137">
-        <v>0</v>
-      </c>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N137">
-        <v>1.89</v>
-      </c>
-      <c r="O137">
-        <v>3.54</v>
-      </c>
-      <c r="P137">
-        <v>3.45</v>
-      </c>
-      <c r="Q137">
-        <v>0</v>
-      </c>
-      <c r="R137">
-        <v>0</v>
-      </c>
-      <c r="S137">
-        <v>0</v>
-      </c>
-      <c r="T137">
-        <v>0</v>
-      </c>
-      <c r="U137">
-        <v>0</v>
-      </c>
-      <c r="V137">
-        <v>0</v>
-      </c>
-      <c r="W137">
-        <v>0</v>
-      </c>
-      <c r="X137">
-        <v>0</v>
-      </c>
-      <c r="Y137">
-        <v>0</v>
-      </c>
-      <c r="Z137">
-        <v>0</v>
-      </c>
-      <c r="AA137">
-        <v>1.72</v>
-      </c>
-      <c r="AB137">
-        <v>1.92</v>
-      </c>
-      <c r="AC137">
-        <v>0</v>
-      </c>
-      <c r="AD137">
-        <v>0</v>
-      </c>
-      <c r="AE137">
-        <v>0</v>
-      </c>
-      <c r="AF137">
-        <v>0</v>
-      </c>
-      <c r="AG137">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ137">
-        <v>0</v>
-      </c>
-      <c r="AK137">
-        <v>0</v>
-      </c>
-      <c r="AL137">
-        <v>0</v>
-      </c>
-      <c r="AM137">
-        <v>-1</v>
-      </c>
-      <c r="AN137">
-        <v>-1</v>
-      </c>
-      <c r="AO137">
-        <v>-1</v>
-      </c>
-      <c r="AP137">
-        <v>-1</v>
-      </c>
-      <c r="AQ137">
-        <v>0</v>
-      </c>
-      <c r="AR137">
-        <v>0</v>
-      </c>
-      <c r="AS137">
-        <v>0</v>
-      </c>
-      <c r="AT137">
-        <v>0</v>
-      </c>
-      <c r="AU137" t="inlineStr">
         <is>
           <t>2026-08-21 23:00:00</t>
         </is>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU130"/>
+  <dimension ref="A1:AU126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O32">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P32">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6222,10 +6222,10 @@
         <v>0</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE36">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,22 +18686,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G115">
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G116">
@@ -19338,22 +19338,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,22 +19501,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G122">
@@ -20311,27 +20311,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G123">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -20474,27 +20474,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G124">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -20637,27 +20637,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G125">
@@ -20788,7 +20788,7 @@
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -20800,27 +20800,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G126">
@@ -20847,13 +20847,13 @@
         </is>
       </c>
       <c r="N126">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O126">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P126">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -20886,10 +20886,10 @@
         <v>0</v>
       </c>
       <c r="AA126">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB126">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC126">
         <v>0</v>
@@ -20950,658 +20950,6 @@
         <v>0</v>
       </c>
       <c r="AU126" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Rangers</t>
-        </is>
-      </c>
-      <c r="G127">
-        <v>0</v>
-      </c>
-      <c r="H127">
-        <v>0</v>
-      </c>
-      <c r="I127">
-        <v>0</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>0</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>0</v>
-      </c>
-      <c r="R127">
-        <v>0</v>
-      </c>
-      <c r="S127">
-        <v>0</v>
-      </c>
-      <c r="T127">
-        <v>0</v>
-      </c>
-      <c r="U127">
-        <v>0</v>
-      </c>
-      <c r="V127">
-        <v>0</v>
-      </c>
-      <c r="W127">
-        <v>0</v>
-      </c>
-      <c r="X127">
-        <v>0</v>
-      </c>
-      <c r="Y127">
-        <v>0</v>
-      </c>
-      <c r="Z127">
-        <v>0</v>
-      </c>
-      <c r="AA127">
-        <v>0</v>
-      </c>
-      <c r="AB127">
-        <v>0</v>
-      </c>
-      <c r="AC127">
-        <v>0</v>
-      </c>
-      <c r="AD127">
-        <v>0</v>
-      </c>
-      <c r="AE127">
-        <v>0</v>
-      </c>
-      <c r="AF127">
-        <v>0</v>
-      </c>
-      <c r="AG127">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>0</v>
-      </c>
-      <c r="AK127">
-        <v>0</v>
-      </c>
-      <c r="AL127">
-        <v>0</v>
-      </c>
-      <c r="AM127">
-        <v>-1</v>
-      </c>
-      <c r="AN127">
-        <v>-1</v>
-      </c>
-      <c r="AO127">
-        <v>-1</v>
-      </c>
-      <c r="AP127">
-        <v>-1</v>
-      </c>
-      <c r="AQ127">
-        <v>0</v>
-      </c>
-      <c r="AR127">
-        <v>0</v>
-      </c>
-      <c r="AS127">
-        <v>0</v>
-      </c>
-      <c r="AT127">
-        <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Unión La Calera</t>
-        </is>
-      </c>
-      <c r="G128">
-        <v>0</v>
-      </c>
-      <c r="H128">
-        <v>0</v>
-      </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>0</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
-      <c r="O128">
-        <v>0</v>
-      </c>
-      <c r="P128">
-        <v>0</v>
-      </c>
-      <c r="Q128">
-        <v>0</v>
-      </c>
-      <c r="R128">
-        <v>0</v>
-      </c>
-      <c r="S128">
-        <v>0</v>
-      </c>
-      <c r="T128">
-        <v>0</v>
-      </c>
-      <c r="U128">
-        <v>0</v>
-      </c>
-      <c r="V128">
-        <v>0</v>
-      </c>
-      <c r="W128">
-        <v>0</v>
-      </c>
-      <c r="X128">
-        <v>0</v>
-      </c>
-      <c r="Y128">
-        <v>0</v>
-      </c>
-      <c r="Z128">
-        <v>0</v>
-      </c>
-      <c r="AA128">
-        <v>0</v>
-      </c>
-      <c r="AB128">
-        <v>0</v>
-      </c>
-      <c r="AC128">
-        <v>0</v>
-      </c>
-      <c r="AD128">
-        <v>0</v>
-      </c>
-      <c r="AE128">
-        <v>0</v>
-      </c>
-      <c r="AF128">
-        <v>0</v>
-      </c>
-      <c r="AG128">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>0</v>
-      </c>
-      <c r="AK128">
-        <v>0</v>
-      </c>
-      <c r="AL128">
-        <v>0</v>
-      </c>
-      <c r="AM128">
-        <v>-1</v>
-      </c>
-      <c r="AN128">
-        <v>-1</v>
-      </c>
-      <c r="AO128">
-        <v>-1</v>
-      </c>
-      <c r="AP128">
-        <v>-1</v>
-      </c>
-      <c r="AQ128">
-        <v>0</v>
-      </c>
-      <c r="AR128">
-        <v>0</v>
-      </c>
-      <c r="AS128">
-        <v>0</v>
-      </c>
-      <c r="AT128">
-        <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
-      <c r="G129">
-        <v>0</v>
-      </c>
-      <c r="H129">
-        <v>0</v>
-      </c>
-      <c r="I129">
-        <v>0</v>
-      </c>
-      <c r="J129">
-        <v>0</v>
-      </c>
-      <c r="K129">
-        <v>0</v>
-      </c>
-      <c r="L129">
-        <v>0</v>
-      </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
-      <c r="O129">
-        <v>0</v>
-      </c>
-      <c r="P129">
-        <v>0</v>
-      </c>
-      <c r="Q129">
-        <v>0</v>
-      </c>
-      <c r="R129">
-        <v>0</v>
-      </c>
-      <c r="S129">
-        <v>0</v>
-      </c>
-      <c r="T129">
-        <v>0</v>
-      </c>
-      <c r="U129">
-        <v>0</v>
-      </c>
-      <c r="V129">
-        <v>0</v>
-      </c>
-      <c r="W129">
-        <v>0</v>
-      </c>
-      <c r="X129">
-        <v>0</v>
-      </c>
-      <c r="Y129">
-        <v>0</v>
-      </c>
-      <c r="Z129">
-        <v>0</v>
-      </c>
-      <c r="AA129">
-        <v>0</v>
-      </c>
-      <c r="AB129">
-        <v>0</v>
-      </c>
-      <c r="AC129">
-        <v>0</v>
-      </c>
-      <c r="AD129">
-        <v>0</v>
-      </c>
-      <c r="AE129">
-        <v>0</v>
-      </c>
-      <c r="AF129">
-        <v>0</v>
-      </c>
-      <c r="AG129">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ129">
-        <v>0</v>
-      </c>
-      <c r="AK129">
-        <v>0</v>
-      </c>
-      <c r="AL129">
-        <v>0</v>
-      </c>
-      <c r="AM129">
-        <v>-1</v>
-      </c>
-      <c r="AN129">
-        <v>-1</v>
-      </c>
-      <c r="AO129">
-        <v>-1</v>
-      </c>
-      <c r="AP129">
-        <v>-1</v>
-      </c>
-      <c r="AQ129">
-        <v>0</v>
-      </c>
-      <c r="AR129">
-        <v>0</v>
-      </c>
-      <c r="AS129">
-        <v>0</v>
-      </c>
-      <c r="AT129">
-        <v>0</v>
-      </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="G130">
-        <v>0</v>
-      </c>
-      <c r="H130">
-        <v>0</v>
-      </c>
-      <c r="I130">
-        <v>0</v>
-      </c>
-      <c r="J130">
-        <v>0</v>
-      </c>
-      <c r="K130">
-        <v>0</v>
-      </c>
-      <c r="L130">
-        <v>0</v>
-      </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N130">
-        <v>1.89</v>
-      </c>
-      <c r="O130">
-        <v>3.54</v>
-      </c>
-      <c r="P130">
-        <v>3.45</v>
-      </c>
-      <c r="Q130">
-        <v>0</v>
-      </c>
-      <c r="R130">
-        <v>0</v>
-      </c>
-      <c r="S130">
-        <v>0</v>
-      </c>
-      <c r="T130">
-        <v>0</v>
-      </c>
-      <c r="U130">
-        <v>0</v>
-      </c>
-      <c r="V130">
-        <v>0</v>
-      </c>
-      <c r="W130">
-        <v>0</v>
-      </c>
-      <c r="X130">
-        <v>0</v>
-      </c>
-      <c r="Y130">
-        <v>0</v>
-      </c>
-      <c r="Z130">
-        <v>0</v>
-      </c>
-      <c r="AA130">
-        <v>1.72</v>
-      </c>
-      <c r="AB130">
-        <v>1.92</v>
-      </c>
-      <c r="AC130">
-        <v>0</v>
-      </c>
-      <c r="AD130">
-        <v>0</v>
-      </c>
-      <c r="AE130">
-        <v>0</v>
-      </c>
-      <c r="AF130">
-        <v>0</v>
-      </c>
-      <c r="AG130">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ130">
-        <v>0</v>
-      </c>
-      <c r="AK130">
-        <v>0</v>
-      </c>
-      <c r="AL130">
-        <v>0</v>
-      </c>
-      <c r="AM130">
-        <v>-1</v>
-      </c>
-      <c r="AN130">
-        <v>-1</v>
-      </c>
-      <c r="AO130">
-        <v>-1</v>
-      </c>
-      <c r="AP130">
-        <v>-1</v>
-      </c>
-      <c r="AQ130">
-        <v>0</v>
-      </c>
-      <c r="AR130">
-        <v>0</v>
-      </c>
-      <c r="AS130">
-        <v>0</v>
-      </c>
-      <c r="AT130">
-        <v>0</v>
-      </c>
-      <c r="AU130" t="inlineStr">
         <is>
           <t>2026-08-21 23:00:00</t>
         </is>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="O29">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P29">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G32">

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU126"/>
+  <dimension ref="A1:AU128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Al Ittihad Kalba</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Shahaniya</t>
+          <t>Al Wasl</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>4.92</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-08-21 11:15:00</t>
+          <t>2026-08-21 11:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,27 +1729,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Al Shahaniya</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-08-21 12:00:00</t>
+          <t>2026-08-21 11:15:00</t>
         </is>
       </c>
     </row>
@@ -1897,22 +1897,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Skopje</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G10">
@@ -2060,22 +2060,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Skopje</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="G11">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G12">
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brinje-Grosuplje</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-08-21 12:30:00</t>
+          <t>2026-08-21 12:00:00</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Brinje-Grosuplje</t>
         </is>
       </c>
       <c r="G14">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G15">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G16">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>2026-08-21 13:00:00</t>
+          <t>2026-08-21 12:30:00</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G17">
@@ -3201,22 +3201,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G18">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G19">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,22 +3690,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G21">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G26">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G27">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-08-21 13:15:00</t>
+          <t>2026-08-21 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-08-21 13:30:00</t>
+          <t>2026-08-21 13:15:00</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5646,7 +5646,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.72</v>
+        <v>1.6</v>
       </c>
       <c r="O33">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P33">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5804,12 +5804,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:00</t>
+          <t>2026-08-21 13:30:00</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA35">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB35">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:00</t>
+          <t>2026-08-21 13:35:00</t>
         </is>
       </c>
     </row>
@@ -6135,22 +6135,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O36">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P36">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6222,10 +6222,10 @@
         <v>0</v>
       </c>
       <c r="AC36">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD36">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE36">
         <v>0</v>
@@ -6293,12 +6293,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G37">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>2026-08-21 14:30:00</t>
+          <t>2026-08-21 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,13 +6503,13 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6548,10 +6548,10 @@
         <v>0</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE38">
         <v>0</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>2026-08-21 14:30:00</t>
+          <t>2026-08-21 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G39">
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G40">
@@ -6950,7 +6950,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7108,12 +7108,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G42">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>2026-08-21 15:00:00</t>
+          <t>2026-08-21 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7271,12 +7271,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P43">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>2026-08-21 15:00:00</t>
+          <t>2026-08-21 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7439,22 +7439,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G44">
@@ -7602,7 +7602,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O45">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P45">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AB45">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7765,22 +7765,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O46">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P46">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,13 +7970,13 @@
         </is>
       </c>
       <c r="N47">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P47">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -8009,10 +8009,10 @@
         <v>0</v>
       </c>
       <c r="AA47">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB47">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P49">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB49">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8417,7 +8417,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G50">
@@ -8580,7 +8580,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.03</v>
+        <v>2.5</v>
       </c>
       <c r="O51">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="P51">
-        <v>3.05</v>
+        <v>2.68</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AB51">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G52">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -8987,10 +8987,10 @@
         <v>0</v>
       </c>
       <c r="AA53">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB53">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC53">
         <v>0</v>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="G54">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G55">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G58">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G59">
@@ -10042,12 +10042,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G60">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AU60" t="inlineStr">
         <is>
-          <t>2026-08-21 15:15:00</t>
+          <t>2026-08-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10205,12 +10205,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G61">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="AU61" t="inlineStr">
         <is>
-          <t>2026-08-21 15:15:00</t>
+          <t>2026-08-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G62">
@@ -10531,12 +10531,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,13 +10578,13 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="O63">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P63">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q63">
         <v>0</v>
@@ -10617,10 +10617,10 @@
         <v>0</v>
       </c>
       <c r="AA63">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB63">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC63">
         <v>0</v>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>2026-08-21 15:30:00</t>
+          <t>2026-08-21 15:15:00</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G64">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>2026-08-21 15:30:00</t>
+          <t>2026-08-21 15:15:00</t>
         </is>
       </c>
     </row>
@@ -10862,7 +10862,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,13 +10904,13 @@
         </is>
       </c>
       <c r="N65">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O65">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P65">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q65">
         <v>0</v>
@@ -10943,10 +10943,10 @@
         <v>0</v>
       </c>
       <c r="AA65">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB65">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC65">
         <v>0</v>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,13 +11067,13 @@
         </is>
       </c>
       <c r="N66">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O66">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P66">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q66">
         <v>0</v>
@@ -11106,10 +11106,10 @@
         <v>0</v>
       </c>
       <c r="AA66">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB66">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC66">
         <v>0</v>
@@ -11188,22 +11188,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G67">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,13 +11393,13 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q68">
         <v>0</v>
@@ -11432,10 +11432,10 @@
         <v>0</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC68">
         <v>0</v>
@@ -11514,22 +11514,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G69">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,13 +11719,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P70">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q70">
         <v>0</v>
@@ -11758,10 +11758,10 @@
         <v>0</v>
       </c>
       <c r="AA70">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB70">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC70">
         <v>0</v>
@@ -11835,12 +11835,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G71">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="AU71" t="inlineStr">
         <is>
-          <t>2026-08-21 15:45:00</t>
+          <t>2026-08-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P72">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12149,7 +12149,7 @@
       </c>
       <c r="AU72" t="inlineStr">
         <is>
-          <t>2026-08-21 15:45:00</t>
+          <t>2026-08-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O73">
-        <v>4.52</v>
+        <v>0</v>
       </c>
       <c r="P73">
-        <v>4.57</v>
+        <v>0</v>
       </c>
       <c r="Q73">
         <v>0</v>
@@ -12253,10 +12253,10 @@
         <v>0</v>
       </c>
       <c r="AC73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD73">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE73">
         <v>0</v>
@@ -12329,22 +12329,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.92</v>
+        <v>1.66</v>
       </c>
       <c r="O74">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="P74">
-        <v>3.97</v>
+        <v>4.21</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -12410,10 +12410,10 @@
         <v>0</v>
       </c>
       <c r="AA74">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB74">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC74">
         <v>0</v>
@@ -12492,22 +12492,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,13 +12534,13 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="O75">
-        <v>3.92</v>
+        <v>4.52</v>
       </c>
       <c r="P75">
-        <v>4.36</v>
+        <v>4.57</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -12579,10 +12579,10 @@
         <v>0</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE75">
         <v>0</v>
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,13 +12697,13 @@
         </is>
       </c>
       <c r="N76">
-        <v>5.08</v>
+        <v>1.92</v>
       </c>
       <c r="O76">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="P76">
-        <v>1.66</v>
+        <v>3.97</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -12736,10 +12736,10 @@
         <v>0</v>
       </c>
       <c r="AA76">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AB76">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -12818,7 +12818,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,13 +12860,13 @@
         </is>
       </c>
       <c r="N77">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="O77">
-        <v>3.6</v>
+        <v>3.92</v>
       </c>
       <c r="P77">
-        <v>3.05</v>
+        <v>4.36</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>2.75</v>
+        <v>5.08</v>
       </c>
       <c r="O78">
-        <v>3.25</v>
+        <v>3.74</v>
       </c>
       <c r="P78">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -13062,10 +13062,10 @@
         <v>0</v>
       </c>
       <c r="AA78">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB78">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,13 +13186,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>6.65</v>
+        <v>2</v>
       </c>
       <c r="O79">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P79">
-        <v>1.49</v>
+        <v>3.05</v>
       </c>
       <c r="Q79">
         <v>0</v>
@@ -13225,10 +13225,10 @@
         <v>0</v>
       </c>
       <c r="AA79">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB79">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC79">
         <v>0</v>
@@ -13317,12 +13317,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>3.7</v>
+        <v>2.75</v>
       </c>
       <c r="O80">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P80">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13470,22 +13470,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="O81">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q81">
         <v>0</v>
@@ -13551,10 +13551,10 @@
         <v>0</v>
       </c>
       <c r="AA81">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB81">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC81">
         <v>0</v>
@@ -13628,27 +13628,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,13 +13675,13 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O82">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="P82">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="Q82">
         <v>0</v>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>2026-08-21 16:00:00</t>
+          <t>2026-08-21 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13791,12 +13791,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="P83">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13883,10 +13883,10 @@
         <v>0</v>
       </c>
       <c r="AC83">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD83">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE83">
         <v>0</v>
@@ -13942,7 +13942,7 @@
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>2026-08-21 16:00:00</t>
+          <t>2026-08-21 15:45:00</t>
         </is>
       </c>
     </row>
@@ -13959,22 +13959,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,13 +14001,13 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.78</v>
+        <v>3.55</v>
       </c>
       <c r="O84">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="P84">
-        <v>2.37</v>
+        <v>2.11</v>
       </c>
       <c r="Q84">
         <v>0</v>
@@ -14122,22 +14122,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G85">
@@ -14160,68 +14160,68 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N85">
-        <v>1.82</v>
+        <v>1.18</v>
       </c>
       <c r="O85">
-        <v>3.58</v>
+        <v>8.5</v>
       </c>
       <c r="P85">
-        <v>4.22</v>
+        <v>21</v>
       </c>
       <c r="Q85">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="R85">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S85">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T85">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U85">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="V85">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W85">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X85">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y85">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z85">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA85">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB85">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC85">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD85">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE85">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF85">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK85">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14285,22 +14285,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,13 +14327,13 @@
         </is>
       </c>
       <c r="N86">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O86">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P86">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q86">
         <v>0</v>
@@ -14448,22 +14448,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G87">
@@ -14486,68 +14486,68 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N87">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O87">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P87">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="Q87">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="R87">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S87">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T87">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U87">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V87">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W87">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X87">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y87">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z87">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA87">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB87">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC87">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD87">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE87">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF87">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG87">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="P88">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G89">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,13 +14979,13 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="O90">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="P90">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q90">
         <v>0</v>
@@ -15100,7 +15100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,13 +15142,13 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="P91">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q91">
         <v>0</v>
@@ -15263,7 +15263,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,13 +15305,13 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.29</v>
+        <v>2.27</v>
       </c>
       <c r="O92">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P92">
-        <v>8.6</v>
+        <v>3.15</v>
       </c>
       <c r="Q92">
         <v>0</v>
@@ -15421,12 +15421,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O93">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P93">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q93">
         <v>0</v>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>2026-08-21 16:15:00</t>
+          <t>2026-08-21 16:00:00</t>
         </is>
       </c>
     </row>
@@ -15584,12 +15584,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,13 +15631,13 @@
         </is>
       </c>
       <c r="N94">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O94">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P94">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q94">
         <v>0</v>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>2026-08-21 16:30:00</t>
+          <t>2026-08-21 16:00:00</t>
         </is>
       </c>
     </row>
@@ -15747,27 +15747,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G95">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-08-21 19:00:00</t>
+          <t>2026-08-21 16:15:00</t>
         </is>
       </c>
     </row>
@@ -15910,27 +15910,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G96">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-08-21 19:30:00</t>
+          <t>2026-08-21 16:30:00</t>
         </is>
       </c>
     </row>
@@ -16073,12 +16073,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G97">
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 19:00:00</t>
         </is>
       </c>
     </row>
@@ -16236,27 +16236,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G98">
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 19:30:00</t>
         </is>
       </c>
     </row>
@@ -16404,22 +16404,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G99">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G102">
@@ -17056,7 +17056,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G103">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,22 +18686,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G114">
@@ -19012,22 +19012,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G115">
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G118">
@@ -19664,7 +19664,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -19674,12 +19674,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G119">
@@ -19827,7 +19827,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -19837,12 +19837,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>Botoşani</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G120">
@@ -19990,7 +19990,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -20000,12 +20000,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G121">
@@ -20153,7 +20153,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -20163,12 +20163,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G122">
@@ -20311,27 +20311,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G123">
@@ -20462,7 +20462,7 @@
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>2026-08-21 21:30:00</t>
+          <t>2026-08-21 21:00:00</t>
         </is>
       </c>
     </row>
@@ -20474,27 +20474,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G124">
@@ -20625,7 +20625,7 @@
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>2026-08-21 21:30:00</t>
+          <t>2026-08-21 21:00:00</t>
         </is>
       </c>
     </row>
@@ -20642,7 +20642,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -20652,12 +20652,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G125">
@@ -20800,156 +20800,482 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Chile Primera División</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N126">
+        <v>0</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+      <c r="Q126">
+        <v>0</v>
+      </c>
+      <c r="R126">
+        <v>0</v>
+      </c>
+      <c r="S126">
+        <v>0</v>
+      </c>
+      <c r="T126">
+        <v>0</v>
+      </c>
+      <c r="U126">
+        <v>0</v>
+      </c>
+      <c r="V126">
+        <v>0</v>
+      </c>
+      <c r="W126">
+        <v>0</v>
+      </c>
+      <c r="X126">
+        <v>0</v>
+      </c>
+      <c r="Y126">
+        <v>0</v>
+      </c>
+      <c r="Z126">
+        <v>0</v>
+      </c>
+      <c r="AA126">
+        <v>0</v>
+      </c>
+      <c r="AB126">
+        <v>0</v>
+      </c>
+      <c r="AC126">
+        <v>0</v>
+      </c>
+      <c r="AD126">
+        <v>0</v>
+      </c>
+      <c r="AE126">
+        <v>0</v>
+      </c>
+      <c r="AF126">
+        <v>0</v>
+      </c>
+      <c r="AG126">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ126">
+        <v>0</v>
+      </c>
+      <c r="AK126">
+        <v>0</v>
+      </c>
+      <c r="AL126">
+        <v>0</v>
+      </c>
+      <c r="AM126">
+        <v>-1</v>
+      </c>
+      <c r="AN126">
+        <v>-1</v>
+      </c>
+      <c r="AO126">
+        <v>-1</v>
+      </c>
+      <c r="AP126">
+        <v>-1</v>
+      </c>
+      <c r="AQ126">
+        <v>0</v>
+      </c>
+      <c r="AR126">
+        <v>0</v>
+      </c>
+      <c r="AS126">
+        <v>0</v>
+      </c>
+      <c r="AT126">
+        <v>0</v>
+      </c>
+      <c r="AU126" t="inlineStr">
+        <is>
+          <t>2026-08-21 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N127">
+        <v>0</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+      <c r="Q127">
+        <v>0</v>
+      </c>
+      <c r="R127">
+        <v>0</v>
+      </c>
+      <c r="S127">
+        <v>0</v>
+      </c>
+      <c r="T127">
+        <v>0</v>
+      </c>
+      <c r="U127">
+        <v>0</v>
+      </c>
+      <c r="V127">
+        <v>0</v>
+      </c>
+      <c r="W127">
+        <v>0</v>
+      </c>
+      <c r="X127">
+        <v>0</v>
+      </c>
+      <c r="Y127">
+        <v>0</v>
+      </c>
+      <c r="Z127">
+        <v>0</v>
+      </c>
+      <c r="AA127">
+        <v>0</v>
+      </c>
+      <c r="AB127">
+        <v>0</v>
+      </c>
+      <c r="AC127">
+        <v>0</v>
+      </c>
+      <c r="AD127">
+        <v>0</v>
+      </c>
+      <c r="AE127">
+        <v>0</v>
+      </c>
+      <c r="AF127">
+        <v>0</v>
+      </c>
+      <c r="AG127">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ127">
+        <v>0</v>
+      </c>
+      <c r="AK127">
+        <v>0</v>
+      </c>
+      <c r="AL127">
+        <v>0</v>
+      </c>
+      <c r="AM127">
+        <v>-1</v>
+      </c>
+      <c r="AN127">
+        <v>-1</v>
+      </c>
+      <c r="AO127">
+        <v>-1</v>
+      </c>
+      <c r="AP127">
+        <v>-1</v>
+      </c>
+      <c r="AQ127">
+        <v>0</v>
+      </c>
+      <c r="AR127">
+        <v>0</v>
+      </c>
+      <c r="AS127">
+        <v>0</v>
+      </c>
+      <c r="AT127">
+        <v>0</v>
+      </c>
+      <c r="AU127" t="inlineStr">
+        <is>
+          <t>2026-08-21 21:30:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
+      <c r="C128" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
+      <c r="E128" t="inlineStr">
         <is>
           <t>San Diego Wave</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F128" t="inlineStr">
         <is>
           <t>Utah Royals</t>
         </is>
       </c>
-      <c r="G126">
-        <v>0</v>
-      </c>
-      <c r="H126">
-        <v>0</v>
-      </c>
-      <c r="I126">
-        <v>0</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126">
-        <v>0</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126" t="inlineStr">
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N126">
+      <c r="N128">
         <v>1.89</v>
       </c>
-      <c r="O126">
+      <c r="O128">
         <v>3.54</v>
       </c>
-      <c r="P126">
+      <c r="P128">
         <v>3.45</v>
       </c>
-      <c r="Q126">
-        <v>0</v>
-      </c>
-      <c r="R126">
-        <v>0</v>
-      </c>
-      <c r="S126">
-        <v>0</v>
-      </c>
-      <c r="T126">
-        <v>0</v>
-      </c>
-      <c r="U126">
-        <v>0</v>
-      </c>
-      <c r="V126">
-        <v>0</v>
-      </c>
-      <c r="W126">
-        <v>0</v>
-      </c>
-      <c r="X126">
-        <v>0</v>
-      </c>
-      <c r="Y126">
-        <v>0</v>
-      </c>
-      <c r="Z126">
-        <v>0</v>
-      </c>
-      <c r="AA126">
+      <c r="Q128">
+        <v>0</v>
+      </c>
+      <c r="R128">
+        <v>0</v>
+      </c>
+      <c r="S128">
+        <v>0</v>
+      </c>
+      <c r="T128">
+        <v>0</v>
+      </c>
+      <c r="U128">
+        <v>0</v>
+      </c>
+      <c r="V128">
+        <v>0</v>
+      </c>
+      <c r="W128">
+        <v>0</v>
+      </c>
+      <c r="X128">
+        <v>0</v>
+      </c>
+      <c r="Y128">
+        <v>0</v>
+      </c>
+      <c r="Z128">
+        <v>0</v>
+      </c>
+      <c r="AA128">
         <v>1.72</v>
       </c>
-      <c r="AB126">
+      <c r="AB128">
         <v>1.92</v>
       </c>
-      <c r="AC126">
-        <v>0</v>
-      </c>
-      <c r="AD126">
-        <v>0</v>
-      </c>
-      <c r="AE126">
-        <v>0</v>
-      </c>
-      <c r="AF126">
-        <v>0</v>
-      </c>
-      <c r="AG126">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>0</v>
-      </c>
-      <c r="AK126">
-        <v>0</v>
-      </c>
-      <c r="AL126">
-        <v>0</v>
-      </c>
-      <c r="AM126">
-        <v>-1</v>
-      </c>
-      <c r="AN126">
-        <v>-1</v>
-      </c>
-      <c r="AO126">
-        <v>-1</v>
-      </c>
-      <c r="AP126">
-        <v>-1</v>
-      </c>
-      <c r="AQ126">
-        <v>0</v>
-      </c>
-      <c r="AR126">
-        <v>0</v>
-      </c>
-      <c r="AS126">
-        <v>0</v>
-      </c>
-      <c r="AT126">
-        <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
+      <c r="AC128">
+        <v>0</v>
+      </c>
+      <c r="AD128">
+        <v>0</v>
+      </c>
+      <c r="AE128">
+        <v>0</v>
+      </c>
+      <c r="AF128">
+        <v>0</v>
+      </c>
+      <c r="AG128">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ128">
+        <v>0</v>
+      </c>
+      <c r="AK128">
+        <v>0</v>
+      </c>
+      <c r="AL128">
+        <v>0</v>
+      </c>
+      <c r="AM128">
+        <v>-1</v>
+      </c>
+      <c r="AN128">
+        <v>-1</v>
+      </c>
+      <c r="AO128">
+        <v>-1</v>
+      </c>
+      <c r="AP128">
+        <v>-1</v>
+      </c>
+      <c r="AQ128">
+        <v>0</v>
+      </c>
+      <c r="AR128">
+        <v>0</v>
+      </c>
+      <c r="AS128">
+        <v>0</v>
+      </c>
+      <c r="AT128">
+        <v>0</v>
+      </c>
+      <c r="AU128" t="inlineStr">
         <is>
           <t>2026-08-21 23:00:00</t>
         </is>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G113">
@@ -18859,12 +18859,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G114">

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -807,34 +807,34 @@
         <v>5.22</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA3">
         <v>1.83</v>
@@ -843,19 +843,19 @@
         <v>1.98</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,34 +970,34 @@
         <v>6.45</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA4">
         <v>1.85</v>
@@ -1006,19 +1006,19 @@
         <v>1.87</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G13">
@@ -2437,10 +2437,10 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2449,10 +2449,10 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
         <v>0</v>
@@ -2467,25 +2467,25 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3753,10 +3753,10 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W21">
         <v>0</v>
@@ -3777,10 +3777,10 @@
         <v>0</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE21">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6216,10 +6216,10 @@
         <v>0</v>
       </c>
       <c r="AA36">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB36">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC36">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6705,10 +6705,10 @@
         <v>0</v>
       </c>
       <c r="AA39">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB39">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC39">
         <v>0</v>
@@ -6992,13 +6992,13 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="N42">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P42">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="O83">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P83">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13877,10 +13877,10 @@
         <v>0</v>
       </c>
       <c r="AA83">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB83">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC83">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -2428,19 +2428,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q13">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="R13">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2449,10 +2449,10 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W13">
         <v>0</v>
@@ -2467,25 +2467,25 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G16">
@@ -6512,40 +6512,40 @@
         <v>4.11</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AC38">
         <v>1.9</v>
@@ -6554,13 +6554,13 @@
         <v>1.78</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -10741,13 +10741,13 @@
         </is>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P64">
-        <v>0</v>
+        <v>5.28</v>
       </c>
       <c r="Q64">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU128"/>
+  <dimension ref="A1:AU122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5860,55 +5860,55 @@
         <v>2.24</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -7001,55 +7001,55 @@
         <v>1.88</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7164,55 +7164,55 @@
         <v>2.04</v>
       </c>
       <c r="Q42">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R42">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S42">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U42">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V42">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W42">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X42">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z42">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA42">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB42">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AC42">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD42">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE42">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AF42">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG42">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK42">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7816,55 +7816,55 @@
         <v>0</v>
       </c>
       <c r="Q46">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="S46">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="T46">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="U46">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="V46">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W46">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X46">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="Y46">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z46">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA46">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB46">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC46">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="AD46">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE46">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF46">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG46">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AK46">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -14988,55 +14988,55 @@
         <v>3.25</v>
       </c>
       <c r="Q90">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R90">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S90">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T90">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U90">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V90">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W90">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X90">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z90">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA90">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB90">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC90">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD90">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE90">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF90">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG90">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK90">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15151,10 +15151,10 @@
         <v>0</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -15163,43 +15163,43 @@
         <v>0</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X91">
         <v>0</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE91">
         <v>0</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15314,10 +15314,10 @@
         <v>3.15</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -15326,43 +15326,43 @@
         <v>0</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X92">
         <v>0</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE92">
         <v>0</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15477,55 +15477,55 @@
         <v>3.11</v>
       </c>
       <c r="Q93">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R93">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S93">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T93">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U93">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V93">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W93">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X93">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y93">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z93">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA93">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB93">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC93">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AD93">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE93">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF93">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG93">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK93">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15640,10 +15640,10 @@
         <v>8.6</v>
       </c>
       <c r="Q94">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R94">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S94">
         <v>0</v>
@@ -15652,43 +15652,43 @@
         <v>0</v>
       </c>
       <c r="U94">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V94">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W94">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X94">
         <v>0</v>
       </c>
       <c r="Y94">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z94">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA94">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB94">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC94">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD94">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE94">
         <v>0</v>
       </c>
       <c r="AF94">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG94">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Várda SE</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Debrecen</t>
         </is>
       </c>
       <c r="G108">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G109">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G110">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>ETO</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="G111">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Vasas</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Puskás</t>
         </is>
       </c>
       <c r="G112">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G113">
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G114">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G115">
@@ -19175,22 +19175,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G116">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G117">
@@ -19501,7 +19501,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -19511,12 +19511,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G118">
@@ -19659,27 +19659,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G119">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19822,27 +19822,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Botoşani</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G120">
@@ -19973,7 +19973,7 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19985,27 +19985,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G121">
@@ -20136,7 +20136,7 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -20148,27 +20148,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G122">
@@ -20195,13 +20195,13 @@
         </is>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P122">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q122">
         <v>0</v>
@@ -20234,10 +20234,10 @@
         <v>0</v>
       </c>
       <c r="AA122">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB122">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC122">
         <v>0</v>
@@ -20298,984 +20298,6 @@
         <v>0</v>
       </c>
       <c r="AU122" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Bulgaria First League</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>Botev Vratsa</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Botev Plovdiv</t>
-        </is>
-      </c>
-      <c r="G123">
-        <v>0</v>
-      </c>
-      <c r="H123">
-        <v>0</v>
-      </c>
-      <c r="I123">
-        <v>0</v>
-      </c>
-      <c r="J123">
-        <v>0</v>
-      </c>
-      <c r="K123">
-        <v>0</v>
-      </c>
-      <c r="L123">
-        <v>0</v>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
-      <c r="O123">
-        <v>0</v>
-      </c>
-      <c r="P123">
-        <v>0</v>
-      </c>
-      <c r="Q123">
-        <v>0</v>
-      </c>
-      <c r="R123">
-        <v>0</v>
-      </c>
-      <c r="S123">
-        <v>0</v>
-      </c>
-      <c r="T123">
-        <v>0</v>
-      </c>
-      <c r="U123">
-        <v>0</v>
-      </c>
-      <c r="V123">
-        <v>0</v>
-      </c>
-      <c r="W123">
-        <v>0</v>
-      </c>
-      <c r="X123">
-        <v>0</v>
-      </c>
-      <c r="Y123">
-        <v>0</v>
-      </c>
-      <c r="Z123">
-        <v>0</v>
-      </c>
-      <c r="AA123">
-        <v>0</v>
-      </c>
-      <c r="AB123">
-        <v>0</v>
-      </c>
-      <c r="AC123">
-        <v>0</v>
-      </c>
-      <c r="AD123">
-        <v>0</v>
-      </c>
-      <c r="AE123">
-        <v>0</v>
-      </c>
-      <c r="AF123">
-        <v>0</v>
-      </c>
-      <c r="AG123">
-        <v>0</v>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ123">
-        <v>0</v>
-      </c>
-      <c r="AK123">
-        <v>0</v>
-      </c>
-      <c r="AL123">
-        <v>0</v>
-      </c>
-      <c r="AM123">
-        <v>-1</v>
-      </c>
-      <c r="AN123">
-        <v>-1</v>
-      </c>
-      <c r="AO123">
-        <v>-1</v>
-      </c>
-      <c r="AP123">
-        <v>-1</v>
-      </c>
-      <c r="AQ123">
-        <v>0</v>
-      </c>
-      <c r="AR123">
-        <v>0</v>
-      </c>
-      <c r="AS123">
-        <v>0</v>
-      </c>
-      <c r="AT123">
-        <v>0</v>
-      </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Bulgaria First League</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Lokomotiv Sofia 1929</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>CSKA Sofia</t>
-        </is>
-      </c>
-      <c r="G124">
-        <v>0</v>
-      </c>
-      <c r="H124">
-        <v>0</v>
-      </c>
-      <c r="I124">
-        <v>0</v>
-      </c>
-      <c r="J124">
-        <v>0</v>
-      </c>
-      <c r="K124">
-        <v>0</v>
-      </c>
-      <c r="L124">
-        <v>0</v>
-      </c>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
-      <c r="O124">
-        <v>0</v>
-      </c>
-      <c r="P124">
-        <v>0</v>
-      </c>
-      <c r="Q124">
-        <v>0</v>
-      </c>
-      <c r="R124">
-        <v>0</v>
-      </c>
-      <c r="S124">
-        <v>0</v>
-      </c>
-      <c r="T124">
-        <v>0</v>
-      </c>
-      <c r="U124">
-        <v>0</v>
-      </c>
-      <c r="V124">
-        <v>0</v>
-      </c>
-      <c r="W124">
-        <v>0</v>
-      </c>
-      <c r="X124">
-        <v>0</v>
-      </c>
-      <c r="Y124">
-        <v>0</v>
-      </c>
-      <c r="Z124">
-        <v>0</v>
-      </c>
-      <c r="AA124">
-        <v>0</v>
-      </c>
-      <c r="AB124">
-        <v>0</v>
-      </c>
-      <c r="AC124">
-        <v>0</v>
-      </c>
-      <c r="AD124">
-        <v>0</v>
-      </c>
-      <c r="AE124">
-        <v>0</v>
-      </c>
-      <c r="AF124">
-        <v>0</v>
-      </c>
-      <c r="AG124">
-        <v>0</v>
-      </c>
-      <c r="AH124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ124">
-        <v>0</v>
-      </c>
-      <c r="AK124">
-        <v>0</v>
-      </c>
-      <c r="AL124">
-        <v>0</v>
-      </c>
-      <c r="AM124">
-        <v>-1</v>
-      </c>
-      <c r="AN124">
-        <v>-1</v>
-      </c>
-      <c r="AO124">
-        <v>-1</v>
-      </c>
-      <c r="AP124">
-        <v>-1</v>
-      </c>
-      <c r="AQ124">
-        <v>0</v>
-      </c>
-      <c r="AR124">
-        <v>0</v>
-      </c>
-      <c r="AS124">
-        <v>0</v>
-      </c>
-      <c r="AT124">
-        <v>0</v>
-      </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Rangers</t>
-        </is>
-      </c>
-      <c r="G125">
-        <v>0</v>
-      </c>
-      <c r="H125">
-        <v>0</v>
-      </c>
-      <c r="I125">
-        <v>0</v>
-      </c>
-      <c r="J125">
-        <v>0</v>
-      </c>
-      <c r="K125">
-        <v>0</v>
-      </c>
-      <c r="L125">
-        <v>0</v>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
-      <c r="O125">
-        <v>0</v>
-      </c>
-      <c r="P125">
-        <v>0</v>
-      </c>
-      <c r="Q125">
-        <v>0</v>
-      </c>
-      <c r="R125">
-        <v>0</v>
-      </c>
-      <c r="S125">
-        <v>0</v>
-      </c>
-      <c r="T125">
-        <v>0</v>
-      </c>
-      <c r="U125">
-        <v>0</v>
-      </c>
-      <c r="V125">
-        <v>0</v>
-      </c>
-      <c r="W125">
-        <v>0</v>
-      </c>
-      <c r="X125">
-        <v>0</v>
-      </c>
-      <c r="Y125">
-        <v>0</v>
-      </c>
-      <c r="Z125">
-        <v>0</v>
-      </c>
-      <c r="AA125">
-        <v>0</v>
-      </c>
-      <c r="AB125">
-        <v>0</v>
-      </c>
-      <c r="AC125">
-        <v>0</v>
-      </c>
-      <c r="AD125">
-        <v>0</v>
-      </c>
-      <c r="AE125">
-        <v>0</v>
-      </c>
-      <c r="AF125">
-        <v>0</v>
-      </c>
-      <c r="AG125">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ125">
-        <v>0</v>
-      </c>
-      <c r="AK125">
-        <v>0</v>
-      </c>
-      <c r="AL125">
-        <v>0</v>
-      </c>
-      <c r="AM125">
-        <v>-1</v>
-      </c>
-      <c r="AN125">
-        <v>-1</v>
-      </c>
-      <c r="AO125">
-        <v>-1</v>
-      </c>
-      <c r="AP125">
-        <v>-1</v>
-      </c>
-      <c r="AQ125">
-        <v>0</v>
-      </c>
-      <c r="AR125">
-        <v>0</v>
-      </c>
-      <c r="AS125">
-        <v>0</v>
-      </c>
-      <c r="AT125">
-        <v>0</v>
-      </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Unión La Calera</t>
-        </is>
-      </c>
-      <c r="G126">
-        <v>0</v>
-      </c>
-      <c r="H126">
-        <v>0</v>
-      </c>
-      <c r="I126">
-        <v>0</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126">
-        <v>0</v>
-      </c>
-      <c r="L126">
-        <v>0</v>
-      </c>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
-      <c r="O126">
-        <v>0</v>
-      </c>
-      <c r="P126">
-        <v>0</v>
-      </c>
-      <c r="Q126">
-        <v>0</v>
-      </c>
-      <c r="R126">
-        <v>0</v>
-      </c>
-      <c r="S126">
-        <v>0</v>
-      </c>
-      <c r="T126">
-        <v>0</v>
-      </c>
-      <c r="U126">
-        <v>0</v>
-      </c>
-      <c r="V126">
-        <v>0</v>
-      </c>
-      <c r="W126">
-        <v>0</v>
-      </c>
-      <c r="X126">
-        <v>0</v>
-      </c>
-      <c r="Y126">
-        <v>0</v>
-      </c>
-      <c r="Z126">
-        <v>0</v>
-      </c>
-      <c r="AA126">
-        <v>0</v>
-      </c>
-      <c r="AB126">
-        <v>0</v>
-      </c>
-      <c r="AC126">
-        <v>0</v>
-      </c>
-      <c r="AD126">
-        <v>0</v>
-      </c>
-      <c r="AE126">
-        <v>0</v>
-      </c>
-      <c r="AF126">
-        <v>0</v>
-      </c>
-      <c r="AG126">
-        <v>0</v>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ126">
-        <v>0</v>
-      </c>
-      <c r="AK126">
-        <v>0</v>
-      </c>
-      <c r="AL126">
-        <v>0</v>
-      </c>
-      <c r="AM126">
-        <v>-1</v>
-      </c>
-      <c r="AN126">
-        <v>-1</v>
-      </c>
-      <c r="AO126">
-        <v>-1</v>
-      </c>
-      <c r="AP126">
-        <v>-1</v>
-      </c>
-      <c r="AQ126">
-        <v>0</v>
-      </c>
-      <c r="AR126">
-        <v>0</v>
-      </c>
-      <c r="AS126">
-        <v>0</v>
-      </c>
-      <c r="AT126">
-        <v>0</v>
-      </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
-      <c r="G127">
-        <v>0</v>
-      </c>
-      <c r="H127">
-        <v>0</v>
-      </c>
-      <c r="I127">
-        <v>0</v>
-      </c>
-      <c r="J127">
-        <v>0</v>
-      </c>
-      <c r="K127">
-        <v>0</v>
-      </c>
-      <c r="L127">
-        <v>0</v>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
-      <c r="O127">
-        <v>0</v>
-      </c>
-      <c r="P127">
-        <v>0</v>
-      </c>
-      <c r="Q127">
-        <v>0</v>
-      </c>
-      <c r="R127">
-        <v>0</v>
-      </c>
-      <c r="S127">
-        <v>0</v>
-      </c>
-      <c r="T127">
-        <v>0</v>
-      </c>
-      <c r="U127">
-        <v>0</v>
-      </c>
-      <c r="V127">
-        <v>0</v>
-      </c>
-      <c r="W127">
-        <v>0</v>
-      </c>
-      <c r="X127">
-        <v>0</v>
-      </c>
-      <c r="Y127">
-        <v>0</v>
-      </c>
-      <c r="Z127">
-        <v>0</v>
-      </c>
-      <c r="AA127">
-        <v>0</v>
-      </c>
-      <c r="AB127">
-        <v>0</v>
-      </c>
-      <c r="AC127">
-        <v>0</v>
-      </c>
-      <c r="AD127">
-        <v>0</v>
-      </c>
-      <c r="AE127">
-        <v>0</v>
-      </c>
-      <c r="AF127">
-        <v>0</v>
-      </c>
-      <c r="AG127">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ127">
-        <v>0</v>
-      </c>
-      <c r="AK127">
-        <v>0</v>
-      </c>
-      <c r="AL127">
-        <v>0</v>
-      </c>
-      <c r="AM127">
-        <v>-1</v>
-      </c>
-      <c r="AN127">
-        <v>-1</v>
-      </c>
-      <c r="AO127">
-        <v>-1</v>
-      </c>
-      <c r="AP127">
-        <v>-1</v>
-      </c>
-      <c r="AQ127">
-        <v>0</v>
-      </c>
-      <c r="AR127">
-        <v>0</v>
-      </c>
-      <c r="AS127">
-        <v>0</v>
-      </c>
-      <c r="AT127">
-        <v>0</v>
-      </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="G128">
-        <v>0</v>
-      </c>
-      <c r="H128">
-        <v>0</v>
-      </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>0</v>
-      </c>
-      <c r="L128">
-        <v>0</v>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N128">
-        <v>1.89</v>
-      </c>
-      <c r="O128">
-        <v>3.54</v>
-      </c>
-      <c r="P128">
-        <v>3.45</v>
-      </c>
-      <c r="Q128">
-        <v>0</v>
-      </c>
-      <c r="R128">
-        <v>0</v>
-      </c>
-      <c r="S128">
-        <v>0</v>
-      </c>
-      <c r="T128">
-        <v>0</v>
-      </c>
-      <c r="U128">
-        <v>0</v>
-      </c>
-      <c r="V128">
-        <v>0</v>
-      </c>
-      <c r="W128">
-        <v>0</v>
-      </c>
-      <c r="X128">
-        <v>0</v>
-      </c>
-      <c r="Y128">
-        <v>0</v>
-      </c>
-      <c r="Z128">
-        <v>0</v>
-      </c>
-      <c r="AA128">
-        <v>1.72</v>
-      </c>
-      <c r="AB128">
-        <v>1.92</v>
-      </c>
-      <c r="AC128">
-        <v>0</v>
-      </c>
-      <c r="AD128">
-        <v>0</v>
-      </c>
-      <c r="AE128">
-        <v>0</v>
-      </c>
-      <c r="AF128">
-        <v>0</v>
-      </c>
-      <c r="AG128">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ128">
-        <v>0</v>
-      </c>
-      <c r="AK128">
-        <v>0</v>
-      </c>
-      <c r="AL128">
-        <v>0</v>
-      </c>
-      <c r="AM128">
-        <v>-1</v>
-      </c>
-      <c r="AN128">
-        <v>-1</v>
-      </c>
-      <c r="AO128">
-        <v>-1</v>
-      </c>
-      <c r="AP128">
-        <v>-1</v>
-      </c>
-      <c r="AQ128">
-        <v>0</v>
-      </c>
-      <c r="AR128">
-        <v>0</v>
-      </c>
-      <c r="AS128">
-        <v>0</v>
-      </c>
-      <c r="AT128">
-        <v>0</v>
-      </c>
-      <c r="AU128" t="inlineStr">
         <is>
           <t>2026-08-21 23:00:00</t>
         </is>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -2437,10 +2437,10 @@
         <v>4.53</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -2449,10 +2449,10 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
         <v>0</v>
@@ -2467,25 +2467,25 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3741,10 +3741,10 @@
         <v>12.2</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -3759,22 +3759,22 @@
         <v>1.75</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X21">
         <v>0</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC21">
         <v>1.95</v>
@@ -3783,13 +3783,13 @@
         <v>1.71</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3863,12 +3863,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G22">
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G27">
@@ -5045,55 +5045,55 @@
         <v>3.36</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T29">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V29">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X29">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y29">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z29">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC29">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD29">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE29">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF29">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG29">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK29">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5534,34 +5534,34 @@
         <v>2.61</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA32">
         <v>1.84</v>
@@ -5570,19 +5570,19 @@
         <v>1.83</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -6186,34 +6186,34 @@
         <v>4.29</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U36">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X36">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z36">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA36">
         <v>1.84</v>
@@ -6222,19 +6222,19 @@
         <v>1.84</v>
       </c>
       <c r="AC36">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AD36">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE36">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF36">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG36">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6675,34 +6675,34 @@
         <v>2.81</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T39">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U39">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V39">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W39">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y39">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z39">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA39">
         <v>2.1</v>
@@ -6711,19 +6711,19 @@
         <v>1.63</v>
       </c>
       <c r="AC39">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD39">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE39">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF39">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK39">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7327,55 +7327,55 @@
         <v>2.21</v>
       </c>
       <c r="Q43">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S43">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U43">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V43">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y43">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z43">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA43">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB43">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC43">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD43">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE43">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF43">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG43">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK43">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P48">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G49">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="O51">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="P51">
-        <v>2.68</v>
+        <v>2.35</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA51">
-        <v>1.84</v>
+        <v>2.26</v>
       </c>
       <c r="AB51">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8957,34 +8957,34 @@
         <v>3.05</v>
       </c>
       <c r="Q53">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R53">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S53">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T53">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U53">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V53">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W53">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X53">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z53">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA53">
         <v>1.78</v>
@@ -8993,19 +8993,19 @@
         <v>1.98</v>
       </c>
       <c r="AC53">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD53">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE53">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF53">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG53">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK53">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G57">
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q58">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G59">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O61">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P61">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q61">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R61">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X61">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z61">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA61">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB61">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC61">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AD61">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF61">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG61">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10750,55 +10750,55 @@
         <v>5.28</v>
       </c>
       <c r="Q64">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10913,34 +10913,34 @@
         <v>2.59</v>
       </c>
       <c r="Q65">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T65">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U65">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X65">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y65">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z65">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA65">
         <v>2.05</v>
@@ -10949,19 +10949,19 @@
         <v>1.66</v>
       </c>
       <c r="AC65">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD65">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE65">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF65">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG65">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK65">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O66">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P66">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q66">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R66">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S66">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T66">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U66">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X66">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z66">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA66">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB66">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC66">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD66">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE66">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF66">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG66">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK66">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11402,34 +11402,34 @@
         <v>2.04</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA68">
         <v>1.98</v>
@@ -11438,19 +11438,19 @@
         <v>1.83</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O69">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P69">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q69">
-        <v>0</v>
+        <v>4.14</v>
       </c>
       <c r="R69">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S69">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="T69">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V69">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W69">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X69">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y69">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z69">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AA69">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AB69">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC69">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AD69">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE69">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF69">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG69">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AK69">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11728,34 +11728,34 @@
         <v>3.05</v>
       </c>
       <c r="Q70">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R70">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T70">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U70">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V70">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W70">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y70">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z70">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA70">
         <v>1.86</v>
@@ -11764,19 +11764,19 @@
         <v>1.81</v>
       </c>
       <c r="AC70">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD70">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE70">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF70">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG70">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK70">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11882,13 +11882,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q71">
         <v>0</v>
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O73">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P73">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q73">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R73">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T73">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U73">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V73">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W73">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X73">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y73">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z73">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA73">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB73">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC73">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD73">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE73">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF73">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG73">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AK73">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12380,55 +12380,55 @@
         <v>4.21</v>
       </c>
       <c r="Q74">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R74">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S74">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T74">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U74">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V74">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W74">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X74">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y74">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z74">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA74">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB74">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC74">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD74">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE74">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF74">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG74">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK74">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12543,40 +12543,40 @@
         <v>4.57</v>
       </c>
       <c r="Q75">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC75">
         <v>2</v>
@@ -12585,13 +12585,13 @@
         <v>1.71</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12706,34 +12706,34 @@
         <v>3.97</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA76">
         <v>2.03</v>
@@ -12742,19 +12742,19 @@
         <v>1.78</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.72</v>
+        <v>5.08</v>
       </c>
       <c r="O77">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="P77">
-        <v>4.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>5.08</v>
+        <v>1.72</v>
       </c>
       <c r="O78">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="P78">
-        <v>1.66</v>
+        <v>4.36</v>
       </c>
       <c r="Q78">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R78">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S78">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T78">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U78">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V78">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W78">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X78">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z78">
-        <v>0</v>
+        <v>4.98</v>
       </c>
       <c r="AA78">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AB78">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="AC78">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD78">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF78">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG78">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13195,55 +13195,55 @@
         <v>3.05</v>
       </c>
       <c r="Q79">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R79">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S79">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U79">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="V79">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X79">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y79">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z79">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA79">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB79">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC79">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD79">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE79">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF79">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG79">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13521,34 +13521,34 @@
         <v>1.49</v>
       </c>
       <c r="Q81">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="R81">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T81">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U81">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V81">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W81">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X81">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y81">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z81">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA81">
         <v>1.83</v>
@@ -13557,19 +13557,19 @@
         <v>1.93</v>
       </c>
       <c r="AC81">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD81">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE81">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF81">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG81">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13684,55 +13684,55 @@
         <v>1.75</v>
       </c>
       <c r="Q82">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R82">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S82">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T82">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="V82">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W82">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X82">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y82">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z82">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="AA82">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB82">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AC82">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD82">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE82">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF82">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG82">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK82">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -14010,10 +14010,10 @@
         <v>2.11</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S84">
         <v>0</v>
@@ -14022,43 +14022,43 @@
         <v>0</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X84">
         <v>0</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AA84">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AB84">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE84">
         <v>0</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14173,40 +14173,40 @@
         <v>21</v>
       </c>
       <c r="Q85">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R85">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U85">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="V85">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W85">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z85">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA85">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB85">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC85">
         <v>2.2</v>
@@ -14215,13 +14215,13 @@
         <v>1.6</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF85">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AG85">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14336,55 +14336,55 @@
         <v>2.37</v>
       </c>
       <c r="Q86">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R86">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S86">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T86">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U86">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V86">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W86">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X86">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y86">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z86">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA86">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB86">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC86">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD86">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE86">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF86">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG86">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK86">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15142,19 +15142,19 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O91">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P91">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="Q91">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="R91">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="S91">
         <v>0</v>
@@ -15163,43 +15163,43 @@
         <v>0</v>
       </c>
       <c r="U91">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V91">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W91">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X91">
         <v>0</v>
       </c>
       <c r="Y91">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z91">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA91">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB91">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC91">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD91">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE91">
         <v>0</v>
       </c>
       <c r="AF91">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG91">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O97">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P97">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB97">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O108">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P108">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q108">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R108">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S108">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T108">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="U108">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V108">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W108">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X108">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y108">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z108">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA108">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC108">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD108">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE108">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF108">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG108">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK108">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Nyíregyháza Spartacus</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA110">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB110">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>7.22</v>
       </c>
       <c r="Q111">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R111">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="S111">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="T111">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U111">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V111">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W111">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X111">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y111">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z111">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA111">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AB111">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC111">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AD111">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE111">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF111">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG111">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK111">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19063,55 +19063,55 @@
         <v>0</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19869,64 +19869,64 @@
         </is>
       </c>
       <c r="N120">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O120">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P120">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q120">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R120">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S120">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T120">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U120">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V120">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W120">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X120">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y120">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z120">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA120">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB120">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC120">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD120">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE120">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF120">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG120">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH120" t="inlineStr">
         <is>
@@ -19939,10 +19939,10 @@
         </is>
       </c>
       <c r="AJ120">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK120">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL120">
         <v>0</v>
@@ -20204,34 +20204,34 @@
         <v>3.45</v>
       </c>
       <c r="Q122">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R122">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S122">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T122">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U122">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V122">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W122">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X122">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y122">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z122">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA122">
         <v>1.72</v>
@@ -20240,19 +20240,19 @@
         <v>1.92</v>
       </c>
       <c r="AC122">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD122">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE122">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF122">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG122">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH122" t="inlineStr">
         <is>
@@ -20265,10 +20265,10 @@
         </is>
       </c>
       <c r="AJ122">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK122">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL122">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU122"/>
+  <dimension ref="A1:AU118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Újpest</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Mladost Ždralovi</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HNK Vukovar 1991</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G16">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Mladost Ždralovi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Warta Poznań</t>
+          <t>HNK Vukovar 1991</t>
         </is>
       </c>
       <c r="G17">
@@ -3089,55 +3089,55 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R17">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="W17">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>2026-08-21 13:00:00</t>
+          <t>2026-08-21 12:30:00</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Riyadh</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Nassr</t>
+          <t>Warta Poznań</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>9.050000000000001</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>7</v>
+        <v>2.51</v>
       </c>
       <c r="R18">
-        <v>2.88</v>
+        <v>2.21</v>
       </c>
       <c r="S18">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="T18">
-        <v>5.2</v>
+        <v>3.02</v>
       </c>
       <c r="U18">
-        <v>1.85</v>
+        <v>2.43</v>
       </c>
       <c r="V18">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="W18">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="Z18">
-        <v>6.25</v>
+        <v>3.55</v>
       </c>
       <c r="AA18">
-        <v>1.29</v>
+        <v>1.73</v>
       </c>
       <c r="AB18">
-        <v>3.04</v>
+        <v>1.99</v>
       </c>
       <c r="AC18">
-        <v>1.84</v>
+        <v>2.75</v>
       </c>
       <c r="AD18">
-        <v>1.9</v>
+        <v>1.35</v>
       </c>
       <c r="AE18">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AF18">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG18">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3364,22 +3364,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Al Riyadh</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Al Nassr</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3537,12 +3537,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hammarby</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="G20">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Hammarby</t>
         </is>
       </c>
       <c r="G21">
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="P21">
-        <v>12.2</v>
+        <v>0</v>
       </c>
       <c r="Q21">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="R21">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -3753,43 +3753,43 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V21">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="W21">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="X21">
         <v>0</v>
       </c>
       <c r="Y21">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Z21">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA21">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AB21">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC21">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AD21">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AE21">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG21">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AK21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3853,22 +3853,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G22">
@@ -3895,19 +3895,19 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="S22">
         <v>0</v>
@@ -3916,43 +3916,43 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X22">
         <v>0</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G23">
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G24">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G27">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Hazm</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Al Draih</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G28">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>2026-08-21 13:15:00</t>
+          <t>2026-08-21 13:00:00</t>
         </is>
       </c>
     </row>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al Hazm</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Al Draih</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S29">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="T29">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U29">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V29">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W29">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X29">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y29">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z29">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AA29">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB29">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC29">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD29">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE29">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF29">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG29">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AK29">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>2026-08-21 13:30:00</t>
+          <t>2026-08-21 13:15:00</t>
         </is>
       </c>
     </row>
@@ -5157,7 +5157,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G30">
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.75</v>
+        <v>2.37</v>
       </c>
       <c r="O30">
-        <v>3.8</v>
+        <v>3.06</v>
       </c>
       <c r="P30">
-        <v>3.7</v>
+        <v>3.36</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA30">
-        <v>1.65</v>
+        <v>2.24</v>
       </c>
       <c r="AB30">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="O31">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P31">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>2.46</v>
+        <v>1.86</v>
       </c>
       <c r="O32">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P32">
-        <v>2.61</v>
+        <v>3.5</v>
       </c>
       <c r="Q32">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R32">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S32">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U32">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y32">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z32">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB32">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC32">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD32">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE32">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF32">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK32">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.6</v>
+        <v>2.46</v>
       </c>
       <c r="O33">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P33">
-        <v>4.2</v>
+        <v>2.61</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA33">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AB33">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Arabi</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.72</v>
+        <v>1.6</v>
       </c>
       <c r="O34">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="P34">
-        <v>2.24</v>
+        <v>4.2</v>
       </c>
       <c r="Q34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
         <v>1.6</v>
-      </c>
-      <c r="W34">
-        <v>1.14</v>
-      </c>
-      <c r="X34">
-        <v>1.03</v>
-      </c>
-      <c r="Y34">
-        <v>1.16</v>
-      </c>
-      <c r="Z34">
-        <v>4.75</v>
-      </c>
-      <c r="AA34">
-        <v>1.49</v>
       </c>
       <c r="AB34">
         <v>2.3</v>
       </c>
       <c r="AC34">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>UAE Arabian Gulf League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Arabi</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Wahda</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G35">
@@ -6014,64 +6014,64 @@
         </is>
       </c>
       <c r="N35">
-        <v>3.55</v>
+        <v>2.72</v>
       </c>
       <c r="O35">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q35">
-        <v>4.27</v>
+        <v>3</v>
       </c>
       <c r="R35">
+        <v>2.47</v>
+      </c>
+      <c r="S35">
+        <v>1.24</v>
+      </c>
+      <c r="T35">
+        <v>3.75</v>
+      </c>
+      <c r="U35">
+        <v>2.24</v>
+      </c>
+      <c r="V35">
+        <v>1.6</v>
+      </c>
+      <c r="W35">
+        <v>1.14</v>
+      </c>
+      <c r="X35">
+        <v>1.03</v>
+      </c>
+      <c r="Y35">
+        <v>1.16</v>
+      </c>
+      <c r="Z35">
+        <v>4.75</v>
+      </c>
+      <c r="AA35">
+        <v>1.49</v>
+      </c>
+      <c r="AB35">
         <v>2.3</v>
       </c>
-      <c r="S35">
-        <v>1.3</v>
-      </c>
-      <c r="T35">
-        <v>3.3</v>
-      </c>
-      <c r="U35">
-        <v>2.44</v>
-      </c>
-      <c r="V35">
-        <v>1.46</v>
-      </c>
-      <c r="W35">
-        <v>1.07</v>
-      </c>
-      <c r="X35">
-        <v>1.01</v>
-      </c>
-      <c r="Y35">
-        <v>1.2</v>
-      </c>
-      <c r="Z35">
-        <v>4</v>
-      </c>
-      <c r="AA35">
-        <v>1.67</v>
-      </c>
-      <c r="AB35">
-        <v>2.1</v>
-      </c>
       <c r="AC35">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="AD35">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AE35">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF35">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AG35">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AK35">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6118,7 +6118,7 @@
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>2026-08-21 13:35:00</t>
+          <t>2026-08-21 13:30:00</t>
         </is>
       </c>
     </row>
@@ -6130,12 +6130,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>UAE Arabian Gulf League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -6145,12 +6145,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>Al Wahda</t>
         </is>
       </c>
       <c r="G36">
@@ -6177,64 +6177,64 @@
         </is>
       </c>
       <c r="N36">
-        <v>1.8</v>
+        <v>3.55</v>
       </c>
       <c r="O36">
-        <v>3.52</v>
+        <v>2.9</v>
       </c>
       <c r="P36">
-        <v>4.29</v>
+        <v>2.14</v>
       </c>
       <c r="Q36">
-        <v>2.38</v>
+        <v>4.27</v>
       </c>
       <c r="R36">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U36">
-        <v>2.73</v>
+        <v>2.44</v>
       </c>
       <c r="V36">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W36">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z36">
-        <v>3.42</v>
+        <v>4</v>
       </c>
       <c r="AA36">
-        <v>1.84</v>
+        <v>1.67</v>
       </c>
       <c r="AB36">
-        <v>1.84</v>
+        <v>2.1</v>
       </c>
       <c r="AC36">
-        <v>3.17</v>
+        <v>2.46</v>
       </c>
       <c r="AD36">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AE36">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AF36">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AG36">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AK36">
-        <v>2</v>
+        <v>1.24</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>2026-08-21 14:00:00</t>
+          <t>2026-08-21 13:35:00</t>
         </is>
       </c>
     </row>
@@ -6298,7 +6298,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bregalnica Štip</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="G37">
@@ -6340,64 +6340,64 @@
         </is>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T37">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X37">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z37">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AA37">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB37">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC37">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="AD37">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF37">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6461,22 +6461,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Bregalnica Štip</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Häcken</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O38">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="P38">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="R38">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S38">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="T38">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="U38">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="V38">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="W38">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="X38">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y38">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z38">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA38">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AB38">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AC38">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD38">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE38">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AF38">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG38">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK38">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6619,27 +6619,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Häcken</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,64 +6666,64 @@
         </is>
       </c>
       <c r="N39">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="O39">
-        <v>3.24</v>
+        <v>4.25</v>
       </c>
       <c r="P39">
-        <v>2.81</v>
+        <v>4.11</v>
       </c>
       <c r="Q39">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="R39">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="S39">
-        <v>1.39</v>
+        <v>1.19</v>
       </c>
       <c r="T39">
-        <v>2.7</v>
+        <v>3.92</v>
       </c>
       <c r="U39">
-        <v>2.73</v>
+        <v>1.91</v>
       </c>
       <c r="V39">
-        <v>1.4</v>
+        <v>1.78</v>
       </c>
       <c r="W39">
-        <v>1.06</v>
+        <v>1.19</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Z39">
-        <v>3.38</v>
+        <v>5.6</v>
       </c>
       <c r="AA39">
-        <v>2.1</v>
+        <v>1.32</v>
       </c>
       <c r="AB39">
-        <v>1.63</v>
+        <v>2.89</v>
       </c>
       <c r="AC39">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="AD39">
-        <v>1.3</v>
+        <v>1.78</v>
       </c>
       <c r="AE39">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="AF39">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AG39">
-        <v>2</v>
+        <v>2.65</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AK39">
-        <v>1.62</v>
+        <v>2.07</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>2026-08-21 14:30:00</t>
+          <t>2026-08-21 14:00:00</t>
         </is>
       </c>
     </row>
@@ -6787,22 +6787,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G40">
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P40">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="V40">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W40">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6950,22 +6950,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="G41">
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q41">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R41">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="V41">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W41">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X41">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="O43">
-        <v>3.18</v>
+        <v>3.82</v>
       </c>
       <c r="P43">
+        <v>1.88</v>
+      </c>
+      <c r="Q43">
+        <v>3.5</v>
+      </c>
+      <c r="R43">
+        <v>2.3</v>
+      </c>
+      <c r="S43">
+        <v>1.25</v>
+      </c>
+      <c r="T43">
+        <v>3.3</v>
+      </c>
+      <c r="U43">
+        <v>2.4</v>
+      </c>
+      <c r="V43">
+        <v>1.49</v>
+      </c>
+      <c r="W43">
+        <v>1.09</v>
+      </c>
+      <c r="X43">
+        <v>1.03</v>
+      </c>
+      <c r="Y43">
+        <v>1.2</v>
+      </c>
+      <c r="Z43">
+        <v>4.27</v>
+      </c>
+      <c r="AA43">
+        <v>1.65</v>
+      </c>
+      <c r="AB43">
         <v>2.21</v>
       </c>
-      <c r="Q43">
-        <v>4.2</v>
-      </c>
-      <c r="R43">
-        <v>2.05</v>
-      </c>
-      <c r="S43">
-        <v>1.43</v>
-      </c>
-      <c r="T43">
-        <v>2.59</v>
-      </c>
-      <c r="U43">
-        <v>3.2</v>
-      </c>
-      <c r="V43">
-        <v>1.31</v>
-      </c>
-      <c r="W43">
-        <v>1.07</v>
-      </c>
-      <c r="X43">
-        <v>1.04</v>
-      </c>
-      <c r="Y43">
-        <v>1.32</v>
-      </c>
-      <c r="Z43">
-        <v>2.88</v>
-      </c>
-      <c r="AA43">
-        <v>2.16</v>
-      </c>
-      <c r="AB43">
-        <v>1.68</v>
-      </c>
       <c r="AC43">
-        <v>3.92</v>
+        <v>2.63</v>
       </c>
       <c r="AD43">
-        <v>1.23</v>
+        <v>1.45</v>
       </c>
       <c r="AE43">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.85</v>
+        <v>1.56</v>
       </c>
       <c r="AG43">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
         <v>1.3</v>
@@ -7434,12 +7434,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G44">
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="P44">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q44">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R44">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S44">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U44">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V44">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W44">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z44">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA44">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AB44">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC44">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AD44">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE44">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF44">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG44">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AK44">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>2026-08-21 15:00:00</t>
+          <t>2026-08-21 14:30:00</t>
         </is>
       </c>
     </row>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G45">
@@ -7765,22 +7765,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O46">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="P46">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="Q46">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R46">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S46">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="T46">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U46">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="V46">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W46">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X46">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y46">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z46">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA46">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB46">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AC46">
-        <v>5.82</v>
+        <v>0</v>
       </c>
       <c r="AD46">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AE46">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF46">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG46">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AK46">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7928,22 +7928,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G47">
@@ -7970,64 +7970,64 @@
         </is>
       </c>
       <c r="N47">
-        <v>2.28</v>
+        <v>3.62</v>
       </c>
       <c r="O47">
-        <v>3.42</v>
+        <v>2.94</v>
       </c>
       <c r="P47">
-        <v>2.97</v>
+        <v>2.07</v>
       </c>
       <c r="Q47">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R47">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="S47">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T47">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U47">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="V47">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W47">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X47">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y47">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z47">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA47">
-        <v>1.77</v>
+        <v>2.7</v>
       </c>
       <c r="AB47">
-        <v>1.95</v>
+        <v>1.36</v>
       </c>
       <c r="AC47">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="AD47">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE47">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF47">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG47">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AK47">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="P48">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q48">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R48">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S48">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T48">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U48">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V48">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W48">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X48">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y48">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z48">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA48">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB48">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="P49">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA49">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AB49">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC49">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD49">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF49">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG49">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P50">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="Q50">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V50">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X50">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB50">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE50">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF50">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK50">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="P51">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Q51">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="R51">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="S51">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T51">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="U51">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="V51">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W51">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y51">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z51">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA51">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB51">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC51">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD51">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE51">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF51">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG51">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AK51">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P52">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8824,10 +8824,10 @@
         <v>0</v>
       </c>
       <c r="AA52">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB52">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC52">
         <v>0</v>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O53">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P53">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q53">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R53">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S53">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T53">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U53">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V53">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W53">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X53">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y53">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z53">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA53">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB53">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC53">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD53">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE53">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF53">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG53">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK53">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q54">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R54">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T54">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U54">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA54">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB54">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="G55">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G56">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G57">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="O62">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P62">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="Q62">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="R62">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S62">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T62">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U62">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="V62">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W62">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y62">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z62">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA62">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AB62">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC62">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AD62">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE62">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF62">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK62">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="AU62" t="inlineStr">
         <is>
-          <t>2026-08-21 15:15:00</t>
+          <t>2026-08-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -10536,7 +10536,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P63">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="Q63">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T63">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="U63">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z63">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AA63">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB63">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC63">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AD63">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE63">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF63">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O64">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="P64">
-        <v>5.28</v>
+        <v>0</v>
       </c>
       <c r="Q64">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="R64">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S64">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T64">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="U64">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V64">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W64">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X64">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y64">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z64">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA64">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB64">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC64">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD64">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE64">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG64">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK64">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.61</v>
+        <v>1.6</v>
       </c>
       <c r="O65">
-        <v>3.3</v>
+        <v>3.86</v>
       </c>
       <c r="P65">
-        <v>2.59</v>
+        <v>5.28</v>
       </c>
       <c r="Q65">
-        <v>3.18</v>
+        <v>2.12</v>
       </c>
       <c r="R65">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="S65">
         <v>1.4</v>
       </c>
       <c r="T65">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U65">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="V65">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W65">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X65">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y65">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z65">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="AA65">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AB65">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC65">
-        <v>3.3</v>
+        <v>3.58</v>
       </c>
       <c r="AD65">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE65">
         <v>1.05</v>
       </c>
       <c r="AF65">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AG65">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AK65">
-        <v>1.48</v>
+        <v>2.21</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>2026-08-21 15:30:00</t>
+          <t>2026-08-21 15:15:00</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G66">
@@ -11070,61 +11070,61 @@
         <v>2.61</v>
       </c>
       <c r="O66">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P66">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="Q66">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="R66">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="S66">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T66">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="U66">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="V66">
         <v>1.36</v>
       </c>
       <c r="W66">
+        <v>1.07</v>
+      </c>
+      <c r="X66">
         <v>1.06</v>
       </c>
-      <c r="X66">
-        <v>1.01</v>
-      </c>
       <c r="Y66">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="Z66">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="AA66">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AB66">
-        <v>1.79</v>
+        <v>1.66</v>
       </c>
       <c r="AC66">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AD66">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE66">
         <v>1.05</v>
       </c>
       <c r="AF66">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AG66">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK66">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P68">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S68">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T68">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U68">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V68">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W68">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y68">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z68">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA68">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB68">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC68">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AD68">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AE68">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF68">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG68">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AK68">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11514,22 +11514,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.88</v>
+        <v>3.26</v>
       </c>
       <c r="O69">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="P69">
-        <v>2.6</v>
+        <v>2.04</v>
       </c>
       <c r="Q69">
-        <v>4.14</v>
+        <v>3</v>
       </c>
       <c r="R69">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="S69">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="T69">
-        <v>2.25</v>
+        <v>2.96</v>
       </c>
       <c r="U69">
-        <v>4</v>
+        <v>2.59</v>
       </c>
       <c r="V69">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="W69">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X69">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="Z69">
-        <v>2.09</v>
+        <v>3.58</v>
       </c>
       <c r="AA69">
-        <v>2.9</v>
+        <v>1.98</v>
       </c>
       <c r="AB69">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AC69">
-        <v>6.5</v>
+        <v>2.92</v>
       </c>
       <c r="AD69">
-        <v>1.11</v>
+        <v>1.31</v>
       </c>
       <c r="AE69">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF69">
-        <v>2.32</v>
+        <v>1.62</v>
       </c>
       <c r="AG69">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.37</v>
+        <v>1.24</v>
       </c>
       <c r="AK69">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11677,22 +11677,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,64 +11719,64 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.16</v>
+        <v>2.88</v>
       </c>
       <c r="O70">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="P70">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="Q70">
-        <v>3.05</v>
+        <v>4.14</v>
       </c>
       <c r="R70">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="S70">
+        <v>1.57</v>
+      </c>
+      <c r="T70">
+        <v>2.25</v>
+      </c>
+      <c r="U70">
+        <v>4</v>
+      </c>
+      <c r="V70">
+        <v>1.16</v>
+      </c>
+      <c r="W70">
+        <v>1.03</v>
+      </c>
+      <c r="X70">
+        <v>1.14</v>
+      </c>
+      <c r="Y70">
+        <v>1.66</v>
+      </c>
+      <c r="Z70">
+        <v>2.09</v>
+      </c>
+      <c r="AA70">
+        <v>2.9</v>
+      </c>
+      <c r="AB70">
         <v>1.36</v>
       </c>
-      <c r="T70">
-        <v>3.01</v>
-      </c>
-      <c r="U70">
-        <v>2.69</v>
-      </c>
-      <c r="V70">
-        <v>1.4</v>
-      </c>
-      <c r="W70">
-        <v>1.1</v>
-      </c>
-      <c r="X70">
-        <v>1</v>
-      </c>
-      <c r="Y70">
-        <v>1.25</v>
-      </c>
-      <c r="Z70">
-        <v>3.4</v>
-      </c>
-      <c r="AA70">
-        <v>1.86</v>
-      </c>
-      <c r="AB70">
-        <v>1.81</v>
-      </c>
       <c r="AC70">
-        <v>3.05</v>
+        <v>6.5</v>
       </c>
       <c r="AD70">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AE70">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF70">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="AG70">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AK70">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G71">
@@ -11885,61 +11885,61 @@
         <v>2.16</v>
       </c>
       <c r="O71">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P71">
-        <v>3.17</v>
+        <v>3.05</v>
       </c>
       <c r="Q71">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R71">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S71">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T71">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="U71">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="V71">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W71">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y71">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA71">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AB71">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AC71">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD71">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE71">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF71">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG71">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK71">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="Q72">
         <v>0</v>
@@ -12161,12 +12161,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O73">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P73">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Q73">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R73">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S73">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T73">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U73">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V73">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W73">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X73">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y73">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z73">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AA73">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB73">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AC73">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AD73">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE73">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF73">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG73">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AK73">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="AU73" t="inlineStr">
         <is>
-          <t>2026-08-21 15:45:00</t>
+          <t>2026-08-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -12339,12 +12339,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,80 +12371,80 @@
         </is>
       </c>
       <c r="N74">
-        <v>1.66</v>
+        <v>4</v>
       </c>
       <c r="O74">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="P74">
-        <v>4.21</v>
+        <v>1.75</v>
       </c>
       <c r="Q74">
-        <v>2.2</v>
+        <v>4.5</v>
       </c>
       <c r="R74">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S74">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T74">
+        <v>2.9</v>
+      </c>
+      <c r="U74">
+        <v>2.75</v>
+      </c>
+      <c r="V74">
+        <v>1.4</v>
+      </c>
+      <c r="W74">
+        <v>1.08</v>
+      </c>
+      <c r="X74">
+        <v>1.01</v>
+      </c>
+      <c r="Y74">
+        <v>1.23</v>
+      </c>
+      <c r="Z74">
+        <v>3.42</v>
+      </c>
+      <c r="AA74">
+        <v>1.83</v>
+      </c>
+      <c r="AB74">
+        <v>1.87</v>
+      </c>
+      <c r="AC74">
         <v>3.15</v>
       </c>
-      <c r="U74">
-        <v>2.48</v>
-      </c>
-      <c r="V74">
-        <v>1.44</v>
-      </c>
-      <c r="W74">
-        <v>1.11</v>
-      </c>
-      <c r="X74">
-        <v>1.04</v>
-      </c>
-      <c r="Y74">
+      <c r="AD74">
+        <v>1.33</v>
+      </c>
+      <c r="AE74">
+        <v>1.08</v>
+      </c>
+      <c r="AF74">
+        <v>1.74</v>
+      </c>
+      <c r="AG74">
+        <v>1.95</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ74">
+        <v>1.89</v>
+      </c>
+      <c r="AK74">
         <v>1.22</v>
-      </c>
-      <c r="Z74">
-        <v>3.75</v>
-      </c>
-      <c r="AA74">
-        <v>1.71</v>
-      </c>
-      <c r="AB74">
-        <v>2.02</v>
-      </c>
-      <c r="AC74">
-        <v>2.8</v>
-      </c>
-      <c r="AD74">
-        <v>1.36</v>
-      </c>
-      <c r="AE74">
-        <v>1.11</v>
-      </c>
-      <c r="AF74">
-        <v>1.7</v>
-      </c>
-      <c r="AG74">
-        <v>2.05</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ74">
-        <v>1.15</v>
-      </c>
-      <c r="AK74">
-        <v>2.05</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,80 +12534,80 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="O75">
-        <v>4.52</v>
+        <v>3.85</v>
       </c>
       <c r="P75">
-        <v>4.57</v>
+        <v>4.21</v>
       </c>
       <c r="Q75">
         <v>2.2</v>
       </c>
       <c r="R75">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="S75">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="T75">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="U75">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="V75">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="W75">
+        <v>1.11</v>
+      </c>
+      <c r="X75">
+        <v>1.04</v>
+      </c>
+      <c r="Y75">
+        <v>1.22</v>
+      </c>
+      <c r="Z75">
+        <v>3.75</v>
+      </c>
+      <c r="AA75">
+        <v>1.71</v>
+      </c>
+      <c r="AB75">
+        <v>2.02</v>
+      </c>
+      <c r="AC75">
+        <v>2.8</v>
+      </c>
+      <c r="AD75">
+        <v>1.36</v>
+      </c>
+      <c r="AE75">
+        <v>1.11</v>
+      </c>
+      <c r="AF75">
+        <v>1.7</v>
+      </c>
+      <c r="AG75">
+        <v>2.05</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ75">
         <v>1.15</v>
       </c>
-      <c r="X75">
-        <v>1.03</v>
-      </c>
-      <c r="Y75">
-        <v>1.14</v>
-      </c>
-      <c r="Z75">
-        <v>5</v>
-      </c>
-      <c r="AA75">
-        <v>1.52</v>
-      </c>
-      <c r="AB75">
-        <v>2.4</v>
-      </c>
-      <c r="AC75">
-        <v>2</v>
-      </c>
-      <c r="AD75">
-        <v>1.71</v>
-      </c>
-      <c r="AE75">
-        <v>1.2</v>
-      </c>
-      <c r="AF75">
-        <v>1.5</v>
-      </c>
-      <c r="AG75">
-        <v>2.45</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ75">
-        <v>1.22</v>
-      </c>
       <c r="AK75">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12655,22 +12655,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.92</v>
+        <v>1.74</v>
       </c>
       <c r="O76">
-        <v>3.5</v>
+        <v>4.52</v>
       </c>
       <c r="P76">
-        <v>3.97</v>
+        <v>4.57</v>
       </c>
       <c r="Q76">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="R76">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="S76">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="T76">
-        <v>2.88</v>
+        <v>3.9</v>
       </c>
       <c r="U76">
-        <v>2.88</v>
+        <v>2.3</v>
       </c>
       <c r="V76">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="W76">
+        <v>1.15</v>
+      </c>
+      <c r="X76">
         <v>1.03</v>
       </c>
-      <c r="X76">
-        <v>1.06</v>
-      </c>
       <c r="Y76">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="Z76">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="AA76">
-        <v>2.03</v>
+        <v>1.52</v>
       </c>
       <c r="AB76">
-        <v>1.78</v>
+        <v>2.4</v>
       </c>
       <c r="AC76">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="AD76">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AE76">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="AF76">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="AG76">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK76">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="O78">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="P78">
-        <v>4.36</v>
+        <v>3.97</v>
       </c>
       <c r="Q78">
-        <v>2.24</v>
+        <v>2.8</v>
       </c>
       <c r="R78">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="S78">
+        <v>1.41</v>
+      </c>
+      <c r="T78">
+        <v>2.88</v>
+      </c>
+      <c r="U78">
+        <v>2.88</v>
+      </c>
+      <c r="V78">
+        <v>1.36</v>
+      </c>
+      <c r="W78">
+        <v>1.03</v>
+      </c>
+      <c r="X78">
+        <v>1.06</v>
+      </c>
+      <c r="Y78">
+        <v>1.3</v>
+      </c>
+      <c r="Z78">
+        <v>3.1</v>
+      </c>
+      <c r="AA78">
+        <v>2.03</v>
+      </c>
+      <c r="AB78">
+        <v>1.78</v>
+      </c>
+      <c r="AC78">
+        <v>3.6</v>
+      </c>
+      <c r="AD78">
         <v>1.25</v>
       </c>
-      <c r="T78">
-        <v>3.6</v>
-      </c>
-      <c r="U78">
-        <v>2.2</v>
-      </c>
-      <c r="V78">
-        <v>1.6</v>
-      </c>
-      <c r="W78">
-        <v>1.15</v>
-      </c>
-      <c r="X78">
-        <v>1.03</v>
-      </c>
-      <c r="Y78">
-        <v>1.12</v>
-      </c>
-      <c r="Z78">
-        <v>4.98</v>
-      </c>
-      <c r="AA78">
-        <v>1.57</v>
-      </c>
-      <c r="AB78">
-        <v>2.29</v>
-      </c>
-      <c r="AC78">
-        <v>2.4</v>
-      </c>
-      <c r="AD78">
-        <v>1.49</v>
-      </c>
       <c r="AE78">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="AF78">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="AG78">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK78">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="O79">
+        <v>3.92</v>
+      </c>
+      <c r="P79">
+        <v>4.36</v>
+      </c>
+      <c r="Q79">
+        <v>2.24</v>
+      </c>
+      <c r="R79">
+        <v>2.5</v>
+      </c>
+      <c r="S79">
+        <v>1.25</v>
+      </c>
+      <c r="T79">
         <v>3.6</v>
       </c>
-      <c r="P79">
-        <v>3.05</v>
-      </c>
-      <c r="Q79">
+      <c r="U79">
+        <v>2.2</v>
+      </c>
+      <c r="V79">
+        <v>1.6</v>
+      </c>
+      <c r="W79">
+        <v>1.15</v>
+      </c>
+      <c r="X79">
+        <v>1.03</v>
+      </c>
+      <c r="Y79">
+        <v>1.12</v>
+      </c>
+      <c r="Z79">
+        <v>4.98</v>
+      </c>
+      <c r="AA79">
+        <v>1.57</v>
+      </c>
+      <c r="AB79">
+        <v>2.29</v>
+      </c>
+      <c r="AC79">
         <v>2.4</v>
       </c>
-      <c r="R79">
-        <v>2.2</v>
-      </c>
-      <c r="S79">
-        <v>1.31</v>
-      </c>
-      <c r="T79">
-        <v>3.02</v>
-      </c>
-      <c r="U79">
-        <v>2.59</v>
-      </c>
-      <c r="V79">
-        <v>1.41</v>
-      </c>
-      <c r="W79">
-        <v>1.11</v>
-      </c>
-      <c r="X79">
-        <v>1.04</v>
-      </c>
-      <c r="Y79">
+      <c r="AD79">
+        <v>1.49</v>
+      </c>
+      <c r="AE79">
         <v>1.22</v>
       </c>
-      <c r="Z79">
-        <v>3.85</v>
-      </c>
-      <c r="AA79">
-        <v>1.77</v>
-      </c>
-      <c r="AB79">
-        <v>1.93</v>
-      </c>
-      <c r="AC79">
-        <v>2.75</v>
-      </c>
-      <c r="AD79">
-        <v>1.36</v>
-      </c>
-      <c r="AE79">
-        <v>1.14</v>
-      </c>
       <c r="AF79">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AG79">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.73</v>
+        <v>2.06</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,80 +13512,80 @@
         </is>
       </c>
       <c r="N81">
-        <v>6.65</v>
+        <v>3.7</v>
       </c>
       <c r="O81">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P81">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="Q81">
-        <v>6.89</v>
+        <v>4</v>
       </c>
       <c r="R81">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S81">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T81">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="U81">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="V81">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W81">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X81">
         <v>1.04</v>
       </c>
       <c r="Y81">
+        <v>1.18</v>
+      </c>
+      <c r="Z81">
+        <v>4.52</v>
+      </c>
+      <c r="AA81">
+        <v>1.67</v>
+      </c>
+      <c r="AB81">
+        <v>2.19</v>
+      </c>
+      <c r="AC81">
+        <v>2.65</v>
+      </c>
+      <c r="AD81">
+        <v>1.43</v>
+      </c>
+      <c r="AE81">
+        <v>1.18</v>
+      </c>
+      <c r="AF81">
+        <v>1.57</v>
+      </c>
+      <c r="AG81">
+        <v>2.25</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ81">
         <v>1.2</v>
       </c>
-      <c r="Z81">
-        <v>3.72</v>
-      </c>
-      <c r="AA81">
-        <v>1.83</v>
-      </c>
-      <c r="AB81">
-        <v>1.93</v>
-      </c>
-      <c r="AC81">
-        <v>2.75</v>
-      </c>
-      <c r="AD81">
-        <v>1.39</v>
-      </c>
-      <c r="AE81">
-        <v>1.12</v>
-      </c>
-      <c r="AF81">
-        <v>1.8</v>
-      </c>
-      <c r="AG81">
-        <v>1.91</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ81">
-        <v>1.22</v>
-      </c>
       <c r="AK81">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="O82">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
-        <v>1.75</v>
+        <v>3.05</v>
       </c>
       <c r="Q82">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="R82">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S82">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T82">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U82">
-        <v>2.33</v>
+        <v>2.59</v>
       </c>
       <c r="V82">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="W82">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X82">
         <v>1.04</v>
       </c>
       <c r="Y82">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z82">
-        <v>4.52</v>
+        <v>3.85</v>
       </c>
       <c r="AA82">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AB82">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="AC82">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AD82">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE82">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF82">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG82">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>1.21</v>
+        <v>1.73</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13796,22 +13796,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.98</v>
+        <v>6.65</v>
       </c>
       <c r="O83">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P83">
-        <v>3.96</v>
+        <v>1.49</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AA83">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AB83">
-        <v>1.66</v>
+        <v>1.93</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13954,12 +13954,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.55</v>
+        <v>1.98</v>
       </c>
       <c r="O84">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="P84">
-        <v>2.11</v>
+        <v>3.96</v>
       </c>
       <c r="Q84">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R84">
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <v>0</v>
+      </c>
+      <c r="U84">
+        <v>0</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0</v>
+      </c>
+      <c r="X84">
+        <v>0</v>
+      </c>
+      <c r="Y84">
+        <v>0</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+      <c r="AA84">
         <v>2.05</v>
       </c>
-      <c r="S84">
-        <v>0</v>
-      </c>
-      <c r="T84">
-        <v>0</v>
-      </c>
-      <c r="U84">
-        <v>2.92</v>
-      </c>
-      <c r="V84">
-        <v>1.32</v>
-      </c>
-      <c r="W84">
-        <v>1.07</v>
-      </c>
-      <c r="X84">
-        <v>0</v>
-      </c>
-      <c r="Y84">
-        <v>1.34</v>
-      </c>
-      <c r="Z84">
-        <v>2.82</v>
-      </c>
-      <c r="AA84">
-        <v>2.09</v>
-      </c>
       <c r="AB84">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC84">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE84">
         <v>0</v>
       </c>
       <c r="AF84">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG84">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>2026-08-21 16:00:00</t>
+          <t>2026-08-21 15:45:00</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14122,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>1.18</v>
+        <v>3.55</v>
       </c>
       <c r="O85">
-        <v>8.5</v>
+        <v>3</v>
       </c>
       <c r="P85">
-        <v>21</v>
+        <v>2.11</v>
       </c>
       <c r="Q85">
-        <v>1.55</v>
+        <v>4.22</v>
       </c>
       <c r="R85">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="S85">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="T85">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U85">
-        <v>2.37</v>
+        <v>2.92</v>
       </c>
       <c r="V85">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="W85">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y85">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="Z85">
-        <v>4.75</v>
+        <v>2.82</v>
       </c>
       <c r="AA85">
-        <v>1.59</v>
+        <v>2.09</v>
       </c>
       <c r="AB85">
-        <v>2.35</v>
+        <v>1.63</v>
       </c>
       <c r="AC85">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD85">
-        <v>1.6</v>
+        <v>1.23</v>
       </c>
       <c r="AE85">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF85">
-        <v>2.44</v>
+        <v>1.95</v>
       </c>
       <c r="AG85">
-        <v>1.49</v>
+        <v>1.85</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK85">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14285,22 +14285,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,65 +14327,65 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.78</v>
+        <v>1.18</v>
       </c>
       <c r="O86">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="P86">
+        <v>21</v>
+      </c>
+      <c r="Q86">
+        <v>1.55</v>
+      </c>
+      <c r="R86">
+        <v>2.95</v>
+      </c>
+      <c r="S86">
+        <v>1.25</v>
+      </c>
+      <c r="T86">
+        <v>3.75</v>
+      </c>
+      <c r="U86">
         <v>2.37</v>
       </c>
-      <c r="Q86">
-        <v>3.42</v>
-      </c>
-      <c r="R86">
-        <v>2.3</v>
-      </c>
-      <c r="S86">
-        <v>1.3</v>
-      </c>
-      <c r="T86">
-        <v>3.1</v>
-      </c>
-      <c r="U86">
+      <c r="V86">
+        <v>1.57</v>
+      </c>
+      <c r="W86">
+        <v>1.14</v>
+      </c>
+      <c r="X86">
+        <v>1.01</v>
+      </c>
+      <c r="Y86">
+        <v>1.18</v>
+      </c>
+      <c r="Z86">
+        <v>4.75</v>
+      </c>
+      <c r="AA86">
+        <v>1.59</v>
+      </c>
+      <c r="AB86">
+        <v>2.35</v>
+      </c>
+      <c r="AC86">
+        <v>2.2</v>
+      </c>
+      <c r="AD86">
+        <v>1.6</v>
+      </c>
+      <c r="AE86">
+        <v>1.18</v>
+      </c>
+      <c r="AF86">
         <v>2.44</v>
       </c>
-      <c r="V86">
+      <c r="AG86">
         <v>1.49</v>
       </c>
-      <c r="W86">
-        <v>1.11</v>
-      </c>
-      <c r="X86">
-        <v>1.04</v>
-      </c>
-      <c r="Y86">
-        <v>1.2</v>
-      </c>
-      <c r="Z86">
-        <v>4.05</v>
-      </c>
-      <c r="AA86">
-        <v>1.68</v>
-      </c>
-      <c r="AB86">
-        <v>2.15</v>
-      </c>
-      <c r="AC86">
-        <v>2.54</v>
-      </c>
-      <c r="AD86">
-        <v>1.44</v>
-      </c>
-      <c r="AE86">
-        <v>1.17</v>
-      </c>
-      <c r="AF86">
-        <v>1.53</v>
-      </c>
-      <c r="AG86">
-        <v>2.34</v>
-      </c>
       <c r="AH86" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="AK86">
-        <v>1.39</v>
+        <v>5.2</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14611,22 +14611,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P88">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Q88">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R88">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S88">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="V88">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W88">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X88">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y88">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z88">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AA88">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB88">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC88">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AD88">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE88">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF88">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG88">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK88">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="O89">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P89">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Q89">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R89">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S89">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T89">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U89">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="V89">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W89">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X89">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y89">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z89">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA89">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB89">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AC89">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD89">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE89">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF89">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AG89">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK89">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G90">
@@ -14979,58 +14979,58 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="O90">
-        <v>3.13</v>
+        <v>3.42</v>
       </c>
       <c r="P90">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="Q90">
         <v>2.75</v>
       </c>
       <c r="R90">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="S90">
         <v>1.4</v>
       </c>
       <c r="T90">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="U90">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="V90">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W90">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X90">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y90">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z90">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AA90">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AB90">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AC90">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AD90">
         <v>1.22</v>
       </c>
       <c r="AE90">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF90">
         <v>1.82</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK90">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G91">
@@ -15142,64 +15142,64 @@
         </is>
       </c>
       <c r="N91">
-        <v>1.39</v>
+        <v>2.11</v>
       </c>
       <c r="O91">
-        <v>4.5</v>
+        <v>3.13</v>
       </c>
       <c r="P91">
-        <v>6.76</v>
+        <v>3.25</v>
       </c>
       <c r="Q91">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R91">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S91">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T91">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U91">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V91">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W91">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y91">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z91">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA91">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AB91">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC91">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD91">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE91">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF91">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AG91">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK91">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,19 +15305,19 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.27</v>
+        <v>1.39</v>
       </c>
       <c r="O92">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="P92">
-        <v>3.15</v>
+        <v>6.76</v>
       </c>
       <c r="Q92">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="R92">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -15326,43 +15326,43 @@
         <v>0</v>
       </c>
       <c r="U92">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V92">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W92">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X92">
         <v>0</v>
       </c>
       <c r="Y92">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z92">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA92">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB92">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC92">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD92">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE92">
         <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG92">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="O93">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="P93">
-        <v>3.11</v>
+        <v>3.15</v>
       </c>
       <c r="Q93">
-        <v>3.12</v>
+        <v>2.87</v>
       </c>
       <c r="R93">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="S93">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="T93">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="U93">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="V93">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W93">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X93">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y93">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="Z93">
-        <v>2.66</v>
+        <v>2.97</v>
       </c>
       <c r="AA93">
-        <v>2.23</v>
+        <v>2.04</v>
       </c>
       <c r="AB93">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="AC93">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="AD93">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AE93">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AF93">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AG93">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK93">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
+        <v>2.34</v>
+      </c>
+      <c r="O94">
+        <v>2.83</v>
+      </c>
+      <c r="P94">
+        <v>3.11</v>
+      </c>
+      <c r="Q94">
+        <v>3.12</v>
+      </c>
+      <c r="R94">
+        <v>1.83</v>
+      </c>
+      <c r="S94">
+        <v>1.44</v>
+      </c>
+      <c r="T94">
+        <v>2.63</v>
+      </c>
+      <c r="U94">
+        <v>3.2</v>
+      </c>
+      <c r="V94">
         <v>1.29</v>
       </c>
-      <c r="O94">
-        <v>5</v>
-      </c>
-      <c r="P94">
-        <v>8.6</v>
-      </c>
-      <c r="Q94">
-        <v>1.73</v>
-      </c>
-      <c r="R94">
-        <v>2.55</v>
-      </c>
-      <c r="S94">
-        <v>0</v>
-      </c>
-      <c r="T94">
-        <v>0</v>
-      </c>
-      <c r="U94">
-        <v>2.34</v>
-      </c>
-      <c r="V94">
-        <v>1.49</v>
-      </c>
       <c r="W94">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="X94">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y94">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="Z94">
-        <v>3.8</v>
+        <v>2.66</v>
       </c>
       <c r="AA94">
-        <v>1.68</v>
+        <v>2.23</v>
       </c>
       <c r="AB94">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="AC94">
-        <v>2.62</v>
+        <v>3.95</v>
       </c>
       <c r="AD94">
-        <v>1.39</v>
+        <v>1.17</v>
       </c>
       <c r="AE94">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF94">
-        <v>2.18</v>
+        <v>1.87</v>
       </c>
       <c r="AG94">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK94">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15747,12 +15747,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,19 +15794,19 @@
         </is>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="O95">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P95">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Q95">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R95">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S95">
         <v>0</v>
@@ -15815,43 +15815,43 @@
         <v>0</v>
       </c>
       <c r="U95">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V95">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W95">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X95">
         <v>0</v>
       </c>
       <c r="Y95">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z95">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA95">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB95">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC95">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AD95">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE95">
         <v>0</v>
       </c>
       <c r="AF95">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AG95">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
       </c>
       <c r="AU95" t="inlineStr">
         <is>
-          <t>2026-08-21 16:15:00</t>
+          <t>2026-08-21 16:00:00</t>
         </is>
       </c>
     </row>
@@ -15910,12 +15910,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G96">
@@ -16061,7 +16061,7 @@
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>2026-08-21 16:30:00</t>
+          <t>2026-08-21 16:15:00</t>
         </is>
       </c>
     </row>
@@ -16073,27 +16073,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O97">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="P97">
-        <v>5.16</v>
+        <v>0</v>
       </c>
       <c r="Q97">
         <v>0</v>
@@ -16159,10 +16159,10 @@
         <v>0</v>
       </c>
       <c r="AA97">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AB97">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC97">
         <v>0</v>
@@ -16224,7 +16224,7 @@
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>2026-08-21 19:00:00</t>
+          <t>2026-08-21 16:30:00</t>
         </is>
       </c>
     </row>
@@ -16236,12 +16236,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O98">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P98">
-        <v>0</v>
+        <v>5.16</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16322,10 +16322,10 @@
         <v>0</v>
       </c>
       <c r="AA98">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AB98">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC98">
         <v>0</v>
@@ -16387,7 +16387,7 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>2026-08-21 19:30:00</t>
+          <t>2026-08-21 19:00:00</t>
         </is>
       </c>
     </row>
@@ -16399,12 +16399,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G99">
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 19:30:00</t>
         </is>
       </c>
     </row>
@@ -16567,22 +16567,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G105">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G106">
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Várda SE</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Debrecen</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G108">
@@ -17913,64 +17913,64 @@
         </is>
       </c>
       <c r="N108">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O108">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="P108">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="Q108">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R108">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S108">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="T108">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="U108">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V108">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W108">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X108">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y108">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z108">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA108">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB108">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC108">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD108">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE108">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AF108">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG108">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH108" t="inlineStr">
         <is>
@@ -17983,10 +17983,10 @@
         </is>
       </c>
       <c r="AJ108">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK108">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL108">
         <v>0</v>
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Nyíregyháza Spartacus</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O110">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P110">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R110">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S110">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="T110">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="U110">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="V110">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="W110">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X110">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y110">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z110">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA110">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB110">
-        <v>2.07</v>
+        <v>1.66</v>
       </c>
       <c r="AC110">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AD110">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AE110">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF110">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG110">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK110">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18360,22 +18360,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>ETO</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+      <c r="Q111">
+        <v>4.7</v>
+      </c>
+      <c r="R111">
+        <v>2.1</v>
+      </c>
+      <c r="S111">
+        <v>1.41</v>
+      </c>
+      <c r="T111">
+        <v>2.65</v>
+      </c>
+      <c r="U111">
+        <v>3.07</v>
+      </c>
+      <c r="V111">
+        <v>1.32</v>
+      </c>
+      <c r="W111">
+        <v>1.06</v>
+      </c>
+      <c r="X111">
+        <v>1</v>
+      </c>
+      <c r="Y111">
         <v>1.34</v>
       </c>
-      <c r="O111">
-        <v>4.65</v>
-      </c>
-      <c r="P111">
-        <v>7.22</v>
-      </c>
-      <c r="Q111">
-        <v>1.8</v>
-      </c>
-      <c r="R111">
-        <v>2.6</v>
-      </c>
-      <c r="S111">
-        <v>1.26</v>
-      </c>
-      <c r="T111">
-        <v>3.5</v>
-      </c>
-      <c r="U111">
-        <v>2.25</v>
-      </c>
-      <c r="V111">
-        <v>1.62</v>
-      </c>
-      <c r="W111">
-        <v>1.15</v>
-      </c>
-      <c r="X111">
-        <v>1.03</v>
-      </c>
-      <c r="Y111">
-        <v>1.17</v>
-      </c>
       <c r="Z111">
-        <v>4.6</v>
+        <v>3.08</v>
       </c>
       <c r="AA111">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="AB111">
-        <v>2.27</v>
+        <v>1.74</v>
       </c>
       <c r="AC111">
-        <v>2.33</v>
+        <v>3.58</v>
       </c>
       <c r="AD111">
-        <v>1.48</v>
+        <v>1.21</v>
       </c>
       <c r="AE111">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AF111">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AG111">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.08</v>
+        <v>2.05</v>
       </c>
       <c r="AK111">
-        <v>2.88</v>
+        <v>1.14</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18523,7 +18523,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Vasas</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Puskás</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="O112">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P112">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q112">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="R112">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S112">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="T112">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U112">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="V112">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W112">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X112">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y112">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="Z112">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AA112">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AB112">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC112">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD112">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AE112">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF112">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AG112">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK112">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Újpest</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="N113">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="O113">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="P113">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q113">
         <v>0</v>
@@ -18849,22 +18849,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G114">
@@ -18930,10 +18930,10 @@
         <v>0</v>
       </c>
       <c r="AA114">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB114">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AC114">
         <v>0</v>
@@ -19007,12 +19007,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G115">
@@ -19063,55 +19063,55 @@
         <v>0</v>
       </c>
       <c r="Q115">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="R115">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S115">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T115">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U115">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="V115">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W115">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y115">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z115">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA115">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB115">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC115">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD115">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AE115">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF115">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG115">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AK115">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19158,7 +19158,7 @@
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19170,27 +19170,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O116">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P116">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q116">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R116">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S116">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T116">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U116">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V116">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W116">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X116">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y116">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z116">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA116">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB116">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC116">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD116">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE116">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF116">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG116">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK116">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19333,27 +19333,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G117">
@@ -19484,7 +19484,7 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19496,27 +19496,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G118">
@@ -19543,64 +19543,64 @@
         </is>
       </c>
       <c r="N118">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O118">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P118">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q118">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R118">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S118">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T118">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U118">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V118">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W118">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X118">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y118">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z118">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA118">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB118">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC118">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD118">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE118">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF118">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG118">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH118" t="inlineStr">
         <is>
@@ -19613,10 +19613,10 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK118">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL118">
         <v>0</v>
@@ -19646,658 +19646,6 @@
         <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>Rangers</t>
-        </is>
-      </c>
-      <c r="G119">
-        <v>0</v>
-      </c>
-      <c r="H119">
-        <v>0</v>
-      </c>
-      <c r="I119">
-        <v>0</v>
-      </c>
-      <c r="J119">
-        <v>0</v>
-      </c>
-      <c r="K119">
-        <v>0</v>
-      </c>
-      <c r="L119">
-        <v>0</v>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N119">
-        <v>0</v>
-      </c>
-      <c r="O119">
-        <v>0</v>
-      </c>
-      <c r="P119">
-        <v>0</v>
-      </c>
-      <c r="Q119">
-        <v>0</v>
-      </c>
-      <c r="R119">
-        <v>0</v>
-      </c>
-      <c r="S119">
-        <v>0</v>
-      </c>
-      <c r="T119">
-        <v>0</v>
-      </c>
-      <c r="U119">
-        <v>0</v>
-      </c>
-      <c r="V119">
-        <v>0</v>
-      </c>
-      <c r="W119">
-        <v>0</v>
-      </c>
-      <c r="X119">
-        <v>0</v>
-      </c>
-      <c r="Y119">
-        <v>0</v>
-      </c>
-      <c r="Z119">
-        <v>0</v>
-      </c>
-      <c r="AA119">
-        <v>0</v>
-      </c>
-      <c r="AB119">
-        <v>0</v>
-      </c>
-      <c r="AC119">
-        <v>0</v>
-      </c>
-      <c r="AD119">
-        <v>0</v>
-      </c>
-      <c r="AE119">
-        <v>0</v>
-      </c>
-      <c r="AF119">
-        <v>0</v>
-      </c>
-      <c r="AG119">
-        <v>0</v>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ119">
-        <v>0</v>
-      </c>
-      <c r="AK119">
-        <v>0</v>
-      </c>
-      <c r="AL119">
-        <v>0</v>
-      </c>
-      <c r="AM119">
-        <v>-1</v>
-      </c>
-      <c r="AN119">
-        <v>-1</v>
-      </c>
-      <c r="AO119">
-        <v>-1</v>
-      </c>
-      <c r="AP119">
-        <v>-1</v>
-      </c>
-      <c r="AQ119">
-        <v>0</v>
-      </c>
-      <c r="AR119">
-        <v>0</v>
-      </c>
-      <c r="AS119">
-        <v>0</v>
-      </c>
-      <c r="AT119">
-        <v>0</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Unión La Calera</t>
-        </is>
-      </c>
-      <c r="G120">
-        <v>0</v>
-      </c>
-      <c r="H120">
-        <v>0</v>
-      </c>
-      <c r="I120">
-        <v>0</v>
-      </c>
-      <c r="J120">
-        <v>0</v>
-      </c>
-      <c r="K120">
-        <v>0</v>
-      </c>
-      <c r="L120">
-        <v>0</v>
-      </c>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N120">
-        <v>1.75</v>
-      </c>
-      <c r="O120">
-        <v>3.5</v>
-      </c>
-      <c r="P120">
-        <v>4.1</v>
-      </c>
-      <c r="Q120">
-        <v>2.35</v>
-      </c>
-      <c r="R120">
-        <v>2.2</v>
-      </c>
-      <c r="S120">
-        <v>1.35</v>
-      </c>
-      <c r="T120">
-        <v>2.9</v>
-      </c>
-      <c r="U120">
-        <v>2.8</v>
-      </c>
-      <c r="V120">
-        <v>1.37</v>
-      </c>
-      <c r="W120">
-        <v>1.07</v>
-      </c>
-      <c r="X120">
-        <v>1.01</v>
-      </c>
-      <c r="Y120">
-        <v>1.29</v>
-      </c>
-      <c r="Z120">
-        <v>3.3</v>
-      </c>
-      <c r="AA120">
-        <v>1.95</v>
-      </c>
-      <c r="AB120">
-        <v>1.88</v>
-      </c>
-      <c r="AC120">
-        <v>3.35</v>
-      </c>
-      <c r="AD120">
-        <v>1.26</v>
-      </c>
-      <c r="AE120">
-        <v>1.08</v>
-      </c>
-      <c r="AF120">
-        <v>1.8</v>
-      </c>
-      <c r="AG120">
-        <v>1.91</v>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ120">
-        <v>1.29</v>
-      </c>
-      <c r="AK120">
-        <v>1.95</v>
-      </c>
-      <c r="AL120">
-        <v>0</v>
-      </c>
-      <c r="AM120">
-        <v>-1</v>
-      </c>
-      <c r="AN120">
-        <v>-1</v>
-      </c>
-      <c r="AO120">
-        <v>-1</v>
-      </c>
-      <c r="AP120">
-        <v>-1</v>
-      </c>
-      <c r="AQ120">
-        <v>0</v>
-      </c>
-      <c r="AR120">
-        <v>0</v>
-      </c>
-      <c r="AS120">
-        <v>0</v>
-      </c>
-      <c r="AT120">
-        <v>0</v>
-      </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
-      <c r="G121">
-        <v>0</v>
-      </c>
-      <c r="H121">
-        <v>0</v>
-      </c>
-      <c r="I121">
-        <v>0</v>
-      </c>
-      <c r="J121">
-        <v>0</v>
-      </c>
-      <c r="K121">
-        <v>0</v>
-      </c>
-      <c r="L121">
-        <v>0</v>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N121">
-        <v>0</v>
-      </c>
-      <c r="O121">
-        <v>0</v>
-      </c>
-      <c r="P121">
-        <v>0</v>
-      </c>
-      <c r="Q121">
-        <v>0</v>
-      </c>
-      <c r="R121">
-        <v>0</v>
-      </c>
-      <c r="S121">
-        <v>0</v>
-      </c>
-      <c r="T121">
-        <v>0</v>
-      </c>
-      <c r="U121">
-        <v>0</v>
-      </c>
-      <c r="V121">
-        <v>0</v>
-      </c>
-      <c r="W121">
-        <v>0</v>
-      </c>
-      <c r="X121">
-        <v>0</v>
-      </c>
-      <c r="Y121">
-        <v>0</v>
-      </c>
-      <c r="Z121">
-        <v>0</v>
-      </c>
-      <c r="AA121">
-        <v>0</v>
-      </c>
-      <c r="AB121">
-        <v>0</v>
-      </c>
-      <c r="AC121">
-        <v>0</v>
-      </c>
-      <c r="AD121">
-        <v>0</v>
-      </c>
-      <c r="AE121">
-        <v>0</v>
-      </c>
-      <c r="AF121">
-        <v>0</v>
-      </c>
-      <c r="AG121">
-        <v>0</v>
-      </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ121">
-        <v>0</v>
-      </c>
-      <c r="AK121">
-        <v>0</v>
-      </c>
-      <c r="AL121">
-        <v>0</v>
-      </c>
-      <c r="AM121">
-        <v>-1</v>
-      </c>
-      <c r="AN121">
-        <v>-1</v>
-      </c>
-      <c r="AO121">
-        <v>-1</v>
-      </c>
-      <c r="AP121">
-        <v>-1</v>
-      </c>
-      <c r="AQ121">
-        <v>0</v>
-      </c>
-      <c r="AR121">
-        <v>0</v>
-      </c>
-      <c r="AS121">
-        <v>0</v>
-      </c>
-      <c r="AT121">
-        <v>0</v>
-      </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="G122">
-        <v>0</v>
-      </c>
-      <c r="H122">
-        <v>0</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>0</v>
-      </c>
-      <c r="L122">
-        <v>0</v>
-      </c>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N122">
-        <v>1.89</v>
-      </c>
-      <c r="O122">
-        <v>3.54</v>
-      </c>
-      <c r="P122">
-        <v>3.45</v>
-      </c>
-      <c r="Q122">
-        <v>2.62</v>
-      </c>
-      <c r="R122">
-        <v>2.3</v>
-      </c>
-      <c r="S122">
-        <v>1.28</v>
-      </c>
-      <c r="T122">
-        <v>3.12</v>
-      </c>
-      <c r="U122">
-        <v>2.4</v>
-      </c>
-      <c r="V122">
-        <v>1.5</v>
-      </c>
-      <c r="W122">
-        <v>1.1</v>
-      </c>
-      <c r="X122">
-        <v>1.04</v>
-      </c>
-      <c r="Y122">
-        <v>1.18</v>
-      </c>
-      <c r="Z122">
-        <v>3.84</v>
-      </c>
-      <c r="AA122">
-        <v>1.72</v>
-      </c>
-      <c r="AB122">
-        <v>1.92</v>
-      </c>
-      <c r="AC122">
-        <v>2.7</v>
-      </c>
-      <c r="AD122">
-        <v>1.36</v>
-      </c>
-      <c r="AE122">
-        <v>1.14</v>
-      </c>
-      <c r="AF122">
-        <v>1.58</v>
-      </c>
-      <c r="AG122">
-        <v>2.16</v>
-      </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ122">
-        <v>1.3</v>
-      </c>
-      <c r="AK122">
-        <v>1.6</v>
-      </c>
-      <c r="AL122">
-        <v>0</v>
-      </c>
-      <c r="AM122">
-        <v>-1</v>
-      </c>
-      <c r="AN122">
-        <v>-1</v>
-      </c>
-      <c r="AO122">
-        <v>-1</v>
-      </c>
-      <c r="AP122">
-        <v>-1</v>
-      </c>
-      <c r="AQ122">
-        <v>0</v>
-      </c>
-      <c r="AR122">
-        <v>0</v>
-      </c>
-      <c r="AS122">
-        <v>0</v>
-      </c>
-      <c r="AT122">
-        <v>0</v>
-      </c>
-      <c r="AU122" t="inlineStr">
         <is>
           <t>2026-08-21 23:00:00</t>
         </is>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.19</v>
+        <v>3.28</v>
       </c>
       <c r="O42">
-        <v>3.38</v>
+        <v>3.82</v>
       </c>
       <c r="P42">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="Q42">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R42">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S42">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U42">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V42">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="W42">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X42">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y42">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="Z42">
-        <v>5.05</v>
+        <v>4.27</v>
       </c>
       <c r="AA42">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AB42">
-        <v>2.49</v>
+        <v>2.21</v>
       </c>
       <c r="AC42">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="AD42">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="AE42">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AF42">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AG42">
-        <v>2.71</v>
+        <v>2.25</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.28</v>
+        <v>3.19</v>
       </c>
       <c r="O43">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="P43">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="Q43">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R43">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T43">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U43">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V43">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="W43">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y43">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z43">
-        <v>4.27</v>
+        <v>5.05</v>
       </c>
       <c r="AA43">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AB43">
-        <v>2.21</v>
+        <v>2.49</v>
       </c>
       <c r="AC43">
-        <v>2.63</v>
+        <v>2.02</v>
       </c>
       <c r="AD43">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="AE43">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AF43">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AG43">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="AK43">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>3.7</v>
+        <v>6.65</v>
       </c>
       <c r="O81">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="Q81">
-        <v>4</v>
+        <v>6.89</v>
       </c>
       <c r="R81">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S81">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="T81">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="U81">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="V81">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="W81">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="X81">
         <v>1.04</v>
       </c>
       <c r="Y81">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z81">
-        <v>4.52</v>
+        <v>3.72</v>
       </c>
       <c r="AA81">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AB81">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="AC81">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AD81">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="AE81">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF81">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AG81">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>1.21</v>
+        <v>1.12</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,80 +13838,80 @@
         </is>
       </c>
       <c r="N83">
-        <v>6.65</v>
+        <v>3.7</v>
       </c>
       <c r="O83">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P83">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="Q83">
-        <v>6.89</v>
+        <v>4</v>
       </c>
       <c r="R83">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S83">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T83">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="U83">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="V83">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W83">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X83">
         <v>1.04</v>
       </c>
       <c r="Y83">
+        <v>1.18</v>
+      </c>
+      <c r="Z83">
+        <v>4.52</v>
+      </c>
+      <c r="AA83">
+        <v>1.67</v>
+      </c>
+      <c r="AB83">
+        <v>2.19</v>
+      </c>
+      <c r="AC83">
+        <v>2.65</v>
+      </c>
+      <c r="AD83">
+        <v>1.43</v>
+      </c>
+      <c r="AE83">
+        <v>1.18</v>
+      </c>
+      <c r="AF83">
+        <v>1.57</v>
+      </c>
+      <c r="AG83">
+        <v>2.25</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ83">
         <v>1.2</v>
       </c>
-      <c r="Z83">
-        <v>3.72</v>
-      </c>
-      <c r="AA83">
-        <v>1.83</v>
-      </c>
-      <c r="AB83">
-        <v>1.93</v>
-      </c>
-      <c r="AC83">
-        <v>2.75</v>
-      </c>
-      <c r="AD83">
-        <v>1.39</v>
-      </c>
-      <c r="AE83">
-        <v>1.12</v>
-      </c>
-      <c r="AF83">
-        <v>1.8</v>
-      </c>
-      <c r="AG83">
-        <v>1.91</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ83">
-        <v>1.22</v>
-      </c>
       <c r="AK83">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AL83">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G42">
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.28</v>
+        <v>3.19</v>
       </c>
       <c r="O42">
-        <v>3.82</v>
+        <v>3.38</v>
       </c>
       <c r="P42">
-        <v>1.88</v>
+        <v>2.04</v>
       </c>
       <c r="Q42">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R42">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="S42">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T42">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="U42">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="V42">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="W42">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X42">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="Z42">
-        <v>4.27</v>
+        <v>5.05</v>
       </c>
       <c r="AA42">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AB42">
-        <v>2.21</v>
+        <v>2.49</v>
       </c>
       <c r="AC42">
-        <v>2.63</v>
+        <v>2.02</v>
       </c>
       <c r="AD42">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="AE42">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AF42">
-        <v>1.56</v>
+        <v>1.38</v>
       </c>
       <c r="AG42">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="AK42">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7286,12 +7286,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G43">
@@ -7318,64 +7318,64 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.19</v>
+        <v>3.28</v>
       </c>
       <c r="O43">
-        <v>3.38</v>
+        <v>3.82</v>
       </c>
       <c r="P43">
-        <v>2.04</v>
+        <v>1.88</v>
       </c>
       <c r="Q43">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R43">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="S43">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="U43">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="V43">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="W43">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="X43">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>5.05</v>
+        <v>4.27</v>
       </c>
       <c r="AA43">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AB43">
-        <v>2.49</v>
+        <v>2.21</v>
       </c>
       <c r="AC43">
-        <v>2.02</v>
+        <v>2.63</v>
       </c>
       <c r="AD43">
-        <v>1.71</v>
+        <v>1.45</v>
       </c>
       <c r="AE43">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AG43">
-        <v>2.71</v>
+        <v>2.25</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AK43">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P50">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB50">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P51">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -8661,10 +8661,10 @@
         <v>0</v>
       </c>
       <c r="AA51">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB51">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC51">
         <v>0</v>
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>5.08</v>
+        <v>1.92</v>
       </c>
       <c r="O77">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="P77">
-        <v>1.66</v>
+        <v>3.97</v>
       </c>
       <c r="Q77">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="R77">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S77">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="T77">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="U77">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="V77">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W77">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X77">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y77">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z77">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA77">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="AB77">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AC77">
-        <v>3.14</v>
+        <v>3.6</v>
       </c>
       <c r="AD77">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE77">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AG77">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>1.17</v>
+        <v>1.73</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.92</v>
+        <v>5.08</v>
       </c>
       <c r="O78">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="P78">
-        <v>3.97</v>
+        <v>1.66</v>
       </c>
       <c r="Q78">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="R78">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S78">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="T78">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U78">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="V78">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W78">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X78">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y78">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z78">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA78">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AB78">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC78">
-        <v>3.6</v>
+        <v>3.14</v>
       </c>
       <c r="AD78">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AE78">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF78">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG78">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AK78">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="O82">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P82">
-        <v>3.05</v>
+        <v>1.75</v>
       </c>
       <c r="Q82">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="R82">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S82">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T82">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U82">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="V82">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W82">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X82">
         <v>1.04</v>
       </c>
       <c r="Y82">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z82">
-        <v>3.85</v>
+        <v>4.52</v>
       </c>
       <c r="AA82">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AB82">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="AC82">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AD82">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE82">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF82">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG82">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK82">
-        <v>1.73</v>
+        <v>1.21</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="O83">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P83">
-        <v>1.75</v>
+        <v>3.05</v>
       </c>
       <c r="Q83">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="R83">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S83">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T83">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U83">
-        <v>2.33</v>
+        <v>2.59</v>
       </c>
       <c r="V83">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="W83">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X83">
         <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z83">
-        <v>4.52</v>
+        <v>3.85</v>
       </c>
       <c r="AA83">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AB83">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="AC83">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AD83">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE83">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF83">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG83">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>1.21</v>
+        <v>1.73</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,19 +15305,19 @@
         </is>
       </c>
       <c r="N92">
-        <v>1.39</v>
+        <v>2.27</v>
       </c>
       <c r="O92">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="P92">
-        <v>6.76</v>
+        <v>3.15</v>
       </c>
       <c r="Q92">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R92">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S92">
         <v>0</v>
@@ -15326,43 +15326,43 @@
         <v>0</v>
       </c>
       <c r="U92">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V92">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W92">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X92">
         <v>0</v>
       </c>
       <c r="Y92">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z92">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA92">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB92">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC92">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD92">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE92">
         <v>0</v>
       </c>
       <c r="AF92">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG92">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.27</v>
+        <v>1.39</v>
       </c>
       <c r="O93">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="P93">
+        <v>6.76</v>
+      </c>
+      <c r="Q93">
+        <v>1.92</v>
+      </c>
+      <c r="R93">
+        <v>2.31</v>
+      </c>
+      <c r="S93">
+        <v>0</v>
+      </c>
+      <c r="T93">
+        <v>0</v>
+      </c>
+      <c r="U93">
+        <v>2.62</v>
+      </c>
+      <c r="V93">
+        <v>1.39</v>
+      </c>
+      <c r="W93">
+        <v>1.09</v>
+      </c>
+      <c r="X93">
+        <v>0</v>
+      </c>
+      <c r="Y93">
+        <v>1.29</v>
+      </c>
+      <c r="Z93">
         <v>3.15</v>
       </c>
-      <c r="Q93">
-        <v>2.87</v>
-      </c>
-      <c r="R93">
-        <v>2.07</v>
-      </c>
-      <c r="S93">
-        <v>0</v>
-      </c>
-      <c r="T93">
-        <v>0</v>
-      </c>
-      <c r="U93">
-        <v>2.82</v>
-      </c>
-      <c r="V93">
-        <v>1.34</v>
-      </c>
-      <c r="W93">
-        <v>1.07</v>
-      </c>
-      <c r="X93">
-        <v>0</v>
-      </c>
-      <c r="Y93">
-        <v>1.31</v>
-      </c>
-      <c r="Z93">
-        <v>2.97</v>
-      </c>
       <c r="AA93">
-        <v>2.04</v>
+        <v>1.9</v>
       </c>
       <c r="AB93">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="AC93">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="AD93">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE93">
         <v>0</v>
       </c>
       <c r="AF93">
-        <v>1.89</v>
+        <v>2.23</v>
       </c>
       <c r="AG93">
-        <v>1.91</v>
+        <v>1.65</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="O3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P3">
-        <v>5.22</v>
+        <v>5</v>
       </c>
       <c r="Q3">
         <v>2.2</v>
@@ -813,10 +813,10 @@
         <v>2.17</v>
       </c>
       <c r="S3">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T3">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="U3">
         <v>2.71</v>
@@ -825,28 +825,28 @@
         <v>1.44</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="Z3">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="AA3">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AB3">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AC3">
         <v>3.03</v>
       </c>
       <c r="AD3">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE3">
         <v>1.13</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,61 +964,61 @@
         <v>1.52</v>
       </c>
       <c r="O4">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="P4">
-        <v>6.45</v>
+        <v>5.7</v>
       </c>
       <c r="Q4">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="R4">
         <v>2.25</v>
       </c>
       <c r="S4">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
+        <v>2.94</v>
+      </c>
+      <c r="U4">
         <v>2.73</v>
       </c>
-      <c r="U4">
-        <v>2.83</v>
-      </c>
       <c r="V4">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
         <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z4">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB4">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AC4">
         <v>3.25</v>
       </c>
       <c r="AD4">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE4">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG4">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK4">
         <v>2.45</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Tukums</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tukums</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,58 +2428,58 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="R13">
+        <v>2.4</v>
+      </c>
+      <c r="S13">
+        <v>1.25</v>
+      </c>
+      <c r="T13">
+        <v>3.5</v>
+      </c>
+      <c r="U13">
+        <v>2.1</v>
+      </c>
+      <c r="V13">
+        <v>1.57</v>
+      </c>
+      <c r="W13">
+        <v>1.14</v>
+      </c>
+      <c r="X13">
+        <v>1.01</v>
+      </c>
+      <c r="Y13">
+        <v>1.14</v>
+      </c>
+      <c r="Z13">
+        <v>5</v>
+      </c>
+      <c r="AA13">
+        <v>1.53</v>
+      </c>
+      <c r="AB13">
         <v>2.38</v>
       </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>2.2</v>
-      </c>
-      <c r="V13">
-        <v>1.5</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>1.57</v>
-      </c>
-      <c r="AB13">
-        <v>2.14</v>
-      </c>
       <c r="AC13">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AD13">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF13">
         <v>1.53</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="O14">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -3753,10 +3753,10 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W21">
         <v>0</v>
@@ -3765,31 +3765,31 @@
         <v>0</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3910,10 +3910,10 @@
         <v>3.1</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>1.93</v>
@@ -3925,7 +3925,7 @@
         <v>1.2</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y22">
         <v>1.08</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.46</v>
+        <v>1.6</v>
       </c>
       <c r="O33">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="P33">
-        <v>2.61</v>
+        <v>4.2</v>
       </c>
       <c r="Q33">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AB33">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AC33">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.6</v>
+        <v>2.46</v>
       </c>
       <c r="O34">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P34">
-        <v>4.2</v>
+        <v>2.61</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA34">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AB34">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6992,19 +6992,19 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="S41">
         <v>0</v>
@@ -7013,10 +7013,10 @@
         <v>0</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W41">
         <v>0</v>
@@ -7025,31 +7025,31 @@
         <v>0</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE41">
         <v>0</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7481,10 +7481,10 @@
         </is>
       </c>
       <c r="N44">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="O44">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="P44">
         <v>2.21</v>
@@ -7493,40 +7493,40 @@
         <v>4.2</v>
       </c>
       <c r="R44">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="S44">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T44">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="U44">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V44">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="W44">
         <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z44">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA44">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AB44">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC44">
-        <v>3.92</v>
+        <v>3.82</v>
       </c>
       <c r="AD44">
         <v>1.23</v>
@@ -7535,10 +7535,10 @@
         <v>1.04</v>
       </c>
       <c r="AF44">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AG44">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7970,16 +7970,16 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="O47">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="P47">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="Q47">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="R47">
         <v>1.83</v>
@@ -7991,31 +7991,31 @@
         <v>2.2</v>
       </c>
       <c r="U47">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="V47">
         <v>1.18</v>
       </c>
       <c r="W47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X47">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y47">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="Z47">
-        <v>2.25</v>
+        <v>2.48</v>
       </c>
       <c r="AA47">
         <v>2.7</v>
       </c>
       <c r="AB47">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AC47">
-        <v>5.82</v>
+        <v>5.75</v>
       </c>
       <c r="AD47">
         <v>1.08</v>
@@ -8024,10 +8024,10 @@
         <v>1.03</v>
       </c>
       <c r="AF47">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AG47">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="AK47">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.5</v>
+        <v>2.91</v>
       </c>
       <c r="O48">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="P48">
-        <v>2.68</v>
+        <v>2.41</v>
       </c>
       <c r="Q48">
-        <v>2.9</v>
+        <v>3.32</v>
       </c>
       <c r="R48">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="S48">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T48">
-        <v>3.07</v>
+        <v>2.81</v>
       </c>
       <c r="U48">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="V48">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W48">
         <v>1.05</v>
       </c>
       <c r="X48">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y48">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="Z48">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="AA48">
-        <v>1.84</v>
+        <v>2.05</v>
       </c>
       <c r="AB48">
-        <v>1.87</v>
+        <v>1.66</v>
       </c>
       <c r="AC48">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AD48">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AE48">
         <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>1.6</v>
+        <v>1.77</v>
       </c>
       <c r="AG48">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AK48">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="O49">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="Q49">
-        <v>3.92</v>
+        <v>3.55</v>
       </c>
       <c r="R49">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="S49">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T49">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="U49">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V49">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W49">
         <v>1.05</v>
       </c>
       <c r="X49">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="Y49">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="Z49">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="AA49">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="AB49">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AC49">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="AD49">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE49">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AF49">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG49">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="AK49">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.91</v>
+        <v>2.28</v>
       </c>
       <c r="O50">
-        <v>3.24</v>
+        <v>3.42</v>
       </c>
       <c r="P50">
-        <v>2.41</v>
+        <v>2.97</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -8498,10 +8498,10 @@
         <v>0</v>
       </c>
       <c r="AA50">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AB50">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AC50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="O51">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="P51">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="Q51">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="R51">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S51">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T51">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="U51">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V51">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W51">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z51">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA51">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="AB51">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AC51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD51">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE51">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF51">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG51">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK51">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="O52">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="P52">
-        <v>2.97</v>
+        <v>2.68</v>
       </c>
       <c r="Q52">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R52">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S52">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T52">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="U52">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA52">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="AB52">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,13 +8948,13 @@
         </is>
       </c>
       <c r="N53">
-        <v>0</v>
+        <v>4.91</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P53">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P54">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q54">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R54">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S54">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T54">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U54">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V54">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W54">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X54">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y54">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z54">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA54">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB54">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC54">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AD54">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AE54">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF54">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG54">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK54">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q55">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R55">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S55">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T55">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AA55">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB55">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="O58">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="P58">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q58">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="R58">
-        <v>2.13</v>
+        <v>2.45</v>
       </c>
       <c r="S58">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="T58">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="U58">
-        <v>2.47</v>
+        <v>2.29</v>
       </c>
       <c r="V58">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="W58">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X58">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y58">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="Z58">
-        <v>4.13</v>
+        <v>4.85</v>
       </c>
       <c r="AA58">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="AB58">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="AC58">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="AD58">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AE58">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF58">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AG58">
-        <v>2.24</v>
+        <v>2.58</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AK58">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>3.55</v>
+        <v>1.98</v>
       </c>
       <c r="O60">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P60">
-        <v>1.92</v>
+        <v>3.25</v>
       </c>
       <c r="Q60">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="R60">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S60">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="T60">
-        <v>3.05</v>
+        <v>3.44</v>
       </c>
       <c r="U60">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="V60">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="W60">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X60">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y60">
         <v>1.17</v>
       </c>
       <c r="Z60">
-        <v>4</v>
+        <v>5.06</v>
       </c>
       <c r="AA60">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AB60">
-        <v>2.09</v>
+        <v>2.49</v>
       </c>
       <c r="AC60">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="AD60">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AE60">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AF60">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG60">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="AK60">
-        <v>1.26</v>
+        <v>1.75</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="O61">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="P61">
-        <v>3.25</v>
+        <v>2.57</v>
       </c>
       <c r="Q61">
+        <v>2.9</v>
+      </c>
+      <c r="R61">
+        <v>2.12</v>
+      </c>
+      <c r="S61">
+        <v>1.34</v>
+      </c>
+      <c r="T61">
+        <v>2.95</v>
+      </c>
+      <c r="U61">
+        <v>2.47</v>
+      </c>
+      <c r="V61">
+        <v>1.45</v>
+      </c>
+      <c r="W61">
+        <v>1.08</v>
+      </c>
+      <c r="X61">
+        <v>1</v>
+      </c>
+      <c r="Y61">
+        <v>1.21</v>
+      </c>
+      <c r="Z61">
+        <v>3.75</v>
+      </c>
+      <c r="AA61">
+        <v>1.72</v>
+      </c>
+      <c r="AB61">
+        <v>2.06</v>
+      </c>
+      <c r="AC61">
+        <v>2.8</v>
+      </c>
+      <c r="AD61">
+        <v>1.36</v>
+      </c>
+      <c r="AE61">
+        <v>1.13</v>
+      </c>
+      <c r="AF61">
+        <v>1.57</v>
+      </c>
+      <c r="AG61">
         <v>2.3</v>
-      </c>
-      <c r="R61">
-        <v>2.5</v>
-      </c>
-      <c r="S61">
-        <v>1.2</v>
-      </c>
-      <c r="T61">
-        <v>3.75</v>
-      </c>
-      <c r="U61">
-        <v>2.22</v>
-      </c>
-      <c r="V61">
-        <v>1.62</v>
-      </c>
-      <c r="W61">
-        <v>1.12</v>
-      </c>
-      <c r="X61">
-        <v>1.03</v>
-      </c>
-      <c r="Y61">
-        <v>1.15</v>
-      </c>
-      <c r="Z61">
-        <v>5</v>
-      </c>
-      <c r="AA61">
-        <v>1.5</v>
-      </c>
-      <c r="AB61">
-        <v>2.45</v>
-      </c>
-      <c r="AC61">
-        <v>2.24</v>
-      </c>
-      <c r="AD61">
-        <v>1.6</v>
-      </c>
-      <c r="AE61">
-        <v>1.25</v>
-      </c>
-      <c r="AF61">
-        <v>1.44</v>
-      </c>
-      <c r="AG61">
-        <v>2.55</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.25</v>
       </c>
       <c r="AK61">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P62">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q62">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T62">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U62">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X62">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z62">
-        <v>0</v>
+        <v>5.54</v>
       </c>
       <c r="AA62">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB62">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC62">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AD62">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE62">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF62">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK62">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,7 +10587,7 @@
         <v>5.3</v>
       </c>
       <c r="Q63">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="R63">
         <v>2.38</v>
@@ -10596,46 +10596,46 @@
         <v>1.28</v>
       </c>
       <c r="T63">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="U63">
-        <v>2.34</v>
+        <v>2.41</v>
       </c>
       <c r="V63">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="W63">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X63">
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z63">
-        <v>4.2</v>
+        <v>3.94</v>
       </c>
       <c r="AA63">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB63">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AC63">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="AD63">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="AE63">
         <v>1.13</v>
       </c>
       <c r="AF63">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG63">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AK63">
         <v>2.38</v>
@@ -10904,46 +10904,46 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="O65">
-        <v>3.86</v>
+        <v>3.8</v>
       </c>
       <c r="P65">
-        <v>5.28</v>
+        <v>5.3</v>
       </c>
       <c r="Q65">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R65">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S65">
         <v>1.4</v>
       </c>
       <c r="T65">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="U65">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="V65">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W65">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X65">
         <v>1.05</v>
       </c>
       <c r="Y65">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z65">
         <v>2.97</v>
       </c>
       <c r="AA65">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AB65">
         <v>1.75</v>
@@ -10952,16 +10952,16 @@
         <v>3.58</v>
       </c>
       <c r="AD65">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AE65">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF65">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG65">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.23</v>
       </c>
       <c r="AK65">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11402,55 +11402,55 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11719,37 +11719,37 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="O70">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P70">
         <v>2.6</v>
       </c>
       <c r="Q70">
-        <v>4.14</v>
+        <v>3.96</v>
       </c>
       <c r="R70">
         <v>1.73</v>
       </c>
       <c r="S70">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="T70">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U70">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="V70">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W70">
         <v>1.03</v>
       </c>
       <c r="X70">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y70">
         <v>1.66</v>
@@ -11758,10 +11758,10 @@
         <v>2.09</v>
       </c>
       <c r="AA70">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="AB70">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AC70">
         <v>6.5</v>
@@ -11773,10 +11773,10 @@
         <v>1.03</v>
       </c>
       <c r="AF70">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="AG70">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AK70">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>5.08</v>
+        <v>1.72</v>
       </c>
       <c r="O78">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="P78">
-        <v>1.66</v>
+        <v>4.36</v>
       </c>
       <c r="Q78">
-        <v>5.2</v>
+        <v>2.24</v>
       </c>
       <c r="R78">
+        <v>2.5</v>
+      </c>
+      <c r="S78">
+        <v>1.25</v>
+      </c>
+      <c r="T78">
+        <v>3.6</v>
+      </c>
+      <c r="U78">
         <v>2.2</v>
       </c>
-      <c r="S78">
-        <v>1.35</v>
-      </c>
-      <c r="T78">
-        <v>2.9</v>
-      </c>
-      <c r="U78">
-        <v>2.76</v>
-      </c>
       <c r="V78">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="W78">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="X78">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y78">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="Z78">
-        <v>3.4</v>
+        <v>4.98</v>
       </c>
       <c r="AA78">
-        <v>1.98</v>
+        <v>1.57</v>
       </c>
       <c r="AB78">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="AC78">
-        <v>3.14</v>
+        <v>2.4</v>
       </c>
       <c r="AD78">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="AE78">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AF78">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AG78">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>1.17</v>
+        <v>2.06</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.72</v>
+        <v>5.08</v>
       </c>
       <c r="O79">
-        <v>3.92</v>
+        <v>3.74</v>
       </c>
       <c r="P79">
-        <v>4.36</v>
+        <v>1.66</v>
       </c>
       <c r="Q79">
-        <v>2.24</v>
+        <v>5.2</v>
       </c>
       <c r="R79">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="S79">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="T79">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="U79">
-        <v>2.2</v>
+        <v>2.76</v>
       </c>
       <c r="V79">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="W79">
-        <v>1.15</v>
+        <v>1.05</v>
       </c>
       <c r="X79">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y79">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="Z79">
-        <v>4.98</v>
+        <v>3.4</v>
       </c>
       <c r="AA79">
-        <v>1.57</v>
+        <v>1.98</v>
       </c>
       <c r="AB79">
-        <v>2.29</v>
+        <v>1.83</v>
       </c>
       <c r="AC79">
-        <v>2.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD79">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="AE79">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AF79">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AG79">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AK79">
-        <v>2.06</v>
+        <v>1.17</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,46 +13512,46 @@
         </is>
       </c>
       <c r="N81">
-        <v>6.65</v>
+        <v>2</v>
       </c>
       <c r="O81">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P81">
-        <v>1.49</v>
+        <v>3.05</v>
       </c>
       <c r="Q81">
-        <v>6.89</v>
+        <v>2.4</v>
       </c>
       <c r="R81">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S81">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="T81">
-        <v>3.27</v>
+        <v>3.02</v>
       </c>
       <c r="U81">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="V81">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W81">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X81">
         <v>1.04</v>
       </c>
       <c r="Y81">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z81">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="AA81">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB81">
         <v>1.93</v>
@@ -13560,16 +13560,16 @@
         <v>2.75</v>
       </c>
       <c r="AD81">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE81">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF81">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG81">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>1.12</v>
+        <v>1.73</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,46 +13838,46 @@
         </is>
       </c>
       <c r="N83">
-        <v>2</v>
+        <v>6.65</v>
       </c>
       <c r="O83">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P83">
-        <v>3.05</v>
+        <v>1.49</v>
       </c>
       <c r="Q83">
-        <v>2.4</v>
+        <v>6.89</v>
       </c>
       <c r="R83">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S83">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="T83">
-        <v>3.02</v>
+        <v>3.27</v>
       </c>
       <c r="U83">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="V83">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W83">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X83">
         <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z83">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="AA83">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AB83">
         <v>1.93</v>
@@ -13886,16 +13886,16 @@
         <v>2.75</v>
       </c>
       <c r="AD83">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE83">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF83">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AG83">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>1.73</v>
+        <v>1.12</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14816,64 +14816,64 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O89">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P89">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q89">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R89">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S89">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T89">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U89">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="V89">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W89">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X89">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y89">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z89">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA89">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB89">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC89">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD89">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE89">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF89">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG89">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK89">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,52 +14979,52 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="O90">
-        <v>3.42</v>
+        <v>3.28</v>
       </c>
       <c r="P90">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q90">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="R90">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S90">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T90">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U90">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="V90">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W90">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X90">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y90">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z90">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="AA90">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="AB90">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC90">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AD90">
         <v>1.22</v>
@@ -15033,10 +15033,10 @@
         <v>1.08</v>
       </c>
       <c r="AF90">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG90">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK90">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -18239,43 +18239,43 @@
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O110">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P110">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q110">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R110">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S110">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T110">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U110">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V110">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W110">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X110">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z110">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA110">
         <v>2.15</v>
@@ -18284,19 +18284,19 @@
         <v>1.66</v>
       </c>
       <c r="AC110">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD110">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE110">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF110">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG110">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK110">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL110">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G28">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="O32">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB32">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.6</v>
+        <v>2.46</v>
       </c>
       <c r="O33">
-        <v>4</v>
+        <v>3.45</v>
       </c>
       <c r="P33">
-        <v>4.2</v>
+        <v>2.61</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U33">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V33">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA33">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AB33">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AC33">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD33">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE33">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF33">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK33">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.46</v>
+        <v>1.86</v>
       </c>
       <c r="O34">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P34">
-        <v>2.61</v>
+        <v>3.5</v>
       </c>
       <c r="Q34">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB34">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC34">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,46 +13512,46 @@
         </is>
       </c>
       <c r="N81">
-        <v>2</v>
+        <v>6.65</v>
       </c>
       <c r="O81">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
-        <v>3.05</v>
+        <v>1.49</v>
       </c>
       <c r="Q81">
-        <v>2.4</v>
+        <v>6.89</v>
       </c>
       <c r="R81">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S81">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="T81">
-        <v>3.02</v>
+        <v>3.27</v>
       </c>
       <c r="U81">
-        <v>2.59</v>
+        <v>2.35</v>
       </c>
       <c r="V81">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="W81">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X81">
         <v>1.04</v>
       </c>
       <c r="Y81">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z81">
-        <v>3.85</v>
+        <v>3.72</v>
       </c>
       <c r="AA81">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AB81">
         <v>1.93</v>
@@ -13560,16 +13560,16 @@
         <v>2.75</v>
       </c>
       <c r="AD81">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE81">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF81">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AG81">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13585,7 +13585,7 @@
         <v>1.22</v>
       </c>
       <c r="AK81">
-        <v>1.73</v>
+        <v>1.12</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,46 +13838,46 @@
         </is>
       </c>
       <c r="N83">
-        <v>6.65</v>
+        <v>2</v>
       </c>
       <c r="O83">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P83">
-        <v>1.49</v>
+        <v>3.05</v>
       </c>
       <c r="Q83">
-        <v>6.89</v>
+        <v>2.4</v>
       </c>
       <c r="R83">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S83">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="T83">
-        <v>3.27</v>
+        <v>3.02</v>
       </c>
       <c r="U83">
-        <v>2.35</v>
+        <v>2.59</v>
       </c>
       <c r="V83">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W83">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X83">
         <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z83">
-        <v>3.72</v>
+        <v>3.85</v>
       </c>
       <c r="AA83">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AB83">
         <v>1.93</v>
@@ -13886,16 +13886,16 @@
         <v>2.75</v>
       </c>
       <c r="AD83">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE83">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF83">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AG83">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13911,7 +13911,7 @@
         <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>1.12</v>
+        <v>1.73</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14218,10 +14218,10 @@
         <v>0</v>
       </c>
       <c r="AF85">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AG85">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -15142,22 +15142,22 @@
         </is>
       </c>
       <c r="N91">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="O91">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="P91">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="Q91">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R91">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="S91">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T91">
         <v>2.5</v>
@@ -15166,10 +15166,10 @@
         <v>3</v>
       </c>
       <c r="V91">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X91">
         <v>1.03</v>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
         <v>1.58</v>
@@ -15359,10 +15359,10 @@
         <v>0</v>
       </c>
       <c r="AF92">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="AG92">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15522,10 +15522,10 @@
         <v>0</v>
       </c>
       <c r="AF93">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AG93">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15631,25 +15631,25 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="O94">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="P94">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="Q94">
         <v>3.12</v>
       </c>
       <c r="R94">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S94">
         <v>1.44</v>
       </c>
       <c r="T94">
-        <v>2.63</v>
+        <v>2.31</v>
       </c>
       <c r="U94">
         <v>3.2</v>
@@ -15704,7 +15704,7 @@
         <v>1.33</v>
       </c>
       <c r="AK94">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15803,7 +15803,7 @@
         <v>8.6</v>
       </c>
       <c r="Q95">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R95">
         <v>2.55</v>
@@ -15848,10 +15848,10 @@
         <v>0</v>
       </c>
       <c r="AF95">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AG95">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -1622,13 +1622,13 @@
         <v>1.52</v>
       </c>
       <c r="Q8">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="R8">
         <v>2.44</v>
       </c>
       <c r="S8">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T8">
         <v>3.58</v>
@@ -1637,25 +1637,25 @@
         <v>2.22</v>
       </c>
       <c r="V8">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z8">
         <v>5</v>
       </c>
       <c r="AA8">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AB8">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="AC8">
         <v>2.27</v>
@@ -1670,7 +1670,7 @@
         <v>1.57</v>
       </c>
       <c r="AG8">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>Kapfenberger SV</t>
         </is>
       </c>
       <c r="G31">
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="O31">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P31">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5401,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="AA31">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB31">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC31">
         <v>0</v>
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kapfenberger SV</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="O32">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB32">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,64 +5688,64 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.46</v>
+        <v>1.86</v>
       </c>
       <c r="O33">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P33">
-        <v>2.61</v>
+        <v>3.5</v>
       </c>
       <c r="Q33">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R33">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S33">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U33">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W33">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y33">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z33">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB33">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC33">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD33">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF33">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK33">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.86</v>
+        <v>2.46</v>
       </c>
       <c r="O34">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="P34">
-        <v>3.5</v>
+        <v>2.61</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W34">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z34">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC34">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD34">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE34">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6017,55 +6017,55 @@
         <v>2.72</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P35">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="Q35">
         <v>3</v>
       </c>
       <c r="R35">
-        <v>2.47</v>
+        <v>2.26</v>
       </c>
       <c r="S35">
         <v>1.24</v>
       </c>
       <c r="T35">
-        <v>3.75</v>
+        <v>3.34</v>
       </c>
       <c r="U35">
         <v>2.24</v>
       </c>
       <c r="V35">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W35">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z35">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AA35">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="AB35">
         <v>2.3</v>
       </c>
       <c r="AC35">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="AD35">
         <v>1.55</v>
       </c>
       <c r="AE35">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF35">
         <v>1.44</v>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,61 +6180,61 @@
         <v>3.55</v>
       </c>
       <c r="O36">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="P36">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="Q36">
-        <v>4.27</v>
+        <v>3.55</v>
       </c>
       <c r="R36">
         <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T36">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="U36">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V36">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z36">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA36">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AB36">
         <v>2.1</v>
       </c>
       <c r="AC36">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AD36">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AE36">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF36">
         <v>1.52</v>
       </c>
       <c r="AG36">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.67</v>
       </c>
       <c r="AK36">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7155,16 +7155,16 @@
         </is>
       </c>
       <c r="N42">
-        <v>3.19</v>
+        <v>2.9</v>
       </c>
       <c r="O42">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="P42">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="Q42">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="R42">
         <v>2.12</v>
@@ -7176,19 +7176,19 @@
         <v>4</v>
       </c>
       <c r="U42">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V42">
         <v>1.7</v>
       </c>
       <c r="W42">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z42">
         <v>5.05</v>
@@ -7200,19 +7200,19 @@
         <v>2.49</v>
       </c>
       <c r="AC42">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AD42">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AE42">
         <v>1.29</v>
       </c>
       <c r="AF42">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG42">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AK42">
         <v>1.33</v>
@@ -7318,61 +7318,61 @@
         </is>
       </c>
       <c r="N43">
-        <v>3.28</v>
+        <v>3.05</v>
       </c>
       <c r="O43">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="P43">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="Q43">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R43">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T43">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="U43">
         <v>2.4</v>
       </c>
       <c r="V43">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W43">
         <v>1.09</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="Z43">
-        <v>4.27</v>
+        <v>4.1</v>
       </c>
       <c r="AA43">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB43">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AC43">
-        <v>2.63</v>
+        <v>2.52</v>
       </c>
       <c r="AD43">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AE43">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF43">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG43">
         <v>2.25</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="O82">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
-        <v>1.75</v>
+        <v>3.05</v>
       </c>
       <c r="Q82">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="R82">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S82">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T82">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U82">
-        <v>2.33</v>
+        <v>2.59</v>
       </c>
       <c r="V82">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="W82">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X82">
         <v>1.04</v>
       </c>
       <c r="Y82">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z82">
-        <v>4.52</v>
+        <v>3.85</v>
       </c>
       <c r="AA82">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AB82">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="AC82">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AD82">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE82">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF82">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG82">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK82">
-        <v>1.21</v>
+        <v>1.73</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="O83">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P83">
-        <v>3.05</v>
+        <v>1.75</v>
       </c>
       <c r="Q83">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="R83">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S83">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T83">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U83">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="V83">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W83">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X83">
         <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z83">
-        <v>3.85</v>
+        <v>4.52</v>
       </c>
       <c r="AA83">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AB83">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="AC83">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AD83">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE83">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF83">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG83">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK83">
-        <v>1.73</v>
+        <v>1.21</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15166,7 +15166,7 @@
         <v>3</v>
       </c>
       <c r="V91">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W91">
         <v>1.03</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK91">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15631,25 +15631,25 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O94">
         <v>2.8</v>
       </c>
       <c r="P94">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q94">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="R94">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="S94">
         <v>1.44</v>
       </c>
       <c r="T94">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="U94">
         <v>3.2</v>
@@ -15676,7 +15676,7 @@
         <v>1.57</v>
       </c>
       <c r="AC94">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="AD94">
         <v>1.17</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK94">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL94">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="O3">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P3">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="Q3">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R3">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="S3">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T3">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="U3">
-        <v>2.71</v>
+        <v>2.51</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W3">
         <v>1.05</v>
@@ -834,19 +834,19 @@
         <v>1.21</v>
       </c>
       <c r="Z3">
-        <v>3.75</v>
+        <v>3.88</v>
       </c>
       <c r="AA3">
         <v>1.86</v>
       </c>
       <c r="AB3">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC3">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="AD3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE3">
         <v>1.13</v>
@@ -871,7 +871,7 @@
         <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O4">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P4">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>1.95</v>
@@ -997,13 +997,13 @@
         <v>1.28</v>
       </c>
       <c r="Z4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA4">
         <v>1.86</v>
       </c>
       <c r="AB4">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC4">
         <v>3.25</v>
@@ -2274,7 +2274,7 @@
         <v>4.53</v>
       </c>
       <c r="Q12">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R12">
         <v>2.38</v>
@@ -2286,10 +2286,10 @@
         <v>3.5</v>
       </c>
       <c r="U12">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="V12">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W12">
         <v>1.13</v>
@@ -2307,10 +2307,10 @@
         <v>1.57</v>
       </c>
       <c r="AB12">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AC12">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="AD12">
         <v>1.45</v>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK12">
         <v>1.85</v>
@@ -2437,7 +2437,7 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R13">
         <v>2.4</v>
@@ -2449,7 +2449,7 @@
         <v>3.5</v>
       </c>
       <c r="U13">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="V13">
         <v>1.57</v>
@@ -2470,13 +2470,13 @@
         <v>1.53</v>
       </c>
       <c r="AB13">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC13">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AD13">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE13">
         <v>1.2</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="O14">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P14">
         <v>2.75</v>
@@ -2609,7 +2609,7 @@
         <v>1.39</v>
       </c>
       <c r="T14">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U14">
         <v>2.7</v>
@@ -2627,13 +2627,13 @@
         <v>1.29</v>
       </c>
       <c r="Z14">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA14">
         <v>1.89</v>
       </c>
       <c r="AB14">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC14">
         <v>3.08</v>
@@ -2642,7 +2642,7 @@
         <v>1.28</v>
       </c>
       <c r="AE14">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF14">
         <v>1.7</v>
@@ -2763,13 +2763,13 @@
         <v>4.5</v>
       </c>
       <c r="Q15">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="R15">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="S15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
         <v>3.74</v>
@@ -2778,31 +2778,31 @@
         <v>2</v>
       </c>
       <c r="V15">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W15">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
         <v>5.5</v>
       </c>
       <c r="AA15">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB15">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AC15">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="AD15">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AE15">
         <v>1.25</v>
@@ -2811,7 +2811,7 @@
         <v>1.38</v>
       </c>
       <c r="AG15">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK15">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3252,25 +3252,25 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>2.51</v>
+        <v>2.45</v>
       </c>
       <c r="R18">
         <v>2.21</v>
       </c>
       <c r="S18">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T18">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U18">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="V18">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X18">
         <v>1.01</v>
@@ -3279,7 +3279,7 @@
         <v>1.22</v>
       </c>
       <c r="Z18">
-        <v>3.55</v>
+        <v>3.68</v>
       </c>
       <c r="AA18">
         <v>1.73</v>
@@ -3288,7 +3288,7 @@
         <v>1.99</v>
       </c>
       <c r="AC18">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="AD18">
         <v>1.35</v>
@@ -3297,10 +3297,10 @@
         <v>1.11</v>
       </c>
       <c r="AF18">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG18">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,40 +3415,40 @@
         <v>1.24</v>
       </c>
       <c r="Q19">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="R19">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="S19">
         <v>1.18</v>
       </c>
       <c r="T19">
-        <v>5.2</v>
+        <v>4.33</v>
       </c>
       <c r="U19">
         <v>1.85</v>
       </c>
       <c r="V19">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="W19">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Z19">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="AA19">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AB19">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="AC19">
         <v>1.84</v>
@@ -3460,10 +3460,10 @@
         <v>1.36</v>
       </c>
       <c r="AF19">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG19">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3898,16 +3898,16 @@
         <v>1.17</v>
       </c>
       <c r="O22">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="P22">
-        <v>12.2</v>
+        <v>11</v>
       </c>
       <c r="Q22">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="R22">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="S22">
         <v>1.14</v>
@@ -3916,44 +3916,44 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="V22">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="W22">
         <v>1.2</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Z22">
-        <v>5.6</v>
+        <v>6.75</v>
       </c>
       <c r="AA22">
-        <v>1.37</v>
+        <v>1.28</v>
       </c>
       <c r="AB22">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="AC22">
-        <v>1.95</v>
+        <v>1.71</v>
       </c>
       <c r="AD22">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="AE22">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AF22">
+        <v>1.76</v>
+      </c>
+      <c r="AG22">
         <v>1.88</v>
       </c>
-      <c r="AG22">
-        <v>1.77</v>
-      </c>
       <c r="AH22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AK22">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -5199,19 +5199,19 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.37</v>
+        <v>1.92</v>
       </c>
       <c r="O30">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="P30">
-        <v>3.36</v>
+        <v>3.4</v>
       </c>
       <c r="Q30">
-        <v>2.85</v>
+        <v>2.54</v>
       </c>
       <c r="R30">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="S30">
         <v>1.46</v>
@@ -5220,7 +5220,7 @@
         <v>2.5</v>
       </c>
       <c r="U30">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V30">
         <v>1.32</v>
@@ -5229,34 +5229,34 @@
         <v>1.03</v>
       </c>
       <c r="X30">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y30">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z30">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="AA30">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="AB30">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC30">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="AD30">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE30">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF30">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG30">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>1.59</v>
+        <v>1.81</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="O31">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="P31">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="P32">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB32">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>1.86</v>
       </c>
       <c r="O33">
-        <v>3.55</v>
+        <v>3.74</v>
       </c>
       <c r="P33">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.46</v>
+        <v>2.85</v>
       </c>
       <c r="O34">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>2.61</v>
+        <v>2.15</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -5866,49 +5866,49 @@
         <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U34">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="V34">
         <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X34">
         <v>1</v>
       </c>
       <c r="Y34">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z34">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="AA34">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AB34">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC34">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD34">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE34">
         <v>1.06</v>
       </c>
       <c r="AF34">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
         <v>1.25</v>
       </c>
       <c r="AK34">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O37">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>4.29</v>
+        <v>3.9</v>
       </c>
       <c r="Q37">
         <v>2.38</v>
@@ -6355,46 +6355,46 @@
         <v>2.15</v>
       </c>
       <c r="S37">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U37">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V37">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W37">
         <v>1.04</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z37">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AA37">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="AB37">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AC37">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="AD37">
         <v>1.33</v>
       </c>
       <c r="AE37">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AG37">
         <v>1.95</v>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK37">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6829,64 +6829,64 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="O40">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P40">
-        <v>2.81</v>
+        <v>3.25</v>
       </c>
       <c r="Q40">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="R40">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="S40">
         <v>1.39</v>
       </c>
       <c r="T40">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="U40">
-        <v>2.73</v>
+        <v>2.85</v>
       </c>
       <c r="V40">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W40">
+        <v>1.08</v>
+      </c>
+      <c r="X40">
         <v>1.06</v>
       </c>
-      <c r="X40">
-        <v>1</v>
-      </c>
       <c r="Y40">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z40">
-        <v>3.38</v>
+        <v>2.99</v>
       </c>
       <c r="AA40">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB40">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AC40">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AD40">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE40">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF40">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG40">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AK40">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7481,19 +7481,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O44">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="P44">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="Q44">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="R44">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="S44">
         <v>1.38</v>
@@ -7502,19 +7502,19 @@
         <v>2.63</v>
       </c>
       <c r="U44">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="V44">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X44">
         <v>1.01</v>
       </c>
       <c r="Y44">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z44">
         <v>2.9</v>
@@ -7523,10 +7523,10 @@
         <v>2.05</v>
       </c>
       <c r="AB44">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AC44">
-        <v>3.82</v>
+        <v>4.02</v>
       </c>
       <c r="AD44">
         <v>1.23</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AK44">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7988,7 +7988,7 @@
         <v>1.59</v>
       </c>
       <c r="T47">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="U47">
         <v>3.85</v>
@@ -7997,7 +7997,7 @@
         <v>1.18</v>
       </c>
       <c r="W47">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X47">
         <v>1.08</v>
@@ -8024,10 +8024,10 @@
         <v>1.03</v>
       </c>
       <c r="AF47">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="AG47">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>1.36</v>
       </c>
       <c r="AK47">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,25 +8133,25 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.91</v>
+        <v>2.62</v>
       </c>
       <c r="O48">
-        <v>3.24</v>
+        <v>3.46</v>
       </c>
       <c r="P48">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="Q48">
-        <v>3.32</v>
+        <v>3.05</v>
       </c>
       <c r="R48">
         <v>2.15</v>
       </c>
       <c r="S48">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T48">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="U48">
         <v>3</v>
@@ -8160,7 +8160,7 @@
         <v>1.33</v>
       </c>
       <c r="W48">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X48">
         <v>1.01</v>
@@ -8172,10 +8172,10 @@
         <v>3.1</v>
       </c>
       <c r="AA48">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB48">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC48">
         <v>3.75</v>
@@ -8187,10 +8187,10 @@
         <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AG48">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="AK48">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,52 +8296,52 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.09</v>
+        <v>2.8</v>
       </c>
       <c r="O49">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="P49">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="Q49">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="R49">
         <v>2.05</v>
       </c>
       <c r="S49">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T49">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U49">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V49">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="W49">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X49">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y49">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z49">
         <v>2.94</v>
       </c>
       <c r="AA49">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB49">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="AC49">
-        <v>3.44</v>
+        <v>3.55</v>
       </c>
       <c r="AD49">
         <v>1.23</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AK49">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.28</v>
+        <v>3.15</v>
       </c>
       <c r="O50">
-        <v>3.42</v>
+        <v>3.05</v>
       </c>
       <c r="P50">
-        <v>2.97</v>
+        <v>2.3</v>
       </c>
       <c r="Q50">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S50">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T50">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U50">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V50">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W50">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X50">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z50">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA50">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="AB50">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.15</v>
+        <v>2.4</v>
       </c>
       <c r="O51">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="P51">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="Q51">
-        <v>3.92</v>
+        <v>2.95</v>
       </c>
       <c r="R51">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="S51">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T51">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="U51">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="V51">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="W51">
         <v>1.05</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y51">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="Z51">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA51">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="AB51">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="AC51">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AD51">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AE51">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="AG51">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK51">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="O52">
         <v>3.34</v>
       </c>
       <c r="P52">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="Q52">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R52">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T52">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="U52">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V52">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="W52">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X52">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y52">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z52">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AA52">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AB52">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC52">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD52">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF52">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG52">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK52">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8954,7 +8954,7 @@
         <v>3.9</v>
       </c>
       <c r="P53">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -9277,10 +9277,10 @@
         <v>2.25</v>
       </c>
       <c r="O55">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P55">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q55">
         <v>2.7</v>
@@ -9316,22 +9316,22 @@
         <v>1.73</v>
       </c>
       <c r="AB55">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="AC55">
         <v>2.8</v>
       </c>
       <c r="AD55">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE55">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF55">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG55">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9600,19 +9600,19 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.45</v>
+        <v>3.84</v>
       </c>
       <c r="O57">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="P57">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="Q57">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="R57">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S57">
         <v>1.25</v>
@@ -9621,43 +9621,43 @@
         <v>3.52</v>
       </c>
       <c r="U57">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V57">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="W57">
         <v>1.13</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="Z57">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AA57">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AB57">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AC57">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="AD57">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="AE57">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF57">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AG57">
-        <v>2.53</v>
+        <v>2.28</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK57">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,80 +9763,80 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O58">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P58">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="Q58">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="R58">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="S58">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T58">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="U58">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="V58">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W58">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X58">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z58">
-        <v>4.85</v>
+        <v>4.5</v>
       </c>
       <c r="AA58">
+        <v>1.53</v>
+      </c>
+      <c r="AB58">
+        <v>2.28</v>
+      </c>
+      <c r="AC58">
+        <v>2.32</v>
+      </c>
+      <c r="AD58">
+        <v>1.52</v>
+      </c>
+      <c r="AE58">
+        <v>1.2</v>
+      </c>
+      <c r="AF58">
+        <v>1.46</v>
+      </c>
+      <c r="AG58">
+        <v>2.48</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ58">
+        <v>1.24</v>
+      </c>
+      <c r="AK58">
         <v>1.56</v>
-      </c>
-      <c r="AB58">
-        <v>2.3</v>
-      </c>
-      <c r="AC58">
-        <v>2.28</v>
-      </c>
-      <c r="AD58">
-        <v>1.5</v>
-      </c>
-      <c r="AE58">
-        <v>1.17</v>
-      </c>
-      <c r="AF58">
-        <v>1.44</v>
-      </c>
-      <c r="AG58">
-        <v>2.58</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ58">
-        <v>1.42</v>
-      </c>
-      <c r="AK58">
-        <v>1.53</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10116,7 +10116,7 @@
         <v>1.62</v>
       </c>
       <c r="W60">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X60">
         <v>1.03</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,65 +10252,65 @@
         </is>
       </c>
       <c r="N61">
+        <v>2.25</v>
+      </c>
+      <c r="O61">
+        <v>3.64</v>
+      </c>
+      <c r="P61">
+        <v>2.71</v>
+      </c>
+      <c r="Q61">
+        <v>2.65</v>
+      </c>
+      <c r="R61">
+        <v>2.45</v>
+      </c>
+      <c r="S61">
+        <v>1.2</v>
+      </c>
+      <c r="T61">
+        <v>4</v>
+      </c>
+      <c r="U61">
+        <v>2.17</v>
+      </c>
+      <c r="V61">
+        <v>1.58</v>
+      </c>
+      <c r="W61">
+        <v>1.15</v>
+      </c>
+      <c r="X61">
+        <v>1.03</v>
+      </c>
+      <c r="Y61">
+        <v>1.15</v>
+      </c>
+      <c r="Z61">
+        <v>4.6</v>
+      </c>
+      <c r="AA61">
+        <v>1.5</v>
+      </c>
+      <c r="AB61">
+        <v>2.4</v>
+      </c>
+      <c r="AC61">
+        <v>2.25</v>
+      </c>
+      <c r="AD61">
+        <v>1.55</v>
+      </c>
+      <c r="AE61">
+        <v>1.21</v>
+      </c>
+      <c r="AF61">
+        <v>1.44</v>
+      </c>
+      <c r="AG61">
         <v>2.5</v>
       </c>
-      <c r="O61">
-        <v>3.32</v>
-      </c>
-      <c r="P61">
-        <v>2.57</v>
-      </c>
-      <c r="Q61">
-        <v>2.9</v>
-      </c>
-      <c r="R61">
-        <v>2.12</v>
-      </c>
-      <c r="S61">
-        <v>1.34</v>
-      </c>
-      <c r="T61">
-        <v>2.95</v>
-      </c>
-      <c r="U61">
-        <v>2.47</v>
-      </c>
-      <c r="V61">
-        <v>1.45</v>
-      </c>
-      <c r="W61">
-        <v>1.08</v>
-      </c>
-      <c r="X61">
-        <v>1</v>
-      </c>
-      <c r="Y61">
-        <v>1.21</v>
-      </c>
-      <c r="Z61">
-        <v>3.75</v>
-      </c>
-      <c r="AA61">
-        <v>1.72</v>
-      </c>
-      <c r="AB61">
-        <v>2.06</v>
-      </c>
-      <c r="AC61">
-        <v>2.8</v>
-      </c>
-      <c r="AD61">
-        <v>1.36</v>
-      </c>
-      <c r="AE61">
-        <v>1.13</v>
-      </c>
-      <c r="AF61">
-        <v>1.57</v>
-      </c>
-      <c r="AG61">
-        <v>2.3</v>
-      </c>
       <c r="AH61" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK61">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="O62">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P62">
+        <v>2.57</v>
+      </c>
+      <c r="Q62">
+        <v>2.9</v>
+      </c>
+      <c r="R62">
+        <v>2.12</v>
+      </c>
+      <c r="S62">
+        <v>1.34</v>
+      </c>
+      <c r="T62">
+        <v>2.95</v>
+      </c>
+      <c r="U62">
+        <v>2.47</v>
+      </c>
+      <c r="V62">
+        <v>1.45</v>
+      </c>
+      <c r="W62">
+        <v>1.08</v>
+      </c>
+      <c r="X62">
+        <v>1</v>
+      </c>
+      <c r="Y62">
+        <v>1.21</v>
+      </c>
+      <c r="Z62">
+        <v>3.9</v>
+      </c>
+      <c r="AA62">
+        <v>1.72</v>
+      </c>
+      <c r="AB62">
+        <v>2</v>
+      </c>
+      <c r="AC62">
         <v>2.8</v>
       </c>
-      <c r="Q62">
-        <v>2.7</v>
-      </c>
-      <c r="R62">
-        <v>2.55</v>
-      </c>
-      <c r="S62">
-        <v>1.2</v>
-      </c>
-      <c r="T62">
-        <v>4</v>
-      </c>
-      <c r="U62">
-        <v>2.11</v>
-      </c>
-      <c r="V62">
-        <v>1.67</v>
-      </c>
-      <c r="W62">
-        <v>1.2</v>
-      </c>
-      <c r="X62">
-        <v>1.03</v>
-      </c>
-      <c r="Y62">
-        <v>1.12</v>
-      </c>
-      <c r="Z62">
-        <v>5.54</v>
-      </c>
-      <c r="AA62">
-        <v>1.53</v>
-      </c>
-      <c r="AB62">
-        <v>2.4</v>
-      </c>
-      <c r="AC62">
-        <v>2.09</v>
-      </c>
       <c r="AD62">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AE62">
+        <v>1.13</v>
+      </c>
+      <c r="AF62">
+        <v>1.57</v>
+      </c>
+      <c r="AG62">
+        <v>2.3</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
         <v>1.25</v>
       </c>
-      <c r="AF62">
-        <v>1.44</v>
-      </c>
-      <c r="AG62">
-        <v>2.6</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.22</v>
-      </c>
       <c r="AK62">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10581,7 +10581,7 @@
         <v>1.5</v>
       </c>
       <c r="O63">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P63">
         <v>5.3</v>
@@ -10593,13 +10593,13 @@
         <v>2.38</v>
       </c>
       <c r="S63">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T63">
         <v>3.3</v>
       </c>
       <c r="U63">
-        <v>2.41</v>
+        <v>2.55</v>
       </c>
       <c r="V63">
         <v>1.38</v>
@@ -10611,13 +10611,13 @@
         <v>1.01</v>
       </c>
       <c r="Y63">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z63">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="AA63">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AB63">
         <v>1.79</v>
@@ -10629,13 +10629,13 @@
         <v>1.28</v>
       </c>
       <c r="AE63">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF63">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG63">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK63">
         <v>2.38</v>
@@ -10910,10 +10910,10 @@
         <v>3.8</v>
       </c>
       <c r="P65">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="Q65">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="R65">
         <v>2.15</v>
@@ -10922,7 +10922,7 @@
         <v>1.4</v>
       </c>
       <c r="T65">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="U65">
         <v>2.95</v>
@@ -10955,7 +10955,7 @@
         <v>1.21</v>
       </c>
       <c r="AE65">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF65">
         <v>1.95</v>
@@ -11067,34 +11067,34 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="O66">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P66">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="Q66">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="R66">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="S66">
         <v>1.4</v>
       </c>
       <c r="T66">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U66">
         <v>2.94</v>
       </c>
       <c r="V66">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W66">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X66">
         <v>1.06</v>
@@ -11103,28 +11103,28 @@
         <v>1.33</v>
       </c>
       <c r="Z66">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="AA66">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="AB66">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC66">
-        <v>3.3</v>
+        <v>3.38</v>
       </c>
       <c r="AD66">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE66">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF66">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AG66">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11239,16 +11239,16 @@
         <v>2.41</v>
       </c>
       <c r="Q67">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R67">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S67">
         <v>1.36</v>
       </c>
       <c r="T67">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="U67">
         <v>2.78</v>
@@ -11275,10 +11275,10 @@
         <v>1.79</v>
       </c>
       <c r="AC67">
-        <v>3.1</v>
+        <v>3.28</v>
       </c>
       <c r="AD67">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AE67">
         <v>1.05</v>
@@ -11287,7 +11287,7 @@
         <v>1.7</v>
       </c>
       <c r="AG67">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AK67">
         <v>1.38</v>
@@ -11402,55 +11402,55 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="R68">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S68">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T68">
-        <v>3.17</v>
+        <v>2.94</v>
       </c>
       <c r="U68">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="V68">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W68">
         <v>1.08</v>
       </c>
       <c r="X68">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y68">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z68">
-        <v>3.74</v>
+        <v>3.9</v>
       </c>
       <c r="AA68">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AB68">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AC68">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="AD68">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE68">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF68">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="AG68">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.22</v>
+        <v>2.75</v>
       </c>
       <c r="AK68">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,16 +11556,16 @@
         </is>
       </c>
       <c r="N69">
-        <v>3.26</v>
+        <v>2.45</v>
       </c>
       <c r="O69">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P69">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="Q69">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R69">
         <v>2.2</v>
@@ -11577,43 +11577,43 @@
         <v>2.96</v>
       </c>
       <c r="U69">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="V69">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W69">
+        <v>1.08</v>
+      </c>
+      <c r="X69">
         <v>1.05</v>
-      </c>
-      <c r="X69">
-        <v>1.04</v>
       </c>
       <c r="Y69">
         <v>1.25</v>
       </c>
       <c r="Z69">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AA69">
+        <v>1.81</v>
+      </c>
+      <c r="AB69">
         <v>1.98</v>
       </c>
-      <c r="AB69">
-        <v>1.83</v>
-      </c>
       <c r="AC69">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AD69">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE69">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF69">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG69">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK69">
         <v>1.44</v>
@@ -11725,7 +11725,7 @@
         <v>2.7</v>
       </c>
       <c r="P70">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q70">
         <v>3.96</v>
@@ -11734,10 +11734,10 @@
         <v>1.73</v>
       </c>
       <c r="S70">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="T70">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="U70">
         <v>3.7</v>
@@ -11749,13 +11749,13 @@
         <v>1.03</v>
       </c>
       <c r="X70">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y70">
         <v>1.66</v>
       </c>
       <c r="Z70">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AA70">
         <v>3.18</v>
@@ -11773,10 +11773,10 @@
         <v>1.03</v>
       </c>
       <c r="AF70">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AG70">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AK70">
         <v>1.36</v>
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="O71">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P71">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="Q71">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="R71">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S71">
+        <v>1.31</v>
+      </c>
+      <c r="T71">
+        <v>2.95</v>
+      </c>
+      <c r="U71">
+        <v>2.63</v>
+      </c>
+      <c r="V71">
+        <v>1.46</v>
+      </c>
+      <c r="W71">
+        <v>1.11</v>
+      </c>
+      <c r="X71">
+        <v>1.05</v>
+      </c>
+      <c r="Y71">
+        <v>1.19</v>
+      </c>
+      <c r="Z71">
+        <v>3.8</v>
+      </c>
+      <c r="AA71">
+        <v>1.75</v>
+      </c>
+      <c r="AB71">
+        <v>1.95</v>
+      </c>
+      <c r="AC71">
+        <v>2.66</v>
+      </c>
+      <c r="AD71">
         <v>1.36</v>
       </c>
-      <c r="T71">
-        <v>3.01</v>
-      </c>
-      <c r="U71">
-        <v>2.69</v>
-      </c>
-      <c r="V71">
-        <v>1.4</v>
-      </c>
-      <c r="W71">
-        <v>1.1</v>
-      </c>
-      <c r="X71">
-        <v>1</v>
-      </c>
-      <c r="Y71">
-        <v>1.25</v>
-      </c>
-      <c r="Z71">
-        <v>3.4</v>
-      </c>
-      <c r="AA71">
-        <v>1.86</v>
-      </c>
-      <c r="AB71">
-        <v>1.81</v>
-      </c>
-      <c r="AC71">
-        <v>3.05</v>
-      </c>
-      <c r="AD71">
-        <v>1.28</v>
-      </c>
       <c r="AE71">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF71">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AG71">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK71">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12371,64 +12371,64 @@
         </is>
       </c>
       <c r="N74">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="O74">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P74">
-        <v>1.75</v>
+        <v>1.93</v>
       </c>
       <c r="Q74">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="R74">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S74">
         <v>1.33</v>
       </c>
       <c r="T74">
-        <v>2.9</v>
+        <v>3.11</v>
       </c>
       <c r="U74">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="V74">
         <v>1.4</v>
       </c>
       <c r="W74">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X74">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y74">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z74">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="AA74">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB74">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC74">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="AD74">
         <v>1.33</v>
       </c>
       <c r="AE74">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF74">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AG74">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.89</v>
+        <v>1.3</v>
       </c>
       <c r="AK74">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="O75">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="P75">
-        <v>4.21</v>
+        <v>3.55</v>
       </c>
       <c r="Q75">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="R75">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S75">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T75">
-        <v>3.15</v>
+        <v>3.27</v>
       </c>
       <c r="U75">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="V75">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W75">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X75">
         <v>1.04</v>
       </c>
       <c r="Y75">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z75">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA75">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AB75">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="AC75">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD75">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE75">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF75">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AG75">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,31 +12697,31 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="O76">
-        <v>4.52</v>
+        <v>4.1</v>
       </c>
       <c r="P76">
-        <v>4.57</v>
+        <v>4.33</v>
       </c>
       <c r="Q76">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R76">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="S76">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T76">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U76">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V76">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W76">
         <v>1.15</v>
@@ -12730,10 +12730,10 @@
         <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z76">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AA76">
         <v>1.52</v>
@@ -12742,16 +12742,16 @@
         <v>2.4</v>
       </c>
       <c r="AC76">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AD76">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AE76">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AF76">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG76">
         <v>2.45</v>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK76">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="O82">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P82">
-        <v>3.05</v>
+        <v>1.75</v>
       </c>
       <c r="Q82">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="R82">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="S82">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T82">
-        <v>3.02</v>
+        <v>3.3</v>
       </c>
       <c r="U82">
-        <v>2.59</v>
+        <v>2.33</v>
       </c>
       <c r="V82">
-        <v>1.41</v>
+        <v>1.53</v>
       </c>
       <c r="W82">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X82">
         <v>1.04</v>
       </c>
       <c r="Y82">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z82">
-        <v>3.85</v>
+        <v>4.52</v>
       </c>
       <c r="AA82">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AB82">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="AC82">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="AD82">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="AE82">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AF82">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG82">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK82">
-        <v>1.73</v>
+        <v>1.21</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="O83">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P83">
-        <v>1.75</v>
+        <v>3.05</v>
       </c>
       <c r="Q83">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="R83">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="S83">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T83">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U83">
-        <v>2.33</v>
+        <v>2.59</v>
       </c>
       <c r="V83">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="W83">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X83">
         <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z83">
-        <v>4.52</v>
+        <v>3.85</v>
       </c>
       <c r="AA83">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AB83">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="AC83">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="AD83">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="AE83">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF83">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG83">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK83">
-        <v>1.21</v>
+        <v>1.73</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14330,61 +14330,61 @@
         <v>1.18</v>
       </c>
       <c r="O86">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="P86">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Q86">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R86">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="S86">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T86">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="U86">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="V86">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W86">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X86">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z86">
         <v>4.75</v>
       </c>
       <c r="AA86">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="AB86">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC86">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="AD86">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AE86">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF86">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="AG86">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK86">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14828,19 +14828,19 @@
         <v>3.52</v>
       </c>
       <c r="R89">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="S89">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="T89">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U89">
-        <v>3.09</v>
+        <v>2.89</v>
       </c>
       <c r="V89">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W89">
         <v>1.05</v>
@@ -14849,31 +14849,31 @@
         <v>1.06</v>
       </c>
       <c r="Y89">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="Z89">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AA89">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AB89">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC89">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AD89">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE89">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF89">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AG89">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK89">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="O90">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P90">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="Q90">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="R90">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="S90">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T90">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="U90">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="V90">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W90">
         <v>1.04</v>
       </c>
       <c r="X90">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y90">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z90">
-        <v>3.04</v>
+        <v>3.14</v>
       </c>
       <c r="AA90">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AB90">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC90">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="AD90">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE90">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF90">
         <v>1.85</v>
       </c>
       <c r="AG90">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="O98">
-        <v>3.02</v>
+        <v>2.8</v>
       </c>
       <c r="P98">
-        <v>5.16</v>
+        <v>4.45</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -17590,16 +17590,16 @@
         <v>2.78</v>
       </c>
       <c r="O106">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="P106">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="Q106">
         <v>2.9</v>
       </c>
       <c r="R106">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="S106">
         <v>1.24</v>
@@ -17608,10 +17608,10 @@
         <v>3.5</v>
       </c>
       <c r="U106">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V106">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W106">
         <v>1.13</v>
@@ -17620,31 +17620,31 @@
         <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z106">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AA106">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AB106">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AC106">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AD106">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE106">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF106">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG106">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AK106">
         <v>1.4</v>
@@ -18239,13 +18239,13 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="O110">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P110">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q110">
         <v>2.88</v>
@@ -18272,10 +18272,10 @@
         <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z110">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA110">
         <v>2.15</v>
@@ -18284,19 +18284,19 @@
         <v>1.66</v>
       </c>
       <c r="AC110">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="AD110">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE110">
         <v>1.03</v>
       </c>
       <c r="AF110">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AG110">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18411,52 +18411,52 @@
         <v>0</v>
       </c>
       <c r="Q111">
-        <v>4.7</v>
+        <v>5.45</v>
       </c>
       <c r="R111">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="S111">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="T111">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="U111">
-        <v>3.07</v>
+        <v>2.96</v>
       </c>
       <c r="V111">
         <v>1.32</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X111">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y111">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z111">
         <v>3.08</v>
       </c>
       <c r="AA111">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AB111">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AC111">
-        <v>3.58</v>
+        <v>3.63</v>
       </c>
       <c r="AD111">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AE111">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF111">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG111">
         <v>1.75</v>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AK111">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AL111">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU118"/>
+  <dimension ref="A1:AU117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3741,7 +3741,7 @@
         <v>2.89</v>
       </c>
       <c r="Q21">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R21">
         <v>2.18</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -5362,13 +5362,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="O31">
         <v>4.17</v>
       </c>
       <c r="P31">
-        <v>4.4</v>
+        <v>4.38</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="O32">
-        <v>3.92</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>3.71</v>
+        <v>3.65</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,7 +5688,7 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="O33">
         <v>3.74</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P34">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -5866,19 +5866,19 @@
         <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T34">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U34">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="V34">
         <v>1.4</v>
       </c>
       <c r="W34">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X34">
         <v>1</v>
@@ -5887,13 +5887,13 @@
         <v>1.28</v>
       </c>
       <c r="Z34">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="AA34">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="AB34">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AC34">
         <v>3.25</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="AK34">
         <v>1.35</v>
@@ -6666,61 +6666,61 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O39">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="P39">
-        <v>4.11</v>
+        <v>3.7</v>
       </c>
       <c r="Q39">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R39">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="S39">
         <v>1.19</v>
       </c>
       <c r="T39">
-        <v>3.92</v>
+        <v>4.8</v>
       </c>
       <c r="U39">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V39">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="W39">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X39">
         <v>1.01</v>
       </c>
       <c r="Y39">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Z39">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA39">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AB39">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AC39">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AD39">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AE39">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AF39">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG39">
         <v>2.65</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK39">
-        <v>2.07</v>
+        <v>1.9</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,80 +8133,80 @@
         </is>
       </c>
       <c r="N48">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="O48">
-        <v>3.46</v>
+        <v>3.05</v>
       </c>
       <c r="P48">
-        <v>2.61</v>
+        <v>2.3</v>
       </c>
       <c r="Q48">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="R48">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S48">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T48">
+        <v>2.65</v>
+      </c>
+      <c r="U48">
+        <v>2.88</v>
+      </c>
+      <c r="V48">
+        <v>1.36</v>
+      </c>
+      <c r="W48">
+        <v>1.02</v>
+      </c>
+      <c r="X48">
+        <v>1.08</v>
+      </c>
+      <c r="Y48">
+        <v>1.4</v>
+      </c>
+      <c r="Z48">
         <v>2.8</v>
       </c>
-      <c r="U48">
-        <v>3</v>
-      </c>
-      <c r="V48">
+      <c r="AA48">
+        <v>2.2</v>
+      </c>
+      <c r="AB48">
+        <v>1.6</v>
+      </c>
+      <c r="AC48">
+        <v>4</v>
+      </c>
+      <c r="AD48">
+        <v>1.2</v>
+      </c>
+      <c r="AE48">
+        <v>1.04</v>
+      </c>
+      <c r="AF48">
+        <v>1.91</v>
+      </c>
+      <c r="AG48">
+        <v>1.86</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ48">
+        <v>1.53</v>
+      </c>
+      <c r="AK48">
         <v>1.33</v>
-      </c>
-      <c r="W48">
-        <v>1.04</v>
-      </c>
-      <c r="X48">
-        <v>1.01</v>
-      </c>
-      <c r="Y48">
-        <v>1.33</v>
-      </c>
-      <c r="Z48">
-        <v>3.1</v>
-      </c>
-      <c r="AA48">
-        <v>2.1</v>
-      </c>
-      <c r="AB48">
-        <v>1.7</v>
-      </c>
-      <c r="AC48">
-        <v>3.75</v>
-      </c>
-      <c r="AD48">
-        <v>1.25</v>
-      </c>
-      <c r="AE48">
-        <v>1.08</v>
-      </c>
-      <c r="AF48">
-        <v>1.75</v>
-      </c>
-      <c r="AG48">
-        <v>1.94</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ48">
-        <v>1.33</v>
-      </c>
-      <c r="AK48">
-        <v>1.44</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
+        <v>2.4</v>
+      </c>
+      <c r="O49">
+        <v>3.2</v>
+      </c>
+      <c r="P49">
+        <v>2.5</v>
+      </c>
+      <c r="Q49">
+        <v>2.95</v>
+      </c>
+      <c r="R49">
+        <v>2.08</v>
+      </c>
+      <c r="S49">
+        <v>1.36</v>
+      </c>
+      <c r="T49">
         <v>2.8</v>
       </c>
-      <c r="O49">
-        <v>3.34</v>
-      </c>
-      <c r="P49">
-        <v>2.36</v>
-      </c>
-      <c r="Q49">
-        <v>3.35</v>
-      </c>
-      <c r="R49">
-        <v>2.05</v>
-      </c>
-      <c r="S49">
+      <c r="U49">
+        <v>2.75</v>
+      </c>
+      <c r="V49">
         <v>1.38</v>
       </c>
-      <c r="T49">
-        <v>2.65</v>
-      </c>
-      <c r="U49">
-        <v>2.94</v>
-      </c>
-      <c r="V49">
-        <v>1.3</v>
-      </c>
       <c r="W49">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X49">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y49">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z49">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="AA49">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="AB49">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC49">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AD49">
-        <v>1.23</v>
+        <v>1.35</v>
       </c>
       <c r="AE49">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF49">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG49">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK49">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.15</v>
+        <v>2.27</v>
       </c>
       <c r="O50">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="P50">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="Q50">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S50">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T50">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U50">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="V50">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W50">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X50">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y50">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z50">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA50">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB50">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="AC50">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD50">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE50">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF50">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG50">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AK50">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,80 +8622,80 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="O51">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P51">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q51">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="R51">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S51">
+        <v>1.38</v>
+      </c>
+      <c r="T51">
+        <v>2.65</v>
+      </c>
+      <c r="U51">
+        <v>2.94</v>
+      </c>
+      <c r="V51">
+        <v>1.3</v>
+      </c>
+      <c r="W51">
+        <v>1.04</v>
+      </c>
+      <c r="X51">
+        <v>1.02</v>
+      </c>
+      <c r="Y51">
+        <v>1.33</v>
+      </c>
+      <c r="Z51">
+        <v>2.94</v>
+      </c>
+      <c r="AA51">
+        <v>2.15</v>
+      </c>
+      <c r="AB51">
+        <v>1.66</v>
+      </c>
+      <c r="AC51">
+        <v>3.55</v>
+      </c>
+      <c r="AD51">
+        <v>1.23</v>
+      </c>
+      <c r="AE51">
+        <v>1.05</v>
+      </c>
+      <c r="AF51">
+        <v>1.85</v>
+      </c>
+      <c r="AG51">
+        <v>1.85</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ51">
+        <v>1.3</v>
+      </c>
+      <c r="AK51">
         <v>1.36</v>
-      </c>
-      <c r="T51">
-        <v>2.8</v>
-      </c>
-      <c r="U51">
-        <v>2.75</v>
-      </c>
-      <c r="V51">
-        <v>1.38</v>
-      </c>
-      <c r="W51">
-        <v>1.05</v>
-      </c>
-      <c r="X51">
-        <v>1.05</v>
-      </c>
-      <c r="Y51">
-        <v>1.29</v>
-      </c>
-      <c r="Z51">
-        <v>3.2</v>
-      </c>
-      <c r="AA51">
-        <v>1.85</v>
-      </c>
-      <c r="AB51">
-        <v>1.85</v>
-      </c>
-      <c r="AC51">
-        <v>3.1</v>
-      </c>
-      <c r="AD51">
-        <v>1.35</v>
-      </c>
-      <c r="AE51">
-        <v>1.08</v>
-      </c>
-      <c r="AF51">
-        <v>1.61</v>
-      </c>
-      <c r="AG51">
-        <v>2.1</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ51">
-        <v>1.28</v>
-      </c>
-      <c r="AK51">
-        <v>1.45</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.27</v>
+        <v>2.62</v>
       </c>
       <c r="O52">
-        <v>3.34</v>
+        <v>3.46</v>
       </c>
       <c r="P52">
+        <v>2.61</v>
+      </c>
+      <c r="Q52">
+        <v>3.05</v>
+      </c>
+      <c r="R52">
+        <v>2.15</v>
+      </c>
+      <c r="S52">
+        <v>1.38</v>
+      </c>
+      <c r="T52">
+        <v>2.8</v>
+      </c>
+      <c r="U52">
         <v>3</v>
       </c>
-      <c r="Q52">
-        <v>0</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
-        <v>0</v>
-      </c>
-      <c r="T52">
-        <v>0</v>
-      </c>
-      <c r="U52">
-        <v>0</v>
-      </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA52">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB52">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC52">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD52">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE52">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG52">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -11882,31 +11882,31 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O71">
         <v>3.6</v>
       </c>
       <c r="P71">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q71">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="R71">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S71">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="T71">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="U71">
         <v>2.63</v>
       </c>
       <c r="V71">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W71">
         <v>1.11</v>
@@ -11921,10 +11921,10 @@
         <v>3.8</v>
       </c>
       <c r="AA71">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB71">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AC71">
         <v>2.66</v>
@@ -11933,13 +11933,13 @@
         <v>1.36</v>
       </c>
       <c r="AE71">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF71">
         <v>1.57</v>
       </c>
       <c r="AG71">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK71">
         <v>1.53</v>
@@ -12860,34 +12860,34 @@
         </is>
       </c>
       <c r="N77">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="O77">
+        <v>3.3</v>
+      </c>
+      <c r="P77">
         <v>3.5</v>
-      </c>
-      <c r="P77">
-        <v>3.97</v>
       </c>
       <c r="Q77">
         <v>2.8</v>
       </c>
       <c r="R77">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S77">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T77">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="U77">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V77">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W77">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X77">
         <v>1.06</v>
@@ -12899,10 +12899,10 @@
         <v>3.1</v>
       </c>
       <c r="AA77">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB77">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC77">
         <v>3.6</v>
@@ -12914,10 +12914,10 @@
         <v>1.08</v>
       </c>
       <c r="AF77">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG77">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12933,7 +12933,7 @@
         <v>1.3</v>
       </c>
       <c r="AK77">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,19 +13023,19 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O78">
-        <v>3.92</v>
+        <v>4.05</v>
       </c>
       <c r="P78">
-        <v>4.36</v>
+        <v>4</v>
       </c>
       <c r="Q78">
         <v>2.24</v>
       </c>
       <c r="R78">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="S78">
         <v>1.25</v>
@@ -13044,10 +13044,10 @@
         <v>3.6</v>
       </c>
       <c r="U78">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="V78">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="W78">
         <v>1.15</v>
@@ -13059,22 +13059,22 @@
         <v>1.12</v>
       </c>
       <c r="Z78">
-        <v>4.98</v>
+        <v>4.35</v>
       </c>
       <c r="AA78">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AB78">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AC78">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AD78">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE78">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF78">
         <v>1.53</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK78">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13186,55 +13186,55 @@
         </is>
       </c>
       <c r="N79">
-        <v>5.08</v>
+        <v>4.4</v>
       </c>
       <c r="O79">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="P79">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q79">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="R79">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S79">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T79">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U79">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="V79">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="W79">
         <v>1.05</v>
       </c>
       <c r="X79">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y79">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z79">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="AA79">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB79">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AC79">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AD79">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE79">
         <v>1.11</v>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK79">
         <v>1.17</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="O80">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="P80">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13512,58 +13512,58 @@
         </is>
       </c>
       <c r="N81">
-        <v>6.65</v>
+        <v>4.85</v>
       </c>
       <c r="O81">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="P81">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q81">
-        <v>6.89</v>
+        <v>6.96</v>
       </c>
       <c r="R81">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S81">
         <v>1.39</v>
       </c>
       <c r="T81">
-        <v>3.27</v>
+        <v>2.66</v>
       </c>
       <c r="U81">
-        <v>2.35</v>
+        <v>2.53</v>
       </c>
       <c r="V81">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W81">
         <v>1.07</v>
       </c>
       <c r="X81">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y81">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z81">
-        <v>3.72</v>
+        <v>3.95</v>
       </c>
       <c r="AA81">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AB81">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC81">
         <v>2.75</v>
       </c>
       <c r="AD81">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE81">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF81">
         <v>1.8</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.22</v>
+        <v>2.26</v>
       </c>
       <c r="AK81">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,19 +13675,19 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O82">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P82">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="Q82">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="R82">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="S82">
         <v>1.29</v>
@@ -13696,43 +13696,43 @@
         <v>3.3</v>
       </c>
       <c r="U82">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="V82">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W82">
         <v>1.09</v>
       </c>
       <c r="X82">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y82">
         <v>1.18</v>
       </c>
       <c r="Z82">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="AA82">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AB82">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AC82">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AD82">
         <v>1.43</v>
       </c>
       <c r="AE82">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF82">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG82">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.2</v>
+        <v>1.85</v>
       </c>
       <c r="AK82">
         <v>1.21</v>
@@ -13838,16 +13838,16 @@
         </is>
       </c>
       <c r="N83">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="O83">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P83">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="Q83">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="R83">
         <v>2.2</v>
@@ -13865,37 +13865,37 @@
         <v>1.41</v>
       </c>
       <c r="W83">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X83">
         <v>1.04</v>
       </c>
       <c r="Y83">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z83">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AA83">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB83">
-        <v>1.93</v>
+        <v>1.99</v>
       </c>
       <c r="AC83">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AD83">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE83">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF83">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG83">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK83">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -14330,16 +14330,16 @@
         <v>1.18</v>
       </c>
       <c r="O86">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="P86">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Q86">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="R86">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="S86">
         <v>1.26</v>
@@ -14348,7 +14348,7 @@
         <v>3.66</v>
       </c>
       <c r="U86">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="V86">
         <v>1.6</v>
@@ -14357,28 +14357,28 @@
         <v>1.13</v>
       </c>
       <c r="X86">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
         <v>1.13</v>
       </c>
       <c r="Z86">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA86">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AB86">
         <v>2.37</v>
       </c>
       <c r="AC86">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AD86">
         <v>1.5</v>
       </c>
       <c r="AE86">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF86">
         <v>2.41</v>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK86">
         <v>4.8</v>
@@ -14490,43 +14490,43 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="O87">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="P87">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="Q87">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="R87">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S87">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T87">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="U87">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="V87">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W87">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X87">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y87">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z87">
-        <v>3.5</v>
+        <v>3.79</v>
       </c>
       <c r="AA87">
         <v>1.95</v>
@@ -14535,19 +14535,19 @@
         <v>1.85</v>
       </c>
       <c r="AC87">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="AD87">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE87">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF87">
         <v>1.75</v>
       </c>
       <c r="AG87">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK87">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,19 +14653,19 @@
         </is>
       </c>
       <c r="N88">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="O88">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P88">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q88">
         <v>3.42</v>
       </c>
       <c r="R88">
-        <v>2.3</v>
+        <v>2.23</v>
       </c>
       <c r="S88">
         <v>1.3</v>
@@ -14680,16 +14680,16 @@
         <v>1.49</v>
       </c>
       <c r="W88">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X88">
         <v>1.04</v>
       </c>
       <c r="Y88">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z88">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AA88">
         <v>1.68</v>
@@ -14701,10 +14701,10 @@
         <v>2.54</v>
       </c>
       <c r="AD88">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AE88">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF88">
         <v>1.53</v>
@@ -16567,22 +16567,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G100">
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Servette</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17545,7 +17545,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Shkendija</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Servette</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="P106">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Q106">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R106">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S106">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="T106">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U106">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V106">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="W106">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X106">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y106">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Z106">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA106">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB106">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AC106">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AD106">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE106">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AF106">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG106">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AK106">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17708,7 +17708,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -17718,12 +17718,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shkendija</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G107">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,22 +18034,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G109">
@@ -18076,64 +18076,64 @@
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O109">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P109">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q109">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R109">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S109">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T109">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U109">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V109">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W109">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X109">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z109">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA109">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB109">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC109">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD109">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE109">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF109">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG109">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK109">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18207,12 +18207,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O110">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P110">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>2.88</v>
+        <v>5.45</v>
       </c>
       <c r="R110">
-        <v>2.09</v>
+        <v>2.21</v>
       </c>
       <c r="S110">
         <v>1.38</v>
       </c>
       <c r="T110">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="U110">
+        <v>2.96</v>
+      </c>
+      <c r="V110">
+        <v>1.32</v>
+      </c>
+      <c r="W110">
+        <v>1.05</v>
+      </c>
+      <c r="X110">
+        <v>1.05</v>
+      </c>
+      <c r="Y110">
+        <v>1.3</v>
+      </c>
+      <c r="Z110">
         <v>3.08</v>
       </c>
-      <c r="V110">
-        <v>1.3</v>
-      </c>
-      <c r="W110">
-        <v>1.04</v>
-      </c>
-      <c r="X110">
-        <v>1.03</v>
-      </c>
-      <c r="Y110">
-        <v>1.36</v>
-      </c>
-      <c r="Z110">
-        <v>2.8</v>
-      </c>
       <c r="AA110">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AB110">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC110">
-        <v>3.84</v>
+        <v>3.63</v>
       </c>
       <c r="AD110">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE110">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AF110">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="AG110">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AK110">
-        <v>1.56</v>
+        <v>1.11</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18360,22 +18360,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G111">
@@ -18411,55 +18411,55 @@
         <v>0</v>
       </c>
       <c r="Q111">
-        <v>5.45</v>
+        <v>0</v>
       </c>
       <c r="R111">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S111">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T111">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U111">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="V111">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="W111">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X111">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y111">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z111">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA111">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB111">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC111">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="AD111">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE111">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF111">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG111">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AK111">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18533,12 +18533,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G112">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -18696,12 +18696,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G113">
@@ -18844,27 +18844,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G114">
@@ -18995,7 +18995,7 @@
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -19022,12 +19022,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rangers</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G115">
@@ -19054,64 +19054,64 @@
         </is>
       </c>
       <c r="N115">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O115">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P115">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Q115">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="R115">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S115">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T115">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U115">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V115">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W115">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X115">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z115">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA115">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB115">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC115">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD115">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE115">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF115">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG115">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK115">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19175,7 +19175,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -19185,12 +19185,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Unión La Calera</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G116">
@@ -19217,64 +19217,64 @@
         </is>
       </c>
       <c r="N116">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O116">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P116">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Q116">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="R116">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S116">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="T116">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U116">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V116">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="W116">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X116">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y116">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z116">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA116">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB116">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC116">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD116">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE116">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF116">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG116">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19287,10 +19287,10 @@
         </is>
       </c>
       <c r="AJ116">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK116">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AL116">
         <v>0</v>
@@ -19333,12 +19333,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Oriente Petrolero</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G117">
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL117">
         <v>0</v>
@@ -19483,169 +19483,6 @@
         <v>0</v>
       </c>
       <c r="AU117" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-      <c r="H118">
-        <v>0</v>
-      </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>0</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N118">
-        <v>1.89</v>
-      </c>
-      <c r="O118">
-        <v>3.54</v>
-      </c>
-      <c r="P118">
-        <v>3.45</v>
-      </c>
-      <c r="Q118">
-        <v>2.62</v>
-      </c>
-      <c r="R118">
-        <v>2.3</v>
-      </c>
-      <c r="S118">
-        <v>1.28</v>
-      </c>
-      <c r="T118">
-        <v>3.12</v>
-      </c>
-      <c r="U118">
-        <v>2.4</v>
-      </c>
-      <c r="V118">
-        <v>1.5</v>
-      </c>
-      <c r="W118">
-        <v>1.1</v>
-      </c>
-      <c r="X118">
-        <v>1.04</v>
-      </c>
-      <c r="Y118">
-        <v>1.18</v>
-      </c>
-      <c r="Z118">
-        <v>3.84</v>
-      </c>
-      <c r="AA118">
-        <v>1.72</v>
-      </c>
-      <c r="AB118">
-        <v>1.92</v>
-      </c>
-      <c r="AC118">
-        <v>2.7</v>
-      </c>
-      <c r="AD118">
-        <v>1.36</v>
-      </c>
-      <c r="AE118">
-        <v>1.14</v>
-      </c>
-      <c r="AF118">
-        <v>1.58</v>
-      </c>
-      <c r="AG118">
-        <v>2.16</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>1.3</v>
-      </c>
-      <c r="AK118">
-        <v>1.6</v>
-      </c>
-      <c r="AL118">
-        <v>0</v>
-      </c>
-      <c r="AM118">
-        <v>-1</v>
-      </c>
-      <c r="AN118">
-        <v>-1</v>
-      </c>
-      <c r="AO118">
-        <v>-1</v>
-      </c>
-      <c r="AP118">
-        <v>-1</v>
-      </c>
-      <c r="AQ118">
-        <v>0</v>
-      </c>
-      <c r="AR118">
-        <v>0</v>
-      </c>
-      <c r="AS118">
-        <v>0</v>
-      </c>
-      <c r="AT118">
-        <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
         <is>
           <t>2026-08-21 23:00:00</t>
         </is>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -7979,19 +7979,19 @@
         <v>2.09</v>
       </c>
       <c r="Q47">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="R47">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S47">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="T47">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U47">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="V47">
         <v>1.18</v>
@@ -8003,16 +8003,16 @@
         <v>1.08</v>
       </c>
       <c r="Y47">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="Z47">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="AA47">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB47">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="AC47">
         <v>5.75</v>
@@ -8043,7 +8043,7 @@
         <v>1.36</v>
       </c>
       <c r="AK47">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -11719,16 +11719,16 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O70">
         <v>2.7</v>
       </c>
       <c r="P70">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="Q70">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="R70">
         <v>1.73</v>
@@ -11737,13 +11737,13 @@
         <v>1.68</v>
       </c>
       <c r="T70">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="U70">
         <v>3.7</v>
       </c>
       <c r="V70">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="W70">
         <v>1.03</v>
@@ -11752,10 +11752,10 @@
         <v>1.14</v>
       </c>
       <c r="Y70">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Z70">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AA70">
         <v>3.18</v>
@@ -11767,7 +11767,7 @@
         <v>6.5</v>
       </c>
       <c r="AD70">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AE70">
         <v>1.03</v>
@@ -11776,7 +11776,7 @@
         <v>2.25</v>
       </c>
       <c r="AG70">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AK70">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -16283,7 +16283,7 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O98">
         <v>2.8</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -1631,22 +1631,22 @@
         <v>1.22</v>
       </c>
       <c r="T8">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="U8">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="V8">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X8">
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="Z8">
         <v>5</v>
@@ -1655,7 +1655,7 @@
         <v>1.46</v>
       </c>
       <c r="AB8">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AC8">
         <v>2.27</v>
@@ -1667,7 +1667,7 @@
         <v>1.22</v>
       </c>
       <c r="AF8">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG8">
         <v>2.23</v>
@@ -3406,22 +3406,22 @@
         </is>
       </c>
       <c r="N19">
-        <v>9.050000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O19">
-        <v>5.8</v>
+        <v>5.95</v>
       </c>
       <c r="P19">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="Q19">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="R19">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="S19">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="T19">
         <v>4.33</v>
@@ -3430,16 +3430,16 @@
         <v>1.85</v>
       </c>
       <c r="V19">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="W19">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Z19">
         <v>6.5</v>
@@ -3451,16 +3451,16 @@
         <v>3.1</v>
       </c>
       <c r="AC19">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AD19">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AE19">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AF19">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG19">
         <v>2.05</v>
@@ -3479,7 +3479,7 @@
         <v>1.12</v>
       </c>
       <c r="AK19">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4067,55 +4067,55 @@
         <v>2.65</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,55 +4393,55 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U25">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="V25">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z25">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC25">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AD25">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE25">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF25">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG25">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK25">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4556,55 +4556,55 @@
         <v>5.4</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4719,55 +4719,55 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V28">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB29">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -6026,22 +6026,22 @@
         <v>3</v>
       </c>
       <c r="R35">
-        <v>2.26</v>
+        <v>2.45</v>
       </c>
       <c r="S35">
         <v>1.24</v>
       </c>
       <c r="T35">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
       <c r="U35">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="V35">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="W35">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X35">
         <v>1.02</v>
@@ -6056,22 +6056,22 @@
         <v>1.55</v>
       </c>
       <c r="AB35">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC35">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AD35">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AE35">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AF35">
         <v>1.44</v>
       </c>
       <c r="AG35">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>1.2</v>
       </c>
       <c r="AK35">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6180,58 +6180,58 @@
         <v>3.55</v>
       </c>
       <c r="O36">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P36">
         <v>2.06</v>
       </c>
       <c r="Q36">
-        <v>3.55</v>
+        <v>4.15</v>
       </c>
       <c r="R36">
         <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T36">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="U36">
         <v>2.5</v>
       </c>
       <c r="V36">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y36">
         <v>1.16</v>
       </c>
       <c r="Z36">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA36">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AB36">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC36">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="AD36">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AE36">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF36">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG36">
         <v>2.25</v>
@@ -6250,7 +6250,7 @@
         <v>1.67</v>
       </c>
       <c r="AK36">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P45">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AA45">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB45">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P46">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="Q46">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="R46">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S46">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T46">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U46">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V46">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W46">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X46">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z46">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA46">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AB46">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AC46">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AD46">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE46">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF46">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG46">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O51">
-        <v>3.34</v>
+        <v>3.46</v>
       </c>
       <c r="P51">
-        <v>2.36</v>
+        <v>2.61</v>
       </c>
       <c r="Q51">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="R51">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S51">
         <v>1.38</v>
       </c>
       <c r="T51">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U51">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V51">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W51">
         <v>1.04</v>
       </c>
       <c r="X51">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y51">
         <v>1.33</v>
       </c>
       <c r="Z51">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="AA51">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB51">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC51">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="AD51">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE51">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF51">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG51">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK51">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O52">
-        <v>3.46</v>
+        <v>3.34</v>
       </c>
       <c r="P52">
-        <v>2.61</v>
+        <v>2.36</v>
       </c>
       <c r="Q52">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="R52">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S52">
         <v>1.38</v>
       </c>
       <c r="T52">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U52">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V52">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W52">
         <v>1.04</v>
       </c>
       <c r="X52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y52">
         <v>1.33</v>
       </c>
       <c r="Z52">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="AA52">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB52">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC52">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AD52">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF52">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG52">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK52">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,80 +10252,80 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="O61">
-        <v>3.64</v>
+        <v>3.4</v>
       </c>
       <c r="P61">
-        <v>2.71</v>
+        <v>2.57</v>
       </c>
       <c r="Q61">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="R61">
-        <v>2.45</v>
+        <v>2.12</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="T61">
-        <v>4</v>
+        <v>2.95</v>
       </c>
       <c r="U61">
-        <v>2.17</v>
+        <v>2.47</v>
       </c>
       <c r="V61">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="W61">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y61">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="Z61">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA61">
+        <v>1.72</v>
+      </c>
+      <c r="AB61">
+        <v>2</v>
+      </c>
+      <c r="AC61">
+        <v>2.8</v>
+      </c>
+      <c r="AD61">
+        <v>1.36</v>
+      </c>
+      <c r="AE61">
+        <v>1.13</v>
+      </c>
+      <c r="AF61">
+        <v>1.57</v>
+      </c>
+      <c r="AG61">
+        <v>2.3</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
+        <v>1.25</v>
+      </c>
+      <c r="AK61">
         <v>1.5</v>
-      </c>
-      <c r="AB61">
-        <v>2.4</v>
-      </c>
-      <c r="AC61">
-        <v>2.25</v>
-      </c>
-      <c r="AD61">
-        <v>1.55</v>
-      </c>
-      <c r="AE61">
-        <v>1.21</v>
-      </c>
-      <c r="AF61">
-        <v>1.44</v>
-      </c>
-      <c r="AG61">
-        <v>2.5</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>1.24</v>
-      </c>
-      <c r="AK61">
-        <v>1.55</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
+        <v>2.25</v>
+      </c>
+      <c r="O62">
+        <v>3.64</v>
+      </c>
+      <c r="P62">
+        <v>2.71</v>
+      </c>
+      <c r="Q62">
+        <v>2.65</v>
+      </c>
+      <c r="R62">
+        <v>2.45</v>
+      </c>
+      <c r="S62">
+        <v>1.2</v>
+      </c>
+      <c r="T62">
+        <v>4</v>
+      </c>
+      <c r="U62">
+        <v>2.17</v>
+      </c>
+      <c r="V62">
+        <v>1.58</v>
+      </c>
+      <c r="W62">
+        <v>1.15</v>
+      </c>
+      <c r="X62">
+        <v>1.03</v>
+      </c>
+      <c r="Y62">
+        <v>1.15</v>
+      </c>
+      <c r="Z62">
+        <v>4.6</v>
+      </c>
+      <c r="AA62">
+        <v>1.5</v>
+      </c>
+      <c r="AB62">
         <v>2.4</v>
       </c>
-      <c r="O62">
-        <v>3.4</v>
-      </c>
-      <c r="P62">
-        <v>2.57</v>
-      </c>
-      <c r="Q62">
-        <v>2.9</v>
-      </c>
-      <c r="R62">
-        <v>2.12</v>
-      </c>
-      <c r="S62">
-        <v>1.34</v>
-      </c>
-      <c r="T62">
-        <v>2.95</v>
-      </c>
-      <c r="U62">
-        <v>2.47</v>
-      </c>
-      <c r="V62">
-        <v>1.45</v>
-      </c>
-      <c r="W62">
-        <v>1.08</v>
-      </c>
-      <c r="X62">
-        <v>1</v>
-      </c>
-      <c r="Y62">
+      <c r="AC62">
+        <v>2.25</v>
+      </c>
+      <c r="AD62">
+        <v>1.55</v>
+      </c>
+      <c r="AE62">
         <v>1.21</v>
       </c>
-      <c r="Z62">
-        <v>3.9</v>
-      </c>
-      <c r="AA62">
-        <v>1.72</v>
-      </c>
-      <c r="AB62">
-        <v>2</v>
-      </c>
-      <c r="AC62">
-        <v>2.8</v>
-      </c>
-      <c r="AD62">
-        <v>1.36</v>
-      </c>
-      <c r="AE62">
-        <v>1.13</v>
-      </c>
       <c r="AF62">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AG62">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK62">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -11076,16 +11076,16 @@
         <v>2.7</v>
       </c>
       <c r="Q66">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="R66">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="S66">
         <v>1.4</v>
       </c>
       <c r="T66">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U66">
         <v>2.94</v>
@@ -11100,13 +11100,13 @@
         <v>1.06</v>
       </c>
       <c r="Y66">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z66">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AA66">
-        <v>2.01</v>
+        <v>2.16</v>
       </c>
       <c r="AB66">
         <v>1.7</v>
@@ -11121,10 +11121,10 @@
         <v>1.08</v>
       </c>
       <c r="AF66">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AG66">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>4.85</v>
+        <v>3.5</v>
       </c>
       <c r="O81">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P81">
-        <v>1.51</v>
+        <v>1.86</v>
       </c>
       <c r="Q81">
-        <v>6.96</v>
+        <v>3.85</v>
       </c>
       <c r="R81">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="S81">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="T81">
-        <v>2.66</v>
+        <v>3.3</v>
       </c>
       <c r="U81">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="V81">
+        <v>1.52</v>
+      </c>
+      <c r="W81">
+        <v>1.09</v>
+      </c>
+      <c r="X81">
+        <v>1.02</v>
+      </c>
+      <c r="Y81">
+        <v>1.18</v>
+      </c>
+      <c r="Z81">
+        <v>4.5</v>
+      </c>
+      <c r="AA81">
+        <v>1.61</v>
+      </c>
+      <c r="AB81">
+        <v>2.17</v>
+      </c>
+      <c r="AC81">
+        <v>2.5</v>
+      </c>
+      <c r="AD81">
         <v>1.43</v>
       </c>
-      <c r="W81">
-        <v>1.07</v>
-      </c>
-      <c r="X81">
-        <v>1.01</v>
-      </c>
-      <c r="Y81">
-        <v>1.25</v>
-      </c>
-      <c r="Z81">
-        <v>3.95</v>
-      </c>
-      <c r="AA81">
-        <v>1.75</v>
-      </c>
-      <c r="AB81">
-        <v>2.05</v>
-      </c>
-      <c r="AC81">
-        <v>2.75</v>
-      </c>
-      <c r="AD81">
-        <v>1.44</v>
-      </c>
       <c r="AE81">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF81">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AG81">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>2.26</v>
+        <v>1.85</v>
       </c>
       <c r="AK81">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>3.5</v>
+        <v>1.88</v>
       </c>
       <c r="O82">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P82">
-        <v>1.86</v>
+        <v>3.45</v>
       </c>
       <c r="Q82">
-        <v>3.85</v>
+        <v>2.45</v>
       </c>
       <c r="R82">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S82">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T82">
-        <v>3.3</v>
+        <v>3.02</v>
       </c>
       <c r="U82">
-        <v>2.38</v>
+        <v>2.59</v>
       </c>
       <c r="V82">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="W82">
+        <v>1.06</v>
+      </c>
+      <c r="X82">
+        <v>1.04</v>
+      </c>
+      <c r="Y82">
+        <v>1.24</v>
+      </c>
+      <c r="Z82">
+        <v>3.8</v>
+      </c>
+      <c r="AA82">
+        <v>1.75</v>
+      </c>
+      <c r="AB82">
+        <v>1.99</v>
+      </c>
+      <c r="AC82">
+        <v>2.88</v>
+      </c>
+      <c r="AD82">
+        <v>1.33</v>
+      </c>
+      <c r="AE82">
         <v>1.09</v>
       </c>
-      <c r="X82">
-        <v>1.02</v>
-      </c>
-      <c r="Y82">
-        <v>1.18</v>
-      </c>
-      <c r="Z82">
-        <v>4.5</v>
-      </c>
-      <c r="AA82">
-        <v>1.61</v>
-      </c>
-      <c r="AB82">
-        <v>2.17</v>
-      </c>
-      <c r="AC82">
-        <v>2.5</v>
-      </c>
-      <c r="AD82">
-        <v>1.43</v>
-      </c>
-      <c r="AE82">
-        <v>1.14</v>
-      </c>
       <c r="AF82">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AG82">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.85</v>
+        <v>1.21</v>
       </c>
       <c r="AK82">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>1.88</v>
+        <v>4.85</v>
       </c>
       <c r="O83">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="P83">
-        <v>3.45</v>
+        <v>1.51</v>
       </c>
       <c r="Q83">
-        <v>2.45</v>
+        <v>6.96</v>
       </c>
       <c r="R83">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="S83">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="T83">
-        <v>3.02</v>
+        <v>2.66</v>
       </c>
       <c r="U83">
-        <v>2.59</v>
+        <v>2.53</v>
       </c>
       <c r="V83">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W83">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X83">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y83">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z83">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AA83">
         <v>1.75</v>
       </c>
       <c r="AB83">
-        <v>1.99</v>
+        <v>2.05</v>
       </c>
       <c r="AC83">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AD83">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AE83">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF83">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AG83">
-        <v>2.07</v>
+        <v>1.91</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>1.21</v>
+        <v>2.26</v>
       </c>
       <c r="AK83">
-        <v>1.75</v>
+        <v>1.07</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -15157,7 +15157,7 @@
         <v>2</v>
       </c>
       <c r="S91">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T91">
         <v>2.5</v>
@@ -15169,7 +15169,7 @@
         <v>1.32</v>
       </c>
       <c r="W91">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X91">
         <v>1.03</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK91">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15634,13 +15634,13 @@
         <v>2.3</v>
       </c>
       <c r="O94">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="P94">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q94">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="R94">
         <v>1.83</v>
@@ -15649,7 +15649,7 @@
         <v>1.44</v>
       </c>
       <c r="T94">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="U94">
         <v>3.2</v>
@@ -15676,7 +15676,7 @@
         <v>1.57</v>
       </c>
       <c r="AC94">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="AD94">
         <v>1.17</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK94">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AL94">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -801,25 +801,25 @@
         <v>1.61</v>
       </c>
       <c r="O3">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="P3">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="Q3">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
         <v>1.35</v>
       </c>
       <c r="T3">
-        <v>2.94</v>
+        <v>2.82</v>
       </c>
       <c r="U3">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="V3">
         <v>1.42</v>
@@ -834,16 +834,16 @@
         <v>1.21</v>
       </c>
       <c r="Z3">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="AA3">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AB3">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AC3">
-        <v>3.01</v>
+        <v>2.85</v>
       </c>
       <c r="AD3">
         <v>1.33</v>
@@ -852,7 +852,7 @@
         <v>1.13</v>
       </c>
       <c r="AF3">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG3">
         <v>1.93</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK3">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -964,10 +964,10 @@
         <v>1.5</v>
       </c>
       <c r="O4">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P4">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q4">
         <v>1.95</v>
@@ -976,10 +976,10 @@
         <v>2.25</v>
       </c>
       <c r="S4">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="T4">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="U4">
         <v>2.73</v>
@@ -988,10 +988,10 @@
         <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
         <v>1.28</v>
@@ -1003,10 +1003,10 @@
         <v>1.86</v>
       </c>
       <c r="AB4">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AC4">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AD4">
         <v>1.29</v>
@@ -1015,10 +1015,10 @@
         <v>1.11</v>
       </c>
       <c r="AF4">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG4">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -2274,22 +2274,22 @@
         <v>4.53</v>
       </c>
       <c r="Q12">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="R12">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
         <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U12">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V12">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="W12">
         <v>1.13</v>
@@ -2298,47 +2298,47 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
+        <v>1.14</v>
+      </c>
+      <c r="Z12">
+        <v>4.4</v>
+      </c>
+      <c r="AA12">
+        <v>1.58</v>
+      </c>
+      <c r="AB12">
+        <v>2.18</v>
+      </c>
+      <c r="AC12">
+        <v>2.46</v>
+      </c>
+      <c r="AD12">
+        <v>1.43</v>
+      </c>
+      <c r="AE12">
+        <v>1.14</v>
+      </c>
+      <c r="AF12">
+        <v>1.58</v>
+      </c>
+      <c r="AG12">
+        <v>2.15</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.17</v>
       </c>
-      <c r="Z12">
-        <v>4.5</v>
-      </c>
-      <c r="AA12">
-        <v>1.57</v>
-      </c>
-      <c r="AB12">
-        <v>2.25</v>
-      </c>
-      <c r="AC12">
-        <v>2.63</v>
-      </c>
-      <c r="AD12">
-        <v>1.45</v>
-      </c>
-      <c r="AE12">
-        <v>1.17</v>
-      </c>
-      <c r="AF12">
-        <v>1.53</v>
-      </c>
-      <c r="AG12">
-        <v>2.18</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.2</v>
-      </c>
       <c r="AK12">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,49 +2437,49 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="R13">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="S13">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="T13">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U13">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V13">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W13">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z13">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="AA13">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AB13">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AC13">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AD13">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE13">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF13">
         <v>1.53</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AK13">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O14">
         <v>3.1</v>
@@ -2600,16 +2600,16 @@
         <v>2.75</v>
       </c>
       <c r="Q14">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R14">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S14">
         <v>1.39</v>
       </c>
       <c r="T14">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="U14">
         <v>2.7</v>
@@ -2642,13 +2642,13 @@
         <v>1.28</v>
       </c>
       <c r="AE14">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF14">
         <v>1.7</v>
       </c>
       <c r="AG14">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2763,22 +2763,22 @@
         <v>4.5</v>
       </c>
       <c r="Q15">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="R15">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="S15">
         <v>1.2</v>
       </c>
       <c r="T15">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="U15">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="V15">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="W15">
         <v>1.2</v>
@@ -2787,19 +2787,19 @@
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z15">
-        <v>5.5</v>
+        <v>6.08</v>
       </c>
       <c r="AA15">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AB15">
         <v>2.5</v>
       </c>
       <c r="AC15">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AD15">
         <v>1.7</v>
@@ -2808,10 +2808,10 @@
         <v>1.25</v>
       </c>
       <c r="AF15">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AG15">
-        <v>2.77</v>
+        <v>2.71</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>1.18</v>
       </c>
       <c r="AK15">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3258,10 +3258,10 @@
         <v>2.21</v>
       </c>
       <c r="S18">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T18">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U18">
         <v>2.63</v>
@@ -3316,7 +3316,7 @@
         <v>1.25</v>
       </c>
       <c r="AK18">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3904,7 +3904,7 @@
         <v>11</v>
       </c>
       <c r="Q22">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R22">
         <v>2.96</v>
@@ -3913,7 +3913,7 @@
         <v>1.14</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="U22">
         <v>1.88</v>
@@ -3922,7 +3922,7 @@
         <v>1.82</v>
       </c>
       <c r="W22">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="X22">
         <v>1.01</v>
@@ -3934,25 +3934,25 @@
         <v>6.75</v>
       </c>
       <c r="AA22">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AB22">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AC22">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AD22">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AE22">
         <v>1.4</v>
       </c>
       <c r="AF22">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AG22">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK22">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G24">
@@ -4230,10 +4230,10 @@
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="R24">
-        <v>2.18</v>
+        <v>2.23</v>
       </c>
       <c r="S24">
         <v>1.31</v>
@@ -4242,59 +4242,59 @@
         <v>2.97</v>
       </c>
       <c r="U24">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="V24">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
         <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
+        <v>1.19</v>
+      </c>
+      <c r="Z24">
+        <v>3.78</v>
+      </c>
+      <c r="AA24">
+        <v>1.69</v>
+      </c>
+      <c r="AB24">
+        <v>2.02</v>
+      </c>
+      <c r="AC24">
+        <v>2.66</v>
+      </c>
+      <c r="AD24">
+        <v>1.37</v>
+      </c>
+      <c r="AE24">
+        <v>1.12</v>
+      </c>
+      <c r="AF24">
+        <v>1.69</v>
+      </c>
+      <c r="AG24">
+        <v>1.97</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ24">
         <v>1.18</v>
       </c>
-      <c r="Z24">
-        <v>3.88</v>
-      </c>
-      <c r="AA24">
-        <v>1.71</v>
-      </c>
-      <c r="AB24">
-        <v>2</v>
-      </c>
-      <c r="AC24">
-        <v>2.74</v>
-      </c>
-      <c r="AD24">
-        <v>1.36</v>
-      </c>
-      <c r="AE24">
-        <v>1.11</v>
-      </c>
-      <c r="AF24">
-        <v>1.6</v>
-      </c>
-      <c r="AG24">
-        <v>2.15</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ24">
-        <v>1.22</v>
-      </c>
       <c r="AK24">
-        <v>1.66</v>
+        <v>2.07</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,65 +4384,65 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q25">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="R25">
-        <v>2.23</v>
+        <v>2.41</v>
       </c>
       <c r="S25">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T25">
-        <v>2.97</v>
+        <v>3.75</v>
       </c>
       <c r="U25">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y25">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="Z25">
-        <v>3.78</v>
+        <v>5.5</v>
       </c>
       <c r="AA25">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="AB25">
+        <v>2.6</v>
+      </c>
+      <c r="AC25">
+        <v>2.35</v>
+      </c>
+      <c r="AD25">
+        <v>1.48</v>
+      </c>
+      <c r="AE25">
+        <v>1.21</v>
+      </c>
+      <c r="AF25">
+        <v>1.68</v>
+      </c>
+      <c r="AG25">
         <v>2.02</v>
       </c>
-      <c r="AC25">
-        <v>2.66</v>
-      </c>
-      <c r="AD25">
-        <v>1.37</v>
-      </c>
-      <c r="AE25">
-        <v>1.12</v>
-      </c>
-      <c r="AF25">
-        <v>1.69</v>
-      </c>
-      <c r="AG25">
-        <v>1.97</v>
-      </c>
       <c r="AH25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK25">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q26">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="R26">
-        <v>2.41</v>
+        <v>2.18</v>
       </c>
       <c r="S26">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="U26">
+        <v>2.45</v>
+      </c>
+      <c r="V26">
+        <v>1.48</v>
+      </c>
+      <c r="W26">
+        <v>1.11</v>
+      </c>
+      <c r="X26">
+        <v>1.04</v>
+      </c>
+      <c r="Y26">
+        <v>1.25</v>
+      </c>
+      <c r="Z26">
+        <v>3.65</v>
+      </c>
+      <c r="AA26">
+        <v>1.73</v>
+      </c>
+      <c r="AB26">
         <v>2</v>
       </c>
-      <c r="V26">
-        <v>1.73</v>
-      </c>
-      <c r="W26">
-        <v>1.2</v>
-      </c>
-      <c r="X26">
-        <v>1.02</v>
-      </c>
-      <c r="Y26">
-        <v>1.1</v>
-      </c>
-      <c r="Z26">
-        <v>5.5</v>
-      </c>
-      <c r="AA26">
-        <v>1.47</v>
-      </c>
-      <c r="AB26">
-        <v>2.6</v>
-      </c>
       <c r="AC26">
-        <v>2.35</v>
+        <v>2.65</v>
       </c>
       <c r="AD26">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AE26">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF26">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG26">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>2.3</v>
+        <v>1.49</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G27">
@@ -4719,71 +4719,71 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="R27">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T27">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="U27">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="V27">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Z27">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="AA27">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AB27">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AC27">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="AD27">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AE27">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AF27">
+        <v>1.72</v>
+      </c>
+      <c r="AG27">
+        <v>1.93</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.24</v>
+      </c>
+      <c r="AK27">
         <v>1.62</v>
-      </c>
-      <c r="AG27">
-        <v>2.18</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.27</v>
-      </c>
-      <c r="AK27">
-        <v>1.49</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G28">
@@ -4882,55 +4882,55 @@
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="R28">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="S28">
+        <v>1.31</v>
+      </c>
+      <c r="T28">
+        <v>2.97</v>
+      </c>
+      <c r="U28">
+        <v>2.5</v>
+      </c>
+      <c r="V28">
+        <v>1.43</v>
+      </c>
+      <c r="W28">
+        <v>1.08</v>
+      </c>
+      <c r="X28">
+        <v>1.01</v>
+      </c>
+      <c r="Y28">
+        <v>1.18</v>
+      </c>
+      <c r="Z28">
+        <v>3.88</v>
+      </c>
+      <c r="AA28">
+        <v>1.71</v>
+      </c>
+      <c r="AB28">
+        <v>2</v>
+      </c>
+      <c r="AC28">
+        <v>2.74</v>
+      </c>
+      <c r="AD28">
         <v>1.36</v>
       </c>
-      <c r="T28">
-        <v>2.75</v>
-      </c>
-      <c r="U28">
-        <v>2.75</v>
-      </c>
-      <c r="V28">
-        <v>1.36</v>
-      </c>
-      <c r="W28">
-        <v>1.04</v>
-      </c>
-      <c r="X28">
-        <v>1</v>
-      </c>
-      <c r="Y28">
-        <v>1.26</v>
-      </c>
-      <c r="Z28">
-        <v>3.2</v>
-      </c>
-      <c r="AA28">
-        <v>1.9</v>
-      </c>
-      <c r="AB28">
-        <v>1.79</v>
-      </c>
-      <c r="AC28">
-        <v>3.2</v>
-      </c>
-      <c r="AD28">
-        <v>1.26</v>
-      </c>
       <c r="AE28">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF28">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="AG28">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5208,19 +5208,19 @@
         <v>3.4</v>
       </c>
       <c r="Q30">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="R30">
-        <v>2.13</v>
+        <v>1.98</v>
       </c>
       <c r="S30">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T30">
         <v>2.5</v>
       </c>
       <c r="U30">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="V30">
         <v>1.32</v>
@@ -5238,10 +5238,10 @@
         <v>2.99</v>
       </c>
       <c r="AA30">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AB30">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC30">
         <v>3.58</v>
@@ -5256,7 +5256,7 @@
         <v>1.92</v>
       </c>
       <c r="AG30">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK30">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,10 +5362,10 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="O31">
-        <v>4.17</v>
+        <v>3.68</v>
       </c>
       <c r="P31">
         <v>4.38</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="O32">
-        <v>3.8</v>
+        <v>3.41</v>
       </c>
       <c r="P32">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>1.88</v>
       </c>
       <c r="O33">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="P33">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="O34">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P34">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="Q34">
         <v>3.6</v>
@@ -5866,13 +5866,13 @@
         <v>2.2</v>
       </c>
       <c r="S34">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T34">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="U34">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="V34">
         <v>1.4</v>
@@ -5881,10 +5881,10 @@
         <v>1.05</v>
       </c>
       <c r="X34">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y34">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z34">
         <v>3.4</v>
@@ -5908,7 +5908,7 @@
         <v>1.72</v>
       </c>
       <c r="AG34">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AK34">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -6343,25 +6343,25 @@
         <v>1.75</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P37">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q37">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="R37">
         <v>2.15</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T37">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U37">
-        <v>2.77</v>
+        <v>2.55</v>
       </c>
       <c r="V37">
         <v>1.38</v>
@@ -6370,7 +6370,7 @@
         <v>1.04</v>
       </c>
       <c r="X37">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y37">
         <v>1.24</v>
@@ -6385,19 +6385,19 @@
         <v>1.87</v>
       </c>
       <c r="AC37">
-        <v>3.21</v>
+        <v>3.08</v>
       </c>
       <c r="AD37">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE37">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AF37">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6666,31 +6666,31 @@
         </is>
       </c>
       <c r="N39">
+        <v>1.77</v>
+      </c>
+      <c r="O39">
+        <v>4</v>
+      </c>
+      <c r="P39">
+        <v>3.8</v>
+      </c>
+      <c r="Q39">
+        <v>2.25</v>
+      </c>
+      <c r="R39">
+        <v>2.71</v>
+      </c>
+      <c r="S39">
+        <v>1.2</v>
+      </c>
+      <c r="T39">
+        <v>4.2</v>
+      </c>
+      <c r="U39">
+        <v>1.91</v>
+      </c>
+      <c r="V39">
         <v>1.8</v>
-      </c>
-      <c r="O39">
-        <v>4.15</v>
-      </c>
-      <c r="P39">
-        <v>3.7</v>
-      </c>
-      <c r="Q39">
-        <v>2.2</v>
-      </c>
-      <c r="R39">
-        <v>2.55</v>
-      </c>
-      <c r="S39">
-        <v>1.19</v>
-      </c>
-      <c r="T39">
-        <v>4.8</v>
-      </c>
-      <c r="U39">
-        <v>1.93</v>
-      </c>
-      <c r="V39">
-        <v>1.75</v>
       </c>
       <c r="W39">
         <v>1.2</v>
@@ -6708,10 +6708,10 @@
         <v>1.36</v>
       </c>
       <c r="AB39">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AC39">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AD39">
         <v>1.82</v>
@@ -6720,7 +6720,7 @@
         <v>1.3</v>
       </c>
       <c r="AF39">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AG39">
         <v>2.65</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK39">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6829,80 +6829,80 @@
         </is>
       </c>
       <c r="N40">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="O40">
-        <v>3.2</v>
+        <v>3.48</v>
       </c>
       <c r="P40">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="Q40">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R40">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S40">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="T40">
-        <v>2.87</v>
+        <v>2.7</v>
       </c>
       <c r="U40">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="V40">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W40">
         <v>1.08</v>
       </c>
       <c r="X40">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y40">
+        <v>1.25</v>
+      </c>
+      <c r="Z40">
+        <v>3.25</v>
+      </c>
+      <c r="AA40">
+        <v>1.95</v>
+      </c>
+      <c r="AB40">
+        <v>1.83</v>
+      </c>
+      <c r="AC40">
+        <v>3.45</v>
+      </c>
+      <c r="AD40">
         <v>1.3</v>
       </c>
-      <c r="Z40">
-        <v>2.99</v>
-      </c>
-      <c r="AA40">
-        <v>2.04</v>
-      </c>
-      <c r="AB40">
-        <v>1.71</v>
-      </c>
-      <c r="AC40">
-        <v>3.75</v>
-      </c>
-      <c r="AD40">
-        <v>1.25</v>
-      </c>
       <c r="AE40">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF40">
+        <v>1.75</v>
+      </c>
+      <c r="AG40">
+        <v>2</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ40">
+        <v>1.29</v>
+      </c>
+      <c r="AK40">
         <v>1.8</v>
-      </c>
-      <c r="AG40">
-        <v>1.9</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ40">
-        <v>1.28</v>
-      </c>
-      <c r="AK40">
-        <v>1.73</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7007,10 +7007,10 @@
         <v>2.33</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U41">
         <v>2.28</v>
@@ -7019,10 +7019,10 @@
         <v>1.48</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y41">
         <v>1.18</v>
@@ -7043,7 +7043,7 @@
         <v>1.41</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF41">
         <v>1.6</v>
@@ -7155,64 +7155,64 @@
         </is>
       </c>
       <c r="N42">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
       <c r="O42">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P42">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="Q42">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="R42">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="S42">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="T42">
         <v>4</v>
       </c>
       <c r="U42">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="V42">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="W42">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="Z42">
-        <v>5.05</v>
+        <v>5.39</v>
       </c>
       <c r="AA42">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AB42">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="AC42">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AD42">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AE42">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AF42">
         <v>1.4</v>
       </c>
       <c r="AG42">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AK42">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7321,25 +7321,25 @@
         <v>3.05</v>
       </c>
       <c r="O43">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P43">
         <v>1.98</v>
       </c>
       <c r="Q43">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R43">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S43">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T43">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="U43">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V43">
         <v>1.52</v>
@@ -7348,19 +7348,19 @@
         <v>1.09</v>
       </c>
       <c r="X43">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y43">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z43">
-        <v>4.1</v>
+        <v>4.27</v>
       </c>
       <c r="AA43">
         <v>1.62</v>
       </c>
       <c r="AB43">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AC43">
         <v>2.52</v>
@@ -7369,7 +7369,7 @@
         <v>1.41</v>
       </c>
       <c r="AE43">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF43">
         <v>1.57</v>
@@ -7388,10 +7388,10 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.22</v>
+        <v>1.8</v>
       </c>
       <c r="AK43">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AL43">
         <v>0</v>
@@ -7484,10 +7484,10 @@
         <v>3.2</v>
       </c>
       <c r="O44">
-        <v>3.18</v>
+        <v>3.1</v>
       </c>
       <c r="P44">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="Q44">
         <v>4.24</v>
@@ -7496,46 +7496,46 @@
         <v>1.99</v>
       </c>
       <c r="S44">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T44">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="U44">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="V44">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W44">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X44">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y44">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="Z44">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="AA44">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AB44">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AC44">
         <v>4.02</v>
       </c>
       <c r="AD44">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE44">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF44">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AG44">
         <v>1.8</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="AK44">
         <v>1.28</v>
@@ -8133,10 +8133,10 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O48">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="P48">
         <v>2.3</v>
@@ -8148,37 +8148,37 @@
         <v>2</v>
       </c>
       <c r="S48">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T48">
         <v>2.65</v>
       </c>
       <c r="U48">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V48">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W48">
         <v>1.02</v>
       </c>
       <c r="X48">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z48">
         <v>2.8</v>
       </c>
       <c r="AA48">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB48">
         <v>1.6</v>
       </c>
       <c r="AC48">
-        <v>4</v>
+        <v>3.62</v>
       </c>
       <c r="AD48">
         <v>1.2</v>
@@ -8190,7 +8190,7 @@
         <v>1.91</v>
       </c>
       <c r="AG48">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AK48">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8311,28 +8311,28 @@
         <v>2.08</v>
       </c>
       <c r="S49">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="T49">
-        <v>2.8</v>
+        <v>2.89</v>
       </c>
       <c r="U49">
         <v>2.75</v>
       </c>
       <c r="V49">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="W49">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X49">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y49">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z49">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA49">
         <v>1.85</v>
@@ -8341,7 +8341,7 @@
         <v>1.85</v>
       </c>
       <c r="AC49">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AD49">
         <v>1.35</v>
@@ -8353,7 +8353,7 @@
         <v>1.61</v>
       </c>
       <c r="AG49">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AK49">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,10 +8459,10 @@
         </is>
       </c>
       <c r="N50">
-        <v>2.27</v>
+        <v>2.05</v>
       </c>
       <c r="O50">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="P50">
         <v>3</v>
@@ -8622,16 +8622,16 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O51">
-        <v>3.46</v>
+        <v>3.1</v>
       </c>
       <c r="P51">
-        <v>2.61</v>
+        <v>2.45</v>
       </c>
       <c r="Q51">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="R51">
         <v>2.15</v>
@@ -8649,37 +8649,37 @@
         <v>1.33</v>
       </c>
       <c r="W51">
+        <v>1.07</v>
+      </c>
+      <c r="X51">
         <v>1.04</v>
       </c>
-      <c r="X51">
-        <v>1.01</v>
-      </c>
       <c r="Y51">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z51">
         <v>3.1</v>
       </c>
       <c r="AA51">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB51">
         <v>1.7</v>
       </c>
       <c r="AC51">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="AD51">
         <v>1.25</v>
       </c>
       <c r="AE51">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF51">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG51">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK51">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8788,25 +8788,25 @@
         <v>2.8</v>
       </c>
       <c r="O52">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="P52">
         <v>2.36</v>
       </c>
       <c r="Q52">
-        <v>3.35</v>
+        <v>3.71</v>
       </c>
       <c r="R52">
         <v>2.05</v>
       </c>
       <c r="S52">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T52">
         <v>2.65</v>
       </c>
       <c r="U52">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V52">
         <v>1.3</v>
@@ -8821,19 +8821,19 @@
         <v>1.33</v>
       </c>
       <c r="Z52">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="AA52">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AB52">
         <v>1.66</v>
       </c>
       <c r="AC52">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="AD52">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE52">
         <v>1.05</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AK52">
         <v>1.36</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="O55">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P55">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q55">
         <v>2.7</v>
@@ -9289,7 +9289,7 @@
         <v>2.3</v>
       </c>
       <c r="S55">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T55">
         <v>3.12</v>
@@ -9301,28 +9301,28 @@
         <v>1.48</v>
       </c>
       <c r="W55">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X55">
         <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z55">
-        <v>3.7</v>
+        <v>3.94</v>
       </c>
       <c r="AA55">
         <v>1.73</v>
       </c>
       <c r="AB55">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="AC55">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD55">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE55">
         <v>1.14</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9600,22 +9600,22 @@
         </is>
       </c>
       <c r="N57">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="O57">
-        <v>3.92</v>
+        <v>3.75</v>
       </c>
       <c r="P57">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Q57">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="R57">
         <v>2.45</v>
       </c>
       <c r="S57">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T57">
         <v>3.52</v>
@@ -9624,22 +9624,22 @@
         <v>2.2</v>
       </c>
       <c r="V57">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="W57">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X57">
         <v>1.02</v>
       </c>
       <c r="Y57">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z57">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AA57">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AB57">
         <v>2.42</v>
@@ -9651,13 +9651,13 @@
         <v>1.63</v>
       </c>
       <c r="AE57">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF57">
         <v>1.54</v>
       </c>
       <c r="AG57">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.21</v>
+        <v>1.85</v>
       </c>
       <c r="AK57">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,16 +9763,16 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.37</v>
+        <v>2.1</v>
       </c>
       <c r="O58">
         <v>3.5</v>
       </c>
       <c r="P58">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q58">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="R58">
         <v>2.43</v>
@@ -9781,10 +9781,10 @@
         <v>1.25</v>
       </c>
       <c r="T58">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U58">
-        <v>2.18</v>
+        <v>2.29</v>
       </c>
       <c r="V58">
         <v>1.58</v>
@@ -9796,31 +9796,31 @@
         <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z58">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA58">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AB58">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AC58">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="AD58">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AE58">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF58">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AG58">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK58">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9929,13 +9929,13 @@
         <v>3.25</v>
       </c>
       <c r="O59">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P59">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q59">
-        <v>4.18</v>
+        <v>3.6</v>
       </c>
       <c r="R59">
         <v>2.37</v>
@@ -9944,7 +9944,7 @@
         <v>1.29</v>
       </c>
       <c r="T59">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U59">
         <v>2.52</v>
@@ -9953,22 +9953,22 @@
         <v>1.49</v>
       </c>
       <c r="W59">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X59">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y59">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z59">
         <v>4.15</v>
       </c>
       <c r="AA59">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB59">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AC59">
         <v>2.69</v>
@@ -9977,10 +9977,10 @@
         <v>1.44</v>
       </c>
       <c r="AE59">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF59">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AG59">
         <v>2.25</v>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="AK59">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10095,16 +10095,16 @@
         <v>3.7</v>
       </c>
       <c r="P60">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="Q60">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="R60">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S60">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="T60">
         <v>3.44</v>
@@ -10122,10 +10122,10 @@
         <v>1.03</v>
       </c>
       <c r="Y60">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="Z60">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="AA60">
         <v>1.5</v>
@@ -10134,13 +10134,13 @@
         <v>2.49</v>
       </c>
       <c r="AC60">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AD60">
         <v>1.6</v>
       </c>
       <c r="AE60">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AF60">
         <v>1.44</v>
@@ -10159,7 +10159,7 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK60">
         <v>1.75</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,80 +10252,80 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="O61">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="Q61">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R61">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="S61">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>2.95</v>
+        <v>3.9</v>
       </c>
       <c r="U61">
-        <v>2.47</v>
+        <v>2.1</v>
       </c>
       <c r="V61">
+        <v>1.65</v>
+      </c>
+      <c r="W61">
+        <v>1.17</v>
+      </c>
+      <c r="X61">
+        <v>1.02</v>
+      </c>
+      <c r="Y61">
+        <v>1.14</v>
+      </c>
+      <c r="Z61">
+        <v>5.65</v>
+      </c>
+      <c r="AA61">
         <v>1.45</v>
       </c>
-      <c r="W61">
-        <v>1.08</v>
-      </c>
-      <c r="X61">
-        <v>1</v>
-      </c>
-      <c r="Y61">
-        <v>1.21</v>
-      </c>
-      <c r="Z61">
-        <v>3.9</v>
-      </c>
-      <c r="AA61">
-        <v>1.72</v>
-      </c>
       <c r="AB61">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AC61">
-        <v>2.8</v>
+        <v>2.08</v>
       </c>
       <c r="AD61">
+        <v>1.7</v>
+      </c>
+      <c r="AE61">
+        <v>1.3</v>
+      </c>
+      <c r="AF61">
         <v>1.36</v>
       </c>
-      <c r="AE61">
-        <v>1.13</v>
-      </c>
-      <c r="AF61">
+      <c r="AG61">
+        <v>2.89</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
+        <v>1.29</v>
+      </c>
+      <c r="AK61">
         <v>1.57</v>
-      </c>
-      <c r="AG61">
-        <v>2.3</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>1.25</v>
-      </c>
-      <c r="AK61">
-        <v>1.5</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,80 +10415,80 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="O62">
-        <v>3.64</v>
+        <v>3.38</v>
       </c>
       <c r="P62">
-        <v>2.71</v>
+        <v>2.54</v>
       </c>
       <c r="Q62">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="R62">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="S62">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T62">
+        <v>3.25</v>
+      </c>
+      <c r="U62">
+        <v>2.43</v>
+      </c>
+      <c r="V62">
+        <v>1.47</v>
+      </c>
+      <c r="W62">
+        <v>1.08</v>
+      </c>
+      <c r="X62">
+        <v>1</v>
+      </c>
+      <c r="Y62">
+        <v>1.22</v>
+      </c>
+      <c r="Z62">
         <v>4</v>
       </c>
-      <c r="U62">
-        <v>2.17</v>
-      </c>
-      <c r="V62">
-        <v>1.58</v>
-      </c>
-      <c r="W62">
-        <v>1.15</v>
-      </c>
-      <c r="X62">
-        <v>1.03</v>
-      </c>
-      <c r="Y62">
-        <v>1.15</v>
-      </c>
-      <c r="Z62">
-        <v>4.6</v>
-      </c>
       <c r="AA62">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AB62">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AC62">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD62">
+        <v>1.4</v>
+      </c>
+      <c r="AE62">
+        <v>1.17</v>
+      </c>
+      <c r="AF62">
         <v>1.55</v>
       </c>
-      <c r="AE62">
-        <v>1.21</v>
-      </c>
-      <c r="AF62">
+      <c r="AG62">
+        <v>2.28</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ62">
+        <v>1.25</v>
+      </c>
+      <c r="AK62">
         <v>1.44</v>
-      </c>
-      <c r="AG62">
-        <v>2.5</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ62">
-        <v>1.24</v>
-      </c>
-      <c r="AK62">
-        <v>1.55</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10584,58 +10584,58 @@
         <v>4</v>
       </c>
       <c r="P63">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="Q63">
-        <v>2.2</v>
+        <v>2.02</v>
       </c>
       <c r="R63">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S63">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T63">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U63">
-        <v>2.55</v>
+        <v>2.41</v>
       </c>
       <c r="V63">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="W63">
         <v>1.11</v>
       </c>
       <c r="X63">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y63">
         <v>1.18</v>
       </c>
       <c r="Z63">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="AA63">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AB63">
-        <v>1.79</v>
+        <v>2.13</v>
       </c>
       <c r="AC63">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="AD63">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AE63">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF63">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AG63">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AK63">
         <v>2.38</v>
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="O65">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P65">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Q65">
         <v>2.15</v>
       </c>
       <c r="R65">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S65">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T65">
-        <v>2.78</v>
+        <v>2.59</v>
       </c>
       <c r="U65">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V65">
         <v>1.36</v>
       </c>
       <c r="W65">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X65">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y65">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z65">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AA65">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AB65">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AC65">
-        <v>3.58</v>
+        <v>3.9</v>
       </c>
       <c r="AD65">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE65">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF65">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AG65">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>1.23</v>
       </c>
       <c r="AK65">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11248,7 +11248,7 @@
         <v>1.36</v>
       </c>
       <c r="T67">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U67">
         <v>2.78</v>
@@ -11284,10 +11284,10 @@
         <v>1.05</v>
       </c>
       <c r="AF67">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG67">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AK67">
         <v>1.38</v>
@@ -11402,7 +11402,7 @@
         <v>0</v>
       </c>
       <c r="Q68">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="R68">
         <v>2.25</v>
@@ -11411,16 +11411,16 @@
         <v>1.3</v>
       </c>
       <c r="T68">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="U68">
         <v>2.56</v>
       </c>
       <c r="V68">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="W68">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X68">
         <v>1.04</v>
@@ -11429,28 +11429,28 @@
         <v>1.18</v>
       </c>
       <c r="Z68">
-        <v>3.9</v>
+        <v>3.88</v>
       </c>
       <c r="AA68">
         <v>1.78</v>
       </c>
       <c r="AB68">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="AC68">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="AD68">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE68">
         <v>1.15</v>
       </c>
       <c r="AF68">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG68">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>2.75</v>
       </c>
       <c r="AK68">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,28 +11556,28 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O69">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P69">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="Q69">
         <v>3.1</v>
       </c>
       <c r="R69">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S69">
         <v>1.3</v>
       </c>
       <c r="T69">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="U69">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="V69">
         <v>1.44</v>
@@ -11586,34 +11586,34 @@
         <v>1.08</v>
       </c>
       <c r="X69">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y69">
         <v>1.25</v>
       </c>
       <c r="Z69">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="AA69">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AB69">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC69">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="AD69">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE69">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AF69">
         <v>1.61</v>
       </c>
       <c r="AG69">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11885,61 +11885,61 @@
         <v>2.35</v>
       </c>
       <c r="O71">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P71">
+        <v>2.58</v>
+      </c>
+      <c r="Q71">
+        <v>3</v>
+      </c>
+      <c r="R71">
+        <v>2.08</v>
+      </c>
+      <c r="S71">
+        <v>1.35</v>
+      </c>
+      <c r="T71">
+        <v>2.95</v>
+      </c>
+      <c r="U71">
         <v>2.55</v>
       </c>
-      <c r="Q71">
-        <v>2.88</v>
-      </c>
-      <c r="R71">
-        <v>2.2</v>
-      </c>
-      <c r="S71">
-        <v>1.36</v>
-      </c>
-      <c r="T71">
-        <v>3.01</v>
-      </c>
-      <c r="U71">
-        <v>2.63</v>
-      </c>
       <c r="V71">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W71">
         <v>1.11</v>
       </c>
       <c r="X71">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z71">
-        <v>3.8</v>
+        <v>3.93</v>
       </c>
       <c r="AA71">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB71">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC71">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="AD71">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE71">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF71">
         <v>1.57</v>
       </c>
       <c r="AG71">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.16</v>
+        <v>2.07</v>
       </c>
       <c r="O72">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P72">
-        <v>3.17</v>
+        <v>3.4</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R72">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S72">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U72">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V72">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X72">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z72">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA72">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB72">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC72">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD72">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE72">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF72">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG72">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK72">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12374,25 +12374,25 @@
         <v>3.25</v>
       </c>
       <c r="O74">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P74">
         <v>1.93</v>
       </c>
       <c r="Q74">
-        <v>4.14</v>
+        <v>3.8</v>
       </c>
       <c r="R74">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S74">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T74">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="U74">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="V74">
         <v>1.4</v>
@@ -12401,25 +12401,25 @@
         <v>1.1</v>
       </c>
       <c r="X74">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y74">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z74">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AA74">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB74">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC74">
-        <v>3.1</v>
+        <v>2.92</v>
       </c>
       <c r="AD74">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE74">
         <v>1.12</v>
@@ -12428,7 +12428,7 @@
         <v>1.67</v>
       </c>
       <c r="AG74">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.3</v>
+        <v>1.73</v>
       </c>
       <c r="AK74">
         <v>1.23</v>
@@ -12534,64 +12534,64 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="O75">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P75">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="Q75">
-        <v>2.32</v>
+        <v>2.43</v>
       </c>
       <c r="R75">
         <v>2.25</v>
       </c>
       <c r="S75">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T75">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="U75">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="V75">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W75">
         <v>1.1</v>
       </c>
       <c r="X75">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y75">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z75">
         <v>3.9</v>
       </c>
       <c r="AA75">
+        <v>1.73</v>
+      </c>
+      <c r="AB75">
+        <v>2</v>
+      </c>
+      <c r="AC75">
+        <v>2.89</v>
+      </c>
+      <c r="AD75">
+        <v>1.38</v>
+      </c>
+      <c r="AE75">
+        <v>1.11</v>
+      </c>
+      <c r="AF75">
         <v>1.67</v>
       </c>
-      <c r="AB75">
-        <v>2.08</v>
-      </c>
-      <c r="AC75">
-        <v>2.7</v>
-      </c>
-      <c r="AD75">
-        <v>1.4</v>
-      </c>
-      <c r="AE75">
-        <v>1.15</v>
-      </c>
-      <c r="AF75">
-        <v>1.62</v>
-      </c>
       <c r="AG75">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,46 +12697,46 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O76">
         <v>4.1</v>
       </c>
       <c r="P76">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q76">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="R76">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S76">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T76">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="U76">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V76">
         <v>1.62</v>
       </c>
       <c r="W76">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z76">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AA76">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AB76">
         <v>2.4</v>
@@ -12745,7 +12745,7 @@
         <v>2.35</v>
       </c>
       <c r="AD76">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE76">
         <v>1.21</v>
@@ -12754,7 +12754,7 @@
         <v>1.53</v>
       </c>
       <c r="AG76">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK76">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -13349,13 +13349,13 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O80">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P80">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q80">
         <v>0</v>
@@ -13388,10 +13388,10 @@
         <v>0</v>
       </c>
       <c r="AA80">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB80">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC80">
         <v>0</v>
@@ -13515,7 +13515,7 @@
         <v>3.5</v>
       </c>
       <c r="O81">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P81">
         <v>1.86</v>
@@ -13524,52 +13524,52 @@
         <v>3.85</v>
       </c>
       <c r="R81">
-        <v>2.38</v>
+        <v>2.23</v>
       </c>
       <c r="S81">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T81">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="U81">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V81">
         <v>1.52</v>
       </c>
       <c r="W81">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X81">
         <v>1.02</v>
       </c>
       <c r="Y81">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z81">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="AA81">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB81">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AC81">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="AD81">
         <v>1.43</v>
       </c>
       <c r="AE81">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF81">
         <v>1.55</v>
       </c>
       <c r="AG81">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.85</v>
+        <v>1.17</v>
       </c>
       <c r="AK81">
         <v>1.21</v>
@@ -13681,16 +13681,16 @@
         <v>3.65</v>
       </c>
       <c r="P82">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="Q82">
         <v>2.45</v>
       </c>
       <c r="R82">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S82">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T82">
         <v>3.02</v>
@@ -13708,19 +13708,19 @@
         <v>1.04</v>
       </c>
       <c r="Y82">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z82">
         <v>3.8</v>
       </c>
       <c r="AA82">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AB82">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="AC82">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AD82">
         <v>1.33</v>
@@ -13729,10 +13729,10 @@
         <v>1.09</v>
       </c>
       <c r="AF82">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG82">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13841,13 +13841,13 @@
         <v>4.85</v>
       </c>
       <c r="O83">
-        <v>3.95</v>
+        <v>3.45</v>
       </c>
       <c r="P83">
         <v>1.51</v>
       </c>
       <c r="Q83">
-        <v>6.96</v>
+        <v>6.6</v>
       </c>
       <c r="R83">
         <v>2.05</v>
@@ -13880,7 +13880,7 @@
         <v>1.75</v>
       </c>
       <c r="AB83">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC83">
         <v>2.75</v>
@@ -14336,49 +14336,49 @@
         <v>13.5</v>
       </c>
       <c r="Q86">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="R86">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="S86">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T86">
-        <v>3.66</v>
+        <v>3.75</v>
       </c>
       <c r="U86">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="V86">
         <v>1.6</v>
       </c>
       <c r="W86">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
         <v>1.13</v>
       </c>
       <c r="Z86">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="AA86">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AB86">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="AC86">
         <v>2.31</v>
       </c>
       <c r="AD86">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE86">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF86">
         <v>2.41</v>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AK86">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14816,31 +14816,31 @@
         </is>
       </c>
       <c r="N89">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O89">
         <v>3.1</v>
       </c>
       <c r="P89">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q89">
-        <v>3.52</v>
+        <v>3.68</v>
       </c>
       <c r="R89">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S89">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T89">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U89">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="V89">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W89">
         <v>1.05</v>
@@ -14849,31 +14849,31 @@
         <v>1.06</v>
       </c>
       <c r="Y89">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z89">
-        <v>3.12</v>
+        <v>3.44</v>
       </c>
       <c r="AA89">
-        <v>2.06</v>
+        <v>1.9</v>
       </c>
       <c r="AB89">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="AC89">
-        <v>3.55</v>
+        <v>2.99</v>
       </c>
       <c r="AD89">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE89">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF89">
         <v>1.75</v>
       </c>
       <c r="AG89">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14979,64 +14979,64 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="O90">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P90">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="Q90">
-        <v>2.71</v>
+        <v>2.63</v>
       </c>
       <c r="R90">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S90">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="T90">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="U90">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="V90">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W90">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X90">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y90">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z90">
         <v>3.14</v>
       </c>
       <c r="AA90">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AB90">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC90">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AD90">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE90">
         <v>1.1</v>
       </c>
       <c r="AF90">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG90">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK90">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O96">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P96">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q96">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R96">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U96">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V96">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W96">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y96">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z96">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA96">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB96">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC96">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD96">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF96">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG96">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -17424,58 +17424,58 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="O105">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="P105">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="Q105">
-        <v>2.9</v>
+        <v>3.33</v>
       </c>
       <c r="R105">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S105">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T105">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="U105">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="V105">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W105">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X105">
         <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z105">
-        <v>5.05</v>
+        <v>5.36</v>
       </c>
       <c r="AA105">
         <v>1.53</v>
       </c>
       <c r="AB105">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="AC105">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AD105">
         <v>1.62</v>
       </c>
       <c r="AE105">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF105">
         <v>1.44</v>
@@ -17494,7 +17494,7 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AK105">
         <v>1.4</v>
@@ -18079,61 +18079,61 @@
         <v>2.15</v>
       </c>
       <c r="O109">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P109">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Q109">
         <v>2.88</v>
       </c>
       <c r="R109">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="S109">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T109">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U109">
-        <v>3.08</v>
+        <v>2.8</v>
       </c>
       <c r="V109">
         <v>1.3</v>
       </c>
       <c r="W109">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X109">
         <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z109">
         <v>2.8</v>
       </c>
       <c r="AA109">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB109">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC109">
         <v>3.84</v>
       </c>
       <c r="AD109">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE109">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF109">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="AG109">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH109" t="inlineStr">
         <is>
@@ -18146,10 +18146,10 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="AK109">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AL109">
         <v>0</v>
@@ -18248,34 +18248,34 @@
         <v>0</v>
       </c>
       <c r="Q110">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="R110">
         <v>2.21</v>
       </c>
       <c r="S110">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T110">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U110">
-        <v>2.96</v>
+        <v>3.07</v>
       </c>
       <c r="V110">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W110">
         <v>1.05</v>
       </c>
       <c r="X110">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y110">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z110">
-        <v>3.08</v>
+        <v>3.12</v>
       </c>
       <c r="AA110">
         <v>1.95</v>
@@ -18284,19 +18284,19 @@
         <v>1.75</v>
       </c>
       <c r="AC110">
-        <v>3.63</v>
+        <v>3.5</v>
       </c>
       <c r="AD110">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE110">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF110">
         <v>1.95</v>
       </c>
       <c r="AG110">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AK110">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -19054,31 +19054,31 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O115">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P115">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="Q115">
-        <v>2.35</v>
+        <v>2.43</v>
       </c>
       <c r="R115">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="S115">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T115">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="U115">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="V115">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W115">
         <v>1.07</v>
@@ -19087,31 +19087,31 @@
         <v>1.01</v>
       </c>
       <c r="Y115">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z115">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="AA115">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AB115">
-        <v>1.88</v>
+        <v>1.73</v>
       </c>
       <c r="AC115">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AD115">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AE115">
         <v>1.08</v>
       </c>
       <c r="AF115">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG115">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH115" t="inlineStr">
         <is>
@@ -19124,10 +19124,10 @@
         </is>
       </c>
       <c r="AJ115">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK115">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AL115">
         <v>0</v>
@@ -19389,22 +19389,22 @@
         <v>3.45</v>
       </c>
       <c r="Q117">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R117">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="S117">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T117">
-        <v>3.12</v>
+        <v>2.99</v>
       </c>
       <c r="U117">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="V117">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W117">
         <v>1.1</v>
@@ -19419,10 +19419,10 @@
         <v>3.84</v>
       </c>
       <c r="AA117">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB117">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
       <c r="AC117">
         <v>2.7</v>
@@ -19431,7 +19431,7 @@
         <v>1.36</v>
       </c>
       <c r="AE117">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF117">
         <v>1.58</v>
@@ -19453,7 +19453,7 @@
         <v>1.3</v>
       </c>
       <c r="AK117">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AL117">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -3747,10 +3747,10 @@
         <v>2.18</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U21">
         <v>2.55</v>
@@ -3759,10 +3759,10 @@
         <v>1.38</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
         <v>1.25</v>
@@ -3783,7 +3783,7 @@
         <v>1.3</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF21">
         <v>1.63</v>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G23">
@@ -4058,64 +4058,64 @@
         </is>
       </c>
       <c r="N23">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P23">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q23">
-        <v>2.87</v>
+        <v>2.15</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="S23">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="T23">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="U23">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="V23">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W23">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y23">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="Z23">
-        <v>3.4</v>
+        <v>3.78</v>
       </c>
       <c r="AA23">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AB23">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AC23">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="AD23">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="AE23">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF23">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="AG23">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="AK23">
-        <v>1.53</v>
+        <v>2.07</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,65 +4221,65 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q24">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="R24">
-        <v>2.23</v>
+        <v>2.41</v>
       </c>
       <c r="S24">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="T24">
-        <v>2.97</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.46</v>
+        <v>2</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X24">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>3.78</v>
+        <v>5.5</v>
       </c>
       <c r="AA24">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="AB24">
+        <v>2.6</v>
+      </c>
+      <c r="AC24">
+        <v>2.35</v>
+      </c>
+      <c r="AD24">
+        <v>1.48</v>
+      </c>
+      <c r="AE24">
+        <v>1.21</v>
+      </c>
+      <c r="AF24">
+        <v>1.68</v>
+      </c>
+      <c r="AG24">
         <v>2.02</v>
       </c>
-      <c r="AC24">
-        <v>2.66</v>
-      </c>
-      <c r="AD24">
-        <v>1.37</v>
-      </c>
-      <c r="AE24">
-        <v>1.12</v>
-      </c>
-      <c r="AF24">
-        <v>1.69</v>
-      </c>
-      <c r="AG24">
-        <v>1.97</v>
-      </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK24">
-        <v>2.07</v>
+        <v>2.3</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q25">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="R25">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="S25">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="T25">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="U25">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="V25">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="W25">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="X25">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="Z25">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="AA25">
-        <v>1.47</v>
+        <v>1.9</v>
       </c>
       <c r="AB25">
-        <v>2.6</v>
+        <v>1.79</v>
       </c>
       <c r="AC25">
-        <v>2.35</v>
+        <v>3.2</v>
       </c>
       <c r="AD25">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="AE25">
-        <v>1.21</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG25">
-        <v>2.02</v>
+        <v>1.93</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AK25">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G26">
@@ -4556,55 +4556,55 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>3</v>
+        <v>2.53</v>
       </c>
       <c r="R26">
         <v>2.18</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T26">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="U26">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V26">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
-        <v>3.65</v>
+        <v>3.88</v>
       </c>
       <c r="AA26">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="AB26">
         <v>2</v>
       </c>
       <c r="AC26">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="AD26">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AF26">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G27">
@@ -4719,55 +4719,55 @@
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="R27">
-        <v>2.07</v>
+        <v>2.18</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="U27">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="V27">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="W27">
+        <v>1.11</v>
+      </c>
+      <c r="X27">
         <v>1.04</v>
       </c>
-      <c r="X27">
-        <v>1</v>
-      </c>
       <c r="Y27">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AA27">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AB27">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AC27">
-        <v>3.2</v>
+        <v>2.65</v>
       </c>
       <c r="AD27">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE27">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AF27">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AG27">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK27">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q28">
-        <v>2.53</v>
+        <v>2.87</v>
       </c>
       <c r="R28">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T28">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="U28">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V28">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X28">
         <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="Z28">
-        <v>3.88</v>
+        <v>3.4</v>
       </c>
       <c r="AA28">
+        <v>1.85</v>
+      </c>
+      <c r="AB28">
+        <v>1.85</v>
+      </c>
+      <c r="AC28">
+        <v>3</v>
+      </c>
+      <c r="AD28">
+        <v>1.32</v>
+      </c>
+      <c r="AE28">
+        <v>1.08</v>
+      </c>
+      <c r="AF28">
         <v>1.71</v>
       </c>
-      <c r="AB28">
-        <v>2</v>
-      </c>
-      <c r="AC28">
-        <v>2.74</v>
-      </c>
-      <c r="AD28">
-        <v>1.36</v>
-      </c>
-      <c r="AE28">
-        <v>1.11</v>
-      </c>
-      <c r="AF28">
-        <v>1.6</v>
-      </c>
       <c r="AG28">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AK28">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -7493,13 +7493,13 @@
         <v>4.24</v>
       </c>
       <c r="R44">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="S44">
         <v>1.44</v>
       </c>
       <c r="T44">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="U44">
         <v>3.25</v>
@@ -7517,13 +7517,13 @@
         <v>1.32</v>
       </c>
       <c r="Z44">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="AA44">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="AB44">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC44">
         <v>4.02</v>
@@ -7538,7 +7538,7 @@
         <v>1.85</v>
       </c>
       <c r="AG44">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7982,10 +7982,10 @@
         <v>4.33</v>
       </c>
       <c r="R47">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="S47">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="T47">
         <v>2.2</v>
@@ -7997,10 +7997,10 @@
         <v>1.18</v>
       </c>
       <c r="W47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X47">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y47">
         <v>1.57</v>
@@ -8015,19 +8015,19 @@
         <v>1.39</v>
       </c>
       <c r="AC47">
-        <v>5.75</v>
+        <v>5.89</v>
       </c>
       <c r="AD47">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AE47">
         <v>1.03</v>
       </c>
       <c r="AF47">
-        <v>2.02</v>
+        <v>2.25</v>
       </c>
       <c r="AG47">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.36</v>
+        <v>1.61</v>
       </c>
       <c r="AK47">
         <v>1.25</v>
@@ -9277,28 +9277,28 @@
         <v>2.2</v>
       </c>
       <c r="O55">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P55">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Q55">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="R55">
         <v>2.3</v>
       </c>
       <c r="S55">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T55">
         <v>3.12</v>
       </c>
       <c r="U55">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V55">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="W55">
         <v>1.11</v>
@@ -9313,7 +9313,7 @@
         <v>3.94</v>
       </c>
       <c r="AA55">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB55">
         <v>1.99</v>
@@ -9322,7 +9322,7 @@
         <v>2.9</v>
       </c>
       <c r="AD55">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AE55">
         <v>1.14</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK55">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -11408,7 +11408,7 @@
         <v>2.25</v>
       </c>
       <c r="S68">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T68">
         <v>3.2</v>
@@ -11435,19 +11435,19 @@
         <v>1.78</v>
       </c>
       <c r="AB68">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="AC68">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AD68">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE68">
         <v>1.15</v>
       </c>
       <c r="AF68">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG68">
         <v>1.83</v>
@@ -11719,16 +11719,16 @@
         </is>
       </c>
       <c r="N70">
+        <v>2.95</v>
+      </c>
+      <c r="O70">
         <v>2.75</v>
       </c>
-      <c r="O70">
-        <v>2.7</v>
-      </c>
       <c r="P70">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="Q70">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R70">
         <v>1.73</v>
@@ -11743,7 +11743,7 @@
         <v>3.7</v>
       </c>
       <c r="V70">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W70">
         <v>1.03</v>
@@ -11764,7 +11764,7 @@
         <v>1.31</v>
       </c>
       <c r="AC70">
-        <v>6.5</v>
+        <v>6.29</v>
       </c>
       <c r="AD70">
         <v>1.07</v>
@@ -12860,19 +12860,19 @@
         </is>
       </c>
       <c r="N77">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="O77">
+        <v>3.2</v>
+      </c>
+      <c r="P77">
         <v>3.3</v>
       </c>
-      <c r="P77">
-        <v>3.5</v>
-      </c>
       <c r="Q77">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="R77">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S77">
         <v>1.36</v>
@@ -12887,7 +12887,7 @@
         <v>1.34</v>
       </c>
       <c r="W77">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X77">
         <v>1.06</v>
@@ -12896,13 +12896,13 @@
         <v>1.3</v>
       </c>
       <c r="Z77">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="AA77">
         <v>2</v>
       </c>
       <c r="AB77">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC77">
         <v>3.6</v>
@@ -12914,26 +12914,26 @@
         <v>1.08</v>
       </c>
       <c r="AF77">
+        <v>1.82</v>
+      </c>
+      <c r="AG77">
+        <v>1.82</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ77">
+        <v>1.22</v>
+      </c>
+      <c r="AK77">
         <v>1.85</v>
-      </c>
-      <c r="AG77">
-        <v>1.85</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ77">
-        <v>1.3</v>
-      </c>
-      <c r="AK77">
-        <v>1.8</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13026,61 +13026,61 @@
         <v>1.7</v>
       </c>
       <c r="O78">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P78">
         <v>4</v>
       </c>
       <c r="Q78">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="R78">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="S78">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T78">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U78">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="V78">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="W78">
+        <v>1.09</v>
+      </c>
+      <c r="X78">
+        <v>1.02</v>
+      </c>
+      <c r="Y78">
+        <v>1.13</v>
+      </c>
+      <c r="Z78">
+        <v>4.68</v>
+      </c>
+      <c r="AA78">
+        <v>1.53</v>
+      </c>
+      <c r="AB78">
+        <v>2.23</v>
+      </c>
+      <c r="AC78">
+        <v>2.48</v>
+      </c>
+      <c r="AD78">
+        <v>1.52</v>
+      </c>
+      <c r="AE78">
         <v>1.15</v>
-      </c>
-      <c r="X78">
-        <v>1.03</v>
-      </c>
-      <c r="Y78">
-        <v>1.12</v>
-      </c>
-      <c r="Z78">
-        <v>4.35</v>
-      </c>
-      <c r="AA78">
-        <v>1.52</v>
-      </c>
-      <c r="AB78">
-        <v>2.25</v>
-      </c>
-      <c r="AC78">
-        <v>2.45</v>
-      </c>
-      <c r="AD78">
-        <v>1.5</v>
-      </c>
-      <c r="AE78">
-        <v>1.18</v>
       </c>
       <c r="AF78">
         <v>1.53</v>
       </c>
       <c r="AG78">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK78">
         <v>2.05</v>
@@ -13186,7 +13186,7 @@
         </is>
       </c>
       <c r="N79">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O79">
         <v>3.5</v>
@@ -13195,46 +13195,46 @@
         <v>1.65</v>
       </c>
       <c r="Q79">
-        <v>5.3</v>
+        <v>5.41</v>
       </c>
       <c r="R79">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="S79">
+        <v>1.39</v>
+      </c>
+      <c r="T79">
+        <v>3</v>
+      </c>
+      <c r="U79">
+        <v>2.7</v>
+      </c>
+      <c r="V79">
+        <v>1.4</v>
+      </c>
+      <c r="W79">
+        <v>1.04</v>
+      </c>
+      <c r="X79">
+        <v>1</v>
+      </c>
+      <c r="Y79">
+        <v>1.29</v>
+      </c>
+      <c r="Z79">
+        <v>3.43</v>
+      </c>
+      <c r="AA79">
+        <v>1.93</v>
+      </c>
+      <c r="AB79">
+        <v>1.85</v>
+      </c>
+      <c r="AC79">
+        <v>3.3</v>
+      </c>
+      <c r="AD79">
         <v>1.33</v>
-      </c>
-      <c r="T79">
-        <v>3.1</v>
-      </c>
-      <c r="U79">
-        <v>2.69</v>
-      </c>
-      <c r="V79">
-        <v>1.44</v>
-      </c>
-      <c r="W79">
-        <v>1.05</v>
-      </c>
-      <c r="X79">
-        <v>1.01</v>
-      </c>
-      <c r="Y79">
-        <v>1.23</v>
-      </c>
-      <c r="Z79">
-        <v>3.69</v>
-      </c>
-      <c r="AA79">
-        <v>1.85</v>
-      </c>
-      <c r="AB79">
-        <v>1.91</v>
-      </c>
-      <c r="AC79">
-        <v>3.25</v>
-      </c>
-      <c r="AD79">
-        <v>1.35</v>
       </c>
       <c r="AE79">
         <v>1.11</v>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -14490,7 +14490,7 @@
         </is>
       </c>
       <c r="N87">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="O87">
         <v>3.3</v>
@@ -14499,40 +14499,40 @@
         <v>4</v>
       </c>
       <c r="Q87">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="R87">
         <v>2.05</v>
       </c>
       <c r="S87">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T87">
         <v>2.77</v>
       </c>
       <c r="U87">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="V87">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W87">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="X87">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y87">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z87">
         <v>3.79</v>
       </c>
       <c r="AA87">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AB87">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AC87">
         <v>3.08</v>
@@ -14541,7 +14541,7 @@
         <v>1.28</v>
       </c>
       <c r="AE87">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AF87">
         <v>1.75</v>
@@ -14656,13 +14656,13 @@
         <v>2.89</v>
       </c>
       <c r="O88">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P88">
         <v>2.25</v>
       </c>
       <c r="Q88">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="R88">
         <v>2.23</v>
@@ -14671,46 +14671,46 @@
         <v>1.3</v>
       </c>
       <c r="T88">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="U88">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V88">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W88">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X88">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y88">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z88">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA88">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AB88">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC88">
-        <v>2.54</v>
+        <v>2.61</v>
       </c>
       <c r="AD88">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AE88">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF88">
         <v>1.53</v>
       </c>
       <c r="AG88">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14819,31 +14819,31 @@
         <v>2.9</v>
       </c>
       <c r="O89">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P89">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q89">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="R89">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="S89">
         <v>1.36</v>
       </c>
       <c r="T89">
-        <v>2.62</v>
+        <v>2.93</v>
       </c>
       <c r="U89">
-        <v>2.7</v>
+        <v>2.93</v>
       </c>
       <c r="V89">
         <v>1.39</v>
       </c>
       <c r="W89">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X89">
         <v>1.06</v>
@@ -14855,19 +14855,19 @@
         <v>3.44</v>
       </c>
       <c r="AA89">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB89">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AC89">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="AD89">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AE89">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF89">
         <v>1.75</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK89">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,31 +14979,31 @@
         </is>
       </c>
       <c r="N90">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O90">
+        <v>3.4</v>
+      </c>
+      <c r="P90">
         <v>3.5</v>
-      </c>
-      <c r="P90">
-        <v>3.65</v>
       </c>
       <c r="Q90">
         <v>2.63</v>
       </c>
       <c r="R90">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S90">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="T90">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
       <c r="U90">
         <v>2.7</v>
       </c>
       <c r="V90">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W90">
         <v>1.08</v>
@@ -15012,13 +15012,13 @@
         <v>1.06</v>
       </c>
       <c r="Y90">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Z90">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AA90">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="AB90">
         <v>1.8</v>
@@ -15033,7 +15033,7 @@
         <v>1.1</v>
       </c>
       <c r="AF90">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG90">
         <v>1.95</v>
@@ -16283,13 +16283,13 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="O98">
         <v>2.8</v>
       </c>
       <c r="P98">
-        <v>4.45</v>
+        <v>4.65</v>
       </c>
       <c r="Q98">
         <v>0</v>
@@ -16740,12 +16740,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="G101">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Čelik</t>
         </is>
       </c>
       <c r="G102">
@@ -17066,12 +17066,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G103">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G104">

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Wacker Innsbruck</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austria Wien II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="G32">
@@ -5525,64 +5525,64 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.89</v>
+        <v>3.2</v>
       </c>
       <c r="O32">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="P32">
-        <v>3.35</v>
+        <v>1.94</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T32">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="U32">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V32">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X32">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z32">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA32">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="AB32">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="AC32">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE32">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF32">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AK32">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL32">
         <v>0</v>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Amstetten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Wien II</t>
         </is>
       </c>
       <c r="G33">
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="O33">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="P33">
         <v>3.35</v>
@@ -5727,10 +5727,10 @@
         <v>0</v>
       </c>
       <c r="AA33">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AB33">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AC33">
         <v>0</v>
@@ -5819,12 +5819,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wacker Innsbruck</t>
+          <t>Amstetten</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G34">
@@ -5851,64 +5851,64 @@
         </is>
       </c>
       <c r="N34">
-        <v>3.2</v>
+        <v>1.88</v>
       </c>
       <c r="O34">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="P34">
-        <v>1.94</v>
+        <v>3.35</v>
       </c>
       <c r="Q34">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R34">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S34">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T34">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="U34">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V34">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W34">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X34">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y34">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z34">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AB34">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC34">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD34">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE34">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF34">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="AJ34">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AK34">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL34">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="O49">
-        <v>3.2</v>
+        <v>3.39</v>
       </c>
       <c r="P49">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q49">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB49">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC49">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK49">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8427,12 +8427,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
+        <v>2.6</v>
+      </c>
+      <c r="O50">
+        <v>3.1</v>
+      </c>
+      <c r="P50">
+        <v>2.45</v>
+      </c>
+      <c r="Q50">
+        <v>3.25</v>
+      </c>
+      <c r="R50">
+        <v>2.15</v>
+      </c>
+      <c r="S50">
+        <v>1.38</v>
+      </c>
+      <c r="T50">
+        <v>2.8</v>
+      </c>
+      <c r="U50">
+        <v>3</v>
+      </c>
+      <c r="V50">
+        <v>1.33</v>
+      </c>
+      <c r="W50">
+        <v>1.07</v>
+      </c>
+      <c r="X50">
+        <v>1.04</v>
+      </c>
+      <c r="Y50">
+        <v>1.28</v>
+      </c>
+      <c r="Z50">
+        <v>3.1</v>
+      </c>
+      <c r="AA50">
         <v>2.05</v>
       </c>
-      <c r="O50">
-        <v>3.39</v>
-      </c>
-      <c r="P50">
-        <v>3</v>
-      </c>
-      <c r="Q50">
-        <v>0</v>
-      </c>
-      <c r="R50">
-        <v>0</v>
-      </c>
-      <c r="S50">
-        <v>0</v>
-      </c>
-      <c r="T50">
-        <v>0</v>
-      </c>
-      <c r="U50">
-        <v>0</v>
-      </c>
-      <c r="V50">
-        <v>0</v>
-      </c>
-      <c r="W50">
-        <v>0</v>
-      </c>
-      <c r="X50">
-        <v>0</v>
-      </c>
-      <c r="Y50">
-        <v>0</v>
-      </c>
-      <c r="Z50">
-        <v>0</v>
-      </c>
-      <c r="AA50">
-        <v>1.9</v>
-      </c>
       <c r="AB50">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC50">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD50">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE50">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF50">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG50">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8590,12 +8590,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O51">
         <v>3.1</v>
       </c>
       <c r="P51">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="Q51">
-        <v>3.25</v>
+        <v>3.71</v>
       </c>
       <c r="R51">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S51">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T51">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U51">
         <v>3</v>
       </c>
       <c r="V51">
+        <v>1.3</v>
+      </c>
+      <c r="W51">
+        <v>1.04</v>
+      </c>
+      <c r="X51">
+        <v>1.02</v>
+      </c>
+      <c r="Y51">
         <v>1.33</v>
       </c>
-      <c r="W51">
-        <v>1.07</v>
-      </c>
-      <c r="X51">
-        <v>1.04</v>
-      </c>
-      <c r="Y51">
-        <v>1.28</v>
-      </c>
       <c r="Z51">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA51">
-        <v>2.05</v>
+        <v>2.18</v>
       </c>
       <c r="AB51">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AC51">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="AD51">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE51">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF51">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG51">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AK51">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="O52">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P52">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="Q52">
-        <v>3.71</v>
+        <v>2.95</v>
       </c>
       <c r="R52">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="S52">
+        <v>1.3</v>
+      </c>
+      <c r="T52">
+        <v>2.89</v>
+      </c>
+      <c r="U52">
+        <v>2.75</v>
+      </c>
+      <c r="V52">
         <v>1.42</v>
       </c>
-      <c r="T52">
-        <v>2.65</v>
-      </c>
-      <c r="U52">
-        <v>3</v>
-      </c>
-      <c r="V52">
-        <v>1.3</v>
-      </c>
       <c r="W52">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y52">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z52">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AA52">
-        <v>2.18</v>
+        <v>1.85</v>
       </c>
       <c r="AB52">
-        <v>1.66</v>
+        <v>1.85</v>
       </c>
       <c r="AC52">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="AD52">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AE52">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF52">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AG52">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AK52">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="O60">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P60">
-        <v>3.35</v>
+        <v>2.6</v>
       </c>
       <c r="Q60">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R60">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="S60">
         <v>1.2</v>
       </c>
       <c r="T60">
-        <v>3.44</v>
+        <v>3.9</v>
       </c>
       <c r="U60">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="V60">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W60">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X60">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z60">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="AA60">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AB60">
-        <v>2.49</v>
+        <v>2.7</v>
       </c>
       <c r="AC60">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AD60">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AE60">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AF60">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AG60">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK60">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,80 +10252,80 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="O61">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P61">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="Q61">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R61">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="S61">
         <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="U61">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="V61">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="W61">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X61">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z61">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="AA61">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AB61">
-        <v>2.7</v>
+        <v>2.49</v>
       </c>
       <c r="AC61">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AD61">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AE61">
+        <v>1.21</v>
+      </c>
+      <c r="AF61">
+        <v>1.44</v>
+      </c>
+      <c r="AG61">
+        <v>2.5</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ61">
         <v>1.3</v>
       </c>
-      <c r="AF61">
-        <v>1.36</v>
-      </c>
-      <c r="AG61">
-        <v>2.89</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ61">
-        <v>1.29</v>
-      </c>
       <c r="AK61">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,80 +13023,80 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="O78">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="P78">
-        <v>4</v>
+        <v>1.65</v>
       </c>
       <c r="Q78">
+        <v>5.41</v>
+      </c>
+      <c r="R78">
         <v>2.25</v>
       </c>
-      <c r="R78">
-        <v>2.32</v>
-      </c>
       <c r="S78">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="T78">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U78">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="V78">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="W78">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y78">
+        <v>1.29</v>
+      </c>
+      <c r="Z78">
+        <v>3.43</v>
+      </c>
+      <c r="AA78">
+        <v>1.93</v>
+      </c>
+      <c r="AB78">
+        <v>1.85</v>
+      </c>
+      <c r="AC78">
+        <v>3.3</v>
+      </c>
+      <c r="AD78">
+        <v>1.33</v>
+      </c>
+      <c r="AE78">
+        <v>1.11</v>
+      </c>
+      <c r="AF78">
+        <v>1.85</v>
+      </c>
+      <c r="AG78">
+        <v>1.85</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ78">
+        <v>1.22</v>
+      </c>
+      <c r="AK78">
         <v>1.13</v>
-      </c>
-      <c r="Z78">
-        <v>4.68</v>
-      </c>
-      <c r="AA78">
-        <v>1.53</v>
-      </c>
-      <c r="AB78">
-        <v>2.23</v>
-      </c>
-      <c r="AC78">
-        <v>2.48</v>
-      </c>
-      <c r="AD78">
-        <v>1.52</v>
-      </c>
-      <c r="AE78">
-        <v>1.15</v>
-      </c>
-      <c r="AF78">
-        <v>1.53</v>
-      </c>
-      <c r="AG78">
-        <v>2.33</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ78">
-        <v>1.2</v>
-      </c>
-      <c r="AK78">
-        <v>2.05</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>4.7</v>
+        <v>1.7</v>
       </c>
       <c r="O79">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P79">
-        <v>1.65</v>
+        <v>4</v>
       </c>
       <c r="Q79">
-        <v>5.41</v>
+        <v>2.25</v>
       </c>
       <c r="R79">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="S79">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="T79">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="U79">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="V79">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W79">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="X79">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="Z79">
-        <v>3.43</v>
+        <v>4.68</v>
       </c>
       <c r="AA79">
-        <v>1.93</v>
+        <v>1.53</v>
       </c>
       <c r="AB79">
-        <v>1.85</v>
+        <v>2.23</v>
       </c>
       <c r="AC79">
-        <v>3.3</v>
+        <v>2.48</v>
       </c>
       <c r="AD79">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="AE79">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF79">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AG79">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK79">
-        <v>1.13</v>
+        <v>2.05</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -18091,25 +18091,25 @@
         <v>2</v>
       </c>
       <c r="S109">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T109">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="U109">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="V109">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W109">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X109">
         <v>1.03</v>
       </c>
       <c r="Y109">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z109">
         <v>2.8</v>
@@ -18118,19 +18118,19 @@
         <v>2.14</v>
       </c>
       <c r="AB109">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC109">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="AD109">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE109">
         <v>1.06</v>
       </c>
       <c r="AF109">
-        <v>1.86</v>
+        <v>1.77</v>
       </c>
       <c r="AG109">
         <v>1.8</v>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AJ109">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AK109">
         <v>1.6</v>
@@ -18251,31 +18251,31 @@
         <v>5</v>
       </c>
       <c r="R110">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="S110">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T110">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U110">
-        <v>3.07</v>
+        <v>2.8</v>
       </c>
       <c r="V110">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W110">
         <v>1.05</v>
       </c>
       <c r="X110">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y110">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z110">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AA110">
         <v>1.95</v>
@@ -18284,19 +18284,19 @@
         <v>1.75</v>
       </c>
       <c r="AC110">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD110">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE110">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF110">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG110">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AK110">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18891,13 +18891,13 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>4.12</v>
       </c>
       <c r="Q114">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="O3">
         <v>3.8</v>
       </c>
       <c r="P3">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="Q3">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="U3">
-        <v>2.65</v>
+        <v>2.51</v>
       </c>
       <c r="V3">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
         <v>1.05</v>
@@ -834,10 +834,10 @@
         <v>1.21</v>
       </c>
       <c r="Z3">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="AA3">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AB3">
         <v>1.91</v>
@@ -846,13 +846,13 @@
         <v>2.85</v>
       </c>
       <c r="AD3">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AE3">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF3">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG3">
         <v>1.93</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="O4">
         <v>4.15</v>
       </c>
       <c r="P4">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="Q4">
         <v>1.95</v>
       </c>
       <c r="R4">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="S4">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T4">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U4">
         <v>2.73</v>
@@ -991,34 +991,34 @@
         <v>1.08</v>
       </c>
       <c r="X4">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA4">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AB4">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AC4">
         <v>3.05</v>
       </c>
       <c r="AD4">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
         <v>1.95</v>
       </c>
       <c r="AG4">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AK4">
         <v>2.45</v>
@@ -1622,40 +1622,40 @@
         <v>1.52</v>
       </c>
       <c r="Q8">
-        <v>4.5</v>
+        <v>4.92</v>
       </c>
       <c r="R8">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="S8">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T8">
-        <v>3.75</v>
+        <v>3.58</v>
       </c>
       <c r="U8">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="V8">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W8">
+        <v>1.11</v>
+      </c>
+      <c r="X8">
+        <v>1.01</v>
+      </c>
+      <c r="Y8">
         <v>1.13</v>
       </c>
-      <c r="X8">
-        <v>1.03</v>
-      </c>
-      <c r="Y8">
-        <v>1.1</v>
-      </c>
       <c r="Z8">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AA8">
         <v>1.46</v>
       </c>
       <c r="AB8">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="AC8">
         <v>2.27</v>
@@ -1664,13 +1664,13 @@
         <v>1.56</v>
       </c>
       <c r="AE8">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AF8">
         <v>1.55</v>
       </c>
       <c r="AG8">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,7 +1683,7 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>2.24</v>
+        <v>1.14</v>
       </c>
       <c r="AK8">
         <v>1.17</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="O14">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P14">
         <v>2.75</v>
@@ -2603,13 +2603,13 @@
         <v>3</v>
       </c>
       <c r="R14">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="S14">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T14">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="U14">
         <v>2.7</v>
@@ -2627,13 +2627,13 @@
         <v>1.29</v>
       </c>
       <c r="Z14">
-        <v>3.3</v>
+        <v>3.51</v>
       </c>
       <c r="AA14">
         <v>1.89</v>
       </c>
       <c r="AB14">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC14">
         <v>3.08</v>
@@ -2642,10 +2642,10 @@
         <v>1.28</v>
       </c>
       <c r="AE14">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG14">
         <v>2.01</v>
@@ -2766,19 +2766,19 @@
         <v>2.2</v>
       </c>
       <c r="R15">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
         <v>1.2</v>
       </c>
       <c r="T15">
-        <v>4</v>
+        <v>3.76</v>
       </c>
       <c r="U15">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="V15">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="W15">
         <v>1.2</v>
@@ -2796,22 +2796,22 @@
         <v>1.4</v>
       </c>
       <c r="AB15">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AC15">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AD15">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE15">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AF15">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AG15">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -3261,31 +3261,31 @@
         <v>1.31</v>
       </c>
       <c r="T18">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="U18">
-        <v>2.63</v>
+        <v>2.47</v>
       </c>
       <c r="V18">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W18">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z18">
         <v>3.68</v>
       </c>
       <c r="AA18">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB18">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC18">
         <v>2.74</v>
@@ -3406,43 +3406,43 @@
         </is>
       </c>
       <c r="N19">
-        <v>9.449999999999999</v>
+        <v>9.65</v>
       </c>
       <c r="O19">
-        <v>5.95</v>
+        <v>6.21</v>
       </c>
       <c r="P19">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Q19">
         <v>7</v>
       </c>
       <c r="R19">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="S19">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="T19">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="U19">
         <v>1.85</v>
       </c>
       <c r="V19">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="W19">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X19">
         <v>1.01</v>
       </c>
       <c r="Y19">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Z19">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="AA19">
         <v>1.3</v>
@@ -3451,19 +3451,19 @@
         <v>3.1</v>
       </c>
       <c r="AC19">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD19">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AE19">
         <v>1.4</v>
       </c>
       <c r="AF19">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG19">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.12</v>
+        <v>3.7</v>
       </c>
       <c r="AK19">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="R23">
-        <v>2.23</v>
+        <v>2.18</v>
       </c>
       <c r="S23">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T23">
-        <v>2.97</v>
+        <v>3.3</v>
       </c>
       <c r="U23">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="V23">
         <v>1.44</v>
@@ -4088,34 +4088,34 @@
         <v>1.08</v>
       </c>
       <c r="X23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
         <v>1.19</v>
       </c>
       <c r="Z23">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="AA23">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB23">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="AC23">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD23">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE23">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF23">
         <v>1.69</v>
       </c>
       <c r="AG23">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK23">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,34 +4230,34 @@
         <v>5.4</v>
       </c>
       <c r="Q24">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R24">
-        <v>2.41</v>
+        <v>2.63</v>
       </c>
       <c r="S24">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U24">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V24">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="W24">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y24">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z24">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AA24">
         <v>1.47</v>
@@ -4266,19 +4266,19 @@
         <v>2.6</v>
       </c>
       <c r="AC24">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AD24">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="AE24">
         <v>1.21</v>
       </c>
       <c r="AF24">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="AG24">
-        <v>2.02</v>
+        <v>2.09</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AK24">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4393,19 +4393,19 @@
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R25">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
         <v>1.36</v>
       </c>
       <c r="T25">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U25">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="V25">
         <v>1.36</v>
@@ -4414,34 +4414,34 @@
         <v>1.04</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA25">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AB25">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC25">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD25">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE25">
         <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG25">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AK25">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G26">
@@ -4556,55 +4556,55 @@
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>2.53</v>
+        <v>2.8</v>
       </c>
       <c r="R26">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
         <v>2.5</v>
       </c>
       <c r="V26">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="AA26">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AB26">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AC26">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AD26">
         <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
         <v>1.6</v>
       </c>
       <c r="AG26">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK26">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q27">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R27">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="S27">
         <v>1.33</v>
       </c>
       <c r="T27">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="U27">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="V27">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z27">
-        <v>3.65</v>
+        <v>3.34</v>
       </c>
       <c r="AA27">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="AB27">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AC27">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="AD27">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>1.15</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG27">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK27">
         <v>1.49</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>2.87</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
+        <v>1.29</v>
+      </c>
+      <c r="T28">
+        <v>3.2</v>
+      </c>
+      <c r="U28">
+        <v>2.5</v>
+      </c>
+      <c r="V28">
+        <v>1.44</v>
+      </c>
+      <c r="W28">
+        <v>1.06</v>
+      </c>
+      <c r="X28">
+        <v>1.03</v>
+      </c>
+      <c r="Y28">
+        <v>1.18</v>
+      </c>
+      <c r="Z28">
+        <v>3.88</v>
+      </c>
+      <c r="AA28">
+        <v>1.75</v>
+      </c>
+      <c r="AB28">
+        <v>2.05</v>
+      </c>
+      <c r="AC28">
+        <v>2.74</v>
+      </c>
+      <c r="AD28">
         <v>1.35</v>
       </c>
-      <c r="T28">
-        <v>2.95</v>
-      </c>
-      <c r="U28">
-        <v>2.6</v>
-      </c>
-      <c r="V28">
-        <v>1.45</v>
-      </c>
-      <c r="W28">
-        <v>1.1</v>
-      </c>
-      <c r="X28">
-        <v>1.01</v>
-      </c>
-      <c r="Y28">
-        <v>1.26</v>
-      </c>
-      <c r="Z28">
-        <v>3.4</v>
-      </c>
-      <c r="AA28">
-        <v>1.85</v>
-      </c>
-      <c r="AB28">
-        <v>1.85</v>
-      </c>
-      <c r="AC28">
-        <v>3</v>
-      </c>
-      <c r="AD28">
-        <v>1.32</v>
-      </c>
       <c r="AE28">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF28">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="AG28">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AK28">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,13 +5036,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O29">
-        <v>3.61</v>
+        <v>3.75</v>
       </c>
       <c r="P29">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="AA29">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AB29">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AC29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="O30">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P30">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="Q30">
         <v>2.53</v>
@@ -5214,7 +5214,7 @@
         <v>1.98</v>
       </c>
       <c r="S30">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="T30">
         <v>2.5</v>
@@ -5238,7 +5238,7 @@
         <v>2.99</v>
       </c>
       <c r="AA30">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="AB30">
         <v>1.67</v>
@@ -5247,7 +5247,7 @@
         <v>3.58</v>
       </c>
       <c r="AD30">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AE30">
         <v>1.04</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AK30">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="O31">
         <v>3.68</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O32">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P32">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q32">
         <v>3.6</v>
@@ -5540,37 +5540,37 @@
         <v>2.2</v>
       </c>
       <c r="S32">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T32">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U32">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="V32">
         <v>1.4</v>
       </c>
       <c r="W32">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="X32">
         <v>1.05</v>
       </c>
       <c r="Y32">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z32">
         <v>3.4</v>
       </c>
       <c r="AA32">
+        <v>1.9</v>
+      </c>
+      <c r="AB32">
         <v>1.88</v>
       </c>
-      <c r="AB32">
-        <v>1.85</v>
-      </c>
       <c r="AC32">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD32">
         <v>1.3</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="AJ32">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="AK32">
         <v>1.3</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="O33">
-        <v>3.41</v>
+        <v>3.7</v>
       </c>
       <c r="P33">
-        <v>3.35</v>
+        <v>3.76</v>
       </c>
       <c r="Q33">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="O34">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="P34">
-        <v>3.35</v>
+        <v>3.67</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AB34">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -6017,7 +6017,7 @@
         <v>2.72</v>
       </c>
       <c r="O35">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P35">
         <v>2.15</v>
@@ -6029,10 +6029,10 @@
         <v>2.45</v>
       </c>
       <c r="S35">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T35">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="U35">
         <v>2.27</v>
@@ -6041,7 +6041,7 @@
         <v>1.6</v>
       </c>
       <c r="W35">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X35">
         <v>1.02</v>
@@ -6056,22 +6056,22 @@
         <v>1.55</v>
       </c>
       <c r="AB35">
+        <v>2.33</v>
+      </c>
+      <c r="AC35">
         <v>2.35</v>
       </c>
-      <c r="AC35">
-        <v>2.33</v>
-      </c>
       <c r="AD35">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="AE35">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AF35">
         <v>1.44</v>
       </c>
       <c r="AG35">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="AK35">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6192,28 +6192,28 @@
         <v>2.3</v>
       </c>
       <c r="S36">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T36">
-        <v>2.78</v>
+        <v>3.25</v>
       </c>
       <c r="U36">
         <v>2.5</v>
       </c>
       <c r="V36">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W36">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X36">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y36">
         <v>1.16</v>
       </c>
       <c r="Z36">
-        <v>4.1</v>
+        <v>4.32</v>
       </c>
       <c r="AA36">
         <v>1.66</v>
@@ -6222,10 +6222,10 @@
         <v>2.15</v>
       </c>
       <c r="AC36">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AD36">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="AE36">
         <v>1.14</v>
@@ -6250,7 +6250,7 @@
         <v>1.67</v>
       </c>
       <c r="AK36">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O37">
         <v>3.3</v>
       </c>
       <c r="P37">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q37">
         <v>2.37</v>
@@ -6355,13 +6355,13 @@
         <v>2.15</v>
       </c>
       <c r="S37">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T37">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="U37">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="V37">
         <v>1.38</v>
@@ -6370,13 +6370,13 @@
         <v>1.04</v>
       </c>
       <c r="X37">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y37">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z37">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AA37">
         <v>1.88</v>
@@ -6391,13 +6391,13 @@
         <v>1.28</v>
       </c>
       <c r="AE37">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF37">
         <v>1.75</v>
       </c>
       <c r="AG37">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
@@ -6413,7 +6413,7 @@
         <v>1.22</v>
       </c>
       <c r="AK37">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6829,34 +6829,34 @@
         </is>
       </c>
       <c r="N40">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="O40">
-        <v>3.48</v>
+        <v>3.25</v>
       </c>
       <c r="P40">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="Q40">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="R40">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S40">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T40">
         <v>2.7</v>
       </c>
       <c r="U40">
-        <v>2.81</v>
+        <v>2.85</v>
       </c>
       <c r="V40">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W40">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X40">
         <v>1.03</v>
@@ -6865,19 +6865,19 @@
         <v>1.25</v>
       </c>
       <c r="Z40">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA40">
         <v>1.95</v>
       </c>
       <c r="AB40">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AC40">
         <v>3.45</v>
       </c>
       <c r="AD40">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE40">
         <v>1.12</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AK40">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7170,37 +7170,37 @@
         <v>2.4</v>
       </c>
       <c r="S42">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T42">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U42">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="V42">
         <v>1.67</v>
       </c>
       <c r="W42">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X42">
         <v>1.02</v>
       </c>
       <c r="Y42">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z42">
-        <v>5.39</v>
+        <v>5.44</v>
       </c>
       <c r="AA42">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB42">
         <v>2.38</v>
       </c>
       <c r="AC42">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AD42">
         <v>1.65</v>
@@ -7209,10 +7209,10 @@
         <v>1.25</v>
       </c>
       <c r="AF42">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AG42">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7225,10 +7225,10 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.18</v>
+        <v>1.63</v>
       </c>
       <c r="AK42">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7327,13 +7327,13 @@
         <v>1.98</v>
       </c>
       <c r="Q43">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="R43">
         <v>2.3</v>
       </c>
       <c r="S43">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T43">
         <v>3.3</v>
@@ -7345,10 +7345,10 @@
         <v>1.52</v>
       </c>
       <c r="W43">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X43">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y43">
         <v>1.2</v>
@@ -7369,13 +7369,13 @@
         <v>1.41</v>
       </c>
       <c r="AE43">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF43">
         <v>1.57</v>
       </c>
       <c r="AG43">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AK43">
         <v>1.2</v>
@@ -7481,43 +7481,43 @@
         </is>
       </c>
       <c r="N44">
+        <v>3.35</v>
+      </c>
+      <c r="O44">
         <v>3.2</v>
-      </c>
-      <c r="O44">
-        <v>3.1</v>
       </c>
       <c r="P44">
         <v>1.98</v>
       </c>
       <c r="Q44">
-        <v>4.24</v>
+        <v>4.15</v>
       </c>
       <c r="R44">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="S44">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="T44">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="U44">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V44">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X44">
         <v>1.06</v>
       </c>
       <c r="Y44">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="Z44">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="AA44">
         <v>2.2</v>
@@ -7532,7 +7532,7 @@
         <v>1.22</v>
       </c>
       <c r="AE44">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AF44">
         <v>1.85</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AK44">
         <v>1.28</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="O45">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P45">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="O46">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="P46">
-        <v>3.76</v>
+        <v>3.65</v>
       </c>
       <c r="Q46">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R46">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="S46">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T46">
         <v>3.9</v>
       </c>
       <c r="U46">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="V46">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="W46">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X46">
         <v>1.01</v>
       </c>
       <c r="Y46">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z46">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AA46">
-        <v>1.47</v>
+        <v>1.37</v>
       </c>
       <c r="AB46">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="AC46">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AD46">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AE46">
         <v>1.25</v>
       </c>
       <c r="AF46">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG46">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK46">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -8133,16 +8133,16 @@
         </is>
       </c>
       <c r="N48">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O48">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P48">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q48">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="R48">
         <v>2</v>
@@ -8154,7 +8154,7 @@
         <v>2.65</v>
       </c>
       <c r="U48">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="V48">
         <v>1.34</v>
@@ -8166,7 +8166,7 @@
         <v>1.03</v>
       </c>
       <c r="Y48">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z48">
         <v>2.8</v>
@@ -8203,7 +8203,7 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AK48">
         <v>1.32</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O49">
-        <v>3.39</v>
+        <v>3.3</v>
       </c>
       <c r="P49">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
+        <v>2.5</v>
+      </c>
+      <c r="O50">
+        <v>3.45</v>
+      </c>
+      <c r="P50">
         <v>2.6</v>
       </c>
-      <c r="O50">
-        <v>3.1</v>
-      </c>
-      <c r="P50">
-        <v>2.45</v>
-      </c>
       <c r="Q50">
-        <v>3.25</v>
+        <v>3.31</v>
       </c>
       <c r="R50">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="S50">
         <v>1.38</v>
@@ -8501,16 +8501,16 @@
         <v>2.05</v>
       </c>
       <c r="AB50">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC50">
         <v>3.25</v>
       </c>
       <c r="AD50">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE50">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF50">
         <v>1.8</v>
@@ -8532,7 +8532,7 @@
         <v>1.3</v>
       </c>
       <c r="AK50">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,31 +8622,31 @@
         </is>
       </c>
       <c r="N51">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="O51">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="P51">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="Q51">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="R51">
         <v>2.05</v>
       </c>
       <c r="S51">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T51">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U51">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V51">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="W51">
         <v>1.04</v>
@@ -8658,13 +8658,13 @@
         <v>1.33</v>
       </c>
       <c r="Z51">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="AA51">
         <v>2.18</v>
       </c>
       <c r="AB51">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC51">
         <v>3.9</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AK51">
         <v>1.36</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O52">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P52">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="Q52">
         <v>2.95</v>
@@ -8800,25 +8800,25 @@
         <v>2.08</v>
       </c>
       <c r="S52">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T52">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="U52">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V52">
         <v>1.42</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X52">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y52">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z52">
         <v>3.5</v>
@@ -8830,10 +8830,10 @@
         <v>1.85</v>
       </c>
       <c r="AC52">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="AD52">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE52">
         <v>1.08</v>
@@ -8842,7 +8842,7 @@
         <v>1.61</v>
       </c>
       <c r="AG52">
-        <v>1.97</v>
+        <v>2.18</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -9277,10 +9277,10 @@
         <v>2.2</v>
       </c>
       <c r="O55">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P55">
-        <v>2.85</v>
+        <v>2.69</v>
       </c>
       <c r="Q55">
         <v>2.8</v>
@@ -9292,13 +9292,13 @@
         <v>1.29</v>
       </c>
       <c r="T55">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="U55">
         <v>2.5</v>
       </c>
       <c r="V55">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W55">
         <v>1.11</v>
@@ -9307,16 +9307,16 @@
         <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="Z55">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="AA55">
         <v>1.75</v>
       </c>
       <c r="AB55">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="AC55">
         <v>2.9</v>
@@ -9328,7 +9328,7 @@
         <v>1.14</v>
       </c>
       <c r="AF55">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG55">
         <v>2.19</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AK55">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9624,16 +9624,16 @@
         <v>2.2</v>
       </c>
       <c r="V57">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W57">
         <v>1.14</v>
       </c>
       <c r="X57">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y57">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z57">
         <v>5</v>
@@ -9642,7 +9642,7 @@
         <v>1.5</v>
       </c>
       <c r="AB57">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="AC57">
         <v>2.24</v>
@@ -9651,7 +9651,7 @@
         <v>1.63</v>
       </c>
       <c r="AE57">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF57">
         <v>1.54</v>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.85</v>
+        <v>1.18</v>
       </c>
       <c r="AK57">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="O58">
         <v>3.5</v>
@@ -9772,7 +9772,7 @@
         <v>2.8</v>
       </c>
       <c r="Q58">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="R58">
         <v>2.43</v>
@@ -9787,7 +9787,7 @@
         <v>2.29</v>
       </c>
       <c r="V58">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="W58">
         <v>1.11</v>
@@ -9796,7 +9796,7 @@
         <v>1.03</v>
       </c>
       <c r="Y58">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="Z58">
         <v>4.65</v>
@@ -9808,7 +9808,7 @@
         <v>2.35</v>
       </c>
       <c r="AC58">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AD58">
         <v>1.55</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AK58">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9926,55 +9926,55 @@
         </is>
       </c>
       <c r="N59">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="O59">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="P59">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="Q59">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R59">
         <v>2.37</v>
       </c>
       <c r="S59">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T59">
         <v>3.3</v>
       </c>
       <c r="U59">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="V59">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W59">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X59">
         <v>1.04</v>
       </c>
       <c r="Y59">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z59">
         <v>4.15</v>
       </c>
       <c r="AA59">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB59">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC59">
         <v>2.69</v>
       </c>
       <c r="AD59">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE59">
         <v>1.14</v>
@@ -9983,7 +9983,7 @@
         <v>1.59</v>
       </c>
       <c r="AG59">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10092,10 +10092,10 @@
         <v>2.2</v>
       </c>
       <c r="O60">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P60">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="Q60">
         <v>2.5</v>
@@ -10107,40 +10107,40 @@
         <v>1.2</v>
       </c>
       <c r="T60">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="U60">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="V60">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="W60">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X60">
         <v>1.02</v>
       </c>
       <c r="Y60">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="Z60">
-        <v>5.65</v>
+        <v>5.69</v>
       </c>
       <c r="AA60">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB60">
         <v>2.7</v>
       </c>
       <c r="AC60">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AD60">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AE60">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF60">
         <v>1.36</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.29</v>
+        <v>1.45</v>
       </c>
       <c r="AK60">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="O61">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P61">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q61">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="R61">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T61">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="U61">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="V61">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="W61">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y61">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="Z61">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AA61">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AB61">
-        <v>2.49</v>
+        <v>2.08</v>
       </c>
       <c r="AC61">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AD61">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AE61">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AF61">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AG61">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK61">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,64 +10415,64 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.57</v>
+        <v>1.98</v>
       </c>
       <c r="O62">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="P62">
-        <v>2.54</v>
+        <v>3.35</v>
       </c>
       <c r="Q62">
-        <v>2.9</v>
+        <v>2.45</v>
       </c>
       <c r="R62">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="S62">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="T62">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="U62">
-        <v>2.43</v>
+        <v>2.15</v>
       </c>
       <c r="V62">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="W62">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X62">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="Z62">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="AA62">
-        <v>1.7</v>
+        <v>1.45</v>
       </c>
       <c r="AB62">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="AC62">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AD62">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE62">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="AF62">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AG62">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK62">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10587,7 +10587,7 @@
         <v>4.8</v>
       </c>
       <c r="Q63">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R63">
         <v>2.4</v>
@@ -10614,19 +10614,19 @@
         <v>1.18</v>
       </c>
       <c r="Z63">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA63">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AB63">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="AC63">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
       <c r="AD63">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE63">
         <v>1.13</v>
@@ -10635,7 +10635,7 @@
         <v>1.7</v>
       </c>
       <c r="AG63">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AK63">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="O65">
         <v>3.6</v>
@@ -10913,7 +10913,7 @@
         <v>5</v>
       </c>
       <c r="Q65">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="R65">
         <v>2.14</v>
@@ -10934,28 +10934,28 @@
         <v>1.07</v>
       </c>
       <c r="X65">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y65">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z65">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="AA65">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AB65">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC65">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="AD65">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE65">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF65">
         <v>2.05</v>
@@ -11070,16 +11070,16 @@
         <v>2.55</v>
       </c>
       <c r="O66">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="P66">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="Q66">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="R66">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S66">
         <v>1.4</v>
@@ -11097,7 +11097,7 @@
         <v>1.05</v>
       </c>
       <c r="X66">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
         <v>1.28</v>
@@ -11109,22 +11109,22 @@
         <v>2.16</v>
       </c>
       <c r="AB66">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC66">
-        <v>3.38</v>
+        <v>3.85</v>
       </c>
       <c r="AD66">
         <v>1.26</v>
       </c>
       <c r="AE66">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF66">
         <v>1.8</v>
       </c>
       <c r="AG66">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>1.33</v>
       </c>
       <c r="AK66">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="O67">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P67">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="Q67">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="R67">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S67">
+        <v>1.33</v>
+      </c>
+      <c r="T67">
+        <v>3.18</v>
+      </c>
+      <c r="U67">
+        <v>2.56</v>
+      </c>
+      <c r="V67">
+        <v>1.42</v>
+      </c>
+      <c r="W67">
+        <v>1.11</v>
+      </c>
+      <c r="X67">
+        <v>1.04</v>
+      </c>
+      <c r="Y67">
+        <v>1.24</v>
+      </c>
+      <c r="Z67">
+        <v>3.79</v>
+      </c>
+      <c r="AA67">
+        <v>1.8</v>
+      </c>
+      <c r="AB67">
+        <v>1.93</v>
+      </c>
+      <c r="AC67">
+        <v>3.1</v>
+      </c>
+      <c r="AD67">
         <v>1.36</v>
       </c>
-      <c r="T67">
-        <v>2.88</v>
-      </c>
-      <c r="U67">
-        <v>2.78</v>
-      </c>
-      <c r="V67">
-        <v>1.36</v>
-      </c>
-      <c r="W67">
-        <v>1.06</v>
-      </c>
-      <c r="X67">
-        <v>1.01</v>
-      </c>
-      <c r="Y67">
-        <v>1.25</v>
-      </c>
-      <c r="Z67">
-        <v>3.28</v>
-      </c>
-      <c r="AA67">
-        <v>1.92</v>
-      </c>
-      <c r="AB67">
-        <v>1.79</v>
-      </c>
-      <c r="AC67">
-        <v>3.28</v>
-      </c>
-      <c r="AD67">
-        <v>1.25</v>
-      </c>
       <c r="AE67">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF67">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG67">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>1.26</v>
+        <v>1.46</v>
       </c>
       <c r="AK67">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11405,40 +11405,40 @@
         <v>7.2</v>
       </c>
       <c r="R68">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S68">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T68">
         <v>3.2</v>
       </c>
       <c r="U68">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="V68">
         <v>1.47</v>
       </c>
       <c r="W68">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z68">
         <v>3.88</v>
       </c>
       <c r="AA68">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AB68">
         <v>2.1</v>
       </c>
       <c r="AC68">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD68">
         <v>1.4</v>
@@ -11447,10 +11447,10 @@
         <v>1.15</v>
       </c>
       <c r="AF68">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG68">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>2.75</v>
+        <v>1.16</v>
       </c>
       <c r="AK68">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O69">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="P69">
         <v>2.44</v>
       </c>
       <c r="Q69">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R69">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="S69">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="T69">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="U69">
-        <v>2.59</v>
+        <v>2.74</v>
       </c>
       <c r="V69">
         <v>1.44</v>
       </c>
       <c r="W69">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X69">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y69">
         <v>1.25</v>
       </c>
       <c r="Z69">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AA69">
         <v>1.78</v>
       </c>
       <c r="AB69">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AC69">
-        <v>3.13</v>
+        <v>2.92</v>
       </c>
       <c r="AD69">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE69">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AF69">
         <v>1.61</v>
       </c>
       <c r="AG69">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK69">
         <v>1.44</v>
@@ -11882,7 +11882,7 @@
         </is>
       </c>
       <c r="N71">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="O71">
         <v>3.3</v>
@@ -11894,25 +11894,25 @@
         <v>3</v>
       </c>
       <c r="R71">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="S71">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="T71">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="U71">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="V71">
         <v>1.46</v>
       </c>
       <c r="W71">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y71">
         <v>1.25</v>
@@ -11927,13 +11927,13 @@
         <v>1.95</v>
       </c>
       <c r="AC71">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="AD71">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE71">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF71">
         <v>1.57</v>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK71">
         <v>1.53</v>
@@ -12045,65 +12045,65 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.07</v>
+        <v>1.99</v>
       </c>
       <c r="O72">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P72">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q72">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="R72">
+        <v>2.18</v>
+      </c>
+      <c r="S72">
+        <v>1.3</v>
+      </c>
+      <c r="T72">
+        <v>3.1</v>
+      </c>
+      <c r="U72">
+        <v>2.6</v>
+      </c>
+      <c r="V72">
+        <v>1.45</v>
+      </c>
+      <c r="W72">
+        <v>1.07</v>
+      </c>
+      <c r="X72">
+        <v>1.05</v>
+      </c>
+      <c r="Y72">
+        <v>1.22</v>
+      </c>
+      <c r="Z72">
+        <v>3.58</v>
+      </c>
+      <c r="AA72">
+        <v>1.77</v>
+      </c>
+      <c r="AB72">
+        <v>2</v>
+      </c>
+      <c r="AC72">
+        <v>3</v>
+      </c>
+      <c r="AD72">
+        <v>1.35</v>
+      </c>
+      <c r="AE72">
+        <v>1.14</v>
+      </c>
+      <c r="AF72">
+        <v>1.65</v>
+      </c>
+      <c r="AG72">
         <v>2.1</v>
       </c>
-      <c r="S72">
-        <v>1.38</v>
-      </c>
-      <c r="T72">
-        <v>2.77</v>
-      </c>
-      <c r="U72">
-        <v>2.7</v>
-      </c>
-      <c r="V72">
-        <v>1.4</v>
-      </c>
-      <c r="W72">
-        <v>1.05</v>
-      </c>
-      <c r="X72">
-        <v>1.01</v>
-      </c>
-      <c r="Y72">
-        <v>1.26</v>
-      </c>
-      <c r="Z72">
-        <v>3.2</v>
-      </c>
-      <c r="AA72">
-        <v>1.93</v>
-      </c>
-      <c r="AB72">
-        <v>1.83</v>
-      </c>
-      <c r="AC72">
-        <v>3.14</v>
-      </c>
-      <c r="AD72">
-        <v>1.27</v>
-      </c>
-      <c r="AE72">
-        <v>1.07</v>
-      </c>
-      <c r="AF72">
-        <v>1.74</v>
-      </c>
-      <c r="AG72">
-        <v>1.98</v>
-      </c>
       <c r="AH72" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AK72">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12374,7 +12374,7 @@
         <v>3.25</v>
       </c>
       <c r="O74">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P74">
         <v>1.93</v>
@@ -12386,22 +12386,22 @@
         <v>2.2</v>
       </c>
       <c r="S74">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="T74">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="U74">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V74">
         <v>1.4</v>
       </c>
       <c r="W74">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X74">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y74">
         <v>1.25</v>
@@ -12413,7 +12413,7 @@
         <v>1.8</v>
       </c>
       <c r="AB74">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AC74">
         <v>2.92</v>
@@ -12444,7 +12444,7 @@
         <v>1.73</v>
       </c>
       <c r="AK74">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12540,7 +12540,7 @@
         <v>3.8</v>
       </c>
       <c r="P75">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="Q75">
         <v>2.43</v>
@@ -12552,40 +12552,40 @@
         <v>1.29</v>
       </c>
       <c r="T75">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U75">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="V75">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W75">
         <v>1.1</v>
       </c>
       <c r="X75">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y75">
         <v>1.23</v>
       </c>
       <c r="Z75">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="AA75">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB75">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC75">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="AD75">
         <v>1.38</v>
       </c>
       <c r="AE75">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF75">
         <v>1.67</v>
@@ -12607,7 +12607,7 @@
         <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="O76">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="P76">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q76">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="R76">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S76">
         <v>1.25</v>
       </c>
       <c r="T76">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U76">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="V76">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W76">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X76">
         <v>1.01</v>
       </c>
       <c r="Y76">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z76">
         <v>5</v>
       </c>
       <c r="AA76">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AB76">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AC76">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="AD76">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE76">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF76">
         <v>1.53</v>
       </c>
       <c r="AG76">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK76">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -14173,55 +14173,55 @@
         <v>2.11</v>
       </c>
       <c r="Q85">
-        <v>4.22</v>
+        <v>4.17</v>
       </c>
       <c r="R85">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S85">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T85">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U85">
-        <v>2.92</v>
+        <v>3.2</v>
       </c>
       <c r="V85">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W85">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X85">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y85">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z85">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="AA85">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="AB85">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AC85">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AD85">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE85">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF85">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AG85">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK85">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14342,19 +14342,19 @@
         <v>2.8</v>
       </c>
       <c r="S86">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T86">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U86">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="V86">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W86">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X86">
         <v>1.03</v>
@@ -14363,13 +14363,13 @@
         <v>1.13</v>
       </c>
       <c r="Z86">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA86">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AB86">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="AC86">
         <v>2.31</v>
@@ -14381,10 +14381,10 @@
         <v>1.2</v>
       </c>
       <c r="AF86">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AG86">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14400,7 +14400,7 @@
         <v>1.09</v>
       </c>
       <c r="AK86">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14816,7 +14816,7 @@
         </is>
       </c>
       <c r="N89">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="O89">
         <v>3.2</v>
@@ -14834,16 +14834,16 @@
         <v>1.36</v>
       </c>
       <c r="T89">
-        <v>2.93</v>
+        <v>2.65</v>
       </c>
       <c r="U89">
-        <v>2.93</v>
+        <v>2.63</v>
       </c>
       <c r="V89">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W89">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X89">
         <v>1.06</v>
@@ -14852,16 +14852,16 @@
         <v>1.23</v>
       </c>
       <c r="Z89">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="AA89">
         <v>1.85</v>
       </c>
       <c r="AB89">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC89">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AD89">
         <v>1.24</v>
@@ -14870,10 +14870,10 @@
         <v>1.08</v>
       </c>
       <c r="AF89">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AG89">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK89">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15000,16 +15000,16 @@
         <v>2.88</v>
       </c>
       <c r="U90">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="V90">
         <v>1.39</v>
       </c>
       <c r="W90">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X90">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y90">
         <v>1.33</v>
@@ -15018,22 +15018,22 @@
         <v>3.25</v>
       </c>
       <c r="AA90">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AB90">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AC90">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD90">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AE90">
         <v>1.1</v>
       </c>
       <c r="AF90">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AG90">
         <v>1.95</v>
@@ -15049,7 +15049,7 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AK90">
         <v>1.73</v>
@@ -15151,13 +15151,13 @@
         <v>3.4</v>
       </c>
       <c r="Q91">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R91">
         <v>2</v>
       </c>
       <c r="S91">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T91">
         <v>2.5</v>
@@ -15169,7 +15169,7 @@
         <v>1.32</v>
       </c>
       <c r="W91">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X91">
         <v>1.03</v>
@@ -15212,7 +15212,7 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK91">
         <v>1.58</v>
@@ -15631,10 +15631,10 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O94">
-        <v>2.87</v>
+        <v>2.8</v>
       </c>
       <c r="P94">
         <v>2.95</v>
@@ -15646,10 +15646,10 @@
         <v>1.83</v>
       </c>
       <c r="S94">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="T94">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="U94">
         <v>3.2</v>
@@ -15676,7 +15676,7 @@
         <v>1.57</v>
       </c>
       <c r="AC94">
-        <v>3.95</v>
+        <v>3.98</v>
       </c>
       <c r="AD94">
         <v>1.17</v>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK94">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15960,16 +15960,16 @@
         <v>1.82</v>
       </c>
       <c r="O96">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P96">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="Q96">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="R96">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S96">
         <v>1.41</v>
@@ -15978,43 +15978,43 @@
         <v>2.66</v>
       </c>
       <c r="U96">
-        <v>2.99</v>
+        <v>2.86</v>
       </c>
       <c r="V96">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W96">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X96">
         <v>1.06</v>
       </c>
       <c r="Y96">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z96">
         <v>3</v>
       </c>
       <c r="AA96">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB96">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC96">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD96">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE96">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF96">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG96">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK96">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -17424,31 +17424,31 @@
         </is>
       </c>
       <c r="N105">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="O105">
-        <v>3.64</v>
+        <v>3.7</v>
       </c>
       <c r="P105">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q105">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="R105">
         <v>2.3</v>
       </c>
       <c r="S105">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T105">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="U105">
         <v>2.1</v>
       </c>
       <c r="V105">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="W105">
         <v>1.18</v>
@@ -17457,25 +17457,25 @@
         <v>1.03</v>
       </c>
       <c r="Y105">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="Z105">
-        <v>5.36</v>
+        <v>5</v>
       </c>
       <c r="AA105">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="AB105">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AC105">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AD105">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE105">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF105">
         <v>1.44</v>
@@ -17494,7 +17494,7 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK105">
         <v>1.4</v>
@@ -19054,10 +19054,10 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="O115">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P115">
         <v>3.8</v>
@@ -19078,10 +19078,10 @@
         <v>2.75</v>
       </c>
       <c r="V115">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W115">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X115">
         <v>1.01</v>
@@ -19093,13 +19093,13 @@
         <v>3.2</v>
       </c>
       <c r="AA115">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AB115">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC115">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="AD115">
         <v>1.22</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q28">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T28">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U28">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="W28">
         <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y28">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="Z28">
-        <v>3.88</v>
+        <v>3.34</v>
       </c>
       <c r="AA28">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AB28">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC28">
-        <v>2.74</v>
+        <v>2.97</v>
       </c>
       <c r="AD28">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE28">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF28">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AG28">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AK28">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="P29">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q29">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R29">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T29">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U29">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V29">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
         <v>1.06</v>
       </c>
       <c r="X29">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z29">
-        <v>3.34</v>
+        <v>3.88</v>
       </c>
       <c r="AA29">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AB29">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AC29">
-        <v>2.97</v>
+        <v>2.74</v>
       </c>
       <c r="AD29">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AE29">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF29">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AG29">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AK29">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,65 +9111,65 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="O54">
-        <v>3.32</v>
+        <v>3.03</v>
       </c>
       <c r="P54">
-        <v>2.76</v>
+        <v>2.37</v>
       </c>
       <c r="Q54">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="R54">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="S54">
+        <v>1.4</v>
+      </c>
+      <c r="T54">
+        <v>2.7</v>
+      </c>
+      <c r="U54">
+        <v>2.94</v>
+      </c>
+      <c r="V54">
         <v>1.35</v>
       </c>
-      <c r="T54">
-        <v>3</v>
-      </c>
-      <c r="U54">
-        <v>2.62</v>
-      </c>
-      <c r="V54">
-        <v>1.42</v>
-      </c>
       <c r="W54">
+        <v>1.04</v>
+      </c>
+      <c r="X54">
+        <v>1.02</v>
+      </c>
+      <c r="Y54">
+        <v>1.33</v>
+      </c>
+      <c r="Z54">
+        <v>3.02</v>
+      </c>
+      <c r="AA54">
+        <v>2.18</v>
+      </c>
+      <c r="AB54">
+        <v>1.67</v>
+      </c>
+      <c r="AC54">
+        <v>3.9</v>
+      </c>
+      <c r="AD54">
+        <v>1.22</v>
+      </c>
+      <c r="AE54">
         <v>1.05</v>
       </c>
-      <c r="X54">
-        <v>1.05</v>
-      </c>
-      <c r="Y54">
-        <v>1.29</v>
-      </c>
-      <c r="Z54">
-        <v>3.5</v>
-      </c>
-      <c r="AA54">
+      <c r="AF54">
         <v>1.85</v>
       </c>
-      <c r="AB54">
+      <c r="AG54">
         <v>1.85</v>
       </c>
-      <c r="AC54">
-        <v>3.25</v>
-      </c>
-      <c r="AD54">
-        <v>1.33</v>
-      </c>
-      <c r="AE54">
-        <v>1.08</v>
-      </c>
-      <c r="AF54">
-        <v>1.61</v>
-      </c>
-      <c r="AG54">
-        <v>2.18</v>
-      </c>
       <c r="AH54" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="AK54">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,80 +9274,80 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="O55">
-        <v>3.03</v>
+        <v>3.32</v>
       </c>
       <c r="P55">
-        <v>2.37</v>
+        <v>2.76</v>
       </c>
       <c r="Q55">
+        <v>2.95</v>
+      </c>
+      <c r="R55">
+        <v>2.08</v>
+      </c>
+      <c r="S55">
+        <v>1.35</v>
+      </c>
+      <c r="T55">
+        <v>3</v>
+      </c>
+      <c r="U55">
+        <v>2.62</v>
+      </c>
+      <c r="V55">
+        <v>1.42</v>
+      </c>
+      <c r="W55">
+        <v>1.05</v>
+      </c>
+      <c r="X55">
+        <v>1.05</v>
+      </c>
+      <c r="Y55">
+        <v>1.29</v>
+      </c>
+      <c r="Z55">
         <v>3.5</v>
       </c>
-      <c r="R55">
-        <v>2.05</v>
-      </c>
-      <c r="S55">
+      <c r="AA55">
+        <v>1.85</v>
+      </c>
+      <c r="AB55">
+        <v>1.85</v>
+      </c>
+      <c r="AC55">
+        <v>3.25</v>
+      </c>
+      <c r="AD55">
+        <v>1.33</v>
+      </c>
+      <c r="AE55">
+        <v>1.08</v>
+      </c>
+      <c r="AF55">
+        <v>1.61</v>
+      </c>
+      <c r="AG55">
+        <v>2.18</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ55">
         <v>1.4</v>
       </c>
-      <c r="T55">
-        <v>2.7</v>
-      </c>
-      <c r="U55">
-        <v>2.94</v>
-      </c>
-      <c r="V55">
-        <v>1.35</v>
-      </c>
-      <c r="W55">
-        <v>1.04</v>
-      </c>
-      <c r="X55">
-        <v>1.02</v>
-      </c>
-      <c r="Y55">
-        <v>1.33</v>
-      </c>
-      <c r="Z55">
-        <v>3.02</v>
-      </c>
-      <c r="AA55">
-        <v>2.18</v>
-      </c>
-      <c r="AB55">
-        <v>1.67</v>
-      </c>
-      <c r="AC55">
-        <v>3.9</v>
-      </c>
-      <c r="AD55">
-        <v>1.22</v>
-      </c>
-      <c r="AE55">
-        <v>1.05</v>
-      </c>
-      <c r="AF55">
-        <v>1.85</v>
-      </c>
-      <c r="AG55">
-        <v>1.85</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ55">
-        <v>1.53</v>
-      </c>
       <c r="AK55">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,64 +10741,64 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.44</v>
+        <v>1.98</v>
       </c>
       <c r="O64">
+        <v>3.7</v>
+      </c>
+      <c r="P64">
         <v>3.35</v>
       </c>
-      <c r="P64">
-        <v>2.4</v>
-      </c>
       <c r="Q64">
-        <v>2.81</v>
+        <v>2.45</v>
       </c>
       <c r="R64">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="S64">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="T64">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="U64">
-        <v>2.53</v>
+        <v>2.15</v>
       </c>
       <c r="V64">
+        <v>1.62</v>
+      </c>
+      <c r="W64">
+        <v>1.13</v>
+      </c>
+      <c r="X64">
+        <v>1.03</v>
+      </c>
+      <c r="Y64">
+        <v>1.15</v>
+      </c>
+      <c r="Z64">
+        <v>5.25</v>
+      </c>
+      <c r="AA64">
         <v>1.45</v>
       </c>
-      <c r="W64">
-        <v>1.08</v>
-      </c>
-      <c r="X64">
-        <v>1</v>
-      </c>
-      <c r="Y64">
-        <v>1.22</v>
-      </c>
-      <c r="Z64">
-        <v>4</v>
-      </c>
-      <c r="AA64">
-        <v>1.7</v>
-      </c>
       <c r="AB64">
-        <v>2.08</v>
+        <v>2.41</v>
       </c>
       <c r="AC64">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="AD64">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AE64">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AF64">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AG64">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="AH64" t="inlineStr">
         <is>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AK64">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,64 +10904,64 @@
         </is>
       </c>
       <c r="N65">
-        <v>1.98</v>
+        <v>2.44</v>
       </c>
       <c r="O65">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="P65">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="Q65">
-        <v>2.45</v>
+        <v>2.81</v>
       </c>
       <c r="R65">
-        <v>2.52</v>
+        <v>2.33</v>
       </c>
       <c r="S65">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="T65">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="U65">
-        <v>2.15</v>
+        <v>2.53</v>
       </c>
       <c r="V65">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="W65">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X65">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y65">
+        <v>1.22</v>
+      </c>
+      <c r="Z65">
+        <v>4</v>
+      </c>
+      <c r="AA65">
+        <v>1.7</v>
+      </c>
+      <c r="AB65">
+        <v>2.08</v>
+      </c>
+      <c r="AC65">
+        <v>2.75</v>
+      </c>
+      <c r="AD65">
+        <v>1.4</v>
+      </c>
+      <c r="AE65">
         <v>1.15</v>
       </c>
-      <c r="Z65">
-        <v>5.25</v>
-      </c>
-      <c r="AA65">
-        <v>1.45</v>
-      </c>
-      <c r="AB65">
-        <v>2.41</v>
-      </c>
-      <c r="AC65">
-        <v>2.18</v>
-      </c>
-      <c r="AD65">
-        <v>1.6</v>
-      </c>
-      <c r="AE65">
-        <v>1.21</v>
-      </c>
       <c r="AF65">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AG65">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK65">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -12278,7 +12278,7 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK73">
         <v>1.32</v>
@@ -16775,7 +16775,7 @@
         <v>1.92</v>
       </c>
       <c r="O101">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P101">
         <v>4.45</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -8495,7 +8495,7 @@
         <v>1.57</v>
       </c>
       <c r="Z50">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="AA50">
         <v>2.7</v>
@@ -12208,7 +12208,7 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="O73">
         <v>2.7</v>
@@ -12262,10 +12262,10 @@
         <v>1.03</v>
       </c>
       <c r="AF73">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AG73">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK73">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL73">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -1613,7 +1613,7 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O8">
         <v>2.8</v>
@@ -1637,19 +1637,19 @@
         <v>3.34</v>
       </c>
       <c r="V8">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W8">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
         <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="Z8">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="AA8">
         <v>2.41</v>
@@ -1664,13 +1664,13 @@
         <v>1.14</v>
       </c>
       <c r="AE8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
         <v>2.05</v>
       </c>
       <c r="AG8">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O9">
         <v>4.3</v>
       </c>
       <c r="P9">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="Q9">
         <v>4.92</v>
@@ -1797,10 +1797,10 @@
         <v>3.58</v>
       </c>
       <c r="U9">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="V9">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="W9">
         <v>1.11</v>
@@ -1809,10 +1809,10 @@
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z9">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AA9">
         <v>1.46</v>
@@ -1849,7 +1849,7 @@
         <v>1.14</v>
       </c>
       <c r="AK9">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2766,13 +2766,13 @@
         <v>3</v>
       </c>
       <c r="R15">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="S15">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T15">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="U15">
         <v>2.7</v>
@@ -2781,7 +2781,7 @@
         <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X15">
         <v>1.02</v>
@@ -2811,7 +2811,7 @@
         <v>1.7</v>
       </c>
       <c r="AG15">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2935,13 +2935,13 @@
         <v>1.2</v>
       </c>
       <c r="T16">
-        <v>3.76</v>
+        <v>4</v>
       </c>
       <c r="U16">
         <v>2.05</v>
       </c>
       <c r="V16">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="W16">
         <v>1.2</v>
@@ -2959,22 +2959,22 @@
         <v>1.4</v>
       </c>
       <c r="AB16">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="AC16">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD16">
         <v>1.73</v>
       </c>
       <c r="AE16">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF16">
         <v>1.38</v>
       </c>
       <c r="AG16">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="R19">
         <v>2.21</v>
@@ -3424,7 +3424,7 @@
         <v>1.31</v>
       </c>
       <c r="T19">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U19">
         <v>2.47</v>
@@ -3460,7 +3460,7 @@
         <v>1.11</v>
       </c>
       <c r="AF19">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG19">
         <v>2.15</v>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="N20">
-        <v>9.65</v>
+        <v>8.5</v>
       </c>
       <c r="O20">
-        <v>6.21</v>
+        <v>6.31</v>
       </c>
       <c r="P20">
         <v>1.24</v>
@@ -3581,22 +3581,22 @@
         <v>7</v>
       </c>
       <c r="R20">
-        <v>2.83</v>
+        <v>2.93</v>
       </c>
       <c r="S20">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="T20">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="U20">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V20">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="W20">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3605,7 +3605,7 @@
         <v>1.09</v>
       </c>
       <c r="Z20">
-        <v>6.2</v>
+        <v>6.85</v>
       </c>
       <c r="AA20">
         <v>1.3</v>
@@ -3614,19 +3614,19 @@
         <v>3.1</v>
       </c>
       <c r="AC20">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AD20">
-        <v>1.93</v>
+        <v>2.04</v>
       </c>
       <c r="AE20">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AF20">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AG20">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AK20">
         <v>1.05</v>
@@ -4189,12 +4189,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Karviná</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G24">
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q24">
-        <v>2.18</v>
+        <v>1.75</v>
       </c>
       <c r="R24">
-        <v>2.18</v>
+        <v>2.63</v>
       </c>
       <c r="S24">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="T24">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="U24">
-        <v>2.47</v>
+        <v>2.16</v>
       </c>
       <c r="V24">
-        <v>1.44</v>
+        <v>1.73</v>
       </c>
       <c r="W24">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="X24">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y24">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="AA24">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="AB24">
-        <v>2.07</v>
+        <v>2.43</v>
       </c>
       <c r="AC24">
-        <v>2.62</v>
+        <v>2.17</v>
       </c>
       <c r="AD24">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AE24">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AF24">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AG24">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK24">
-        <v>2.04</v>
+        <v>2.7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Karviná</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="Q25">
+        <v>2.6</v>
+      </c>
+      <c r="R25">
+        <v>2.04</v>
+      </c>
+      <c r="S25">
+        <v>1.36</v>
+      </c>
+      <c r="T25">
+        <v>2.73</v>
+      </c>
+      <c r="U25">
+        <v>2.48</v>
+      </c>
+      <c r="V25">
+        <v>1.36</v>
+      </c>
+      <c r="W25">
+        <v>1.04</v>
+      </c>
+      <c r="X25">
+        <v>1</v>
+      </c>
+      <c r="Y25">
+        <v>1.24</v>
+      </c>
+      <c r="Z25">
+        <v>3.4</v>
+      </c>
+      <c r="AA25">
+        <v>1.76</v>
+      </c>
+      <c r="AB25">
+        <v>1.87</v>
+      </c>
+      <c r="AC25">
+        <v>3.14</v>
+      </c>
+      <c r="AD25">
+        <v>1.27</v>
+      </c>
+      <c r="AE25">
+        <v>1.06</v>
+      </c>
+      <c r="AF25">
         <v>1.73</v>
       </c>
-      <c r="R25">
-        <v>2.63</v>
-      </c>
-      <c r="S25">
-        <v>1.23</v>
-      </c>
-      <c r="T25">
-        <v>3.42</v>
-      </c>
-      <c r="U25">
-        <v>2.16</v>
-      </c>
-      <c r="V25">
-        <v>1.6</v>
-      </c>
-      <c r="W25">
-        <v>1.11</v>
-      </c>
-      <c r="X25">
-        <v>1.03</v>
-      </c>
-      <c r="Y25">
-        <v>1.13</v>
-      </c>
-      <c r="Z25">
-        <v>5</v>
-      </c>
-      <c r="AA25">
-        <v>1.47</v>
-      </c>
-      <c r="AB25">
-        <v>2.6</v>
-      </c>
-      <c r="AC25">
-        <v>2.17</v>
-      </c>
-      <c r="AD25">
-        <v>1.62</v>
-      </c>
-      <c r="AE25">
-        <v>1.21</v>
-      </c>
-      <c r="AF25">
-        <v>1.63</v>
-      </c>
       <c r="AG25">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK25">
-        <v>2.7</v>
+        <v>1.67</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q26">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="R26">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T26">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W26">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="Z26">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AA26">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB26">
-        <v>1.81</v>
+        <v>2.05</v>
       </c>
       <c r="AC26">
-        <v>3.14</v>
+        <v>2.74</v>
       </c>
       <c r="AD26">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE26">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AG26">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AK26">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q27">
         <v>2.8</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S27">
+        <v>1.36</v>
+      </c>
+      <c r="T27">
+        <v>3</v>
+      </c>
+      <c r="U27">
+        <v>2.75</v>
+      </c>
+      <c r="V27">
+        <v>1.39</v>
+      </c>
+      <c r="W27">
+        <v>1.08</v>
+      </c>
+      <c r="X27">
+        <v>1.01</v>
+      </c>
+      <c r="Y27">
+        <v>1.24</v>
+      </c>
+      <c r="Z27">
+        <v>3.34</v>
+      </c>
+      <c r="AA27">
+        <v>1.9</v>
+      </c>
+      <c r="AB27">
+        <v>1.9</v>
+      </c>
+      <c r="AC27">
+        <v>2.97</v>
+      </c>
+      <c r="AD27">
         <v>1.3</v>
       </c>
-      <c r="T27">
-        <v>3.1</v>
-      </c>
-      <c r="U27">
-        <v>2.5</v>
-      </c>
-      <c r="V27">
-        <v>1.4</v>
-      </c>
-      <c r="W27">
-        <v>1.11</v>
-      </c>
-      <c r="X27">
-        <v>1</v>
-      </c>
-      <c r="Y27">
-        <v>1.22</v>
-      </c>
-      <c r="Z27">
-        <v>3.8</v>
-      </c>
-      <c r="AA27">
-        <v>1.75</v>
-      </c>
-      <c r="AB27">
-        <v>1.95</v>
-      </c>
-      <c r="AC27">
-        <v>2.88</v>
-      </c>
-      <c r="AD27">
-        <v>1.35</v>
-      </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF27">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK27">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="O28">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="Q28">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T28">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U28">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="V28">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
         <v>1.06</v>
       </c>
       <c r="X28">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z28">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA28">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AB28">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC28">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AD28">
+        <v>1.35</v>
+      </c>
+      <c r="AE28">
+        <v>1.09</v>
+      </c>
+      <c r="AF28">
+        <v>1.59</v>
+      </c>
+      <c r="AG28">
+        <v>2.15</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.3</v>
       </c>
-      <c r="AE28">
-        <v>1.08</v>
-      </c>
-      <c r="AF28">
-        <v>1.65</v>
-      </c>
-      <c r="AG28">
-        <v>2.07</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.26</v>
-      </c>
       <c r="AK28">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q29">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="R29">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S29">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U29">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V29">
         <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z29">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="AA29">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB29">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AC29">
-        <v>2.74</v>
+        <v>2.62</v>
       </c>
       <c r="AD29">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE29">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AG29">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AK29">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="O30">
-        <v>3.75</v>
+        <v>3.59</v>
       </c>
       <c r="P30">
-        <v>2.19</v>
+        <v>2.24</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5238,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="AA30">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB30">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AC30">
         <v>0</v>
@@ -5374,7 +5374,7 @@
         <v>2.64</v>
       </c>
       <c r="R31">
-        <v>1.96</v>
+        <v>2.11</v>
       </c>
       <c r="S31">
         <v>1.47</v>
@@ -5407,7 +5407,7 @@
         <v>1.68</v>
       </c>
       <c r="AC31">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AD31">
         <v>1.23</v>
@@ -5435,7 +5435,7 @@
         <v>1.31</v>
       </c>
       <c r="AK31">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,10 +5528,10 @@
         <v>1.66</v>
       </c>
       <c r="O32">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="P32">
-        <v>4.38</v>
+        <v>4.46</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P33">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="Q33">
         <v>3.6</v>
@@ -5703,7 +5703,7 @@
         <v>2.2</v>
       </c>
       <c r="S33">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="T33">
         <v>3.1</v>
@@ -5715,7 +5715,7 @@
         <v>1.4</v>
       </c>
       <c r="W33">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="X33">
         <v>1.05</v>
@@ -5724,28 +5724,28 @@
         <v>1.27</v>
       </c>
       <c r="Z33">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA33">
         <v>1.9</v>
       </c>
       <c r="AB33">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AC33">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AD33">
         <v>1.3</v>
       </c>
       <c r="AE33">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF33">
         <v>1.72</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -6014,13 +6014,13 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="O35">
-        <v>3.76</v>
+        <v>3.5</v>
       </c>
       <c r="P35">
-        <v>3.67</v>
+        <v>3.35</v>
       </c>
       <c r="Q35">
         <v>0</v>
@@ -6180,7 +6180,7 @@
         <v>2.72</v>
       </c>
       <c r="O36">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="P36">
         <v>2.15</v>
@@ -6210,19 +6210,19 @@
         <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z36">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA36">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AB36">
         <v>2.33</v>
       </c>
       <c r="AC36">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AD36">
         <v>1.56</v>
@@ -6234,7 +6234,7 @@
         <v>1.44</v>
       </c>
       <c r="AG36">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.57</v>
       </c>
       <c r="AK36">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,13 +6340,13 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="O37">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P37">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q37">
         <v>4.15</v>
@@ -6355,7 +6355,7 @@
         <v>2.3</v>
       </c>
       <c r="S37">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T37">
         <v>3.25</v>
@@ -6367,31 +6367,31 @@
         <v>1.5</v>
       </c>
       <c r="W37">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X37">
         <v>1.04</v>
       </c>
       <c r="Y37">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Z37">
         <v>4.32</v>
       </c>
       <c r="AA37">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AB37">
         <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>2.63</v>
+        <v>2.46</v>
       </c>
       <c r="AD37">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AE37">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF37">
         <v>1.53</v>
@@ -6413,7 +6413,7 @@
         <v>1.67</v>
       </c>
       <c r="AK37">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6702,13 +6702,13 @@
         <v>1.37</v>
       </c>
       <c r="Z39">
-        <v>2.79</v>
+        <v>2.66</v>
       </c>
       <c r="AA39">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AB39">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AC39">
         <v>4.33</v>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK39">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6850,7 +6850,7 @@
         <v>2.88</v>
       </c>
       <c r="U40">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V40">
         <v>1.38</v>
@@ -6868,10 +6868,10 @@
         <v>3.4</v>
       </c>
       <c r="AA40">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AB40">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AC40">
         <v>3.08</v>
@@ -6880,7 +6880,7 @@
         <v>1.28</v>
       </c>
       <c r="AE40">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AF40">
         <v>1.75</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK40">
         <v>1.91</v>
@@ -7318,25 +7318,25 @@
         </is>
       </c>
       <c r="N43">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="O43">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="P43">
-        <v>3.45</v>
+        <v>3.49</v>
       </c>
       <c r="Q43">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="R43">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S43">
         <v>1.35</v>
       </c>
       <c r="T43">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U43">
         <v>2.85</v>
@@ -7357,10 +7357,10 @@
         <v>3.3</v>
       </c>
       <c r="AA43">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AB43">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC43">
         <v>3.45</v>
@@ -7369,7 +7369,7 @@
         <v>1.26</v>
       </c>
       <c r="AE43">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF43">
         <v>1.75</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.7</v>
+        <v>2.98</v>
       </c>
       <c r="O45">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="P45">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="Q45">
         <v>3.4</v>
@@ -7659,7 +7659,7 @@
         <v>2.4</v>
       </c>
       <c r="S45">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T45">
         <v>3.9</v>
@@ -7668,10 +7668,10 @@
         <v>2.17</v>
       </c>
       <c r="V45">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="W45">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="X45">
         <v>1.02</v>
@@ -7714,7 +7714,7 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AK45">
         <v>1.23</v>
@@ -7807,22 +7807,22 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O46">
+        <v>4</v>
+      </c>
+      <c r="P46">
+        <v>1.87</v>
+      </c>
+      <c r="Q46">
         <v>3.5</v>
-      </c>
-      <c r="P46">
-        <v>1.98</v>
-      </c>
-      <c r="Q46">
-        <v>3.68</v>
       </c>
       <c r="R46">
         <v>2.3</v>
       </c>
       <c r="S46">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T46">
         <v>3.3</v>
@@ -7834,7 +7834,7 @@
         <v>1.52</v>
       </c>
       <c r="W46">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X46">
         <v>1.01</v>
@@ -7970,34 +7970,34 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O47">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="P47">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="Q47">
-        <v>4.15</v>
+        <v>4.24</v>
       </c>
       <c r="R47">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S47">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T47">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="U47">
         <v>3.1</v>
       </c>
       <c r="V47">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W47">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
         <v>1.06</v>
@@ -8006,13 +8006,13 @@
         <v>1.34</v>
       </c>
       <c r="Z47">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="AA47">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB47">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC47">
         <v>4.02</v>
@@ -8021,7 +8021,7 @@
         <v>1.22</v>
       </c>
       <c r="AE47">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF47">
         <v>1.85</v>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="AK47">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="O48">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P48">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8172,10 +8172,10 @@
         <v>0</v>
       </c>
       <c r="AA48">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AB48">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC48">
         <v>0</v>
@@ -8308,52 +8308,52 @@
         <v>2.2</v>
       </c>
       <c r="R49">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S49">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T49">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U49">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="V49">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="W49">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X49">
         <v>1.01</v>
       </c>
       <c r="Y49">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z49">
-        <v>5.75</v>
+        <v>5.81</v>
       </c>
       <c r="AA49">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AB49">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AC49">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AD49">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AE49">
         <v>1.25</v>
       </c>
       <c r="AF49">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG49">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AK49">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -9769,16 +9769,16 @@
         <v>3.3</v>
       </c>
       <c r="P58">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="Q58">
         <v>2.8</v>
       </c>
       <c r="R58">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S58">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T58">
         <v>3</v>
@@ -9790,22 +9790,22 @@
         <v>1.48</v>
       </c>
       <c r="W58">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X58">
         <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z58">
-        <v>3.82</v>
+        <v>3.94</v>
       </c>
       <c r="AA58">
         <v>1.75</v>
       </c>
       <c r="AB58">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AC58">
         <v>2.9</v>
@@ -9817,7 +9817,7 @@
         <v>1.14</v>
       </c>
       <c r="AF58">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG58">
         <v>2.19</v>
@@ -10089,10 +10089,10 @@
         </is>
       </c>
       <c r="N60">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="O60">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P60">
         <v>1.75</v>
@@ -10116,7 +10116,7 @@
         <v>1.64</v>
       </c>
       <c r="W60">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X60">
         <v>1.04</v>
@@ -10131,7 +10131,7 @@
         <v>1.5</v>
       </c>
       <c r="AB60">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AC60">
         <v>2.24</v>
@@ -10140,7 +10140,7 @@
         <v>1.63</v>
       </c>
       <c r="AE60">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AF60">
         <v>1.54</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.18</v>
+        <v>1.91</v>
       </c>
       <c r="AK60">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10258,13 +10258,13 @@
         <v>3.5</v>
       </c>
       <c r="P61">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q61">
         <v>2.65</v>
       </c>
       <c r="R61">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="S61">
         <v>1.25</v>
@@ -10273,10 +10273,10 @@
         <v>3.8</v>
       </c>
       <c r="U61">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="V61">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="W61">
         <v>1.11</v>
@@ -10285,7 +10285,7 @@
         <v>1.03</v>
       </c>
       <c r="Y61">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z61">
         <v>4.65</v>
@@ -10294,13 +10294,13 @@
         <v>1.57</v>
       </c>
       <c r="AB61">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AC61">
         <v>2.3</v>
       </c>
       <c r="AD61">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="AE61">
         <v>1.22</v>
@@ -10424,13 +10424,13 @@
         <v>2</v>
       </c>
       <c r="Q62">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R62">
         <v>2.37</v>
       </c>
       <c r="S62">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T62">
         <v>3.3</v>
@@ -10442,13 +10442,13 @@
         <v>1.5</v>
       </c>
       <c r="W62">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X62">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z62">
         <v>4.15</v>
@@ -10472,7 +10472,7 @@
         <v>1.59</v>
       </c>
       <c r="AG62">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AK62">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,16 +10578,16 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O63">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P63">
         <v>2.35</v>
       </c>
       <c r="Q63">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="R63">
         <v>2.5</v>
@@ -10617,7 +10617,7 @@
         <v>5.69</v>
       </c>
       <c r="AA63">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AB63">
         <v>2.7</v>
@@ -10626,7 +10626,7 @@
         <v>2.1</v>
       </c>
       <c r="AD63">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AE63">
         <v>1.25</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AK63">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10744,16 +10744,16 @@
         <v>1.98</v>
       </c>
       <c r="O64">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="P64">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="Q64">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="R64">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="S64">
         <v>1.24</v>
@@ -10768,25 +10768,25 @@
         <v>1.62</v>
       </c>
       <c r="W64">
+        <v>1.14</v>
+      </c>
+      <c r="X64">
+        <v>1.02</v>
+      </c>
+      <c r="Y64">
         <v>1.13</v>
-      </c>
-      <c r="X64">
-        <v>1.03</v>
-      </c>
-      <c r="Y64">
-        <v>1.15</v>
       </c>
       <c r="Z64">
         <v>5.25</v>
       </c>
       <c r="AA64">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="AB64">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AC64">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AD64">
         <v>1.6</v>
@@ -10795,7 +10795,7 @@
         <v>1.21</v>
       </c>
       <c r="AF64">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG64">
         <v>2.55</v>
@@ -10814,7 +10814,7 @@
         <v>1.3</v>
       </c>
       <c r="AK64">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10904,16 +10904,16 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="O65">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="P65">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q65">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="R65">
         <v>2.33</v>
@@ -10922,13 +10922,13 @@
         <v>1.33</v>
       </c>
       <c r="T65">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U65">
         <v>2.53</v>
       </c>
       <c r="V65">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="W65">
         <v>1.08</v>
@@ -10955,10 +10955,10 @@
         <v>1.4</v>
       </c>
       <c r="AE65">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AF65">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG65">
         <v>2.28</v>
@@ -11076,10 +11076,10 @@
         <v>4.8</v>
       </c>
       <c r="Q66">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R66">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="S66">
         <v>1.29</v>
@@ -11094,7 +11094,7 @@
         <v>1.47</v>
       </c>
       <c r="W66">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X66">
         <v>1.04</v>
@@ -11112,10 +11112,10 @@
         <v>2.08</v>
       </c>
       <c r="AC66">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="AD66">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AE66">
         <v>1.13</v>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK66">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11399,10 +11399,10 @@
         <v>3.85</v>
       </c>
       <c r="P68">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="Q68">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R68">
         <v>2.16</v>
@@ -11420,7 +11420,7 @@
         <v>1.36</v>
       </c>
       <c r="W68">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X68">
         <v>1.04</v>
@@ -11429,7 +11429,7 @@
         <v>1.3</v>
       </c>
       <c r="Z68">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="AA68">
         <v>2.05</v>
@@ -11447,10 +11447,10 @@
         <v>1.04</v>
       </c>
       <c r="AF68">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AG68">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11559,10 +11559,10 @@
         <v>2.55</v>
       </c>
       <c r="O69">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="P69">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="Q69">
         <v>3.2</v>
@@ -11586,10 +11586,10 @@
         <v>1.05</v>
       </c>
       <c r="X69">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y69">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z69">
         <v>3.08</v>
@@ -11598,22 +11598,22 @@
         <v>2.16</v>
       </c>
       <c r="AB69">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AC69">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AD69">
         <v>1.26</v>
       </c>
       <c r="AE69">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF69">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG69">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AK69">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11719,31 +11719,31 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="O70">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="P70">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="Q70">
-        <v>3.18</v>
+        <v>2.84</v>
       </c>
       <c r="R70">
         <v>2.2</v>
       </c>
       <c r="S70">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T70">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="U70">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="V70">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W70">
         <v>1.11</v>
@@ -11752,16 +11752,16 @@
         <v>1.04</v>
       </c>
       <c r="Y70">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z70">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="AA70">
         <v>1.8</v>
       </c>
       <c r="AB70">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AC70">
         <v>3.1</v>
@@ -11773,10 +11773,10 @@
         <v>1.08</v>
       </c>
       <c r="AF70">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG70">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,7 +11789,7 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="AK70">
         <v>1.43</v>
@@ -11897,10 +11897,10 @@
         <v>2.38</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T71">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="U71">
         <v>2.4</v>
@@ -11912,7 +11912,7 @@
         <v>1.08</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y71">
         <v>1.22</v>
@@ -11924,10 +11924,10 @@
         <v>1.79</v>
       </c>
       <c r="AB71">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC71">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD71">
         <v>1.4</v>
@@ -11936,10 +11936,10 @@
         <v>1.15</v>
       </c>
       <c r="AF71">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG71">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -12045,28 +12045,28 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O72">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="P72">
         <v>2.44</v>
       </c>
       <c r="Q72">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="R72">
         <v>2.1</v>
       </c>
       <c r="S72">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="T72">
         <v>2.77</v>
       </c>
       <c r="U72">
-        <v>2.74</v>
+        <v>2.54</v>
       </c>
       <c r="V72">
         <v>1.44</v>
@@ -12081,13 +12081,13 @@
         <v>1.25</v>
       </c>
       <c r="Z72">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AA72">
         <v>1.78</v>
       </c>
       <c r="AB72">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AC72">
         <v>2.92</v>
@@ -12096,13 +12096,13 @@
         <v>1.31</v>
       </c>
       <c r="AE72">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AF72">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG72">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK72">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12371,13 +12371,13 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O74">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P74">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="Q74">
         <v>3</v>
@@ -12389,7 +12389,7 @@
         <v>1.32</v>
       </c>
       <c r="T74">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="U74">
         <v>2.61</v>
@@ -12398,13 +12398,13 @@
         <v>1.46</v>
       </c>
       <c r="W74">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X74">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y74">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z74">
         <v>3.93</v>
@@ -12413,7 +12413,7 @@
         <v>1.75</v>
       </c>
       <c r="AB74">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC74">
         <v>2.87</v>
@@ -12860,10 +12860,10 @@
         </is>
       </c>
       <c r="N77">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O77">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P77">
         <v>1.93</v>
@@ -12875,10 +12875,10 @@
         <v>2.2</v>
       </c>
       <c r="S77">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T77">
-        <v>2.91</v>
+        <v>3.13</v>
       </c>
       <c r="U77">
         <v>2.62</v>
@@ -12902,10 +12902,10 @@
         <v>1.8</v>
       </c>
       <c r="AB77">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AC77">
-        <v>2.92</v>
+        <v>3.03</v>
       </c>
       <c r="AD77">
         <v>1.31</v>
@@ -13026,19 +13026,19 @@
         <v>1.8</v>
       </c>
       <c r="O78">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P78">
         <v>3.45</v>
       </c>
       <c r="Q78">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="R78">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="S78">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T78">
         <v>3.12</v>
@@ -13047,10 +13047,10 @@
         <v>2.5</v>
       </c>
       <c r="V78">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W78">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X78">
         <v>1.04</v>
@@ -13080,7 +13080,7 @@
         <v>1.67</v>
       </c>
       <c r="AG78">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>2.05</v>
       </c>
       <c r="AB87">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AC87">
         <v>0</v>
@@ -14653,16 +14653,16 @@
         </is>
       </c>
       <c r="N88">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="O88">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P88">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q88">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="R88">
         <v>2</v>
@@ -14686,25 +14686,25 @@
         <v>1.04</v>
       </c>
       <c r="Y88">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z88">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AA88">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB88">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC88">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AD88">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE88">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF88">
         <v>1.85</v>
@@ -14816,10 +14816,10 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="O89">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="P89">
         <v>13.5</v>
@@ -14837,13 +14837,13 @@
         <v>3.5</v>
       </c>
       <c r="U89">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="V89">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="W89">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X89">
         <v>1.03</v>
@@ -14852,28 +14852,28 @@
         <v>1.13</v>
       </c>
       <c r="Z89">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AA89">
         <v>1.53</v>
       </c>
       <c r="AB89">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AC89">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AD89">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE89">
         <v>1.2</v>
       </c>
       <c r="AF89">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="AG89">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="O92">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P92">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q92">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R92">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S92">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T92">
-        <v>2.65</v>
+        <v>3.04</v>
       </c>
       <c r="U92">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="V92">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W92">
+        <v>1.06</v>
+      </c>
+      <c r="X92">
         <v>1.05</v>
       </c>
-      <c r="X92">
-        <v>1.06</v>
-      </c>
       <c r="Y92">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z92">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA92">
         <v>1.85</v>
       </c>
       <c r="AB92">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC92">
-        <v>3.3</v>
+        <v>2.76</v>
       </c>
       <c r="AD92">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AE92">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF92">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AG92">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK92">
         <v>1.35</v>
@@ -15468,19 +15468,19 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="O93">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P93">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="Q93">
         <v>2.63</v>
       </c>
       <c r="R93">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S93">
         <v>1.38</v>
@@ -15489,7 +15489,7 @@
         <v>2.88</v>
       </c>
       <c r="U93">
-        <v>2.73</v>
+        <v>2.9</v>
       </c>
       <c r="V93">
         <v>1.39</v>
@@ -15498,7 +15498,7 @@
         <v>1.05</v>
       </c>
       <c r="X93">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
         <v>1.33</v>
@@ -15507,16 +15507,16 @@
         <v>3.25</v>
       </c>
       <c r="AA93">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AB93">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC93">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD93">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AE93">
         <v>1.1</v>
@@ -15652,13 +15652,13 @@
         <v>2.5</v>
       </c>
       <c r="U94">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="V94">
         <v>1.32</v>
       </c>
       <c r="W94">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X94">
         <v>1.03</v>
@@ -15704,7 +15704,7 @@
         <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15966,16 +15966,16 @@
         <v>6.76</v>
       </c>
       <c r="Q96">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="R96">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="S96">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T96">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U96">
         <v>2.62</v>
@@ -16011,10 +16011,10 @@
         <v>0</v>
       </c>
       <c r="AF96">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="AG96">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK96">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="O97">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="P97">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="Q97">
         <v>3.12</v>
@@ -16135,10 +16135,10 @@
         <v>1.83</v>
       </c>
       <c r="S97">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="T97">
-        <v>2.29</v>
+        <v>2.63</v>
       </c>
       <c r="U97">
         <v>3.2</v>
@@ -16165,7 +16165,7 @@
         <v>1.57</v>
       </c>
       <c r="AC97">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="AD97">
         <v>1.17</v>
@@ -16190,7 +16190,7 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK97">
         <v>1.46</v>
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O98">
         <v>5</v>
       </c>
       <c r="P98">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="Q98">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R98">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S98">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T98">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U98">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="V98">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W98">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X98">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y98">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z98">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA98">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB98">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AC98">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="AD98">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE98">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF98">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AG98">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK98">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="O99">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P99">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="Q99">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="R99">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S99">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T99">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U99">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="V99">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W99">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X99">
         <v>1.06</v>
       </c>
       <c r="Y99">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z99">
         <v>3</v>
       </c>
       <c r="AA99">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AB99">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AC99">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="AD99">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE99">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF99">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG99">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AK99">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -17424,13 +17424,13 @@
         </is>
       </c>
       <c r="N105">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O105">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P105">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q105">
         <v>0</v>
@@ -17454,7 +17454,7 @@
         <v>0</v>
       </c>
       <c r="X105">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y105">
         <v>0</v>
@@ -17463,10 +17463,10 @@
         <v>0</v>
       </c>
       <c r="AA105">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB105">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC105">
         <v>0</v>
@@ -17475,7 +17475,7 @@
         <v>0</v>
       </c>
       <c r="AE105">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF105">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="O2">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P2">
         <v>1.75</v>
       </c>
       <c r="Q2">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="R2">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S2">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="T2">
-        <v>3.42</v>
+        <v>3.2</v>
       </c>
       <c r="U2">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="V2">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="W2">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="Z2">
-        <v>4.9</v>
+        <v>4.25</v>
       </c>
       <c r="AA2">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AB2">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AC2">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="AD2">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="AE2">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AG2">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.2</v>
+        <v>1.81</v>
       </c>
       <c r="AK2">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="O3">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="P3">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="Q3">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R3">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
         <v>1.36</v>
@@ -831,13 +831,13 @@
         <v>1</v>
       </c>
       <c r="Y3">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="Z3">
         <v>3.62</v>
       </c>
       <c r="AA3">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB3">
         <v>1.91</v>
@@ -846,7 +846,7 @@
         <v>2.85</v>
       </c>
       <c r="AD3">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="AE3">
         <v>1.08</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK3">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="O4">
-        <v>4.15</v>
+        <v>3.8</v>
       </c>
       <c r="P4">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="Q4">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="R4">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="S4">
         <v>1.35</v>
@@ -982,13 +982,13 @@
         <v>3</v>
       </c>
       <c r="U4">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="V4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W4">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
         <v>1.03</v>
@@ -1006,19 +1006,19 @@
         <v>1.9</v>
       </c>
       <c r="AC4">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD4">
         <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF4">
         <v>1.95</v>
       </c>
       <c r="AG4">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AK4">
         <v>2.45</v>
@@ -2446,13 +2446,13 @@
         <v>1.25</v>
       </c>
       <c r="T13">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U13">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V13">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W13">
         <v>1.13</v>
@@ -2464,7 +2464,7 @@
         <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA13">
         <v>1.58</v>
@@ -2473,19 +2473,19 @@
         <v>2.21</v>
       </c>
       <c r="AC13">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="AD13">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="AE13">
         <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AG13">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="O14">
         <v>3.9</v>
       </c>
       <c r="P14">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q14">
         <v>2.09</v>
       </c>
       <c r="R14">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="S14">
         <v>1.24</v>
@@ -2627,7 +2627,7 @@
         <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>4.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA14">
         <v>1.51</v>
@@ -2642,13 +2642,13 @@
         <v>1.51</v>
       </c>
       <c r="AE14">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF14">
         <v>1.56</v>
       </c>
       <c r="AG14">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -3904,16 +3904,16 @@
         <v>2.89</v>
       </c>
       <c r="Q22">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="R22">
         <v>2.2</v>
       </c>
       <c r="S22">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T22">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U22">
         <v>2.67</v>
@@ -3928,10 +3928,10 @@
         <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z22">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA22">
         <v>1.8</v>
@@ -3952,7 +3952,7 @@
         <v>1.63</v>
       </c>
       <c r="AG22">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4067,25 +4067,25 @@
         <v>11</v>
       </c>
       <c r="Q23">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="R23">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="S23">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="T23">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="U23">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V23">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="W23">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="X23">
         <v>1.01</v>
@@ -4094,7 +4094,7 @@
         <v>1.03</v>
       </c>
       <c r="Z23">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AA23">
         <v>1.28</v>
@@ -4103,19 +4103,19 @@
         <v>3.5</v>
       </c>
       <c r="AC23">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="AD23">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="AE23">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AF23">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AG23">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.45</v>
+        <v>2.49</v>
       </c>
       <c r="O26">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P26">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q26">
         <v>2.8</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>2.06</v>
       </c>
       <c r="S26">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T26">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U26">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="V26">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z26">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="AA26">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB26">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AC26">
-        <v>2.74</v>
+        <v>2.97</v>
       </c>
       <c r="AD26">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AF26">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG26">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AK26">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.49</v>
+        <v>1.95</v>
       </c>
       <c r="O27">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="Q27">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="R27">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="V27">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y27">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="Z27">
-        <v>3.34</v>
+        <v>3.8</v>
       </c>
       <c r="AA27">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AB27">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AC27">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AD27">
+        <v>1.35</v>
+      </c>
+      <c r="AE27">
+        <v>1.09</v>
+      </c>
+      <c r="AF27">
+        <v>1.59</v>
+      </c>
+      <c r="AG27">
+        <v>2.15</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.3</v>
       </c>
-      <c r="AE27">
-        <v>1.08</v>
-      </c>
-      <c r="AF27">
-        <v>1.67</v>
-      </c>
-      <c r="AG27">
-        <v>2.07</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.26</v>
-      </c>
       <c r="AK27">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.95</v>
+        <v>1.61</v>
       </c>
       <c r="O28">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="P28">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="Q28">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S28">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U28">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V28">
         <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
         <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z28">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AA28">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB28">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AC28">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="AD28">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE28">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AG28">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK28">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.61</v>
+        <v>2.45</v>
       </c>
       <c r="O29">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="P29">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q29">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
       <c r="R29">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U29">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W29">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA29">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB29">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="AC29">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AD29">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE29">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF29">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>2.19</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="AK29">
-        <v>2.1</v>
+        <v>1.43</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -7155,22 +7155,22 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O42">
         <v>3.8</v>
       </c>
       <c r="P42">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="Q42">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="R42">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="S42">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="T42">
         <v>3.94</v>
@@ -7191,22 +7191,22 @@
         <v>1.1</v>
       </c>
       <c r="Z42">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA42">
         <v>1.36</v>
       </c>
       <c r="AB42">
-        <v>2.98</v>
+        <v>2.8</v>
       </c>
       <c r="AC42">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="AD42">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AE42">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AF42">
         <v>1.4</v>
@@ -7499,16 +7499,16 @@
         <v>1.29</v>
       </c>
       <c r="T44">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U44">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="V44">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W44">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
         <v>1.02</v>
@@ -7538,7 +7538,7 @@
         <v>1.6</v>
       </c>
       <c r="AG44">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -8459,13 +8459,13 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O50">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P50">
-        <v>2.09</v>
+        <v>2.03</v>
       </c>
       <c r="Q50">
         <v>4.33</v>
@@ -8474,46 +8474,46 @@
         <v>1.91</v>
       </c>
       <c r="S50">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="T50">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="U50">
         <v>3.75</v>
       </c>
       <c r="V50">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W50">
         <v>1.01</v>
       </c>
       <c r="X50">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Y50">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="Z50">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AA50">
         <v>2.7</v>
       </c>
       <c r="AB50">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AC50">
-        <v>4.5</v>
+        <v>5.45</v>
       </c>
       <c r="AD50">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AE50">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF50">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AG50">
         <v>1.57</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="AK50">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O51">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P51">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q51">
         <v>3.38</v>
@@ -8640,7 +8640,7 @@
         <v>1.46</v>
       </c>
       <c r="T51">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U51">
         <v>2.91</v>
@@ -8670,7 +8670,7 @@
         <v>3.62</v>
       </c>
       <c r="AD51">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AE51">
         <v>1.04</v>
@@ -8695,7 +8695,7 @@
         <v>1.58</v>
       </c>
       <c r="AK51">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="O52">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P52">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="Q52">
         <v>0</v>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="O53">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="P53">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="Q53">
-        <v>3.31</v>
+        <v>2.94</v>
       </c>
       <c r="R53">
         <v>2.05</v>
@@ -8981,22 +8981,22 @@
         <v>1.04</v>
       </c>
       <c r="Y53">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="Z53">
         <v>3.1</v>
       </c>
       <c r="AA53">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AB53">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC53">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AD53">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AE53">
         <v>1.08</v>
@@ -9005,7 +9005,7 @@
         <v>1.8</v>
       </c>
       <c r="AG53">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="AK53">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,7 +9111,7 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="O54">
         <v>3.03</v>
@@ -9153,7 +9153,7 @@
         <v>2.18</v>
       </c>
       <c r="AB54">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AC54">
         <v>3.9</v>
@@ -9274,13 +9274,13 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="O55">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P55">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="Q55">
         <v>2.95</v>
@@ -9289,28 +9289,28 @@
         <v>2.08</v>
       </c>
       <c r="S55">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T55">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="U55">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V55">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W55">
         <v>1.05</v>
       </c>
       <c r="X55">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y55">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z55">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="AA55">
         <v>1.85</v>
@@ -9325,13 +9325,13 @@
         <v>1.33</v>
       </c>
       <c r="AE55">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF55">
         <v>1.61</v>
       </c>
       <c r="AG55">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>1.4</v>
       </c>
       <c r="AK55">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.9</v>
+        <v>2.78</v>
       </c>
       <c r="O73">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="P73">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q73">
         <v>3.4</v>
@@ -12226,25 +12226,25 @@
         <v>1.62</v>
       </c>
       <c r="T73">
-        <v>2.05</v>
+        <v>2.23</v>
       </c>
       <c r="U73">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="V73">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="W73">
         <v>1.03</v>
       </c>
       <c r="X73">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Y73">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="Z73">
-        <v>2.28</v>
+        <v>2.09</v>
       </c>
       <c r="AA73">
         <v>3.18</v>
@@ -12253,16 +12253,16 @@
         <v>1.31</v>
       </c>
       <c r="AC73">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AD73">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE73">
         <v>1.03</v>
       </c>
       <c r="AF73">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AG73">
         <v>1.6</v>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AK73">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12534,61 +12534,61 @@
         </is>
       </c>
       <c r="N75">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="O75">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P75">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q75">
         <v>2.48</v>
       </c>
       <c r="R75">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="S75">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T75">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U75">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="V75">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W75">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X75">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y75">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="Z75">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="AA75">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB75">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AC75">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="AD75">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="AE75">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF75">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AG75">
         <v>2.1</v>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="AK75">
         <v>1.73</v>
@@ -13186,28 +13186,28 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="O79">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="P79">
-        <v>4.33</v>
+        <v>3.65</v>
       </c>
       <c r="Q79">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="R79">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="S79">
         <v>1.25</v>
       </c>
       <c r="T79">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U79">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V79">
         <v>1.64</v>
@@ -13225,7 +13225,7 @@
         <v>5</v>
       </c>
       <c r="AA79">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AB79">
         <v>2.45</v>
@@ -13240,10 +13240,10 @@
         <v>1.22</v>
       </c>
       <c r="AF79">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG79">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AK79">
         <v>2.05</v>
@@ -13349,22 +13349,22 @@
         </is>
       </c>
       <c r="N80">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="O80">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="P80">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="Q80">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="R80">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="S80">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T80">
         <v>2.9</v>
@@ -13376,37 +13376,37 @@
         <v>1.34</v>
       </c>
       <c r="W80">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X80">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="Z80">
-        <v>3.32</v>
+        <v>3.13</v>
       </c>
       <c r="AA80">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AB80">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC80">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AD80">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE80">
         <v>1.08</v>
       </c>
       <c r="AF80">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AG80">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AK80">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,13 +13512,13 @@
         </is>
       </c>
       <c r="N81">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O81">
-        <v>3.74</v>
+        <v>3.5</v>
       </c>
       <c r="P81">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q81">
         <v>5.41</v>
@@ -13554,10 +13554,10 @@
         <v>1.85</v>
       </c>
       <c r="AB81">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AC81">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="AD81">
         <v>1.3</v>
@@ -13675,7 +13675,7 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="O82">
         <v>3.7</v>
@@ -13693,7 +13693,7 @@
         <v>1.28</v>
       </c>
       <c r="T82">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U82">
         <v>2.38</v>
@@ -13708,13 +13708,13 @@
         <v>1.02</v>
       </c>
       <c r="Y82">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z82">
         <v>4.68</v>
       </c>
       <c r="AA82">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AB82">
         <v>2.19</v>
@@ -13723,13 +13723,13 @@
         <v>2.5</v>
       </c>
       <c r="AD82">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE82">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF82">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG82">
         <v>2.33</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="O83">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P83">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -13877,10 +13877,10 @@
         <v>0</v>
       </c>
       <c r="AA83">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB83">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AC83">
         <v>0</v>
@@ -14004,10 +14004,10 @@
         <v>3.3</v>
       </c>
       <c r="O84">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P84">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="Q84">
         <v>3.3</v>
@@ -14016,16 +14016,16 @@
         <v>2.25</v>
       </c>
       <c r="S84">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="T84">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U84">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="V84">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="W84">
         <v>1.12</v>
@@ -14040,25 +14040,25 @@
         <v>3.85</v>
       </c>
       <c r="AA84">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AB84">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AC84">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="AD84">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AE84">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF84">
         <v>1.55</v>
       </c>
       <c r="AG84">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="AK84">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14167,37 +14167,37 @@
         <v>5</v>
       </c>
       <c r="O85">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P85">
         <v>1.5</v>
       </c>
       <c r="Q85">
-        <v>6.96</v>
+        <v>7.06</v>
       </c>
       <c r="R85">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="S85">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T85">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="U85">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="V85">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W85">
         <v>1.11</v>
       </c>
       <c r="X85">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z85">
         <v>3.95</v>
@@ -14206,22 +14206,22 @@
         <v>1.75</v>
       </c>
       <c r="AB85">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC85">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD85">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE85">
         <v>1.15</v>
       </c>
       <c r="AF85">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG85">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AK85">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,16 +14327,16 @@
         </is>
       </c>
       <c r="N86">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="O86">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P86">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="Q86">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R86">
         <v>2.25</v>
@@ -14345,46 +14345,46 @@
         <v>1.3</v>
       </c>
       <c r="T86">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="U86">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="V86">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W86">
         <v>1.06</v>
       </c>
       <c r="X86">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y86">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z86">
-        <v>3.8</v>
+        <v>3.71</v>
       </c>
       <c r="AA86">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AB86">
         <v>1.98</v>
       </c>
       <c r="AC86">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD86">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE86">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF86">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG86">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -15021,7 +15021,7 @@
         <v>1.85</v>
       </c>
       <c r="AB90">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC90">
         <v>3.08</v>
@@ -15030,7 +15030,7 @@
         <v>1.28</v>
       </c>
       <c r="AE90">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF90">
         <v>1.93</v>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AK90">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15148,13 +15148,13 @@
         <v>3.4</v>
       </c>
       <c r="P91">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="Q91">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="R91">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S91">
         <v>1.3</v>
@@ -15166,10 +15166,10 @@
         <v>2.5</v>
       </c>
       <c r="V91">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W91">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X91">
         <v>1.03</v>
@@ -15178,19 +15178,19 @@
         <v>1.2</v>
       </c>
       <c r="Z91">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="AA91">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB91">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AC91">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="AD91">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AE91">
         <v>1.14</v>
@@ -15199,7 +15199,7 @@
         <v>1.53</v>
       </c>
       <c r="AG91">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AK91">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="O101">
         <v>3</v>
       </c>
       <c r="P101">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AB101">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC101">
         <v>0</v>
@@ -18242,28 +18242,28 @@
         <v>2.15</v>
       </c>
       <c r="O110">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P110">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Q110">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="R110">
         <v>2</v>
       </c>
       <c r="S110">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T110">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="U110">
         <v>2.8</v>
       </c>
       <c r="V110">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W110">
         <v>1.04</v>
@@ -18272,22 +18272,22 @@
         <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z110">
         <v>2.8</v>
       </c>
       <c r="AA110">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AB110">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC110">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="AD110">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE110">
         <v>1.06</v>
@@ -18296,7 +18296,7 @@
         <v>1.77</v>
       </c>
       <c r="AG110">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK110">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18417,22 +18417,22 @@
         <v>2.1</v>
       </c>
       <c r="S111">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T111">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U111">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V111">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W111">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X111">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y111">
         <v>1.28</v>
@@ -18444,22 +18444,22 @@
         <v>1.95</v>
       </c>
       <c r="AB111">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AC111">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="AD111">
         <v>1.28</v>
       </c>
       <c r="AE111">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AF111">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG111">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -19054,10 +19054,10 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="O115">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="P115">
         <v>4.12</v>
@@ -19223,13 +19223,13 @@
         <v>3.2</v>
       </c>
       <c r="P116">
-        <v>3.8</v>
+        <v>3.97</v>
       </c>
       <c r="Q116">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="R116">
-        <v>2.08</v>
+        <v>2.01</v>
       </c>
       <c r="S116">
         <v>1.4</v>
@@ -19244,7 +19244,7 @@
         <v>1.4</v>
       </c>
       <c r="W116">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X116">
         <v>1.01</v>
@@ -19253,7 +19253,7 @@
         <v>1.29</v>
       </c>
       <c r="Z116">
-        <v>3.04</v>
+        <v>3.25</v>
       </c>
       <c r="AA116">
         <v>2.07</v>
@@ -19268,13 +19268,13 @@
         <v>1.22</v>
       </c>
       <c r="AE116">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF116">
         <v>1.85</v>
       </c>
       <c r="AG116">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH116" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>3.45</v>
       </c>
       <c r="Q118">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="R118">
         <v>2.28</v>
@@ -19588,7 +19588,7 @@
         <v>2.01</v>
       </c>
       <c r="AC118">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD118">
         <v>1.36</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK118">
         <v>1.6</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -15474,7 +15474,7 @@
         <v>3.28</v>
       </c>
       <c r="P93">
-        <v>3.66</v>
+        <v>3.1</v>
       </c>
       <c r="Q93">
         <v>2.63</v>
@@ -15483,7 +15483,7 @@
         <v>2.15</v>
       </c>
       <c r="S93">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="T93">
         <v>2.88</v>
@@ -15498,7 +15498,7 @@
         <v>1.05</v>
       </c>
       <c r="X93">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y93">
         <v>1.33</v>
@@ -15510,10 +15510,10 @@
         <v>2</v>
       </c>
       <c r="AB93">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AC93">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD93">
         <v>1.29</v>
@@ -15522,7 +15522,7 @@
         <v>1.1</v>
       </c>
       <c r="AF93">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AG93">
         <v>1.95</v>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK93">
         <v>1.73</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,65 +8785,65 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="O52">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="P52">
+        <v>2.65</v>
+      </c>
+      <c r="Q52">
+        <v>2.94</v>
+      </c>
+      <c r="R52">
+        <v>2.05</v>
+      </c>
+      <c r="S52">
+        <v>1.38</v>
+      </c>
+      <c r="T52">
+        <v>2.8</v>
+      </c>
+      <c r="U52">
         <v>3</v>
       </c>
-      <c r="Q52">
-        <v>0</v>
-      </c>
-      <c r="R52">
-        <v>0</v>
-      </c>
-      <c r="S52">
-        <v>0</v>
-      </c>
-      <c r="T52">
-        <v>0</v>
-      </c>
-      <c r="U52">
-        <v>0</v>
-      </c>
       <c r="V52">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W52">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X52">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y52">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z52">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA52">
+        <v>2.1</v>
+      </c>
+      <c r="AB52">
+        <v>1.7</v>
+      </c>
+      <c r="AC52">
+        <v>3.3</v>
+      </c>
+      <c r="AD52">
+        <v>1.25</v>
+      </c>
+      <c r="AE52">
+        <v>1.08</v>
+      </c>
+      <c r="AF52">
+        <v>1.8</v>
+      </c>
+      <c r="AG52">
         <v>1.9</v>
       </c>
-      <c r="AB52">
-        <v>1.9</v>
-      </c>
-      <c r="AC52">
-        <v>0</v>
-      </c>
-      <c r="AD52">
-        <v>0</v>
-      </c>
-      <c r="AE52">
-        <v>0</v>
-      </c>
-      <c r="AF52">
-        <v>0</v>
-      </c>
-      <c r="AG52">
-        <v>0</v>
-      </c>
       <c r="AH52" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AK52">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="O53">
-        <v>3.25</v>
+        <v>3.03</v>
       </c>
       <c r="P53">
-        <v>2.65</v>
+        <v>2.37</v>
       </c>
       <c r="Q53">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="R53">
         <v>2.05</v>
       </c>
       <c r="S53">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T53">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="U53">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V53">
+        <v>1.35</v>
+      </c>
+      <c r="W53">
+        <v>1.04</v>
+      </c>
+      <c r="X53">
+        <v>1.02</v>
+      </c>
+      <c r="Y53">
         <v>1.33</v>
       </c>
-      <c r="W53">
-        <v>1.07</v>
-      </c>
-      <c r="X53">
-        <v>1.04</v>
-      </c>
-      <c r="Y53">
-        <v>1.34</v>
-      </c>
       <c r="Z53">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="AA53">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="AB53">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="AC53">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="AD53">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE53">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF53">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG53">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="AK53">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="O54">
-        <v>3.03</v>
+        <v>3.5</v>
       </c>
       <c r="P54">
-        <v>2.37</v>
+        <v>3</v>
       </c>
       <c r="Q54">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R54">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S54">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T54">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U54">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="V54">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W54">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y54">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z54">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AA54">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="AB54">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AC54">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AD54">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE54">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF54">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG54">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AK54">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -16126,7 +16126,7 @@
         <v>2.9</v>
       </c>
       <c r="P97">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q97">
         <v>3.12</v>
@@ -16144,19 +16144,19 @@
         <v>3.2</v>
       </c>
       <c r="V97">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W97">
         <v>1.04</v>
       </c>
       <c r="X97">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y97">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z97">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AA97">
         <v>2.23</v>
@@ -16165,13 +16165,13 @@
         <v>1.57</v>
       </c>
       <c r="AC97">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AD97">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AE97">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF97">
         <v>1.87</v>
@@ -16283,16 +16283,16 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="O98">
         <v>5</v>
       </c>
       <c r="P98">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="Q98">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R98">
         <v>2.5</v>
@@ -16319,7 +16319,7 @@
         <v>1.2</v>
       </c>
       <c r="Z98">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA98">
         <v>1.67</v>
@@ -16328,10 +16328,10 @@
         <v>2.15</v>
       </c>
       <c r="AC98">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD98">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE98">
         <v>1.14</v>
@@ -19555,7 +19555,7 @@
         <v>2.5</v>
       </c>
       <c r="R118">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="S118">
         <v>1.29</v>
@@ -19564,13 +19564,13 @@
         <v>2.99</v>
       </c>
       <c r="U118">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="V118">
         <v>1.45</v>
       </c>
       <c r="W118">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X118">
         <v>1.04</v>
@@ -19579,22 +19579,22 @@
         <v>1.18</v>
       </c>
       <c r="Z118">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA118">
         <v>1.7</v>
       </c>
       <c r="AB118">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AC118">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD118">
         <v>1.36</v>
       </c>
       <c r="AE118">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF118">
         <v>1.58</v>
@@ -19613,7 +19613,7 @@
         </is>
       </c>
       <c r="AJ118">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AK118">
         <v>1.6</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -635,49 +635,49 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O2">
         <v>3.65</v>
       </c>
       <c r="P2">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q2">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="R2">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S2">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="T2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U2">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V2">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="Z2">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="AA2">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AB2">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AC2">
         <v>2.6</v>
@@ -689,10 +689,10 @@
         <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AG2">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.81</v>
+        <v>1.2</v>
       </c>
       <c r="AK2">
         <v>1.25</v>
@@ -798,19 +798,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="O3">
-        <v>3.6</v>
+        <v>3.84</v>
       </c>
       <c r="P3">
-        <v>4.5</v>
+        <v>5.45</v>
       </c>
       <c r="Q3">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="R3">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
         <v>1.36</v>
@@ -819,10 +819,10 @@
         <v>2.89</v>
       </c>
       <c r="U3">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W3">
         <v>1.05</v>
@@ -840,16 +840,16 @@
         <v>1.8</v>
       </c>
       <c r="AB3">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="AC3">
         <v>2.85</v>
       </c>
       <c r="AD3">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AE3">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF3">
         <v>1.78</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK3">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="O4">
         <v>3.8</v>
@@ -970,10 +970,10 @@
         <v>5.5</v>
       </c>
       <c r="Q4">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="R4">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="S4">
         <v>1.35</v>
@@ -982,43 +982,43 @@
         <v>3</v>
       </c>
       <c r="U4">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="V4">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W4">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z4">
         <v>3.55</v>
       </c>
       <c r="AA4">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AB4">
         <v>1.9</v>
       </c>
       <c r="AC4">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="AD4">
         <v>1.3</v>
       </c>
       <c r="AE4">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF4">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG4">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="O8">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="P8">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="Q8">
         <v>2.8</v>
@@ -1628,16 +1628,16 @@
         <v>2.02</v>
       </c>
       <c r="S8">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T8">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="U8">
-        <v>3.34</v>
+        <v>3.48</v>
       </c>
       <c r="V8">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W8">
         <v>1.05</v>
@@ -1646,28 +1646,28 @@
         <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z8">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="AA8">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="AB8">
         <v>1.53</v>
       </c>
       <c r="AC8">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AD8">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AE8">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF8">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG8">
         <v>1.7</v>
@@ -1686,7 +1686,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="N9">
-        <v>4.5</v>
+        <v>4.35</v>
       </c>
       <c r="O9">
         <v>4.3</v>
@@ -1785,40 +1785,40 @@
         <v>1.57</v>
       </c>
       <c r="Q9">
-        <v>4.92</v>
+        <v>4.5</v>
       </c>
       <c r="R9">
         <v>2.5</v>
       </c>
       <c r="S9">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.58</v>
+        <v>3.75</v>
       </c>
       <c r="U9">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="V9">
         <v>1.58</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA9">
         <v>1.46</v>
       </c>
       <c r="AB9">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AC9">
         <v>2.27</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.69</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2437,28 +2437,28 @@
         <v>4.53</v>
       </c>
       <c r="Q13">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="S13">
         <v>1.25</v>
       </c>
       <c r="T13">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="U13">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="V13">
         <v>1.5</v>
       </c>
       <c r="W13">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
         <v>1.14</v>
@@ -2470,22 +2470,22 @@
         <v>1.58</v>
       </c>
       <c r="AB13">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AC13">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="AD13">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AE13">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AF13">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG13">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="O14">
         <v>3.9</v>
@@ -2627,13 +2627,13 @@
         <v>1.13</v>
       </c>
       <c r="Z14">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AA14">
         <v>1.51</v>
       </c>
       <c r="AB14">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AC14">
         <v>2.36</v>
@@ -2645,10 +2645,10 @@
         <v>1.17</v>
       </c>
       <c r="AF14">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AG14">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2760,19 +2760,19 @@
         <v>3.2</v>
       </c>
       <c r="P15">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="Q15">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="R15">
-        <v>2.21</v>
+        <v>2.03</v>
       </c>
       <c r="S15">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="T15">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="U15">
         <v>2.7</v>
@@ -2790,7 +2790,7 @@
         <v>1.29</v>
       </c>
       <c r="Z15">
-        <v>3.51</v>
+        <v>3.3</v>
       </c>
       <c r="AA15">
         <v>1.89</v>
@@ -2808,10 +2808,10 @@
         <v>1.07</v>
       </c>
       <c r="AF15">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AG15">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>2.2</v>
       </c>
       <c r="R16">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="S16">
         <v>1.2</v>
@@ -2938,7 +2938,7 @@
         <v>4</v>
       </c>
       <c r="U16">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="V16">
         <v>1.74</v>
@@ -2959,7 +2959,7 @@
         <v>1.4</v>
       </c>
       <c r="AB16">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AC16">
         <v>2</v>
@@ -2974,7 +2974,7 @@
         <v>1.38</v>
       </c>
       <c r="AG16">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>2.6</v>
       </c>
       <c r="R19">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
         <v>1.31</v>
@@ -3427,7 +3427,7 @@
         <v>3.02</v>
       </c>
       <c r="U19">
-        <v>2.47</v>
+        <v>2.63</v>
       </c>
       <c r="V19">
         <v>1.45</v>
@@ -3445,13 +3445,13 @@
         <v>3.68</v>
       </c>
       <c r="AA19">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB19">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC19">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AD19">
         <v>1.35</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3572,10 +3572,10 @@
         <v>8.5</v>
       </c>
       <c r="O20">
-        <v>6.31</v>
+        <v>6.47</v>
       </c>
       <c r="P20">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Q20">
         <v>7</v>
@@ -3584,7 +3584,7 @@
         <v>2.93</v>
       </c>
       <c r="S20">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="T20">
         <v>5.2</v>
@@ -3593,7 +3593,7 @@
         <v>1.8</v>
       </c>
       <c r="V20">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="W20">
         <v>1.24</v>
@@ -3602,25 +3602,25 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z20">
-        <v>6.85</v>
+        <v>8</v>
       </c>
       <c r="AA20">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AB20">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AC20">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD20">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AE20">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AF20">
         <v>1.57</v>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AK20">
         <v>1.05</v>
@@ -4061,74 +4061,74 @@
         <v>1.17</v>
       </c>
       <c r="O23">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="P23">
         <v>11</v>
       </c>
       <c r="Q23">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R23">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="S23">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="T23">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="U23">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="V23">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="W23">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
+        <v>1.06</v>
+      </c>
+      <c r="Z23">
+        <v>6.3</v>
+      </c>
+      <c r="AA23">
+        <v>1.36</v>
+      </c>
+      <c r="AB23">
+        <v>3.15</v>
+      </c>
+      <c r="AC23">
+        <v>1.9</v>
+      </c>
+      <c r="AD23">
+        <v>1.85</v>
+      </c>
+      <c r="AE23">
+        <v>1.31</v>
+      </c>
+      <c r="AF23">
+        <v>1.95</v>
+      </c>
+      <c r="AG23">
+        <v>1.86</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ23">
         <v>1.03</v>
-      </c>
-      <c r="Z23">
-        <v>7.4</v>
-      </c>
-      <c r="AA23">
-        <v>1.28</v>
-      </c>
-      <c r="AB23">
-        <v>3.5</v>
-      </c>
-      <c r="AC23">
-        <v>1.65</v>
-      </c>
-      <c r="AD23">
-        <v>2.04</v>
-      </c>
-      <c r="AE23">
-        <v>1.41</v>
-      </c>
-      <c r="AF23">
-        <v>1.73</v>
-      </c>
-      <c r="AG23">
-        <v>1.93</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ23">
-        <v>1.07</v>
       </c>
       <c r="AK23">
         <v>5.5</v>
@@ -4221,64 +4221,64 @@
         </is>
       </c>
       <c r="N24">
-        <v>1.53</v>
+        <v>1.35</v>
       </c>
       <c r="O24">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="P24">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="Q24">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="R24">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="S24">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T24">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="U24">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="V24">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W24">
         <v>1.2</v>
       </c>
       <c r="X24">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Z24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA24">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="AB24">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="AC24">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AD24">
-        <v>1.48</v>
+        <v>1.73</v>
       </c>
       <c r="AE24">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AF24">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>2.06</v>
+        <v>2.25</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK24">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q25">
+        <v>2.45</v>
+      </c>
+      <c r="R25">
+        <v>2.3</v>
+      </c>
+      <c r="S25">
+        <v>1.34</v>
+      </c>
+      <c r="T25">
+        <v>3.02</v>
+      </c>
+      <c r="U25">
         <v>2.6</v>
       </c>
-      <c r="R25">
-        <v>2.04</v>
-      </c>
-      <c r="S25">
-        <v>1.36</v>
-      </c>
-      <c r="T25">
-        <v>2.73</v>
-      </c>
-      <c r="U25">
-        <v>2.48</v>
-      </c>
       <c r="V25">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W25">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
         <v>1</v>
       </c>
       <c r="Y25">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z25">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA25">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AB25">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC25">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AD25">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AE25">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AF25">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG25">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK25">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.49</v>
+        <v>2.19</v>
       </c>
       <c r="O26">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P26">
-        <v>2.65</v>
+        <v>2.9</v>
       </c>
       <c r="Q26">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="R26">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="S26">
         <v>1.36</v>
       </c>
       <c r="T26">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U26">
         <v>2.75</v>
       </c>
       <c r="V26">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X26">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z26">
-        <v>3.34</v>
+        <v>3.14</v>
       </c>
       <c r="AA26">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AB26">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AC26">
-        <v>2.97</v>
+        <v>3.14</v>
       </c>
       <c r="AD26">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AE26">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF26">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AG26">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AK26">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="O27">
         <v>3.4</v>
       </c>
       <c r="P27">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q27">
         <v>2.5</v>
       </c>
       <c r="R27">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S27">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="T27">
         <v>3.2</v>
       </c>
       <c r="U27">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W27">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y27">
         <v>1.18</v>
       </c>
       <c r="Z27">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="AA27">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AC27">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD27">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AE27">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF27">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AG27">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O28">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P28">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Q28">
         <v>2.2</v>
       </c>
       <c r="R28">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T28">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U28">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="V28">
         <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AA28">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB28">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AC28">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD28">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF28">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG28">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5036,40 +5036,40 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="O29">
+        <v>3.3</v>
+      </c>
+      <c r="P29">
+        <v>2.25</v>
+      </c>
+      <c r="Q29">
         <v>3.2</v>
-      </c>
-      <c r="P29">
-        <v>2.5</v>
-      </c>
-      <c r="Q29">
-        <v>2.8</v>
       </c>
       <c r="R29">
         <v>2.25</v>
       </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="U29">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="W29">
         <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z29">
         <v>3.7</v>
@@ -5081,19 +5081,19 @@
         <v>2.05</v>
       </c>
       <c r="AC29">
-        <v>2.74</v>
+        <v>2.89</v>
       </c>
       <c r="AD29">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE29">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AG29">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.37</v>
+        <v>1.53</v>
       </c>
       <c r="AK29">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="O30">
-        <v>3.59</v>
+        <v>3.67</v>
       </c>
       <c r="P30">
-        <v>2.24</v>
+        <v>2.01</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5374,19 +5374,19 @@
         <v>2.64</v>
       </c>
       <c r="R31">
-        <v>2.11</v>
+        <v>1.96</v>
       </c>
       <c r="S31">
         <v>1.47</v>
       </c>
       <c r="T31">
-        <v>2.47</v>
+        <v>2.69</v>
       </c>
       <c r="U31">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="V31">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W31">
         <v>1.03</v>
@@ -5407,10 +5407,10 @@
         <v>1.68</v>
       </c>
       <c r="AC31">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AD31">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE31">
         <v>1.03</v>
@@ -5419,7 +5419,7 @@
         <v>1.9</v>
       </c>
       <c r="AG31">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH31" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>1.31</v>
       </c>
       <c r="AK31">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,10 +5528,10 @@
         <v>1.66</v>
       </c>
       <c r="O32">
-        <v>4.05</v>
+        <v>3.68</v>
       </c>
       <c r="P32">
-        <v>4.46</v>
+        <v>4.04</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="O33">
         <v>3.3</v>
       </c>
       <c r="P33">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q33">
         <v>3.6</v>
@@ -5706,22 +5706,22 @@
         <v>1.35</v>
       </c>
       <c r="T33">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U33">
         <v>2.69</v>
       </c>
       <c r="V33">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W33">
         <v>1.05</v>
       </c>
       <c r="X33">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y33">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z33">
         <v>3.5</v>
@@ -5736,16 +5736,16 @@
         <v>3.25</v>
       </c>
       <c r="AD33">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE33">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF33">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG33">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AK33">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -5851,10 +5851,10 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="O34">
-        <v>3.7</v>
+        <v>4.05</v>
       </c>
       <c r="P34">
         <v>3.76</v>
@@ -6014,10 +6014,10 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O35">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P35">
         <v>3.35</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="O36">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P36">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -6195,7 +6195,7 @@
         <v>1.22</v>
       </c>
       <c r="T36">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U36">
         <v>2.27</v>
@@ -6207,7 +6207,7 @@
         <v>1.14</v>
       </c>
       <c r="X36">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y36">
         <v>1.17</v>
@@ -6219,22 +6219,22 @@
         <v>1.53</v>
       </c>
       <c r="AB36">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AC36">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="AD36">
         <v>1.56</v>
       </c>
       <c r="AE36">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF36">
         <v>1.44</v>
       </c>
       <c r="AG36">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6247,10 +6247,10 @@
         </is>
       </c>
       <c r="AJ36">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6340,25 +6340,25 @@
         </is>
       </c>
       <c r="N37">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="O37">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P37">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="Q37">
         <v>4.15</v>
       </c>
       <c r="R37">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S37">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T37">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U37">
         <v>2.5</v>
@@ -6370,7 +6370,7 @@
         <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y37">
         <v>1.2</v>
@@ -6385,13 +6385,13 @@
         <v>2.15</v>
       </c>
       <c r="AC37">
-        <v>2.46</v>
+        <v>2.63</v>
       </c>
       <c r="AD37">
         <v>1.43</v>
       </c>
       <c r="AE37">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF37">
         <v>1.53</v>
@@ -6471,12 +6471,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Abu Qair Semad</t>
+          <t>Zamalek</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>National Bank of Egypt</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G38">
@@ -6503,64 +6503,64 @@
         </is>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>6.84</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="T38">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U38">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X38">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y38">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z38">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AA38">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB38">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC38">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AD38">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF38">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG38">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK38">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6634,12 +6634,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Zamalek</t>
+          <t>Abu Qair Semad</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>National Bank of Egypt</t>
         </is>
       </c>
       <c r="G39">
@@ -6666,80 +6666,80 @@
         </is>
       </c>
       <c r="N39">
-        <v>1.53</v>
+        <v>3.96</v>
       </c>
       <c r="O39">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="P39">
-        <v>5.5</v>
+        <v>1.95</v>
       </c>
       <c r="Q39">
-        <v>2.15</v>
+        <v>4.5</v>
       </c>
       <c r="R39">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="S39">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="T39">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="U39">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="V39">
+        <v>1.2</v>
+      </c>
+      <c r="W39">
+        <v>1.01</v>
+      </c>
+      <c r="X39">
+        <v>1.1</v>
+      </c>
+      <c r="Y39">
+        <v>1.57</v>
+      </c>
+      <c r="Z39">
+        <v>2.3</v>
+      </c>
+      <c r="AA39">
+        <v>2.75</v>
+      </c>
+      <c r="AB39">
+        <v>1.42</v>
+      </c>
+      <c r="AC39">
+        <v>6</v>
+      </c>
+      <c r="AD39">
+        <v>1.1</v>
+      </c>
+      <c r="AE39">
+        <v>1.03</v>
+      </c>
+      <c r="AF39">
+        <v>2.28</v>
+      </c>
+      <c r="AG39">
+        <v>1.55</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ39">
         <v>1.29</v>
       </c>
-      <c r="W39">
-        <v>1.03</v>
-      </c>
-      <c r="X39">
-        <v>1.07</v>
-      </c>
-      <c r="Y39">
-        <v>1.37</v>
-      </c>
-      <c r="Z39">
-        <v>2.66</v>
-      </c>
-      <c r="AA39">
-        <v>2.32</v>
-      </c>
-      <c r="AB39">
-        <v>1.57</v>
-      </c>
-      <c r="AC39">
-        <v>4.33</v>
-      </c>
-      <c r="AD39">
-        <v>1.2</v>
-      </c>
-      <c r="AE39">
-        <v>1.01</v>
-      </c>
-      <c r="AF39">
-        <v>2.25</v>
-      </c>
-      <c r="AG39">
-        <v>1.54</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ39">
-        <v>1.22</v>
-      </c>
       <c r="AK39">
-        <v>2.26</v>
+        <v>1.16</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -6850,28 +6850,28 @@
         <v>2.88</v>
       </c>
       <c r="U40">
-        <v>2.64</v>
+        <v>2.77</v>
       </c>
       <c r="V40">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W40">
         <v>1.04</v>
       </c>
       <c r="X40">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y40">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z40">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA40">
         <v>1.89</v>
       </c>
       <c r="AB40">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AC40">
         <v>3.08</v>
@@ -6880,7 +6880,7 @@
         <v>1.28</v>
       </c>
       <c r="AE40">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF40">
         <v>1.75</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK40">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -7318,19 +7318,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="O43">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P43">
         <v>3.49</v>
       </c>
       <c r="Q43">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R43">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S43">
         <v>1.35</v>
@@ -7357,19 +7357,19 @@
         <v>3.3</v>
       </c>
       <c r="AA43">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AB43">
         <v>1.88</v>
       </c>
       <c r="AC43">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AD43">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE43">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF43">
         <v>1.75</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AK43">
         <v>1.73</v>
@@ -7481,64 +7481,64 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="O44">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P44">
-        <v>3.79</v>
+        <v>3.7</v>
       </c>
       <c r="Q44">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="R44">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="S44">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T44">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U44">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="V44">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W44">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X44">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y44">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA44">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AB44">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="AC44">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AD44">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AE44">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF44">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG44">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AH44" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>1.2</v>
       </c>
       <c r="AK44">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7644,13 +7644,13 @@
         </is>
       </c>
       <c r="N45">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O45">
         <v>3.6</v>
       </c>
       <c r="P45">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q45">
         <v>3.4</v>
@@ -7659,10 +7659,10 @@
         <v>2.4</v>
       </c>
       <c r="S45">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="T45">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="U45">
         <v>2.17</v>
@@ -7680,7 +7680,7 @@
         <v>1.13</v>
       </c>
       <c r="Z45">
-        <v>5.44</v>
+        <v>5.5</v>
       </c>
       <c r="AA45">
         <v>1.46</v>
@@ -7689,7 +7689,7 @@
         <v>2.38</v>
       </c>
       <c r="AC45">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="AD45">
         <v>1.65</v>
@@ -7698,7 +7698,7 @@
         <v>1.25</v>
       </c>
       <c r="AF45">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AG45">
         <v>2.7</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7810,16 +7810,16 @@
         <v>3.2</v>
       </c>
       <c r="O46">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q46">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="R46">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="S46">
         <v>1.25</v>
@@ -7837,13 +7837,13 @@
         <v>1.12</v>
       </c>
       <c r="X46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z46">
-        <v>4.27</v>
+        <v>4.4</v>
       </c>
       <c r="AA46">
         <v>1.62</v>
@@ -7855,16 +7855,16 @@
         <v>2.52</v>
       </c>
       <c r="AD46">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE46">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF46">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG46">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7880,7 +7880,7 @@
         <v>1.25</v>
       </c>
       <c r="AK46">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7979,10 +7979,10 @@
         <v>2.21</v>
       </c>
       <c r="Q47">
-        <v>4.24</v>
+        <v>4.1</v>
       </c>
       <c r="R47">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S47">
         <v>1.4</v>
@@ -7994,7 +7994,7 @@
         <v>3.1</v>
       </c>
       <c r="V47">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W47">
         <v>1.07</v>
@@ -8003,31 +8003,31 @@
         <v>1.06</v>
       </c>
       <c r="Y47">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z47">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="AA47">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB47">
         <v>1.67</v>
       </c>
       <c r="AC47">
-        <v>4.02</v>
+        <v>4.1</v>
       </c>
       <c r="AD47">
         <v>1.22</v>
       </c>
       <c r="AE47">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF47">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AG47">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AH47" t="inlineStr">
         <is>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AK47">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,13 +8133,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="O48">
         <v>4</v>
       </c>
       <c r="P48">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O49">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="P49">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="Q49">
         <v>2.2</v>
@@ -8311,10 +8311,10 @@
         <v>2.46</v>
       </c>
       <c r="S49">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T49">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U49">
         <v>2.1</v>
@@ -8323,7 +8323,7 @@
         <v>1.69</v>
       </c>
       <c r="W49">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X49">
         <v>1.01</v>
@@ -8332,22 +8332,22 @@
         <v>1.13</v>
       </c>
       <c r="Z49">
-        <v>5.81</v>
+        <v>6</v>
       </c>
       <c r="AA49">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AB49">
         <v>2.65</v>
       </c>
       <c r="AC49">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AD49">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AE49">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF49">
         <v>1.44</v>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>3.38</v>
       </c>
       <c r="R51">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="S51">
         <v>1.46</v>
       </c>
       <c r="T51">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="U51">
         <v>2.91</v>
@@ -8649,7 +8649,7 @@
         <v>1.34</v>
       </c>
       <c r="W51">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X51">
         <v>1.03</v>
@@ -8658,19 +8658,19 @@
         <v>1.4</v>
       </c>
       <c r="Z51">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="AA51">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB51">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC51">
         <v>3.62</v>
       </c>
       <c r="AD51">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE51">
         <v>1.04</v>
@@ -8679,7 +8679,7 @@
         <v>1.91</v>
       </c>
       <c r="AG51">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8785,22 +8785,22 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.49</v>
+        <v>2.55</v>
       </c>
       <c r="O52">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P52">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="Q52">
-        <v>2.94</v>
+        <v>3.32</v>
       </c>
       <c r="R52">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S52">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T52">
         <v>2.8</v>
@@ -8815,7 +8815,7 @@
         <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y52">
         <v>1.34</v>
@@ -8830,10 +8830,10 @@
         <v>1.7</v>
       </c>
       <c r="AC52">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="AD52">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE52">
         <v>1.08</v>
@@ -8842,7 +8842,7 @@
         <v>1.8</v>
       </c>
       <c r="AG52">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
+        <v>1.4</v>
+      </c>
+      <c r="AK52">
         <v>1.45</v>
-      </c>
-      <c r="AK52">
-        <v>1.5</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8948,16 +8948,16 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.8</v>
+        <v>2.47</v>
       </c>
       <c r="O53">
-        <v>3.03</v>
+        <v>3.1</v>
       </c>
       <c r="P53">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="Q53">
-        <v>3.5</v>
+        <v>3.26</v>
       </c>
       <c r="R53">
         <v>2.05</v>
@@ -8966,10 +8966,10 @@
         <v>1.4</v>
       </c>
       <c r="T53">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="U53">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="V53">
         <v>1.35</v>
@@ -8999,7 +8999,7 @@
         <v>1.22</v>
       </c>
       <c r="AE53">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AF53">
         <v>1.85</v>
@@ -9018,7 +9018,7 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AK53">
         <v>1.36</v>
@@ -9111,10 +9111,10 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="O54">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="P54">
         <v>3</v>
@@ -9274,28 +9274,28 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="O55">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P55">
         <v>2.7</v>
       </c>
       <c r="Q55">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="R55">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S55">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T55">
         <v>2.89</v>
       </c>
       <c r="U55">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V55">
         <v>1.4</v>
@@ -9304,13 +9304,13 @@
         <v>1.05</v>
       </c>
       <c r="X55">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y55">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z55">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="AA55">
         <v>1.85</v>
@@ -9325,13 +9325,13 @@
         <v>1.33</v>
       </c>
       <c r="AE55">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AF55">
         <v>1.61</v>
       </c>
       <c r="AG55">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>4.91</v>
+        <v>4.75</v>
       </c>
       <c r="O56">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P56">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="Q56">
         <v>0</v>
@@ -9763,7 +9763,7 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="O58">
         <v>3.3</v>
@@ -9775,10 +9775,10 @@
         <v>2.8</v>
       </c>
       <c r="R58">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S58">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T58">
         <v>3</v>
@@ -9796,7 +9796,7 @@
         <v>1.04</v>
       </c>
       <c r="Y58">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z58">
         <v>3.94</v>
@@ -9817,7 +9817,7 @@
         <v>1.14</v>
       </c>
       <c r="AF58">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG58">
         <v>2.19</v>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AK58">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -10095,7 +10095,7 @@
         <v>3.7</v>
       </c>
       <c r="P60">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q60">
         <v>3.75</v>
@@ -10104,7 +10104,7 @@
         <v>2.45</v>
       </c>
       <c r="S60">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T60">
         <v>3.52</v>
@@ -10113,7 +10113,7 @@
         <v>2.2</v>
       </c>
       <c r="V60">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W60">
         <v>1.13</v>
@@ -10122,7 +10122,7 @@
         <v>1.04</v>
       </c>
       <c r="Y60">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z60">
         <v>5</v>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AK60">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,16 +10252,16 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="O61">
         <v>3.5</v>
       </c>
       <c r="P61">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="Q61">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="R61">
         <v>2.47</v>
@@ -10270,22 +10270,22 @@
         <v>1.25</v>
       </c>
       <c r="T61">
-        <v>3.8</v>
+        <v>3.28</v>
       </c>
       <c r="U61">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="V61">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W61">
         <v>1.11</v>
       </c>
       <c r="X61">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z61">
         <v>4.65</v>
@@ -10294,13 +10294,13 @@
         <v>1.57</v>
       </c>
       <c r="AB61">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="AC61">
         <v>2.3</v>
       </c>
       <c r="AD61">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE61">
         <v>1.22</v>
@@ -10325,7 +10325,7 @@
         <v>1.32</v>
       </c>
       <c r="AK61">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10421,10 +10421,10 @@
         <v>3.45</v>
       </c>
       <c r="P62">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q62">
-        <v>3.75</v>
+        <v>3.41</v>
       </c>
       <c r="R62">
         <v>2.37</v>
@@ -10442,13 +10442,13 @@
         <v>1.5</v>
       </c>
       <c r="W62">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X62">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y62">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z62">
         <v>4.15</v>
@@ -10457,7 +10457,7 @@
         <v>1.72</v>
       </c>
       <c r="AB62">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AC62">
         <v>2.69</v>
@@ -10472,7 +10472,7 @@
         <v>1.59</v>
       </c>
       <c r="AG62">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AK62">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,10 +10578,10 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="O63">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="P63">
         <v>2.35</v>
@@ -10590,7 +10590,7 @@
         <v>2.56</v>
       </c>
       <c r="R63">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
       <c r="S63">
         <v>1.2</v>
@@ -10599,34 +10599,34 @@
         <v>3.6</v>
       </c>
       <c r="U63">
-        <v>2.11</v>
+        <v>2.02</v>
       </c>
       <c r="V63">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W63">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="X63">
         <v>1.02</v>
       </c>
       <c r="Y63">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="Z63">
-        <v>5.69</v>
+        <v>5.65</v>
       </c>
       <c r="AA63">
         <v>1.39</v>
       </c>
       <c r="AB63">
-        <v>2.7</v>
+        <v>2.33</v>
       </c>
       <c r="AC63">
         <v>2.1</v>
       </c>
       <c r="AD63">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AE63">
         <v>1.25</v>
@@ -10635,7 +10635,7 @@
         <v>1.36</v>
       </c>
       <c r="AG63">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="AK63">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,7 +10741,7 @@
         </is>
       </c>
       <c r="N64">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="O64">
         <v>3.68</v>
@@ -10750,13 +10750,13 @@
         <v>2.75</v>
       </c>
       <c r="Q64">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="R64">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="S64">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
         <v>3.55</v>
@@ -10765,28 +10765,28 @@
         <v>2.15</v>
       </c>
       <c r="V64">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="W64">
+        <v>1.13</v>
+      </c>
+      <c r="X64">
+        <v>1.01</v>
+      </c>
+      <c r="Y64">
         <v>1.14</v>
       </c>
-      <c r="X64">
-        <v>1.02</v>
-      </c>
-      <c r="Y64">
-        <v>1.13</v>
-      </c>
       <c r="Z64">
-        <v>5.25</v>
+        <v>5.06</v>
       </c>
       <c r="AA64">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AB64">
         <v>2.49</v>
       </c>
       <c r="AC64">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="AD64">
         <v>1.6</v>
@@ -10904,28 +10904,28 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="O65">
-        <v>3.48</v>
+        <v>3.3</v>
       </c>
       <c r="P65">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q65">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="R65">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="S65">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T65">
         <v>3.3</v>
       </c>
       <c r="U65">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="V65">
         <v>1.5</v>
@@ -10943,13 +10943,13 @@
         <v>4</v>
       </c>
       <c r="AA65">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AB65">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AC65">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AD65">
         <v>1.4</v>
@@ -10961,7 +10961,7 @@
         <v>1.57</v>
       </c>
       <c r="AG65">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH65" t="inlineStr">
         <is>
@@ -11076,16 +11076,16 @@
         <v>4.8</v>
       </c>
       <c r="Q66">
-        <v>2.04</v>
+        <v>2.01</v>
       </c>
       <c r="R66">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="S66">
         <v>1.29</v>
       </c>
       <c r="T66">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U66">
         <v>2.41</v>
@@ -11097,7 +11097,7 @@
         <v>1.13</v>
       </c>
       <c r="X66">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y66">
         <v>1.18</v>
@@ -11109,22 +11109,22 @@
         <v>1.67</v>
       </c>
       <c r="AB66">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC66">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="AD66">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AE66">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="AF66">
         <v>1.7</v>
       </c>
       <c r="AG66">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK66">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11393,19 +11393,19 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="O68">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="P68">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="Q68">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R68">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S68">
         <v>1.36</v>
@@ -11420,22 +11420,22 @@
         <v>1.36</v>
       </c>
       <c r="W68">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X68">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y68">
         <v>1.3</v>
       </c>
       <c r="Z68">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="AA68">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AB68">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AC68">
         <v>3.7</v>
@@ -11444,13 +11444,13 @@
         <v>1.27</v>
       </c>
       <c r="AE68">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF68">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AG68">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK68">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11565,71 +11565,71 @@
         <v>2.7</v>
       </c>
       <c r="Q69">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="R69">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S69">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T69">
         <v>2.75</v>
       </c>
       <c r="U69">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="V69">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W69">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X69">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y69">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="Z69">
         <v>3.08</v>
       </c>
       <c r="AA69">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="AB69">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC69">
         <v>3.8</v>
       </c>
       <c r="AD69">
+        <v>1.22</v>
+      </c>
+      <c r="AE69">
+        <v>1.05</v>
+      </c>
+      <c r="AF69">
+        <v>1.8</v>
+      </c>
+      <c r="AG69">
+        <v>1.9</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ69">
         <v>1.26</v>
       </c>
-      <c r="AE69">
-        <v>1.06</v>
-      </c>
-      <c r="AF69">
-        <v>1.75</v>
-      </c>
-      <c r="AG69">
-        <v>1.93</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ69">
-        <v>1.44</v>
-      </c>
       <c r="AK69">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11722,61 +11722,61 @@
         <v>2.25</v>
       </c>
       <c r="O70">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="P70">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q70">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="R70">
         <v>2.2</v>
       </c>
       <c r="S70">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T70">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="U70">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="V70">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W70">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X70">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
         <v>1.22</v>
       </c>
       <c r="Z70">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AA70">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB70">
         <v>1.95</v>
       </c>
       <c r="AC70">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AD70">
         <v>1.36</v>
       </c>
       <c r="AE70">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AF70">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG70">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AK70">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11897,10 +11897,10 @@
         <v>2.38</v>
       </c>
       <c r="S71">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T71">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="U71">
         <v>2.4</v>
@@ -11909,7 +11909,7 @@
         <v>1.47</v>
       </c>
       <c r="W71">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X71">
         <v>1.04</v>
@@ -11921,13 +11921,13 @@
         <v>3.88</v>
       </c>
       <c r="AA71">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB71">
-        <v>2.11</v>
+        <v>2.01</v>
       </c>
       <c r="AC71">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AD71">
         <v>1.4</v>
@@ -11936,10 +11936,10 @@
         <v>1.15</v>
       </c>
       <c r="AF71">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AG71">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11955,7 +11955,7 @@
         <v>1.16</v>
       </c>
       <c r="AK71">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12045,13 +12045,13 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="O72">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P72">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="Q72">
         <v>3.04</v>
@@ -12060,40 +12060,40 @@
         <v>2.1</v>
       </c>
       <c r="S72">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T72">
         <v>2.77</v>
       </c>
       <c r="U72">
-        <v>2.54</v>
+        <v>2.63</v>
       </c>
       <c r="V72">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W72">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y72">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="Z72">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AA72">
         <v>1.78</v>
       </c>
       <c r="AB72">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AC72">
         <v>2.92</v>
       </c>
       <c r="AD72">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE72">
         <v>1.08</v>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AK72">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12374,25 +12374,25 @@
         <v>2.35</v>
       </c>
       <c r="O74">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P74">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q74">
         <v>3</v>
       </c>
       <c r="R74">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="S74">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T74">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="U74">
-        <v>2.61</v>
+        <v>2.55</v>
       </c>
       <c r="V74">
         <v>1.46</v>
@@ -12401,19 +12401,19 @@
         <v>1.11</v>
       </c>
       <c r="X74">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y74">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z74">
-        <v>3.93</v>
+        <v>3.8</v>
       </c>
       <c r="AA74">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB74">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="AC74">
         <v>2.87</v>
@@ -12422,10 +12422,10 @@
         <v>1.36</v>
       </c>
       <c r="AE74">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF74">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AG74">
         <v>2.25</v>
@@ -12537,58 +12537,58 @@
         <v>2</v>
       </c>
       <c r="O75">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P75">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q75">
         <v>2.48</v>
       </c>
       <c r="R75">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="S75">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="T75">
         <v>3.3</v>
       </c>
       <c r="U75">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V75">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W75">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X75">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="Z75">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA75">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AB75">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AC75">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="AD75">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AE75">
         <v>1.11</v>
       </c>
       <c r="AF75">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AG75">
         <v>2.1</v>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AK75">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12860,7 +12860,7 @@
         </is>
       </c>
       <c r="N77">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="O77">
         <v>3.4</v>
@@ -12875,49 +12875,49 @@
         <v>2.2</v>
       </c>
       <c r="S77">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T77">
-        <v>3.13</v>
+        <v>2.32</v>
       </c>
       <c r="U77">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="V77">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W77">
         <v>1.06</v>
       </c>
       <c r="X77">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y77">
         <v>1.25</v>
       </c>
       <c r="Z77">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="AA77">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AB77">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AC77">
         <v>3.03</v>
       </c>
       <c r="AD77">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE77">
         <v>1.12</v>
       </c>
       <c r="AF77">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG77">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -13026,28 +13026,28 @@
         <v>1.8</v>
       </c>
       <c r="O78">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P78">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="Q78">
+        <v>2.33</v>
+      </c>
+      <c r="R78">
+        <v>2.05</v>
+      </c>
+      <c r="S78">
+        <v>1.29</v>
+      </c>
+      <c r="T78">
+        <v>2.42</v>
+      </c>
+      <c r="U78">
         <v>2.45</v>
       </c>
-      <c r="R78">
-        <v>2.28</v>
-      </c>
-      <c r="S78">
-        <v>1.32</v>
-      </c>
-      <c r="T78">
-        <v>3.12</v>
-      </c>
-      <c r="U78">
-        <v>2.5</v>
-      </c>
       <c r="V78">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="W78">
         <v>1.11</v>
@@ -13056,10 +13056,10 @@
         <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
-        <v>3.87</v>
+        <v>3.95</v>
       </c>
       <c r="AA78">
         <v>1.72</v>
@@ -13096,7 +13096,7 @@
         <v>1.25</v>
       </c>
       <c r="AK78">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13189,16 +13189,16 @@
         <v>1.7</v>
       </c>
       <c r="O79">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="P79">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="Q79">
         <v>2.19</v>
       </c>
       <c r="R79">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="S79">
         <v>1.25</v>
@@ -13207,13 +13207,13 @@
         <v>3.75</v>
       </c>
       <c r="U79">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="V79">
         <v>1.64</v>
       </c>
       <c r="W79">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="X79">
         <v>1.01</v>
@@ -13222,28 +13222,28 @@
         <v>1.13</v>
       </c>
       <c r="Z79">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AA79">
         <v>1.5</v>
       </c>
       <c r="AB79">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AC79">
         <v>2.31</v>
       </c>
       <c r="AD79">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AE79">
         <v>1.22</v>
       </c>
       <c r="AF79">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG79">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AK79">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13838,13 +13838,13 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="O83">
         <v>3.2</v>
       </c>
       <c r="P83">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Q83">
         <v>0</v>
@@ -14001,25 +14001,25 @@
         </is>
       </c>
       <c r="N84">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O84">
         <v>3.5</v>
       </c>
       <c r="P84">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q84">
         <v>3.3</v>
       </c>
       <c r="R84">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S84">
         <v>1.29</v>
       </c>
       <c r="T84">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="U84">
         <v>2.3</v>
@@ -14031,7 +14031,7 @@
         <v>1.12</v>
       </c>
       <c r="X84">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y84">
         <v>1.19</v>
@@ -14040,25 +14040,25 @@
         <v>3.85</v>
       </c>
       <c r="AA84">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AB84">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
       <c r="AC84">
         <v>2.63</v>
       </c>
       <c r="AD84">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE84">
         <v>1.13</v>
       </c>
       <c r="AF84">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG84">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
+        <v>1.17</v>
+      </c>
+      <c r="AK84">
         <v>1.3</v>
-      </c>
-      <c r="AK84">
-        <v>1.26</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14176,28 +14176,28 @@
         <v>7.06</v>
       </c>
       <c r="R85">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="S85">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T85">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="U85">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="V85">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="W85">
         <v>1.11</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y85">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z85">
         <v>3.95</v>
@@ -14206,22 +14206,22 @@
         <v>1.75</v>
       </c>
       <c r="AB85">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC85">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="AD85">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AE85">
         <v>1.15</v>
       </c>
       <c r="AF85">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG85">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.21</v>
+        <v>2.4</v>
       </c>
       <c r="AK85">
         <v>1.11</v>
@@ -14333,7 +14333,7 @@
         <v>3.3</v>
       </c>
       <c r="P86">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q86">
         <v>2.75</v>
@@ -14348,43 +14348,43 @@
         <v>3</v>
       </c>
       <c r="U86">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="V86">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W86">
         <v>1.06</v>
       </c>
       <c r="X86">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y86">
         <v>1.22</v>
       </c>
       <c r="Z86">
-        <v>3.71</v>
+        <v>4.1</v>
       </c>
       <c r="AA86">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AB86">
         <v>1.98</v>
       </c>
       <c r="AC86">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD86">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE86">
         <v>1.13</v>
       </c>
       <c r="AF86">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG86">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK86">
         <v>1.6</v>
@@ -14683,7 +14683,7 @@
         <v>1.05</v>
       </c>
       <c r="X88">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y88">
         <v>1.36</v>
@@ -14695,16 +14695,16 @@
         <v>2.25</v>
       </c>
       <c r="AB88">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC88">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AD88">
         <v>1.2</v>
       </c>
       <c r="AE88">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF88">
         <v>1.85</v>
@@ -14822,55 +14822,55 @@
         <v>6.5</v>
       </c>
       <c r="P89">
-        <v>13.5</v>
+        <v>15.35</v>
       </c>
       <c r="Q89">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R89">
         <v>2.8</v>
       </c>
       <c r="S89">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="T89">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="U89">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V89">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W89">
         <v>1.15</v>
       </c>
       <c r="X89">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y89">
         <v>1.13</v>
       </c>
       <c r="Z89">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA89">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AB89">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="AC89">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AD89">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE89">
         <v>1.2</v>
       </c>
       <c r="AF89">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="AG89">
         <v>1.57</v>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="AK89">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15305,28 +15305,28 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="O92">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="P92">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="Q92">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="R92">
         <v>2.2</v>
       </c>
       <c r="S92">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T92">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="U92">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="V92">
         <v>1.44</v>
@@ -15338,31 +15338,31 @@
         <v>1.05</v>
       </c>
       <c r="Y92">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z92">
         <v>3.6</v>
       </c>
       <c r="AA92">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AB92">
         <v>1.85</v>
       </c>
       <c r="AC92">
-        <v>2.76</v>
+        <v>3.1</v>
       </c>
       <c r="AD92">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AE92">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF92">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG92">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.28</v>
+        <v>1.59</v>
       </c>
       <c r="AK92">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15468,13 +15468,13 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="O93">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="P93">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Q93">
         <v>2.63</v>
@@ -15483,13 +15483,13 @@
         <v>2.15</v>
       </c>
       <c r="S93">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T93">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="U93">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="V93">
         <v>1.39</v>
@@ -15498,22 +15498,22 @@
         <v>1.05</v>
       </c>
       <c r="X93">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y93">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z93">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA93">
         <v>2</v>
       </c>
       <c r="AB93">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AC93">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AD93">
         <v>1.29</v>
@@ -15640,16 +15640,16 @@
         <v>3.4</v>
       </c>
       <c r="Q94">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="R94">
         <v>2</v>
       </c>
       <c r="S94">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T94">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U94">
         <v>2.92</v>
@@ -15688,7 +15688,7 @@
         <v>1.82</v>
       </c>
       <c r="AG94">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK94">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15848,10 +15848,10 @@
         <v>0</v>
       </c>
       <c r="AF95">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AG95">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15978,43 +15978,43 @@
         <v>3</v>
       </c>
       <c r="U96">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="V96">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W96">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X96">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y96">
         <v>1.29</v>
       </c>
       <c r="Z96">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="AA96">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AB96">
         <v>1.8</v>
       </c>
       <c r="AC96">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AD96">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE96">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF96">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="AG96">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16455,43 +16455,43 @@
         <v>3.85</v>
       </c>
       <c r="Q99">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="R99">
-        <v>2.13</v>
+        <v>2.03</v>
       </c>
       <c r="S99">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T99">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U99">
         <v>3.1</v>
       </c>
       <c r="V99">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="W99">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X99">
         <v>1.06</v>
       </c>
       <c r="Y99">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="Z99">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="AA99">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB99">
         <v>1.68</v>
       </c>
       <c r="AC99">
-        <v>3.76</v>
+        <v>3.8</v>
       </c>
       <c r="AD99">
         <v>1.24</v>
@@ -16516,7 +16516,7 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AK99">
         <v>1.8</v>
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O102">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P102">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA102">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB102">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17424,43 +17424,43 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="O105">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P105">
         <v>6</v>
       </c>
       <c r="Q105">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="R105">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S105">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T105">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="U105">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V105">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W105">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X105">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y105">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z105">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA105">
         <v>2</v>
@@ -17469,19 +17469,19 @@
         <v>1.8</v>
       </c>
       <c r="AC105">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD105">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE105">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF105">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG105">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK105">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -18242,28 +18242,28 @@
         <v>2.15</v>
       </c>
       <c r="O110">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P110">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q110">
+        <v>2.8</v>
+      </c>
+      <c r="R110">
+        <v>2.16</v>
+      </c>
+      <c r="S110">
+        <v>1.45</v>
+      </c>
+      <c r="T110">
         <v>2.75</v>
-      </c>
-      <c r="R110">
-        <v>2</v>
-      </c>
-      <c r="S110">
-        <v>1.4</v>
-      </c>
-      <c r="T110">
-        <v>2.62</v>
       </c>
       <c r="U110">
         <v>2.8</v>
       </c>
       <c r="V110">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W110">
         <v>1.04</v>
@@ -18272,31 +18272,31 @@
         <v>1.03</v>
       </c>
       <c r="Y110">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z110">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA110">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AB110">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="AC110">
-        <v>3.9</v>
+        <v>3.86</v>
       </c>
       <c r="AD110">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AE110">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF110">
         <v>1.77</v>
       </c>
       <c r="AG110">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AK110">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18411,22 +18411,22 @@
         <v>0</v>
       </c>
       <c r="Q111">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="R111">
         <v>2.1</v>
       </c>
       <c r="S111">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T111">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="U111">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="V111">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W111">
         <v>1.06</v>
@@ -18435,10 +18435,10 @@
         <v>1</v>
       </c>
       <c r="Y111">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z111">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA111">
         <v>1.95</v>
@@ -18453,13 +18453,13 @@
         <v>1.28</v>
       </c>
       <c r="AE111">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF111">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="AG111">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>2.05</v>
+        <v>1.2</v>
       </c>
       <c r="AK111">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -19054,13 +19054,13 @@
         </is>
       </c>
       <c r="N115">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O115">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P115">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="Q115">
         <v>0</v>
@@ -19380,64 +19380,64 @@
         </is>
       </c>
       <c r="N117">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O117">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P117">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q117">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R117">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S117">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T117">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U117">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V117">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W117">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X117">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y117">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z117">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA117">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB117">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC117">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD117">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE117">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF117">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG117">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH117" t="inlineStr">
         <is>
@@ -19450,10 +19450,10 @@
         </is>
       </c>
       <c r="AJ117">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK117">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL117">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU118"/>
+  <dimension ref="A1:AU114"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -3904,10 +3904,10 @@
         <v>2.89</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="R22">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="S22">
         <v>1.33</v>
@@ -3928,19 +3928,19 @@
         <v>1</v>
       </c>
       <c r="Y22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z22">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB22">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AC22">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="AD22">
         <v>1.28</v>
@@ -3952,7 +3952,7 @@
         <v>1.63</v>
       </c>
       <c r="AG22">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="O26">
+        <v>3.4</v>
+      </c>
+      <c r="P26">
+        <v>3</v>
+      </c>
+      <c r="Q26">
+        <v>2.5</v>
+      </c>
+      <c r="R26">
+        <v>2.2</v>
+      </c>
+      <c r="S26">
+        <v>1.28</v>
+      </c>
+      <c r="T26">
         <v>3.2</v>
       </c>
-      <c r="P26">
-        <v>2.9</v>
-      </c>
-      <c r="Q26">
-        <v>2.91</v>
-      </c>
-      <c r="R26">
-        <v>2.1</v>
-      </c>
-      <c r="S26">
-        <v>1.36</v>
-      </c>
-      <c r="T26">
-        <v>2.9</v>
-      </c>
       <c r="U26">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="V26">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="W26">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="Z26">
-        <v>3.14</v>
+        <v>4.33</v>
       </c>
       <c r="AA26">
-        <v>1.98</v>
+        <v>1.62</v>
       </c>
       <c r="AB26">
-        <v>1.79</v>
+        <v>2.15</v>
       </c>
       <c r="AC26">
-        <v>3.14</v>
+        <v>2.7</v>
       </c>
       <c r="AD26">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AE26">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AF26">
-        <v>1.69</v>
+        <v>1.51</v>
       </c>
       <c r="AG26">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AK26">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,80 +4710,80 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P27">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="Q27">
+        <v>2.2</v>
+      </c>
+      <c r="R27">
+        <v>2.3</v>
+      </c>
+      <c r="S27">
+        <v>1.32</v>
+      </c>
+      <c r="T27">
+        <v>3.1</v>
+      </c>
+      <c r="U27">
         <v>2.5</v>
       </c>
-      <c r="R27">
-        <v>2.2</v>
-      </c>
-      <c r="S27">
-        <v>1.28</v>
-      </c>
-      <c r="T27">
-        <v>3.2</v>
-      </c>
-      <c r="U27">
-        <v>2.38</v>
-      </c>
       <c r="V27">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
         <v>1.02</v>
       </c>
       <c r="Y27">
+        <v>1.22</v>
+      </c>
+      <c r="Z27">
+        <v>3.85</v>
+      </c>
+      <c r="AA27">
+        <v>1.7</v>
+      </c>
+      <c r="AB27">
+        <v>2</v>
+      </c>
+      <c r="AC27">
+        <v>2.66</v>
+      </c>
+      <c r="AD27">
+        <v>1.37</v>
+      </c>
+      <c r="AE27">
+        <v>1.12</v>
+      </c>
+      <c r="AF27">
+        <v>1.67</v>
+      </c>
+      <c r="AG27">
+        <v>2.1</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
         <v>1.18</v>
       </c>
-      <c r="Z27">
-        <v>4.33</v>
-      </c>
-      <c r="AA27">
-        <v>1.62</v>
-      </c>
-      <c r="AB27">
-        <v>2.15</v>
-      </c>
-      <c r="AC27">
-        <v>2.7</v>
-      </c>
-      <c r="AD27">
-        <v>1.44</v>
-      </c>
-      <c r="AE27">
-        <v>1.18</v>
-      </c>
-      <c r="AF27">
-        <v>1.51</v>
-      </c>
-      <c r="AG27">
-        <v>2.3</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.21</v>
-      </c>
       <c r="AK27">
-        <v>1.67</v>
+        <v>2.05</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.65</v>
+        <v>2.65</v>
       </c>
       <c r="O28">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P28">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q28">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="R28">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S28">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T28">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="U28">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W28">
         <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z28">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="AA28">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB28">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AC28">
-        <v>2.66</v>
+        <v>2.89</v>
       </c>
       <c r="AD28">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE28">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG28">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="AK28">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.65</v>
+        <v>2.19</v>
       </c>
       <c r="O29">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P29">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="Q29">
-        <v>3.2</v>
+        <v>2.91</v>
       </c>
       <c r="R29">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="T29">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="U29">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V29">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W29">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X29">
         <v>1.04</v>
       </c>
       <c r="Y29">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z29">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="AA29">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AB29">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AC29">
-        <v>2.89</v>
+        <v>3.14</v>
       </c>
       <c r="AD29">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE29">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF29">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="AG29">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
+        <v>1.27</v>
+      </c>
+      <c r="AK29">
         <v>1.53</v>
-      </c>
-      <c r="AK29">
-        <v>1.4</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -7164,16 +7164,16 @@
         <v>3.5</v>
       </c>
       <c r="Q42">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R42">
         <v>2.65</v>
       </c>
       <c r="S42">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="T42">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="U42">
         <v>1.93</v>
@@ -7188,10 +7188,10 @@
         <v>1.01</v>
       </c>
       <c r="Y42">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Z42">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA42">
         <v>1.36</v>
@@ -7200,10 +7200,10 @@
         <v>2.8</v>
       </c>
       <c r="AC42">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AD42">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AE42">
         <v>1.3</v>
@@ -7225,7 +7225,7 @@
         </is>
       </c>
       <c r="AJ42">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK42">
         <v>1.98</v>
@@ -8091,7 +8091,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>BSK Banja Luka</t>
         </is>
       </c>
       <c r="G48">
@@ -8133,64 +8133,64 @@
         </is>
       </c>
       <c r="N48">
-        <v>4.2</v>
+        <v>1.45</v>
       </c>
       <c r="O48">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P48">
+        <v>6</v>
+      </c>
+      <c r="Q48">
+        <v>2.03</v>
+      </c>
+      <c r="R48">
+        <v>2.3</v>
+      </c>
+      <c r="S48">
+        <v>1.42</v>
+      </c>
+      <c r="T48">
+        <v>2.56</v>
+      </c>
+      <c r="U48">
+        <v>2.7</v>
+      </c>
+      <c r="V48">
+        <v>1.38</v>
+      </c>
+      <c r="W48">
+        <v>1.06</v>
+      </c>
+      <c r="X48">
+        <v>1.05</v>
+      </c>
+      <c r="Y48">
+        <v>1.31</v>
+      </c>
+      <c r="Z48">
+        <v>3.2</v>
+      </c>
+      <c r="AA48">
+        <v>1.95</v>
+      </c>
+      <c r="AB48">
         <v>1.75</v>
       </c>
-      <c r="Q48">
-        <v>0</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48">
-        <v>0</v>
-      </c>
-      <c r="T48">
-        <v>0</v>
-      </c>
-      <c r="U48">
-        <v>0</v>
-      </c>
-      <c r="V48">
-        <v>0</v>
-      </c>
-      <c r="W48">
-        <v>0</v>
-      </c>
-      <c r="X48">
-        <v>0</v>
-      </c>
-      <c r="Y48">
-        <v>0</v>
-      </c>
-      <c r="Z48">
-        <v>0</v>
-      </c>
-      <c r="AA48">
-        <v>1.6</v>
-      </c>
-      <c r="AB48">
-        <v>2.3</v>
-      </c>
       <c r="AC48">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD48">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE48">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF48">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG48">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK48">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8264,12 +8264,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Neom SC</t>
         </is>
       </c>
       <c r="G49">
@@ -8296,64 +8296,64 @@
         </is>
       </c>
       <c r="N49">
-        <v>1.8</v>
+        <v>4.2</v>
       </c>
       <c r="O49">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P49">
-        <v>3.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q49">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="R49">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="S49">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="T49">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="U49">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V49">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="W49">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X49">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y49">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z49">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AB49">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="AC49">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD49">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AE49">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AF49">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG49">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AK49">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8417,22 +8417,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Acassuso</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Godoy Cruz</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G50">
@@ -8459,64 +8459,64 @@
         </is>
       </c>
       <c r="N50">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="O50">
-        <v>3.05</v>
+        <v>4.2</v>
       </c>
       <c r="P50">
-        <v>2.03</v>
+        <v>3.8</v>
       </c>
       <c r="Q50">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="R50">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="S50">
-        <v>1.58</v>
+        <v>1.18</v>
       </c>
       <c r="T50">
-        <v>2.32</v>
+        <v>3.8</v>
       </c>
       <c r="U50">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="V50">
-        <v>1.2</v>
+        <v>1.69</v>
       </c>
       <c r="W50">
+        <v>1.14</v>
+      </c>
+      <c r="X50">
         <v>1.01</v>
       </c>
-      <c r="X50">
-        <v>1.11</v>
-      </c>
       <c r="Y50">
-        <v>1.54</v>
+        <v>1.13</v>
       </c>
       <c r="Z50">
-        <v>2.35</v>
+        <v>6</v>
       </c>
       <c r="AA50">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="AB50">
+        <v>2.65</v>
+      </c>
+      <c r="AC50">
+        <v>2.05</v>
+      </c>
+      <c r="AD50">
+        <v>1.72</v>
+      </c>
+      <c r="AE50">
+        <v>1.28</v>
+      </c>
+      <c r="AF50">
         <v>1.44</v>
       </c>
-      <c r="AC50">
-        <v>5.45</v>
-      </c>
-      <c r="AD50">
-        <v>1.13</v>
-      </c>
-      <c r="AE50">
-        <v>1.04</v>
-      </c>
-      <c r="AF50">
-        <v>2.15</v>
-      </c>
       <c r="AG50">
-        <v>1.57</v>
+        <v>2.5</v>
       </c>
       <c r="AH50" t="inlineStr">
         <is>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="AK50">
-        <v>1.28</v>
+        <v>1.96</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8580,22 +8580,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Acassuso</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Godoy Cruz</t>
         </is>
       </c>
       <c r="G51">
@@ -8622,64 +8622,64 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O51">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="P51">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="Q51">
-        <v>3.38</v>
+        <v>4.33</v>
       </c>
       <c r="R51">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="S51">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
       <c r="T51">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="U51">
-        <v>2.91</v>
+        <v>3.75</v>
       </c>
       <c r="V51">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="W51">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X51">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="Y51">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="Z51">
-        <v>2.88</v>
+        <v>2.35</v>
       </c>
       <c r="AA51">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AB51">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AC51">
-        <v>3.62</v>
+        <v>5.45</v>
       </c>
       <c r="AD51">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AE51">
         <v>1.04</v>
       </c>
       <c r="AF51">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AG51">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,10 +8692,10 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AK51">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AL51">
         <v>0</v>
@@ -8753,12 +8753,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G52">
@@ -8785,64 +8785,64 @@
         </is>
       </c>
       <c r="N52">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="O52">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P52">
-        <v>2.66</v>
+        <v>2.3</v>
       </c>
       <c r="Q52">
-        <v>3.32</v>
+        <v>3.6</v>
       </c>
       <c r="R52">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="S52">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T52">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="U52">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="V52">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W52">
         <v>1.07</v>
       </c>
       <c r="X52">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y52">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z52">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AA52">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AB52">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AC52">
-        <v>3.8</v>
+        <v>3.62</v>
       </c>
       <c r="AD52">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE52">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="AF52">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG52">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="AH52" t="inlineStr">
         <is>
@@ -8855,10 +8855,10 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AK52">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AL52">
         <v>0</v>
@@ -8916,12 +8916,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Guingamp</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="G53">
@@ -8948,64 +8948,64 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="O53">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P53">
-        <v>2.41</v>
+        <v>2.66</v>
       </c>
       <c r="Q53">
-        <v>3.26</v>
+        <v>3.35</v>
       </c>
       <c r="R53">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="S53">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="T53">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="U53">
         <v>3</v>
       </c>
       <c r="V53">
+        <v>1.33</v>
+      </c>
+      <c r="W53">
+        <v>1.07</v>
+      </c>
+      <c r="X53">
+        <v>1.06</v>
+      </c>
+      <c r="Y53">
         <v>1.35</v>
       </c>
-      <c r="W53">
-        <v>1.04</v>
-      </c>
-      <c r="X53">
-        <v>1.02</v>
-      </c>
-      <c r="Y53">
-        <v>1.33</v>
-      </c>
       <c r="Z53">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="AA53">
-        <v>2.18</v>
+        <v>2.05</v>
       </c>
       <c r="AB53">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AC53">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AD53">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE53">
         <v>1.08</v>
       </c>
       <c r="AF53">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG53">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="AK53">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9079,12 +9079,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Guingamp</t>
         </is>
       </c>
       <c r="G54">
@@ -9111,64 +9111,64 @@
         </is>
       </c>
       <c r="N54">
+        <v>2.85</v>
+      </c>
+      <c r="O54">
+        <v>3.2</v>
+      </c>
+      <c r="P54">
+        <v>2.35</v>
+      </c>
+      <c r="Q54">
+        <v>3.35</v>
+      </c>
+      <c r="R54">
         <v>2.05</v>
       </c>
-      <c r="O54">
-        <v>3.1</v>
-      </c>
-      <c r="P54">
+      <c r="S54">
+        <v>1.4</v>
+      </c>
+      <c r="T54">
+        <v>2.69</v>
+      </c>
+      <c r="U54">
         <v>3</v>
       </c>
-      <c r="Q54">
-        <v>0</v>
-      </c>
-      <c r="R54">
-        <v>0</v>
-      </c>
-      <c r="S54">
-        <v>0</v>
-      </c>
-      <c r="T54">
-        <v>0</v>
-      </c>
-      <c r="U54">
-        <v>0</v>
-      </c>
       <c r="V54">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W54">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X54">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y54">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z54">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AA54">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AB54">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AC54">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AD54">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE54">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF54">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG54">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH54" t="inlineStr">
         <is>
@@ -9181,10 +9181,10 @@
         </is>
       </c>
       <c r="AJ54">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK54">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL54">
         <v>0</v>
@@ -9242,12 +9242,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dunkerque</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G55">
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="O55">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P55">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="Q55">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R55">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S55">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T55">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U55">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V55">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W55">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X55">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y55">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z55">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AA55">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB55">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC55">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD55">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE55">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF55">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG55">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK55">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9395,7 +9395,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Rudeš</t>
+          <t>Dunkerque</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G56">
@@ -9437,64 +9437,64 @@
         </is>
       </c>
       <c r="N56">
-        <v>4.75</v>
+        <v>2.45</v>
       </c>
       <c r="O56">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="P56">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="Q56">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R56">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S56">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T56">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="U56">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V56">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W56">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X56">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z56">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA56">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB56">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC56">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD56">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE56">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF56">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG56">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="AJ56">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK56">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -9568,12 +9568,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RSC Anderlecht II</t>
+          <t>Rudeš</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Excelsior Virton</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="G57">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="N57">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="O57">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P57">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q57">
         <v>0</v>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>RSC Anderlecht II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Excelsior Virton</t>
         </is>
       </c>
       <c r="G58">
@@ -9763,64 +9763,64 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P58">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q58">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R58">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S58">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T58">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U58">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V58">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="W58">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X58">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y58">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z58">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AA58">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB58">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC58">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD58">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AE58">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AF58">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG58">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AH58" t="inlineStr">
         <is>
@@ -9833,10 +9833,10 @@
         </is>
       </c>
       <c r="AJ58">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AK58">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL58">
         <v>0</v>
@@ -9884,7 +9884,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -9894,12 +9894,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mornar</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G59">
@@ -9926,64 +9926,64 @@
         </is>
       </c>
       <c r="N59">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O59">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P59">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q59">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R59">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S59">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T59">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U59">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X59">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y59">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z59">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA59">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB59">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC59">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD59">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE59">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AF59">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG59">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9996,10 +9996,10 @@
         </is>
       </c>
       <c r="AJ59">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK59">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -10047,7 +10047,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -10057,12 +10057,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MVV</t>
+          <t>Mornar</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G60">
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="P60">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="Q60">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R60">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="S60">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="T60">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="U60">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="V60">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="W60">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X60">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y60">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Z60">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AA60">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AB60">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AC60">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AD60">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE60">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF60">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG60">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AK60">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10220,12 +10220,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>MVV</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="G61">
@@ -10252,64 +10252,64 @@
         </is>
       </c>
       <c r="N61">
-        <v>2.1</v>
+        <v>3.25</v>
       </c>
       <c r="O61">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P61">
-        <v>2.88</v>
+        <v>1.74</v>
       </c>
       <c r="Q61">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="R61">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="S61">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="T61">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="U61">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="V61">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W61">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X61">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y61">
         <v>1.14</v>
       </c>
       <c r="Z61">
-        <v>4.65</v>
+        <v>5</v>
       </c>
       <c r="AA61">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB61">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AC61">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="AD61">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AE61">
         <v>1.22</v>
       </c>
       <c r="AF61">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="AG61">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10322,10 +10322,10 @@
         </is>
       </c>
       <c r="AJ61">
-        <v>1.32</v>
+        <v>1.96</v>
       </c>
       <c r="AK61">
-        <v>1.64</v>
+        <v>1.19</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10383,12 +10383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G62">
@@ -10415,65 +10415,65 @@
         </is>
       </c>
       <c r="N62">
-        <v>3.52</v>
+        <v>2.1</v>
       </c>
       <c r="O62">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P62">
-        <v>1.93</v>
+        <v>2.88</v>
       </c>
       <c r="Q62">
-        <v>3.41</v>
+        <v>2.55</v>
       </c>
       <c r="R62">
-        <v>2.37</v>
+        <v>2.47</v>
       </c>
       <c r="S62">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T62">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="U62">
+        <v>2.19</v>
+      </c>
+      <c r="V62">
+        <v>1.58</v>
+      </c>
+      <c r="W62">
+        <v>1.11</v>
+      </c>
+      <c r="X62">
+        <v>1.01</v>
+      </c>
+      <c r="Y62">
+        <v>1.14</v>
+      </c>
+      <c r="Z62">
+        <v>4.65</v>
+      </c>
+      <c r="AA62">
+        <v>1.57</v>
+      </c>
+      <c r="AB62">
+        <v>2.33</v>
+      </c>
+      <c r="AC62">
+        <v>2.3</v>
+      </c>
+      <c r="AD62">
+        <v>1.53</v>
+      </c>
+      <c r="AE62">
+        <v>1.22</v>
+      </c>
+      <c r="AF62">
+        <v>1.47</v>
+      </c>
+      <c r="AG62">
         <v>2.5</v>
       </c>
-      <c r="V62">
-        <v>1.5</v>
-      </c>
-      <c r="W62">
-        <v>1.12</v>
-      </c>
-      <c r="X62">
-        <v>1.04</v>
-      </c>
-      <c r="Y62">
-        <v>1.2</v>
-      </c>
-      <c r="Z62">
-        <v>4.15</v>
-      </c>
-      <c r="AA62">
-        <v>1.72</v>
-      </c>
-      <c r="AB62">
-        <v>2.09</v>
-      </c>
-      <c r="AC62">
-        <v>2.69</v>
-      </c>
-      <c r="AD62">
-        <v>1.38</v>
-      </c>
-      <c r="AE62">
-        <v>1.14</v>
-      </c>
-      <c r="AF62">
-        <v>1.59</v>
-      </c>
-      <c r="AG62">
-        <v>2.3</v>
-      </c>
       <c r="AH62" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AK62">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10546,12 +10546,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="G63">
@@ -10578,64 +10578,64 @@
         </is>
       </c>
       <c r="N63">
-        <v>2.33</v>
+        <v>3.52</v>
       </c>
       <c r="O63">
-        <v>3.62</v>
+        <v>3.45</v>
       </c>
       <c r="P63">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="Q63">
-        <v>2.56</v>
+        <v>3.41</v>
       </c>
       <c r="R63">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="S63">
+        <v>1.3</v>
+      </c>
+      <c r="T63">
+        <v>3.3</v>
+      </c>
+      <c r="U63">
+        <v>2.5</v>
+      </c>
+      <c r="V63">
+        <v>1.5</v>
+      </c>
+      <c r="W63">
+        <v>1.12</v>
+      </c>
+      <c r="X63">
+        <v>1.04</v>
+      </c>
+      <c r="Y63">
         <v>1.2</v>
       </c>
-      <c r="T63">
-        <v>3.6</v>
-      </c>
-      <c r="U63">
-        <v>2.02</v>
-      </c>
-      <c r="V63">
-        <v>1.68</v>
-      </c>
-      <c r="W63">
-        <v>1.2</v>
-      </c>
-      <c r="X63">
-        <v>1.02</v>
-      </c>
-      <c r="Y63">
-        <v>1.08</v>
-      </c>
       <c r="Z63">
-        <v>5.65</v>
+        <v>4.15</v>
       </c>
       <c r="AA63">
-        <v>1.39</v>
+        <v>1.72</v>
       </c>
       <c r="AB63">
-        <v>2.33</v>
+        <v>2.09</v>
       </c>
       <c r="AC63">
-        <v>2.1</v>
+        <v>2.69</v>
       </c>
       <c r="AD63">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="AE63">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AF63">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="AG63">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>1.21</v>
       </c>
       <c r="AK63">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10709,12 +10709,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G64">
@@ -10741,80 +10741,80 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.06</v>
+        <v>2.33</v>
       </c>
       <c r="O64">
-        <v>3.68</v>
+        <v>3.62</v>
       </c>
       <c r="P64">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="Q64">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="R64">
-        <v>2.31</v>
+        <v>2.39</v>
       </c>
       <c r="S64">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T64">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="U64">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="V64">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="W64">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="X64">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="Z64">
-        <v>5.06</v>
+        <v>5.65</v>
       </c>
       <c r="AA64">
+        <v>1.39</v>
+      </c>
+      <c r="AB64">
+        <v>2.33</v>
+      </c>
+      <c r="AC64">
+        <v>2.1</v>
+      </c>
+      <c r="AD64">
+        <v>1.71</v>
+      </c>
+      <c r="AE64">
+        <v>1.25</v>
+      </c>
+      <c r="AF64">
+        <v>1.36</v>
+      </c>
+      <c r="AG64">
+        <v>2.9</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ64">
+        <v>1.21</v>
+      </c>
+      <c r="AK64">
         <v>1.5</v>
-      </c>
-      <c r="AB64">
-        <v>2.49</v>
-      </c>
-      <c r="AC64">
-        <v>2.3</v>
-      </c>
-      <c r="AD64">
-        <v>1.6</v>
-      </c>
-      <c r="AE64">
-        <v>1.21</v>
-      </c>
-      <c r="AF64">
-        <v>1.44</v>
-      </c>
-      <c r="AG64">
-        <v>2.55</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ64">
-        <v>1.3</v>
-      </c>
-      <c r="AK64">
-        <v>1.79</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,80 +10904,80 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.57</v>
+        <v>2.06</v>
       </c>
       <c r="O65">
-        <v>3.3</v>
+        <v>3.68</v>
       </c>
       <c r="P65">
+        <v>2.75</v>
+      </c>
+      <c r="Q65">
         <v>2.4</v>
       </c>
-      <c r="Q65">
-        <v>2.81</v>
-      </c>
       <c r="R65">
+        <v>2.31</v>
+      </c>
+      <c r="S65">
+        <v>1.22</v>
+      </c>
+      <c r="T65">
+        <v>3.55</v>
+      </c>
+      <c r="U65">
         <v>2.15</v>
       </c>
-      <c r="S65">
+      <c r="V65">
+        <v>1.61</v>
+      </c>
+      <c r="W65">
+        <v>1.13</v>
+      </c>
+      <c r="X65">
+        <v>1.01</v>
+      </c>
+      <c r="Y65">
+        <v>1.14</v>
+      </c>
+      <c r="Z65">
+        <v>5.06</v>
+      </c>
+      <c r="AA65">
+        <v>1.5</v>
+      </c>
+      <c r="AB65">
+        <v>2.49</v>
+      </c>
+      <c r="AC65">
+        <v>2.3</v>
+      </c>
+      <c r="AD65">
+        <v>1.6</v>
+      </c>
+      <c r="AE65">
+        <v>1.21</v>
+      </c>
+      <c r="AF65">
+        <v>1.44</v>
+      </c>
+      <c r="AG65">
+        <v>2.55</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ65">
         <v>1.3</v>
       </c>
-      <c r="T65">
-        <v>3.3</v>
-      </c>
-      <c r="U65">
-        <v>2.57</v>
-      </c>
-      <c r="V65">
-        <v>1.5</v>
-      </c>
-      <c r="W65">
-        <v>1.08</v>
-      </c>
-      <c r="X65">
-        <v>1</v>
-      </c>
-      <c r="Y65">
-        <v>1.22</v>
-      </c>
-      <c r="Z65">
-        <v>4</v>
-      </c>
-      <c r="AA65">
-        <v>1.72</v>
-      </c>
-      <c r="AB65">
-        <v>2.05</v>
-      </c>
-      <c r="AC65">
-        <v>2.8</v>
-      </c>
-      <c r="AD65">
-        <v>1.4</v>
-      </c>
-      <c r="AE65">
-        <v>1.12</v>
-      </c>
-      <c r="AF65">
-        <v>1.57</v>
-      </c>
-      <c r="AG65">
-        <v>2.3</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ65">
-        <v>1.28</v>
-      </c>
       <c r="AK65">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11020,12 +11020,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,64 +11067,64 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.5</v>
+        <v>2.57</v>
       </c>
       <c r="O66">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="P66">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="Q66">
-        <v>2.01</v>
+        <v>2.81</v>
       </c>
       <c r="R66">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="S66">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T66">
         <v>3.3</v>
       </c>
       <c r="U66">
-        <v>2.41</v>
+        <v>2.57</v>
       </c>
       <c r="V66">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W66">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y66">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z66">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA66">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AB66">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC66">
-        <v>2.63</v>
+        <v>2.8</v>
       </c>
       <c r="AD66">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE66">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AF66">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG66">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AH66" t="inlineStr">
         <is>
@@ -11137,10 +11137,10 @@
         </is>
       </c>
       <c r="AJ66">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AK66">
-        <v>2.38</v>
+        <v>1.48</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>2026-08-21 15:15:00</t>
+          <t>2026-08-21 15:00:00</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -11198,12 +11198,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>Nafta</t>
         </is>
       </c>
       <c r="G67">
@@ -11230,64 +11230,64 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O67">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P67">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="Q67">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="R67">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="S67">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T67">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U67">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V67">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W67">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X67">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z67">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA67">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB67">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC67">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD67">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AE67">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF67">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11300,10 +11300,10 @@
         </is>
       </c>
       <c r="AJ67">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK67">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cherno More</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dunav 2010</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="G68">
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P68">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Q68">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="R68">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S68">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T68">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U68">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V68">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W68">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X68">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y68">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z68">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA68">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB68">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC68">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD68">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AE68">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF68">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG68">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AK68">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11509,12 +11509,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -11524,12 +11524,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Vicenza</t>
+          <t>Cherno More</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>Dunav 2010</t>
         </is>
       </c>
       <c r="G69">
@@ -11556,64 +11556,64 @@
         </is>
       </c>
       <c r="N69">
-        <v>2.55</v>
+        <v>1.56</v>
       </c>
       <c r="O69">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="P69">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="Q69">
+        <v>2.1</v>
+      </c>
+      <c r="R69">
+        <v>2.16</v>
+      </c>
+      <c r="S69">
+        <v>1.36</v>
+      </c>
+      <c r="T69">
+        <v>2.59</v>
+      </c>
+      <c r="U69">
         <v>2.9</v>
-      </c>
-      <c r="R69">
-        <v>1.97</v>
-      </c>
-      <c r="S69">
-        <v>1.42</v>
-      </c>
-      <c r="T69">
-        <v>2.75</v>
-      </c>
-      <c r="U69">
-        <v>2.95</v>
       </c>
       <c r="V69">
         <v>1.36</v>
       </c>
       <c r="W69">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X69">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y69">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z69">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA69">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AB69">
         <v>1.7</v>
       </c>
       <c r="AC69">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AD69">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE69">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AF69">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AG69">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK69">
-        <v>1.41</v>
+        <v>2.2</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11660,7 +11660,7 @@
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>2026-08-21 15:30:00</t>
+          <t>2026-08-21 15:15:00</t>
         </is>
       </c>
     </row>
@@ -11677,7 +11677,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -11687,12 +11687,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Vicenza</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G70">
@@ -11719,10 +11719,10 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="O70">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P70">
         <v>2.7</v>
@@ -11731,52 +11731,52 @@
         <v>2.9</v>
       </c>
       <c r="R70">
-        <v>2.2</v>
+        <v>1.97</v>
       </c>
       <c r="S70">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="T70">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="U70">
-        <v>2.42</v>
+        <v>2.95</v>
       </c>
       <c r="V70">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W70">
         <v>1.07</v>
       </c>
       <c r="X70">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y70">
+        <v>1.28</v>
+      </c>
+      <c r="Z70">
+        <v>3.08</v>
+      </c>
+      <c r="AA70">
+        <v>2.01</v>
+      </c>
+      <c r="AB70">
+        <v>1.7</v>
+      </c>
+      <c r="AC70">
+        <v>3.8</v>
+      </c>
+      <c r="AD70">
         <v>1.22</v>
       </c>
-      <c r="Z70">
-        <v>3.8</v>
-      </c>
-      <c r="AA70">
-        <v>1.74</v>
-      </c>
-      <c r="AB70">
-        <v>1.95</v>
-      </c>
-      <c r="AC70">
-        <v>2.9</v>
-      </c>
-      <c r="AD70">
-        <v>1.36</v>
-      </c>
       <c r="AE70">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AF70">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AG70">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK70">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -11850,12 +11850,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Galatasaray</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G71">
@@ -11882,64 +11882,64 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O71">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P71">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q71">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="R71">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S71">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U71">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V71">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W71">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X71">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y71">
         <v>1.22</v>
       </c>
       <c r="Z71">
-        <v>3.88</v>
+        <v>3.8</v>
       </c>
       <c r="AA71">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AB71">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="AC71">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AD71">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE71">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF71">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="AG71">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="AH71" t="inlineStr">
         <is>
@@ -11952,10 +11952,10 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AK71">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="AL71">
         <v>0</v>
@@ -12003,7 +12003,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Galatasaray</t>
         </is>
       </c>
       <c r="G72">
@@ -12045,64 +12045,64 @@
         </is>
       </c>
       <c r="N72">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O72">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P72">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q72">
-        <v>3.04</v>
+        <v>7.2</v>
       </c>
       <c r="R72">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S72">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="T72">
-        <v>2.77</v>
+        <v>3.3</v>
       </c>
       <c r="U72">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V72">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="W72">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X72">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y72">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z72">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="AA72">
         <v>1.78</v>
       </c>
       <c r="AB72">
-        <v>1.85</v>
+        <v>2.01</v>
       </c>
       <c r="AC72">
-        <v>2.92</v>
+        <v>2.75</v>
       </c>
       <c r="AD72">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE72">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AF72">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AG72">
-        <v>2.05</v>
+        <v>1.87</v>
       </c>
       <c r="AH72" t="inlineStr">
         <is>
@@ -12115,10 +12115,10 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="AK72">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="AL72">
         <v>0</v>
@@ -12166,22 +12166,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>San Telmo</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="G73">
@@ -12208,64 +12208,64 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.78</v>
+        <v>2.49</v>
       </c>
       <c r="O73">
-        <v>2.71</v>
+        <v>3.5</v>
       </c>
       <c r="P73">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="Q73">
-        <v>3.4</v>
+        <v>3.04</v>
       </c>
       <c r="R73">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="S73">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="T73">
-        <v>2.23</v>
+        <v>2.77</v>
       </c>
       <c r="U73">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="V73">
-        <v>1.16</v>
+        <v>1.42</v>
       </c>
       <c r="W73">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X73">
-        <v>1.15</v>
+        <v>1</v>
       </c>
       <c r="Y73">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="Z73">
-        <v>2.09</v>
+        <v>3.58</v>
       </c>
       <c r="AA73">
-        <v>3.18</v>
+        <v>1.78</v>
       </c>
       <c r="AB73">
-        <v>1.31</v>
+        <v>1.85</v>
       </c>
       <c r="AC73">
-        <v>7</v>
+        <v>2.92</v>
       </c>
       <c r="AD73">
-        <v>1.1</v>
+        <v>1.34</v>
       </c>
       <c r="AE73">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF73">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AG73">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AK73">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12329,22 +12329,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>San Telmo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G74">
@@ -12371,65 +12371,65 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.35</v>
+        <v>2.76</v>
       </c>
       <c r="O74">
-        <v>3.3</v>
+        <v>2.71</v>
       </c>
       <c r="P74">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="Q74">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="R74">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="S74">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="T74">
-        <v>2.95</v>
+        <v>2.04</v>
       </c>
       <c r="U74">
-        <v>2.55</v>
+        <v>4.05</v>
       </c>
       <c r="V74">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="W74">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="X74">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="Y74">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="Z74">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="AA74">
-        <v>1.8</v>
+        <v>3.16</v>
       </c>
       <c r="AB74">
-        <v>1.98</v>
+        <v>1.31</v>
       </c>
       <c r="AC74">
-        <v>2.87</v>
+        <v>6.5</v>
       </c>
       <c r="AD74">
-        <v>1.36</v>
+        <v>1.1</v>
       </c>
       <c r="AE74">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AF74">
+        <v>2.18</v>
+      </c>
+      <c r="AG74">
         <v>1.6</v>
       </c>
-      <c r="AG74">
-        <v>2.25</v>
-      </c>
       <c r="AH74" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AK74">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cracovia Kraków</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G75">
@@ -12534,37 +12534,37 @@
         </is>
       </c>
       <c r="N75">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="O75">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P75">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q75">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="R75">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="S75">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T75">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="U75">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="V75">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W75">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X75">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y75">
         <v>1.22</v>
@@ -12573,25 +12573,25 @@
         <v>3.8</v>
       </c>
       <c r="AA75">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB75">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC75">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="AD75">
         <v>1.36</v>
       </c>
       <c r="AE75">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF75">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG75">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12604,10 +12604,10 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK75">
-        <v>1.74</v>
+        <v>1.53</v>
       </c>
       <c r="AL75">
         <v>0</v>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Fatih Karagümrük</t>
+          <t>Cracovia Kraków</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Bursaspor</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="G76">
@@ -12697,64 +12697,64 @@
         </is>
       </c>
       <c r="N76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O76">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P76">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q76">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R76">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S76">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T76">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U76">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V76">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W76">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X76">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y76">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z76">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA76">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB76">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC76">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD76">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE76">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF76">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG76">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12767,10 +12767,10 @@
         </is>
       </c>
       <c r="AJ76">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12813,12 +12813,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Fatih Karagümrük</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bursaspor</t>
         </is>
       </c>
       <c r="G77">
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O77">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P77">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q77">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R77">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S77">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="T77">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="U77">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="V77">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W77">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X77">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y77">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z77">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA77">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AB77">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AC77">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AD77">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AE77">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF77">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG77">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AK77">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12964,7 +12964,7 @@
       </c>
       <c r="AU77" t="inlineStr">
         <is>
-          <t>2026-08-21 15:45:00</t>
+          <t>2026-08-21 15:30:00</t>
         </is>
       </c>
     </row>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,61 +13023,61 @@
         </is>
       </c>
       <c r="N78">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="O78">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P78">
-        <v>3.6</v>
+        <v>1.93</v>
       </c>
       <c r="Q78">
-        <v>2.33</v>
+        <v>3.8</v>
       </c>
       <c r="R78">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S78">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="U78">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="V78">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W78">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X78">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y78">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z78">
-        <v>3.95</v>
+        <v>3.58</v>
       </c>
       <c r="AA78">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AB78">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AC78">
-        <v>2.74</v>
+        <v>3.03</v>
       </c>
       <c r="AD78">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE78">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AF78">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG78">
         <v>2.07</v>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.25</v>
+        <v>1.73</v>
       </c>
       <c r="AK78">
-        <v>1.81</v>
+        <v>1.3</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Strasbourg</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,80 +13186,80 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O79">
-        <v>4.15</v>
+        <v>3.6</v>
       </c>
       <c r="P79">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q79">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="R79">
-        <v>2.36</v>
+        <v>2.05</v>
       </c>
       <c r="S79">
+        <v>1.29</v>
+      </c>
+      <c r="T79">
+        <v>2.42</v>
+      </c>
+      <c r="U79">
+        <v>2.45</v>
+      </c>
+      <c r="V79">
+        <v>1.39</v>
+      </c>
+      <c r="W79">
+        <v>1.11</v>
+      </c>
+      <c r="X79">
+        <v>1.04</v>
+      </c>
+      <c r="Y79">
+        <v>1.22</v>
+      </c>
+      <c r="Z79">
+        <v>3.95</v>
+      </c>
+      <c r="AA79">
+        <v>1.72</v>
+      </c>
+      <c r="AB79">
+        <v>2.04</v>
+      </c>
+      <c r="AC79">
+        <v>2.74</v>
+      </c>
+      <c r="AD79">
+        <v>1.38</v>
+      </c>
+      <c r="AE79">
+        <v>1.14</v>
+      </c>
+      <c r="AF79">
+        <v>1.67</v>
+      </c>
+      <c r="AG79">
+        <v>2.07</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ79">
         <v>1.25</v>
       </c>
-      <c r="T79">
-        <v>3.75</v>
-      </c>
-      <c r="U79">
-        <v>2.26</v>
-      </c>
-      <c r="V79">
-        <v>1.64</v>
-      </c>
-      <c r="W79">
-        <v>1.15</v>
-      </c>
-      <c r="X79">
-        <v>1.01</v>
-      </c>
-      <c r="Y79">
-        <v>1.13</v>
-      </c>
-      <c r="Z79">
-        <v>5.4</v>
-      </c>
-      <c r="AA79">
-        <v>1.5</v>
-      </c>
-      <c r="AB79">
-        <v>2.5</v>
-      </c>
-      <c r="AC79">
-        <v>2.31</v>
-      </c>
-      <c r="AD79">
-        <v>1.6</v>
-      </c>
-      <c r="AE79">
-        <v>1.22</v>
-      </c>
-      <c r="AF79">
-        <v>1.53</v>
-      </c>
-      <c r="AG79">
-        <v>2.45</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ79">
-        <v>1.17</v>
-      </c>
       <c r="AK79">
-        <v>2.11</v>
+        <v>1.81</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13307,22 +13307,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Strasbourg</t>
         </is>
       </c>
       <c r="G80">
@@ -13349,64 +13349,64 @@
         </is>
       </c>
       <c r="N80">
-        <v>2.01</v>
+        <v>1.7</v>
       </c>
       <c r="O80">
-        <v>3.2</v>
+        <v>4.15</v>
       </c>
       <c r="P80">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="Q80">
-        <v>2.55</v>
+        <v>2.19</v>
       </c>
       <c r="R80">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="S80">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="T80">
-        <v>2.9</v>
+        <v>3.75</v>
       </c>
       <c r="U80">
-        <v>2.9</v>
+        <v>2.26</v>
       </c>
       <c r="V80">
-        <v>1.34</v>
+        <v>1.64</v>
       </c>
       <c r="W80">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="X80">
         <v>1.01</v>
       </c>
       <c r="Y80">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="Z80">
-        <v>3.13</v>
+        <v>5.4</v>
       </c>
       <c r="AA80">
-        <v>2.05</v>
+        <v>1.5</v>
       </c>
       <c r="AB80">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="AC80">
-        <v>3.75</v>
+        <v>2.31</v>
       </c>
       <c r="AD80">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AE80">
-        <v>1.08</v>
+        <v>1.22</v>
       </c>
       <c r="AF80">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AG80">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="AK80">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13480,12 +13480,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="G81">
@@ -13512,64 +13512,64 @@
         </is>
       </c>
       <c r="N81">
-        <v>4.5</v>
+        <v>2.02</v>
       </c>
       <c r="O81">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="P81">
-        <v>1.67</v>
+        <v>3.4</v>
       </c>
       <c r="Q81">
-        <v>5.41</v>
+        <v>2.6</v>
       </c>
       <c r="R81">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="S81">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="T81">
         <v>2.9</v>
       </c>
       <c r="U81">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="V81">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W81">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X81">
         <v>1.05</v>
       </c>
       <c r="Y81">
-        <v>1.29</v>
+        <v>1.37</v>
       </c>
       <c r="Z81">
-        <v>3.43</v>
+        <v>3.06</v>
       </c>
       <c r="AA81">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AB81">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="AC81">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD81">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AE81">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF81">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG81">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH81" t="inlineStr">
         <is>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AK81">
-        <v>1.15</v>
+        <v>1.77</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13643,12 +13643,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G82">
@@ -13675,64 +13675,64 @@
         </is>
       </c>
       <c r="N82">
-        <v>1.7</v>
+        <v>4.5</v>
       </c>
       <c r="O82">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P82">
-        <v>4</v>
+        <v>1.68</v>
       </c>
       <c r="Q82">
-        <v>2.27</v>
+        <v>5.41</v>
       </c>
       <c r="R82">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="S82">
+        <v>1.37</v>
+      </c>
+      <c r="T82">
+        <v>2.9</v>
+      </c>
+      <c r="U82">
+        <v>2.81</v>
+      </c>
+      <c r="V82">
+        <v>1.4</v>
+      </c>
+      <c r="W82">
+        <v>1.08</v>
+      </c>
+      <c r="X82">
+        <v>1.03</v>
+      </c>
+      <c r="Y82">
         <v>1.28</v>
       </c>
-      <c r="T82">
-        <v>3.4</v>
-      </c>
-      <c r="U82">
-        <v>2.38</v>
-      </c>
-      <c r="V82">
-        <v>1.53</v>
-      </c>
-      <c r="W82">
+      <c r="Z82">
+        <v>3.43</v>
+      </c>
+      <c r="AA82">
+        <v>1.85</v>
+      </c>
+      <c r="AB82">
+        <v>1.79</v>
+      </c>
+      <c r="AC82">
+        <v>3.3</v>
+      </c>
+      <c r="AD82">
+        <v>1.29</v>
+      </c>
+      <c r="AE82">
         <v>1.11</v>
       </c>
-      <c r="X82">
-        <v>1.02</v>
-      </c>
-      <c r="Y82">
-        <v>1.13</v>
-      </c>
-      <c r="Z82">
-        <v>4.68</v>
-      </c>
-      <c r="AA82">
-        <v>1.57</v>
-      </c>
-      <c r="AB82">
-        <v>2.19</v>
-      </c>
-      <c r="AC82">
-        <v>2.5</v>
-      </c>
-      <c r="AD82">
-        <v>1.44</v>
-      </c>
-      <c r="AE82">
-        <v>1.22</v>
-      </c>
       <c r="AF82">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AG82">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AH82" t="inlineStr">
         <is>
@@ -13745,10 +13745,10 @@
         </is>
       </c>
       <c r="AJ82">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>2.05</v>
+        <v>1.15</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13796,7 +13796,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -13806,12 +13806,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G83">
@@ -13838,64 +13838,64 @@
         </is>
       </c>
       <c r="N83">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="O83">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P83">
-        <v>2.37</v>
+        <v>3.8</v>
       </c>
       <c r="Q83">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="R83">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="S83">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T83">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U83">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V83">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W83">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X83">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y83">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z83">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA83">
-        <v>1.72</v>
+        <v>1.59</v>
       </c>
       <c r="AB83">
-        <v>2.07</v>
+        <v>2.19</v>
       </c>
       <c r="AC83">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD83">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE83">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF83">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG83">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH83" t="inlineStr">
         <is>
@@ -13908,10 +13908,10 @@
         </is>
       </c>
       <c r="AJ83">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK83">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
+        <v>2.6</v>
+      </c>
+      <c r="O84">
         <v>3.2</v>
       </c>
-      <c r="O84">
-        <v>3.5</v>
-      </c>
       <c r="P84">
-        <v>1.93</v>
+        <v>2.37</v>
       </c>
       <c r="Q84">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R84">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S84">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="T84">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U84">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="V84">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W84">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X84">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y84">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Z84">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA84">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AB84">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AC84">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD84">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AE84">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF84">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG84">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK84">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="O85">
         <v>3.5</v>
       </c>
       <c r="P85">
-        <v>1.5</v>
+        <v>1.93</v>
       </c>
       <c r="Q85">
-        <v>7.06</v>
+        <v>3.3</v>
       </c>
       <c r="R85">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S85">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T85">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U85">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="V85">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W85">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X85">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y85">
         <v>1.19</v>
       </c>
       <c r="Z85">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="AA85">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AB85">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AC85">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="AD85">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="AE85">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF85">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AG85">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>2.4</v>
+        <v>1.17</v>
       </c>
       <c r="AK85">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,64 +14327,64 @@
         </is>
       </c>
       <c r="N86">
-        <v>2.15</v>
+        <v>5</v>
       </c>
       <c r="O86">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P86">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="Q86">
-        <v>2.75</v>
+        <v>7.06</v>
       </c>
       <c r="R86">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S86">
         <v>1.3</v>
       </c>
       <c r="T86">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U86">
-        <v>2.71</v>
+        <v>2.4</v>
       </c>
       <c r="V86">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="W86">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X86">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y86">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z86">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AA86">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB86">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AC86">
-        <v>3.1</v>
+        <v>2.59</v>
       </c>
       <c r="AD86">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE86">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF86">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AG86">
-        <v>2.05</v>
+        <v>1.86</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>1.36</v>
+        <v>2.4</v>
       </c>
       <c r="AK86">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14448,22 +14448,22 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Standard Liège</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>RAAL La Louvière</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,65 +14490,65 @@
         </is>
       </c>
       <c r="N87">
+        <v>2.15</v>
+      </c>
+      <c r="O87">
+        <v>3.3</v>
+      </c>
+      <c r="P87">
+        <v>2.9</v>
+      </c>
+      <c r="Q87">
+        <v>2.75</v>
+      </c>
+      <c r="R87">
+        <v>2.25</v>
+      </c>
+      <c r="S87">
+        <v>1.3</v>
+      </c>
+      <c r="T87">
+        <v>3</v>
+      </c>
+      <c r="U87">
+        <v>2.71</v>
+      </c>
+      <c r="V87">
+        <v>1.44</v>
+      </c>
+      <c r="W87">
+        <v>1.06</v>
+      </c>
+      <c r="X87">
+        <v>1.04</v>
+      </c>
+      <c r="Y87">
+        <v>1.22</v>
+      </c>
+      <c r="Z87">
+        <v>4.1</v>
+      </c>
+      <c r="AA87">
+        <v>1.8</v>
+      </c>
+      <c r="AB87">
         <v>1.98</v>
       </c>
-      <c r="O87">
-        <v>3.45</v>
-      </c>
-      <c r="P87">
-        <v>3.96</v>
-      </c>
-      <c r="Q87">
-        <v>0</v>
-      </c>
-      <c r="R87">
-        <v>0</v>
-      </c>
-      <c r="S87">
-        <v>0</v>
-      </c>
-      <c r="T87">
-        <v>0</v>
-      </c>
-      <c r="U87">
-        <v>0</v>
-      </c>
-      <c r="V87">
-        <v>0</v>
-      </c>
-      <c r="W87">
-        <v>0</v>
-      </c>
-      <c r="X87">
-        <v>0</v>
-      </c>
-      <c r="Y87">
-        <v>0</v>
-      </c>
-      <c r="Z87">
-        <v>0</v>
-      </c>
-      <c r="AA87">
+      <c r="AC87">
+        <v>3.1</v>
+      </c>
+      <c r="AD87">
+        <v>1.35</v>
+      </c>
+      <c r="AE87">
+        <v>1.13</v>
+      </c>
+      <c r="AF87">
+        <v>1.67</v>
+      </c>
+      <c r="AG87">
         <v>2.05</v>
       </c>
-      <c r="AB87">
-        <v>1.75</v>
-      </c>
-      <c r="AC87">
-        <v>0</v>
-      </c>
-      <c r="AD87">
-        <v>0</v>
-      </c>
-      <c r="AE87">
-        <v>0</v>
-      </c>
-      <c r="AF87">
-        <v>0</v>
-      </c>
-      <c r="AG87">
-        <v>0</v>
-      </c>
       <c r="AH87" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK87">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14606,12 +14606,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -14621,12 +14621,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Vado</t>
+          <t>Standard Liège</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>RAAL La Louvière</t>
         </is>
       </c>
       <c r="G88">
@@ -14653,64 +14653,64 @@
         </is>
       </c>
       <c r="N88">
-        <v>3.2</v>
+        <v>1.98</v>
       </c>
       <c r="O88">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="P88">
+        <v>3.96</v>
+      </c>
+      <c r="Q88">
+        <v>0</v>
+      </c>
+      <c r="R88">
+        <v>0</v>
+      </c>
+      <c r="S88">
+        <v>0</v>
+      </c>
+      <c r="T88">
+        <v>0</v>
+      </c>
+      <c r="U88">
+        <v>0</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0</v>
+      </c>
+      <c r="X88">
+        <v>0</v>
+      </c>
+      <c r="Y88">
+        <v>0</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+      <c r="AA88">
         <v>2.05</v>
       </c>
-      <c r="Q88">
-        <v>4.14</v>
-      </c>
-      <c r="R88">
-        <v>2</v>
-      </c>
-      <c r="S88">
-        <v>1.4</v>
-      </c>
-      <c r="T88">
-        <v>2.75</v>
-      </c>
-      <c r="U88">
-        <v>3.2</v>
-      </c>
-      <c r="V88">
-        <v>1.3</v>
-      </c>
-      <c r="W88">
-        <v>1.05</v>
-      </c>
-      <c r="X88">
-        <v>1.06</v>
-      </c>
-      <c r="Y88">
-        <v>1.36</v>
-      </c>
-      <c r="Z88">
-        <v>2.88</v>
-      </c>
-      <c r="AA88">
-        <v>2.25</v>
-      </c>
       <c r="AB88">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC88">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD88">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE88">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF88">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG88">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="inlineStr">
         <is>
@@ -14723,10 +14723,10 @@
         </is>
       </c>
       <c r="AJ88">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AK88">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL88">
         <v>0</v>
@@ -14757,7 +14757,7 @@
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>2026-08-21 16:00:00</t>
+          <t>2026-08-21 15:45:00</t>
         </is>
       </c>
     </row>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -14784,12 +14784,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Vado</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G89">
@@ -14816,80 +14816,80 @@
         </is>
       </c>
       <c r="N89">
-        <v>1.19</v>
+        <v>3.2</v>
       </c>
       <c r="O89">
-        <v>6.5</v>
+        <v>3.1</v>
       </c>
       <c r="P89">
-        <v>15.35</v>
+        <v>2.05</v>
       </c>
       <c r="Q89">
-        <v>1.55</v>
+        <v>4.14</v>
       </c>
       <c r="R89">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="S89">
+        <v>1.4</v>
+      </c>
+      <c r="T89">
+        <v>2.75</v>
+      </c>
+      <c r="U89">
+        <v>3.2</v>
+      </c>
+      <c r="V89">
+        <v>1.3</v>
+      </c>
+      <c r="W89">
+        <v>1.05</v>
+      </c>
+      <c r="X89">
+        <v>1.06</v>
+      </c>
+      <c r="Y89">
+        <v>1.36</v>
+      </c>
+      <c r="Z89">
+        <v>2.88</v>
+      </c>
+      <c r="AA89">
+        <v>2.25</v>
+      </c>
+      <c r="AB89">
+        <v>1.62</v>
+      </c>
+      <c r="AC89">
+        <v>4.33</v>
+      </c>
+      <c r="AD89">
+        <v>1.2</v>
+      </c>
+      <c r="AE89">
+        <v>1.06</v>
+      </c>
+      <c r="AF89">
+        <v>1.85</v>
+      </c>
+      <c r="AG89">
+        <v>1.87</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ89">
+        <v>1.3</v>
+      </c>
+      <c r="AK89">
         <v>1.25</v>
-      </c>
-      <c r="T89">
-        <v>3.55</v>
-      </c>
-      <c r="U89">
-        <v>2.25</v>
-      </c>
-      <c r="V89">
-        <v>1.57</v>
-      </c>
-      <c r="W89">
-        <v>1.15</v>
-      </c>
-      <c r="X89">
-        <v>1.02</v>
-      </c>
-      <c r="Y89">
-        <v>1.13</v>
-      </c>
-      <c r="Z89">
-        <v>5</v>
-      </c>
-      <c r="AA89">
-        <v>1.64</v>
-      </c>
-      <c r="AB89">
-        <v>2.47</v>
-      </c>
-      <c r="AC89">
-        <v>2.31</v>
-      </c>
-      <c r="AD89">
-        <v>1.52</v>
-      </c>
-      <c r="AE89">
-        <v>1.2</v>
-      </c>
-      <c r="AF89">
-        <v>2.63</v>
-      </c>
-      <c r="AG89">
-        <v>1.57</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ89">
-        <v>1.02</v>
-      </c>
-      <c r="AK89">
-        <v>5.1</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G90">
@@ -14975,68 +14975,68 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N90">
-        <v>1.75</v>
+        <v>1.19</v>
       </c>
       <c r="O90">
-        <v>3.3</v>
+        <v>6.5</v>
       </c>
       <c r="P90">
-        <v>4</v>
+        <v>15.35</v>
       </c>
       <c r="Q90">
-        <v>2.37</v>
+        <v>1.55</v>
       </c>
       <c r="R90">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="S90">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="T90">
-        <v>2.77</v>
+        <v>3.55</v>
       </c>
       <c r="U90">
-        <v>2.77</v>
+        <v>2.25</v>
       </c>
       <c r="V90">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="W90">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="X90">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.25</v>
+        <v>1.13</v>
       </c>
       <c r="Z90">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="AA90">
-        <v>1.85</v>
+        <v>1.64</v>
       </c>
       <c r="AB90">
-        <v>1.85</v>
+        <v>2.47</v>
       </c>
       <c r="AC90">
-        <v>3.08</v>
+        <v>2.31</v>
       </c>
       <c r="AD90">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AE90">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AF90">
-        <v>1.93</v>
+        <v>2.63</v>
       </c>
       <c r="AG90">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.27</v>
+        <v>1.02</v>
       </c>
       <c r="AK90">
-        <v>1.95</v>
+        <v>5.1</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G91">
@@ -15138,68 +15138,68 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N91">
-        <v>2.89</v>
+        <v>1.75</v>
       </c>
       <c r="O91">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P91">
-        <v>2.31</v>
+        <v>4</v>
       </c>
       <c r="Q91">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="R91">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S91">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="T91">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="U91">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="V91">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W91">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X91">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y91">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="Z91">
-        <v>3.92</v>
+        <v>3.2</v>
       </c>
       <c r="AA91">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB91">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AC91">
-        <v>2.63</v>
+        <v>3.08</v>
       </c>
       <c r="AD91">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE91">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AF91">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AG91">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AH91" t="inlineStr">
         <is>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.58</v>
+        <v>1.27</v>
       </c>
       <c r="AK91">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15263,22 +15263,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G92">
@@ -15305,64 +15305,64 @@
         </is>
       </c>
       <c r="N92">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="O92">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P92">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="Q92">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R92">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S92">
         <v>1.33</v>
       </c>
       <c r="T92">
-        <v>2.77</v>
+        <v>3.04</v>
       </c>
       <c r="U92">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="V92">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W92">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X92">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y92">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z92">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA92">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB92">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AC92">
-        <v>3.1</v>
+        <v>2.63</v>
       </c>
       <c r="AD92">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AE92">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF92">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AG92">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.59</v>
+        <v>1.28</v>
       </c>
       <c r="AK92">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -15436,12 +15436,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G93">
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="O93">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P93">
-        <v>3.5</v>
+        <v>2.15</v>
       </c>
       <c r="Q93">
-        <v>2.63</v>
+        <v>3.55</v>
       </c>
       <c r="R93">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="S93">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T93">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="U93">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="V93">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W93">
+        <v>1.06</v>
+      </c>
+      <c r="X93">
         <v>1.05</v>
       </c>
-      <c r="X93">
-        <v>1.02</v>
-      </c>
       <c r="Y93">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z93">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA93">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AB93">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC93">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD93">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE93">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF93">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AG93">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,10 +15538,10 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="AK93">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="AL93">
         <v>0</v>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -15599,12 +15599,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G94">
@@ -15631,64 +15631,64 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="O94">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="P94">
+        <v>3.5</v>
+      </c>
+      <c r="Q94">
+        <v>2.63</v>
+      </c>
+      <c r="R94">
+        <v>2.15</v>
+      </c>
+      <c r="S94">
+        <v>1.38</v>
+      </c>
+      <c r="T94">
+        <v>2.8</v>
+      </c>
+      <c r="U94">
+        <v>2.73</v>
+      </c>
+      <c r="V94">
+        <v>1.39</v>
+      </c>
+      <c r="W94">
+        <v>1.05</v>
+      </c>
+      <c r="X94">
+        <v>1.02</v>
+      </c>
+      <c r="Y94">
+        <v>1.3</v>
+      </c>
+      <c r="Z94">
         <v>3.4</v>
       </c>
-      <c r="Q94">
-        <v>2.73</v>
-      </c>
-      <c r="R94">
+      <c r="AA94">
         <v>2</v>
       </c>
-      <c r="S94">
-        <v>1.4</v>
-      </c>
-      <c r="T94">
-        <v>2.75</v>
-      </c>
-      <c r="U94">
-        <v>2.92</v>
-      </c>
-      <c r="V94">
-        <v>1.32</v>
-      </c>
-      <c r="W94">
-        <v>1.06</v>
-      </c>
-      <c r="X94">
-        <v>1.03</v>
-      </c>
-      <c r="Y94">
-        <v>1.32</v>
-      </c>
-      <c r="Z94">
-        <v>2.88</v>
-      </c>
-      <c r="AA94">
-        <v>2.06</v>
-      </c>
       <c r="AB94">
-        <v>1.67</v>
+        <v>1.82</v>
       </c>
       <c r="AC94">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AD94">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE94">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF94">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="AG94">
-        <v>1.82</v>
+        <v>1.95</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15701,10 +15701,10 @@
         </is>
       </c>
       <c r="AJ94">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK94">
-        <v>1.58</v>
+        <v>1.73</v>
       </c>
       <c r="AL94">
         <v>0</v>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,80 +15794,80 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="O95">
         <v>3</v>
       </c>
       <c r="P95">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="Q95">
-        <v>2.87</v>
+        <v>2.73</v>
       </c>
       <c r="R95">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="S95">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T95">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U95">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="V95">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W95">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X95">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y95">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="Z95">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="AA95">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AB95">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AC95">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD95">
+        <v>1.22</v>
+      </c>
+      <c r="AE95">
+        <v>1.04</v>
+      </c>
+      <c r="AF95">
+        <v>1.82</v>
+      </c>
+      <c r="AG95">
+        <v>1.82</v>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ95">
         <v>1.26</v>
       </c>
-      <c r="AE95">
-        <v>0</v>
-      </c>
-      <c r="AF95">
-        <v>1.79</v>
-      </c>
-      <c r="AG95">
-        <v>1.98</v>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ95">
-        <v>0</v>
-      </c>
       <c r="AK95">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,64 +15957,64 @@
         </is>
       </c>
       <c r="N96">
-        <v>1.39</v>
+        <v>2.27</v>
       </c>
       <c r="O96">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="P96">
-        <v>6.76</v>
+        <v>3.15</v>
       </c>
       <c r="Q96">
-        <v>1.88</v>
+        <v>2.87</v>
       </c>
       <c r="R96">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="S96">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="T96">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U96">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
       <c r="V96">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="W96">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X96">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y96">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z96">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="AA96">
-        <v>1.91</v>
+        <v>2.04</v>
       </c>
       <c r="AB96">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AC96">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="AD96">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AE96">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF96">
-        <v>2.27</v>
+        <v>1.79</v>
       </c>
       <c r="AG96">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="AH96" t="inlineStr">
         <is>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AK96">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16078,7 +16078,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,64 +16120,64 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="O97">
-        <v>2.9</v>
+        <v>4.5</v>
       </c>
       <c r="P97">
-        <v>3.05</v>
+        <v>6.76</v>
       </c>
       <c r="Q97">
-        <v>3.12</v>
+        <v>1.88</v>
       </c>
       <c r="R97">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="S97">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="T97">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="U97">
+        <v>2.75</v>
+      </c>
+      <c r="V97">
+        <v>1.4</v>
+      </c>
+      <c r="W97">
+        <v>1.08</v>
+      </c>
+      <c r="X97">
+        <v>1.03</v>
+      </c>
+      <c r="Y97">
+        <v>1.29</v>
+      </c>
+      <c r="Z97">
+        <v>3.25</v>
+      </c>
+      <c r="AA97">
+        <v>1.91</v>
+      </c>
+      <c r="AB97">
+        <v>1.8</v>
+      </c>
+      <c r="AC97">
         <v>3.2</v>
       </c>
-      <c r="V97">
-        <v>1.27</v>
-      </c>
-      <c r="W97">
-        <v>1.04</v>
-      </c>
-      <c r="X97">
-        <v>1.07</v>
-      </c>
-      <c r="Y97">
-        <v>1.4</v>
-      </c>
-      <c r="Z97">
-        <v>2.88</v>
-      </c>
-      <c r="AA97">
-        <v>2.23</v>
-      </c>
-      <c r="AB97">
-        <v>1.57</v>
-      </c>
-      <c r="AC97">
-        <v>4.5</v>
-      </c>
       <c r="AD97">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AE97">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF97">
-        <v>1.87</v>
+        <v>2.27</v>
       </c>
       <c r="AG97">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AK97">
-        <v>1.46</v>
+        <v>3</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16251,12 +16251,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G98">
@@ -16283,64 +16283,64 @@
         </is>
       </c>
       <c r="N98">
-        <v>1.25</v>
+        <v>2.3</v>
       </c>
       <c r="O98">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="P98">
-        <v>8.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q98">
-        <v>1.75</v>
+        <v>3.12</v>
       </c>
       <c r="R98">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="S98">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="T98">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="U98">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="V98">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="W98">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X98">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y98">
+        <v>1.4</v>
+      </c>
+      <c r="Z98">
+        <v>2.88</v>
+      </c>
+      <c r="AA98">
+        <v>2.23</v>
+      </c>
+      <c r="AB98">
+        <v>1.57</v>
+      </c>
+      <c r="AC98">
+        <v>4.5</v>
+      </c>
+      <c r="AD98">
         <v>1.2</v>
       </c>
-      <c r="Z98">
-        <v>4.33</v>
-      </c>
-      <c r="AA98">
-        <v>1.67</v>
-      </c>
-      <c r="AB98">
-        <v>2.15</v>
-      </c>
-      <c r="AC98">
-        <v>2.7</v>
-      </c>
-      <c r="AD98">
-        <v>1.44</v>
-      </c>
       <c r="AE98">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AF98">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="AG98">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AK98">
-        <v>3.4</v>
+        <v>1.46</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16399,12 +16399,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -16414,12 +16414,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G99">
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.86</v>
+        <v>1.25</v>
       </c>
       <c r="O99">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="P99">
-        <v>3.85</v>
+        <v>8.1</v>
       </c>
       <c r="Q99">
+        <v>1.75</v>
+      </c>
+      <c r="R99">
         <v>2.5</v>
       </c>
-      <c r="R99">
-        <v>2.03</v>
-      </c>
       <c r="S99">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="T99">
-        <v>2.73</v>
+        <v>3.25</v>
       </c>
       <c r="U99">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="V99">
-        <v>1.31</v>
+        <v>1.5</v>
       </c>
       <c r="W99">
+        <v>1.11</v>
+      </c>
+      <c r="X99">
         <v>1.02</v>
       </c>
-      <c r="X99">
-        <v>1.06</v>
-      </c>
       <c r="Y99">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="Z99">
-        <v>2.92</v>
+        <v>4.33</v>
       </c>
       <c r="AA99">
+        <v>1.67</v>
+      </c>
+      <c r="AB99">
+        <v>2.15</v>
+      </c>
+      <c r="AC99">
+        <v>2.7</v>
+      </c>
+      <c r="AD99">
+        <v>1.44</v>
+      </c>
+      <c r="AE99">
+        <v>1.14</v>
+      </c>
+      <c r="AF99">
         <v>2.1</v>
       </c>
-      <c r="AB99">
-        <v>1.68</v>
-      </c>
-      <c r="AC99">
-        <v>3.8</v>
-      </c>
-      <c r="AD99">
-        <v>1.24</v>
-      </c>
-      <c r="AE99">
-        <v>1.02</v>
-      </c>
-      <c r="AF99">
-        <v>1.89</v>
-      </c>
       <c r="AG99">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK99">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="AL99">
         <v>0</v>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>2026-08-21 16:15:00</t>
+          <t>2026-08-21 16:00:00</t>
         </is>
       </c>
     </row>
@@ -16562,12 +16562,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -16577,12 +16577,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Fafe</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitória Guimarães II</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="G100">
@@ -16609,64 +16609,64 @@
         </is>
       </c>
       <c r="N100">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O100">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P100">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q100">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R100">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S100">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T100">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U100">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V100">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W100">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X100">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y100">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z100">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA100">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB100">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC100">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD100">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE100">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF100">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG100">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH100" t="inlineStr">
         <is>
@@ -16679,10 +16679,10 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK100">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL100">
         <v>0</v>
@@ -16713,7 +16713,7 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>2026-08-21 16:30:00</t>
+          <t>2026-08-21 16:15:00</t>
         </is>
       </c>
     </row>
@@ -16725,27 +16725,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Deportivo Madryn</t>
+          <t>Fafe</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Vitória Guimarães II</t>
         </is>
       </c>
       <c r="G101">
@@ -16772,13 +16772,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O101">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P101">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q101">
         <v>0</v>
@@ -16811,10 +16811,10 @@
         <v>0</v>
       </c>
       <c r="AA101">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AB101">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC101">
         <v>0</v>
@@ -16876,7 +16876,7 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>2026-08-21 19:00:00</t>
+          <t>2026-08-21 16:30:00</t>
         </is>
       </c>
     </row>
@@ -16888,12 +16888,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -16903,12 +16903,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>The Strongest</t>
+          <t>Deportivo Madryn</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G102">
@@ -16935,64 +16935,64 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.15</v>
+        <v>1.89</v>
       </c>
       <c r="O102">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P102">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="Q102">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="R102">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S102">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="T102">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="U102">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V102">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="W102">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X102">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y102">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Z102">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA102">
-        <v>1.36</v>
+        <v>2.87</v>
       </c>
       <c r="AB102">
-        <v>3.1</v>
+        <v>1.4</v>
       </c>
       <c r="AC102">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD102">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AE102">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AF102">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG102">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK102">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="AL102">
         <v>0</v>
@@ -17039,7 +17039,7 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>2026-08-21 19:30:00</t>
+          <t>2026-08-21 19:00:00</t>
         </is>
       </c>
     </row>
@@ -17051,27 +17051,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>The Strongest</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="G103">
@@ -17098,64 +17098,64 @@
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O103">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P103">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q103">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="R103">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S103">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T103">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="U103">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="V103">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="W103">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X103">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Z103">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA103">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB103">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC103">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD103">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE103">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AF103">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG103">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK103">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 19:30:00</t>
         </is>
       </c>
     </row>
@@ -17219,7 +17219,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Raków Częstochowa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Górnik Zabrze</t>
         </is>
       </c>
       <c r="G104">
@@ -17382,7 +17382,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Ferencváros</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>BSK Banja Luka</t>
+          <t>Honvéd</t>
         </is>
       </c>
       <c r="G105">
@@ -17424,64 +17424,64 @@
         </is>
       </c>
       <c r="N105">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="O105">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="P105">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q105">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="R105">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S105">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T105">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="U105">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="V105">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W105">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X105">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y105">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z105">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA105">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB105">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC105">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AD105">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE105">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF105">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG105">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH105" t="inlineStr">
         <is>
@@ -17494,10 +17494,10 @@
         </is>
       </c>
       <c r="AJ105">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK105">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL105">
         <v>0</v>
@@ -17545,22 +17545,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Mushuc Runa SC</t>
         </is>
       </c>
       <c r="G106">
@@ -17587,64 +17587,64 @@
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O106">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P106">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q106">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R106">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S106">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="T106">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U106">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V106">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W106">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y106">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z106">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA106">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB106">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC106">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AD106">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE106">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF106">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG106">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH106" t="inlineStr">
         <is>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK106">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17708,22 +17708,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Leones del Norte</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Čelik</t>
+          <t>CSD Independiente del Valle</t>
         </is>
       </c>
       <c r="G107">
@@ -17759,55 +17759,55 @@
         <v>0</v>
       </c>
       <c r="Q107">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R107">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S107">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T107">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U107">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="V107">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W107">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y107">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z107">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA107">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB107">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC107">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AD107">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE107">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF107">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG107">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AH107" t="inlineStr">
         <is>
@@ -17820,10 +17820,10 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK107">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AL107">
         <v>0</v>
@@ -17871,7 +17871,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -17881,12 +17881,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Raków Częstochowa</t>
+          <t>Hapoel Be'er Sheva</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Górnik Zabrze</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="G108">
@@ -18034,7 +18034,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -18044,12 +18044,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ferencváros</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Honvéd</t>
+          <t>Beitar Jerusalem</t>
         </is>
       </c>
       <c r="G109">
@@ -18197,22 +18197,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Dinamo Zagreb II</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mushuc Runa SC</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G110">
@@ -18239,64 +18239,64 @@
         </is>
       </c>
       <c r="N110">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="O110">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P110">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q110">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R110">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="S110">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="T110">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U110">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V110">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W110">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X110">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y110">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z110">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA110">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB110">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC110">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AD110">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE110">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF110">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG110">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH110" t="inlineStr">
         <is>
@@ -18309,10 +18309,10 @@
         </is>
       </c>
       <c r="AJ110">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AK110">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AL110">
         <v>0</v>
@@ -18355,12 +18355,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -18370,12 +18370,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Leones del Norte</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CSD Independiente del Valle</t>
+          <t>Rangers</t>
         </is>
       </c>
       <c r="G111">
@@ -18402,64 +18402,64 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O111">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P111">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q111">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R111">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S111">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T111">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U111">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="V111">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W111">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y111">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z111">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA111">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB111">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC111">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AD111">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE111">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AF111">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG111">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AH111" t="inlineStr">
         <is>
@@ -18472,10 +18472,10 @@
         </is>
       </c>
       <c r="AJ111">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AK111">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AL111">
         <v>0</v>
@@ -18506,7 +18506,7 @@
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -18518,27 +18518,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Hapoel Be'er Sheva</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Unión La Calera</t>
         </is>
       </c>
       <c r="G112">
@@ -18565,64 +18565,64 @@
         </is>
       </c>
       <c r="N112">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="O112">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P112">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q112">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R112">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S112">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T112">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U112">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V112">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W112">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X112">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y112">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z112">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA112">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB112">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC112">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AD112">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE112">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF112">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG112">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18635,10 +18635,10 @@
         </is>
       </c>
       <c r="AJ112">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK112">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL112">
         <v>0</v>
@@ -18669,7 +18669,7 @@
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -18681,27 +18681,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Oriente Petrolero</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Beitar Jerusalem</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G113">
@@ -18728,64 +18728,64 @@
         </is>
       </c>
       <c r="N113">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O113">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="P113">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q113">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R113">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S113">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T113">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U113">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V113">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="W113">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="X113">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z113">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA113">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB113">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AC113">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AD113">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AE113">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF113">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG113">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK113">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18832,7 +18832,7 @@
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>2026-08-21 21:00:00</t>
+          <t>2026-08-21 21:30:00</t>
         </is>
       </c>
     </row>
@@ -18844,27 +18844,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb II</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G114">
@@ -18891,64 +18891,64 @@
         </is>
       </c>
       <c r="N114">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O114">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P114">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="Q114">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R114">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S114">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T114">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U114">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="V114">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W114">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X114">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y114">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z114">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA114">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC114">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD114">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE114">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF114">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG114">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,10 +18961,10 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK114">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AL114">
         <v>0</v>
@@ -18994,658 +18994,6 @@
         <v>0</v>
       </c>
       <c r="AU114" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>San Marcos</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>Rangers</t>
-        </is>
-      </c>
-      <c r="G115">
-        <v>0</v>
-      </c>
-      <c r="H115">
-        <v>0</v>
-      </c>
-      <c r="I115">
-        <v>0</v>
-      </c>
-      <c r="J115">
-        <v>0</v>
-      </c>
-      <c r="K115">
-        <v>0</v>
-      </c>
-      <c r="L115">
-        <v>0</v>
-      </c>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N115">
-        <v>1.82</v>
-      </c>
-      <c r="O115">
-        <v>3.55</v>
-      </c>
-      <c r="P115">
-        <v>4</v>
-      </c>
-      <c r="Q115">
-        <v>0</v>
-      </c>
-      <c r="R115">
-        <v>0</v>
-      </c>
-      <c r="S115">
-        <v>0</v>
-      </c>
-      <c r="T115">
-        <v>0</v>
-      </c>
-      <c r="U115">
-        <v>0</v>
-      </c>
-      <c r="V115">
-        <v>0</v>
-      </c>
-      <c r="W115">
-        <v>0</v>
-      </c>
-      <c r="X115">
-        <v>0</v>
-      </c>
-      <c r="Y115">
-        <v>0</v>
-      </c>
-      <c r="Z115">
-        <v>0</v>
-      </c>
-      <c r="AA115">
-        <v>0</v>
-      </c>
-      <c r="AB115">
-        <v>0</v>
-      </c>
-      <c r="AC115">
-        <v>0</v>
-      </c>
-      <c r="AD115">
-        <v>0</v>
-      </c>
-      <c r="AE115">
-        <v>0</v>
-      </c>
-      <c r="AF115">
-        <v>0</v>
-      </c>
-      <c r="AG115">
-        <v>0</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ115">
-        <v>0</v>
-      </c>
-      <c r="AK115">
-        <v>0</v>
-      </c>
-      <c r="AL115">
-        <v>0</v>
-      </c>
-      <c r="AM115">
-        <v>-1</v>
-      </c>
-      <c r="AN115">
-        <v>-1</v>
-      </c>
-      <c r="AO115">
-        <v>-1</v>
-      </c>
-      <c r="AP115">
-        <v>-1</v>
-      </c>
-      <c r="AQ115">
-        <v>0</v>
-      </c>
-      <c r="AR115">
-        <v>0</v>
-      </c>
-      <c r="AS115">
-        <v>0</v>
-      </c>
-      <c r="AT115">
-        <v>0</v>
-      </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Chile Primera División</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>Unión La Calera</t>
-        </is>
-      </c>
-      <c r="G116">
-        <v>0</v>
-      </c>
-      <c r="H116">
-        <v>0</v>
-      </c>
-      <c r="I116">
-        <v>0</v>
-      </c>
-      <c r="J116">
-        <v>0</v>
-      </c>
-      <c r="K116">
-        <v>0</v>
-      </c>
-      <c r="L116">
-        <v>0</v>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N116">
-        <v>1.85</v>
-      </c>
-      <c r="O116">
-        <v>3.2</v>
-      </c>
-      <c r="P116">
-        <v>3.97</v>
-      </c>
-      <c r="Q116">
-        <v>2.48</v>
-      </c>
-      <c r="R116">
-        <v>2.01</v>
-      </c>
-      <c r="S116">
-        <v>1.4</v>
-      </c>
-      <c r="T116">
-        <v>2.75</v>
-      </c>
-      <c r="U116">
-        <v>2.9</v>
-      </c>
-      <c r="V116">
-        <v>1.4</v>
-      </c>
-      <c r="W116">
-        <v>1.07</v>
-      </c>
-      <c r="X116">
-        <v>1.01</v>
-      </c>
-      <c r="Y116">
-        <v>1.29</v>
-      </c>
-      <c r="Z116">
-        <v>3.25</v>
-      </c>
-      <c r="AA116">
-        <v>2.07</v>
-      </c>
-      <c r="AB116">
-        <v>1.74</v>
-      </c>
-      <c r="AC116">
-        <v>3.61</v>
-      </c>
-      <c r="AD116">
-        <v>1.22</v>
-      </c>
-      <c r="AE116">
-        <v>1.05</v>
-      </c>
-      <c r="AF116">
-        <v>1.85</v>
-      </c>
-      <c r="AG116">
-        <v>1.87</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ116">
-        <v>1.3</v>
-      </c>
-      <c r="AK116">
-        <v>1.83</v>
-      </c>
-      <c r="AL116">
-        <v>0</v>
-      </c>
-      <c r="AM116">
-        <v>-1</v>
-      </c>
-      <c r="AN116">
-        <v>-1</v>
-      </c>
-      <c r="AO116">
-        <v>-1</v>
-      </c>
-      <c r="AP116">
-        <v>-1</v>
-      </c>
-      <c r="AQ116">
-        <v>0</v>
-      </c>
-      <c r="AR116">
-        <v>0</v>
-      </c>
-      <c r="AS116">
-        <v>0</v>
-      </c>
-      <c r="AT116">
-        <v>0</v>
-      </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Bolivia LFPB</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Oriente Petrolero</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>San Antonio Bulo Bulo</t>
-        </is>
-      </c>
-      <c r="G117">
-        <v>0</v>
-      </c>
-      <c r="H117">
-        <v>0</v>
-      </c>
-      <c r="I117">
-        <v>0</v>
-      </c>
-      <c r="J117">
-        <v>0</v>
-      </c>
-      <c r="K117">
-        <v>0</v>
-      </c>
-      <c r="L117">
-        <v>0</v>
-      </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N117">
-        <v>1.46</v>
-      </c>
-      <c r="O117">
-        <v>4.33</v>
-      </c>
-      <c r="P117">
-        <v>5.25</v>
-      </c>
-      <c r="Q117">
-        <v>1.83</v>
-      </c>
-      <c r="R117">
-        <v>2.7</v>
-      </c>
-      <c r="S117">
-        <v>1.2</v>
-      </c>
-      <c r="T117">
-        <v>4</v>
-      </c>
-      <c r="U117">
-        <v>2.02</v>
-      </c>
-      <c r="V117">
-        <v>1.7</v>
-      </c>
-      <c r="W117">
-        <v>1.19</v>
-      </c>
-      <c r="X117">
-        <v>1.02</v>
-      </c>
-      <c r="Y117">
-        <v>1.1</v>
-      </c>
-      <c r="Z117">
-        <v>6.5</v>
-      </c>
-      <c r="AA117">
-        <v>1.36</v>
-      </c>
-      <c r="AB117">
-        <v>2.7</v>
-      </c>
-      <c r="AC117">
-        <v>1.99</v>
-      </c>
-      <c r="AD117">
-        <v>1.7</v>
-      </c>
-      <c r="AE117">
-        <v>1.3</v>
-      </c>
-      <c r="AF117">
-        <v>1.51</v>
-      </c>
-      <c r="AG117">
-        <v>2.36</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ117">
-        <v>1.1</v>
-      </c>
-      <c r="AK117">
-        <v>2.25</v>
-      </c>
-      <c r="AL117">
-        <v>0</v>
-      </c>
-      <c r="AM117">
-        <v>-1</v>
-      </c>
-      <c r="AN117">
-        <v>-1</v>
-      </c>
-      <c r="AO117">
-        <v>-1</v>
-      </c>
-      <c r="AP117">
-        <v>-1</v>
-      </c>
-      <c r="AQ117">
-        <v>0</v>
-      </c>
-      <c r="AR117">
-        <v>0</v>
-      </c>
-      <c r="AS117">
-        <v>0</v>
-      </c>
-      <c r="AT117">
-        <v>0</v>
-      </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>2026-08-21 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>2026-08-21</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>San Diego Wave</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Utah Royals</t>
-        </is>
-      </c>
-      <c r="G118">
-        <v>0</v>
-      </c>
-      <c r="H118">
-        <v>0</v>
-      </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>0</v>
-      </c>
-      <c r="L118">
-        <v>0</v>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N118">
-        <v>1.89</v>
-      </c>
-      <c r="O118">
-        <v>3.54</v>
-      </c>
-      <c r="P118">
-        <v>3.45</v>
-      </c>
-      <c r="Q118">
-        <v>2.5</v>
-      </c>
-      <c r="R118">
-        <v>2.3</v>
-      </c>
-      <c r="S118">
-        <v>1.29</v>
-      </c>
-      <c r="T118">
-        <v>2.99</v>
-      </c>
-      <c r="U118">
-        <v>2.52</v>
-      </c>
-      <c r="V118">
-        <v>1.45</v>
-      </c>
-      <c r="W118">
-        <v>1.08</v>
-      </c>
-      <c r="X118">
-        <v>1.04</v>
-      </c>
-      <c r="Y118">
-        <v>1.18</v>
-      </c>
-      <c r="Z118">
-        <v>3.8</v>
-      </c>
-      <c r="AA118">
-        <v>1.7</v>
-      </c>
-      <c r="AB118">
-        <v>2</v>
-      </c>
-      <c r="AC118">
-        <v>2.75</v>
-      </c>
-      <c r="AD118">
-        <v>1.36</v>
-      </c>
-      <c r="AE118">
-        <v>1.1</v>
-      </c>
-      <c r="AF118">
-        <v>1.58</v>
-      </c>
-      <c r="AG118">
-        <v>2.16</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ118">
-        <v>1.22</v>
-      </c>
-      <c r="AK118">
-        <v>1.6</v>
-      </c>
-      <c r="AL118">
-        <v>0</v>
-      </c>
-      <c r="AM118">
-        <v>-1</v>
-      </c>
-      <c r="AN118">
-        <v>-1</v>
-      </c>
-      <c r="AO118">
-        <v>-1</v>
-      </c>
-      <c r="AP118">
-        <v>-1</v>
-      </c>
-      <c r="AQ118">
-        <v>0</v>
-      </c>
-      <c r="AR118">
-        <v>0</v>
-      </c>
-      <c r="AS118">
-        <v>0</v>
-      </c>
-      <c r="AT118">
-        <v>0</v>
-      </c>
-      <c r="AU118" t="inlineStr">
         <is>
           <t>2026-08-21 23:00:00</t>
         </is>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="O7">
         <v>3.3</v>
       </c>
       <c r="P7">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="O11">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="P11">
-        <v>8.4</v>
+        <v>7.47</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -5365,10 +5365,10 @@
         <v>1.99</v>
       </c>
       <c r="O31">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="P31">
-        <v>3.7</v>
+        <v>3.28</v>
       </c>
       <c r="Q31">
         <v>2.64</v>
@@ -5380,7 +5380,7 @@
         <v>1.47</v>
       </c>
       <c r="T31">
-        <v>2.69</v>
+        <v>2.47</v>
       </c>
       <c r="U31">
         <v>3.1</v>
@@ -5401,16 +5401,16 @@
         <v>2.74</v>
       </c>
       <c r="AA31">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB31">
         <v>1.68</v>
       </c>
       <c r="AC31">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AD31">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE31">
         <v>1.03</v>
@@ -16283,31 +16283,31 @@
         </is>
       </c>
       <c r="N98">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="O98">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="P98">
-        <v>3.05</v>
+        <v>2.7</v>
       </c>
       <c r="Q98">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="R98">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="S98">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="T98">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="U98">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="V98">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="W98">
         <v>1.04</v>
@@ -16316,31 +16316,31 @@
         <v>1.07</v>
       </c>
       <c r="Y98">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Z98">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="AA98">
-        <v>2.23</v>
+        <v>2.49</v>
       </c>
       <c r="AB98">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AC98">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AD98">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE98">
         <v>1.05</v>
       </c>
       <c r="AF98">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="AG98">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AH98" t="inlineStr">
         <is>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK98">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,64 +16446,64 @@
         </is>
       </c>
       <c r="N99">
+        <v>1.28</v>
+      </c>
+      <c r="O99">
+        <v>4.6</v>
+      </c>
+      <c r="P99">
+        <v>8.5</v>
+      </c>
+      <c r="Q99">
+        <v>1.77</v>
+      </c>
+      <c r="R99">
+        <v>2.38</v>
+      </c>
+      <c r="S99">
+        <v>1.33</v>
+      </c>
+      <c r="T99">
+        <v>3.2</v>
+      </c>
+      <c r="U99">
+        <v>2.6</v>
+      </c>
+      <c r="V99">
+        <v>1.4</v>
+      </c>
+      <c r="W99">
+        <v>1.1</v>
+      </c>
+      <c r="X99">
+        <v>1.03</v>
+      </c>
+      <c r="Y99">
         <v>1.25</v>
       </c>
-      <c r="O99">
-        <v>5</v>
-      </c>
-      <c r="P99">
-        <v>8.1</v>
-      </c>
-      <c r="Q99">
-        <v>1.75</v>
-      </c>
-      <c r="R99">
-        <v>2.5</v>
-      </c>
-      <c r="S99">
-        <v>1.29</v>
-      </c>
-      <c r="T99">
-        <v>3.25</v>
-      </c>
-      <c r="U99">
-        <v>2.5</v>
-      </c>
-      <c r="V99">
-        <v>1.5</v>
-      </c>
-      <c r="W99">
+      <c r="Z99">
+        <v>3.8</v>
+      </c>
+      <c r="AA99">
+        <v>1.8</v>
+      </c>
+      <c r="AB99">
+        <v>1.93</v>
+      </c>
+      <c r="AC99">
+        <v>3.1</v>
+      </c>
+      <c r="AD99">
+        <v>1.36</v>
+      </c>
+      <c r="AE99">
         <v>1.11</v>
       </c>
-      <c r="X99">
-        <v>1.02</v>
-      </c>
-      <c r="Y99">
-        <v>1.2</v>
-      </c>
-      <c r="Z99">
-        <v>4.33</v>
-      </c>
-      <c r="AA99">
-        <v>1.67</v>
-      </c>
-      <c r="AB99">
-        <v>2.15</v>
-      </c>
-      <c r="AC99">
-        <v>2.7</v>
-      </c>
-      <c r="AD99">
-        <v>1.44</v>
-      </c>
-      <c r="AE99">
-        <v>1.14</v>
-      </c>
       <c r="AF99">
-        <v>2.1</v>
+        <v>2.22</v>
       </c>
       <c r="AG99">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>
@@ -16516,10 +16516,10 @@
         </is>
       </c>
       <c r="AJ99">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AK99">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AL99">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -638,34 +638,34 @@
         <v>3.7</v>
       </c>
       <c r="O2">
-        <v>3.65</v>
+        <v>3.38</v>
       </c>
       <c r="P2">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="Q2">
         <v>4.2</v>
       </c>
       <c r="R2">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S2">
         <v>1.29</v>
       </c>
       <c r="T2">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="U2">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V2">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W2">
         <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y2">
         <v>1.16</v>
@@ -674,25 +674,25 @@
         <v>4.15</v>
       </c>
       <c r="AA2">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AB2">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="AC2">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="AD2">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AE2">
         <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AG2">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,25 +798,25 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="O3">
-        <v>3.84</v>
+        <v>3.7</v>
       </c>
       <c r="P3">
-        <v>5.45</v>
+        <v>5.8</v>
       </c>
       <c r="Q3">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R3">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S3">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="T3">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="U3">
         <v>2.5</v>
@@ -828,34 +828,34 @@
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
         <v>1.25</v>
       </c>
       <c r="Z3">
-        <v>3.62</v>
+        <v>3.55</v>
       </c>
       <c r="AA3">
+        <v>1.78</v>
+      </c>
+      <c r="AB3">
+        <v>2.05</v>
+      </c>
+      <c r="AC3">
+        <v>2.8</v>
+      </c>
+      <c r="AD3">
+        <v>1.4</v>
+      </c>
+      <c r="AE3">
+        <v>1.12</v>
+      </c>
+      <c r="AF3">
         <v>1.8</v>
       </c>
-      <c r="AB3">
-        <v>1.98</v>
-      </c>
-      <c r="AC3">
-        <v>2.85</v>
-      </c>
-      <c r="AD3">
-        <v>1.39</v>
-      </c>
-      <c r="AE3">
-        <v>1.13</v>
-      </c>
-      <c r="AF3">
-        <v>1.78</v>
-      </c>
       <c r="AG3">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         <v>1.13</v>
       </c>
       <c r="AK3">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O4">
         <v>3.8</v>
@@ -973,7 +973,7 @@
         <v>1.91</v>
       </c>
       <c r="R4">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="S4">
         <v>1.35</v>
@@ -994,31 +994,31 @@
         <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z4">
         <v>3.55</v>
       </c>
       <c r="AA4">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB4">
         <v>1.9</v>
       </c>
       <c r="AC4">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="AD4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE4">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AF4">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.1</v>
       </c>
       <c r="AK4">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="O7">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P7">
-        <v>4.38</v>
+        <v>4.65</v>
       </c>
       <c r="Q7">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="R7">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="S7">
         <v>1.36</v>
@@ -1471,10 +1471,10 @@
         <v>2.75</v>
       </c>
       <c r="U7">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="V7">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W7">
         <v>1.06</v>
@@ -1483,25 +1483,25 @@
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z7">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="AA7">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB7">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AC7">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD7">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF7">
         <v>1.85</v>
@@ -1523,7 +1523,7 @@
         <v>1.27</v>
       </c>
       <c r="AK7">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="O8">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="P8">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="Q8">
         <v>2.8</v>
@@ -1634,10 +1634,10 @@
         <v>2.23</v>
       </c>
       <c r="U8">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="V8">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W8">
         <v>1.05</v>
@@ -1649,19 +1649,19 @@
         <v>1.44</v>
       </c>
       <c r="Z8">
+        <v>2.53</v>
+      </c>
+      <c r="AA8">
         <v>2.52</v>
-      </c>
-      <c r="AA8">
-        <v>2.49</v>
       </c>
       <c r="AB8">
         <v>1.53</v>
       </c>
       <c r="AC8">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AD8">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AE8">
         <v>1.01</v>
@@ -1670,7 +1670,7 @@
         <v>2.1</v>
       </c>
       <c r="AG8">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="N9">
+        <v>4.5</v>
+      </c>
+      <c r="O9">
         <v>4.35</v>
       </c>
-      <c r="O9">
-        <v>4.3</v>
-      </c>
       <c r="P9">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="Q9">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="R9">
         <v>2.5</v>
@@ -1797,16 +1797,16 @@
         <v>3.75</v>
       </c>
       <c r="U9">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="V9">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
         <v>1.14</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
         <v>1.14</v>
@@ -1815,19 +1815,19 @@
         <v>5.5</v>
       </c>
       <c r="AA9">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB9">
         <v>2.31</v>
       </c>
       <c r="AC9">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="AD9">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE9">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
         <v>1.55</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AK9">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="O10">
-        <v>3.69</v>
+        <v>3.6</v>
       </c>
       <c r="P10">
-        <v>3.58</v>
+        <v>3.3</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2102,28 +2102,28 @@
         </is>
       </c>
       <c r="N11">
+        <v>1.23</v>
+      </c>
+      <c r="O11">
+        <v>5.25</v>
+      </c>
+      <c r="P11">
+        <v>10</v>
+      </c>
+      <c r="Q11">
+        <v>1.67</v>
+      </c>
+      <c r="R11">
+        <v>2.39</v>
+      </c>
+      <c r="S11">
         <v>1.25</v>
-      </c>
-      <c r="O11">
-        <v>5.1</v>
-      </c>
-      <c r="P11">
-        <v>7.47</v>
-      </c>
-      <c r="Q11">
-        <v>1.69</v>
-      </c>
-      <c r="R11">
-        <v>2.45</v>
-      </c>
-      <c r="S11">
-        <v>1.29</v>
       </c>
       <c r="T11">
         <v>3.25</v>
       </c>
       <c r="U11">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="V11">
         <v>1.5</v>
@@ -2138,13 +2138,13 @@
         <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="AA11">
         <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AC11">
         <v>2.61</v>
@@ -2159,7 +2159,7 @@
         <v>2</v>
       </c>
       <c r="AG11">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK11">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,31 +2428,31 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="O13">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P13">
-        <v>4.53</v>
+        <v>4.2</v>
       </c>
       <c r="Q13">
         <v>2.11</v>
       </c>
       <c r="R13">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S13">
         <v>1.25</v>
       </c>
       <c r="T13">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="U13">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="V13">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W13">
         <v>1.08</v>
@@ -2464,22 +2464,22 @@
         <v>1.14</v>
       </c>
       <c r="Z13">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AA13">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AB13">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC13">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AD13">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AE13">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
         <v>1.6</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="O14">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="P14">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="Q14">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="R14">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="S14">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="T14">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="U14">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="V14">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W14">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X14">
         <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z14">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA14">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="AB14">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AC14">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="AD14">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AE14">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG14">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2664,7 +2664,7 @@
         <v>1.13</v>
       </c>
       <c r="AK14">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2766,13 +2766,13 @@
         <v>2.92</v>
       </c>
       <c r="R15">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="S15">
         <v>1.35</v>
       </c>
       <c r="T15">
-        <v>2.66</v>
+        <v>2.9</v>
       </c>
       <c r="U15">
         <v>2.7</v>
@@ -2781,28 +2781,28 @@
         <v>1.4</v>
       </c>
       <c r="W15">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z15">
         <v>3.3</v>
       </c>
       <c r="AA15">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AB15">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC15">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD15">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE15">
         <v>1.07</v>
@@ -2811,7 +2811,7 @@
         <v>1.61</v>
       </c>
       <c r="AG15">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.59</v>
+        <v>1.85</v>
       </c>
       <c r="O16">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="Q16">
         <v>2.2</v>
       </c>
       <c r="R16">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S16">
         <v>1.2</v>
@@ -2938,10 +2938,10 @@
         <v>4</v>
       </c>
       <c r="U16">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="V16">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="W16">
         <v>1.2</v>
@@ -2953,7 +2953,7 @@
         <v>1.11</v>
       </c>
       <c r="Z16">
-        <v>6.08</v>
+        <v>6.4</v>
       </c>
       <c r="AA16">
         <v>1.4</v>
@@ -2962,7 +2962,7 @@
         <v>2.75</v>
       </c>
       <c r="AC16">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AD16">
         <v>1.73</v>
@@ -2971,7 +2971,7 @@
         <v>1.28</v>
       </c>
       <c r="AF16">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AG16">
         <v>2.88</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>5.98</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3252,55 +3252,55 @@
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3433,7 +3433,7 @@
         <v>1.45</v>
       </c>
       <c r="W19">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
         <v>1.73</v>
@@ -3572,19 +3572,19 @@
         <v>8.5</v>
       </c>
       <c r="O20">
-        <v>6.47</v>
+        <v>6.21</v>
       </c>
       <c r="P20">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Q20">
         <v>7</v>
       </c>
       <c r="R20">
-        <v>2.93</v>
+        <v>2.84</v>
       </c>
       <c r="S20">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="T20">
         <v>5.2</v>
@@ -3596,7 +3596,7 @@
         <v>1.85</v>
       </c>
       <c r="W20">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X20">
         <v>1.01</v>
@@ -3611,7 +3611,7 @@
         <v>1.29</v>
       </c>
       <c r="AB20">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AC20">
         <v>1.75</v>
@@ -3623,10 +3623,10 @@
         <v>1.44</v>
       </c>
       <c r="AF20">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="AG20">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3747,19 +3747,19 @@
         <v>0</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X21">
         <v>0</v>
@@ -3786,10 +3786,10 @@
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3895,61 +3895,61 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.31</v>
+        <v>2.6</v>
       </c>
       <c r="O22">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P22">
-        <v>2.89</v>
+        <v>2.05</v>
       </c>
       <c r="Q22">
+        <v>3.58</v>
+      </c>
+      <c r="R22">
+        <v>2.11</v>
+      </c>
+      <c r="S22">
+        <v>1.32</v>
+      </c>
+      <c r="T22">
         <v>2.92</v>
       </c>
-      <c r="R22">
-        <v>2.09</v>
-      </c>
-      <c r="S22">
-        <v>1.33</v>
-      </c>
-      <c r="T22">
-        <v>2.88</v>
-      </c>
       <c r="U22">
-        <v>2.67</v>
+        <v>2.63</v>
       </c>
       <c r="V22">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W22">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X22">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z22">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AA22">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB22">
         <v>1.82</v>
       </c>
       <c r="AC22">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="AD22">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE22">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG22">
         <v>2.06</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK22">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="O23">
-        <v>7.75</v>
+        <v>7.65</v>
       </c>
       <c r="P23">
         <v>11</v>
@@ -4070,49 +4070,49 @@
         <v>1.44</v>
       </c>
       <c r="R23">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="S23">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T23">
         <v>4</v>
       </c>
       <c r="U23">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="V23">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="W23">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z23">
-        <v>6.3</v>
+        <v>6.55</v>
       </c>
       <c r="AA23">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB23">
         <v>3.15</v>
       </c>
       <c r="AC23">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AD23">
         <v>1.85</v>
       </c>
       <c r="AE23">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AF23">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="AG23">
         <v>1.86</v>
@@ -4131,7 +4131,7 @@
         <v>1.03</v>
       </c>
       <c r="AK23">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4224,19 +4224,19 @@
         <v>1.35</v>
       </c>
       <c r="O24">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="P24">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="R24">
         <v>2.8</v>
       </c>
       <c r="S24">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="T24">
         <v>4.2</v>
@@ -4257,22 +4257,22 @@
         <v>1.07</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AA24">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AB24">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="AC24">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AD24">
         <v>1.73</v>
       </c>
       <c r="AE24">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AF24">
         <v>1.57</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="O25">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="P25">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q25">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R25">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="S25">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="T25">
-        <v>3.02</v>
+        <v>3.28</v>
       </c>
       <c r="U25">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="V25">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z25">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA25">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AB25">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC25">
-        <v>3</v>
+        <v>2.52</v>
       </c>
       <c r="AD25">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AE25">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="AF25">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AG25">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AK25">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.05</v>
+        <v>1.71</v>
       </c>
       <c r="O26">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="P26">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="Q26">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="R26">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T26">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="U26">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V26">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="AA26">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="AB26">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AC26">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AD26">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AE26">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="AG26">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4620,7 +4620,7 @@
         <v>1.21</v>
       </c>
       <c r="AK26">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4710,7 +4710,7 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="O27">
         <v>3.7</v>
@@ -4719,19 +4719,19 @@
         <v>4.2</v>
       </c>
       <c r="Q27">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="R27">
         <v>2.3</v>
       </c>
       <c r="S27">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T27">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="U27">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="V27">
         <v>1.44</v>
@@ -4740,34 +4740,34 @@
         <v>1.11</v>
       </c>
       <c r="X27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y27">
         <v>1.22</v>
       </c>
       <c r="Z27">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AA27">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB27">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC27">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="AD27">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AE27">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF27">
         <v>1.67</v>
       </c>
       <c r="AG27">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK27">
         <v>2.05</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="O28">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P28">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="Q28">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="R28">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S28">
-        <v>1.3</v>
+        <v>1.39</v>
       </c>
       <c r="T28">
-        <v>3.07</v>
+        <v>2.9</v>
       </c>
       <c r="U28">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V28">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X28">
         <v>1.04</v>
       </c>
       <c r="Y28">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z28">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="AA28">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AB28">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC28">
-        <v>2.89</v>
+        <v>3.14</v>
       </c>
       <c r="AD28">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE28">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AF28">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="AG28">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AK28">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="O29">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P29">
-        <v>2.9</v>
+        <v>2.21</v>
       </c>
       <c r="Q29">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="R29">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S29">
+        <v>1.3</v>
+      </c>
+      <c r="T29">
+        <v>3.09</v>
+      </c>
+      <c r="U29">
+        <v>2.4</v>
+      </c>
+      <c r="V29">
+        <v>1.48</v>
+      </c>
+      <c r="W29">
+        <v>1.11</v>
+      </c>
+      <c r="X29">
+        <v>1.03</v>
+      </c>
+      <c r="Y29">
+        <v>1.19</v>
+      </c>
+      <c r="Z29">
+        <v>3.76</v>
+      </c>
+      <c r="AA29">
+        <v>1.74</v>
+      </c>
+      <c r="AB29">
+        <v>2.04</v>
+      </c>
+      <c r="AC29">
+        <v>2.85</v>
+      </c>
+      <c r="AD29">
         <v>1.36</v>
       </c>
-      <c r="T29">
-        <v>2.9</v>
-      </c>
-      <c r="U29">
-        <v>2.75</v>
-      </c>
-      <c r="V29">
-        <v>1.36</v>
-      </c>
-      <c r="W29">
-        <v>1.05</v>
-      </c>
-      <c r="X29">
-        <v>1.04</v>
-      </c>
-      <c r="Y29">
-        <v>1.27</v>
-      </c>
-      <c r="Z29">
-        <v>3.14</v>
-      </c>
-      <c r="AA29">
-        <v>1.98</v>
-      </c>
-      <c r="AB29">
-        <v>1.79</v>
-      </c>
-      <c r="AC29">
-        <v>3.14</v>
-      </c>
-      <c r="AD29">
-        <v>1.27</v>
-      </c>
       <c r="AE29">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF29">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="AG29">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="AK29">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,13 +5199,13 @@
         </is>
       </c>
       <c r="N30">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O30">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="P30">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="N31">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="O31">
         <v>2.98</v>
@@ -5404,7 +5404,7 @@
         <v>2.2</v>
       </c>
       <c r="AB31">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AC31">
         <v>3.72</v>
@@ -5435,7 +5435,7 @@
         <v>1.31</v>
       </c>
       <c r="AK31">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5525,13 +5525,13 @@
         </is>
       </c>
       <c r="N32">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="O32">
-        <v>3.68</v>
+        <v>4</v>
       </c>
       <c r="P32">
-        <v>4.04</v>
+        <v>4.4</v>
       </c>
       <c r="Q32">
         <v>0</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AB32">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         </is>
       </c>
       <c r="N33">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="O33">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P33">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q33">
         <v>3.6</v>
@@ -5727,7 +5727,7 @@
         <v>3.5</v>
       </c>
       <c r="AA33">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AB33">
         <v>1.9</v>
@@ -5739,7 +5739,7 @@
         <v>1.33</v>
       </c>
       <c r="AE33">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF33">
         <v>1.73</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AK33">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AL33">
         <v>0</v>
@@ -6014,43 +6014,43 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="O35">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P35">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T35">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="U35">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V35">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W35">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X35">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z35">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA35">
         <v>1.7</v>
@@ -6059,19 +6059,19 @@
         <v>2.1</v>
       </c>
       <c r="AC35">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD35">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE35">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF35">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG35">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK35">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6177,10 +6177,10 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="O36">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="P36">
         <v>2.2</v>
@@ -6192,13 +6192,13 @@
         <v>2.45</v>
       </c>
       <c r="S36">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T36">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="U36">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="V36">
         <v>1.6</v>
@@ -6213,28 +6213,28 @@
         <v>1.17</v>
       </c>
       <c r="Z36">
-        <v>4.75</v>
+        <v>4.85</v>
       </c>
       <c r="AA36">
         <v>1.53</v>
       </c>
       <c r="AB36">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="AC36">
         <v>2.3</v>
       </c>
       <c r="AD36">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AE36">
         <v>1.22</v>
       </c>
       <c r="AF36">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AG36">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AH36" t="inlineStr">
         <is>
@@ -6250,7 +6250,7 @@
         <v>1.2</v>
       </c>
       <c r="AK36">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,13 +6343,13 @@
         <v>3</v>
       </c>
       <c r="O37">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P37">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q37">
-        <v>4.15</v>
+        <v>3.94</v>
       </c>
       <c r="R37">
         <v>2.25</v>
@@ -6370,31 +6370,31 @@
         <v>1.07</v>
       </c>
       <c r="X37">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y37">
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="AA37">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB37">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC37">
         <v>2.63</v>
       </c>
       <c r="AD37">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE37">
         <v>1.17</v>
       </c>
       <c r="AF37">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AG37">
         <v>2.25</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="AJ37">
-        <v>1.67</v>
+        <v>1.28</v>
       </c>
       <c r="AK37">
         <v>1.3</v>
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="O38">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P38">
-        <v>6.84</v>
+        <v>5.5</v>
       </c>
       <c r="Q38">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="R38">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S38">
         <v>1.49</v>
@@ -6524,7 +6524,7 @@
         <v>2.36</v>
       </c>
       <c r="U38">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V38">
         <v>1.33</v>
@@ -6548,7 +6548,7 @@
         <v>1.57</v>
       </c>
       <c r="AC38">
-        <v>4.33</v>
+        <v>4.37</v>
       </c>
       <c r="AD38">
         <v>1.17</v>
@@ -6557,10 +6557,10 @@
         <v>1.01</v>
       </c>
       <c r="AF38">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AG38">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.22</v>
+        <v>1.04</v>
       </c>
       <c r="AK38">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6678,19 +6678,19 @@
         <v>4.5</v>
       </c>
       <c r="R39">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S39">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="T39">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="U39">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="V39">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W39">
         <v>1.01</v>
@@ -6699,7 +6699,7 @@
         <v>1.1</v>
       </c>
       <c r="Y39">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z39">
         <v>2.3</v>
@@ -6711,19 +6711,19 @@
         <v>1.42</v>
       </c>
       <c r="AC39">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AD39">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AE39">
         <v>1.03</v>
       </c>
       <c r="AF39">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="AG39">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6832,13 +6832,13 @@
         <v>1.8</v>
       </c>
       <c r="O40">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P40">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="Q40">
-        <v>2.37</v>
+        <v>2.42</v>
       </c>
       <c r="R40">
         <v>2.15</v>
@@ -6847,10 +6847,10 @@
         <v>1.36</v>
       </c>
       <c r="T40">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="U40">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="V40">
         <v>1.4</v>
@@ -6859,19 +6859,19 @@
         <v>1.04</v>
       </c>
       <c r="X40">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y40">
         <v>1.29</v>
       </c>
       <c r="Z40">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA40">
         <v>1.89</v>
       </c>
       <c r="AB40">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AC40">
         <v>3.08</v>
@@ -6880,10 +6880,10 @@
         <v>1.28</v>
       </c>
       <c r="AE40">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AG40">
         <v>1.95</v>
@@ -6902,7 +6902,7 @@
         <v>1.19</v>
       </c>
       <c r="AK40">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,64 +6992,64 @@
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P41">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="Q41">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,31 +7155,31 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="O42">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P42">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="Q42">
         <v>2.3</v>
       </c>
       <c r="R42">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="S42">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="T42">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="U42">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V42">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="W42">
         <v>1.18</v>
@@ -7194,13 +7194,13 @@
         <v>6.5</v>
       </c>
       <c r="AA42">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AB42">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AC42">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AD42">
         <v>1.8</v>
@@ -7209,10 +7209,10 @@
         <v>1.3</v>
       </c>
       <c r="AF42">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AG42">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
@@ -7228,7 +7228,7 @@
         <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.98</v>
+        <v>1.86</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,13 +7318,13 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="O43">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="P43">
-        <v>3.49</v>
+        <v>3.51</v>
       </c>
       <c r="Q43">
         <v>2.62</v>
@@ -7342,7 +7342,7 @@
         <v>2.85</v>
       </c>
       <c r="V43">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="W43">
         <v>1.1</v>
@@ -7357,7 +7357,7 @@
         <v>3.3</v>
       </c>
       <c r="AA43">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AB43">
         <v>1.88</v>
@@ -7369,7 +7369,7 @@
         <v>1.29</v>
       </c>
       <c r="AE43">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF43">
         <v>1.75</v>
@@ -7388,7 +7388,7 @@
         </is>
       </c>
       <c r="AJ43">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AK43">
         <v>1.73</v>
@@ -7490,25 +7490,25 @@
         <v>3.7</v>
       </c>
       <c r="Q44">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="R44">
         <v>2.33</v>
       </c>
       <c r="S44">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T44">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="U44">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="V44">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W44">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X44">
         <v>1.04</v>
@@ -7517,22 +7517,22 @@
         <v>1.22</v>
       </c>
       <c r="Z44">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA44">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AB44">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="AC44">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="AD44">
         <v>1.4</v>
       </c>
       <c r="AE44">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF44">
         <v>1.64</v>
@@ -7551,10 +7551,10 @@
         </is>
       </c>
       <c r="AJ44">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -7650,7 +7650,7 @@
         <v>3.6</v>
       </c>
       <c r="P45">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="Q45">
         <v>3.4</v>
@@ -7668,7 +7668,7 @@
         <v>2.17</v>
       </c>
       <c r="V45">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W45">
         <v>1.13</v>
@@ -7677,16 +7677,16 @@
         <v>1.02</v>
       </c>
       <c r="Y45">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z45">
         <v>5.5</v>
       </c>
       <c r="AA45">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="AB45">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AC45">
         <v>2.1</v>
@@ -7828,7 +7828,7 @@
         <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="V46">
         <v>1.52</v>
@@ -7837,7 +7837,7 @@
         <v>1.12</v>
       </c>
       <c r="X46">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y46">
         <v>1.18</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="N47">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O47">
         <v>3.18</v>
@@ -7988,16 +7988,16 @@
         <v>1.4</v>
       </c>
       <c r="T47">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="U47">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="V47">
         <v>1.36</v>
       </c>
       <c r="W47">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X47">
         <v>1.06</v>
@@ -8009,7 +8009,7 @@
         <v>3.1</v>
       </c>
       <c r="AA47">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="AB47">
         <v>1.67</v>
@@ -8024,11 +8024,11 @@
         <v>1.07</v>
       </c>
       <c r="AF47">
+        <v>1.84</v>
+      </c>
+      <c r="AG47">
         <v>1.86</v>
       </c>
-      <c r="AG47">
-        <v>1.84</v>
-      </c>
       <c r="AH47" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8040,10 +8040,10 @@
         </is>
       </c>
       <c r="AJ47">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK47">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8133,37 +8133,37 @@
         </is>
       </c>
       <c r="N48">
-        <v>1.45</v>
+        <v>1.2</v>
       </c>
       <c r="O48">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="P48">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q48">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="R48">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="S48">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T48">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="U48">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="V48">
         <v>1.38</v>
       </c>
       <c r="W48">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X48">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y48">
         <v>1.31</v>
@@ -8172,25 +8172,25 @@
         <v>3.2</v>
       </c>
       <c r="AA48">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AB48">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AC48">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AD48">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE48">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AF48">
-        <v>2.05</v>
+        <v>2.64</v>
       </c>
       <c r="AG48">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="AJ48">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK48">
-        <v>2.45</v>
+        <v>3.6</v>
       </c>
       <c r="AL48">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O49">
         <v>4</v>
       </c>
       <c r="P49">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8335,10 +8335,10 @@
         <v>0</v>
       </c>
       <c r="AA49">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB49">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AC49">
         <v>0</v>
@@ -8459,31 +8459,31 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O50">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="P50">
-        <v>3.8</v>
+        <v>4.05</v>
       </c>
       <c r="Q50">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="R50">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="S50">
         <v>1.18</v>
       </c>
       <c r="T50">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U50">
         <v>2.1</v>
       </c>
       <c r="V50">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W50">
         <v>1.14</v>
@@ -8492,22 +8492,22 @@
         <v>1.01</v>
       </c>
       <c r="Y50">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z50">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA50">
         <v>1.44</v>
       </c>
       <c r="AB50">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AC50">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AD50">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AE50">
         <v>1.28</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK50">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -8785,13 +8785,13 @@
         </is>
       </c>
       <c r="N52">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O52">
         <v>3</v>
       </c>
       <c r="P52">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q52">
         <v>3.6</v>
@@ -8803,7 +8803,7 @@
         <v>1.46</v>
       </c>
       <c r="T52">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="U52">
         <v>2.91</v>
@@ -8824,10 +8824,10 @@
         <v>2.88</v>
       </c>
       <c r="AA52">
-        <v>2.2</v>
+        <v>2.11</v>
       </c>
       <c r="AB52">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC52">
         <v>3.62</v>
@@ -8855,7 +8855,7 @@
         </is>
       </c>
       <c r="AJ52">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AK52">
         <v>1.31</v>
@@ -8948,25 +8948,25 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="O53">
         <v>3.2</v>
       </c>
       <c r="P53">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q53">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="R53">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="S53">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T53">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U53">
         <v>3</v>
@@ -8990,10 +8990,10 @@
         <v>2.05</v>
       </c>
       <c r="AB53">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC53">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="AD53">
         <v>1.26</v>
@@ -9005,7 +9005,7 @@
         <v>1.8</v>
       </c>
       <c r="AG53">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="AH53" t="inlineStr">
         <is>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AK53">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="O54">
         <v>3.2</v>
       </c>
       <c r="P54">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="Q54">
         <v>3.35</v>
@@ -9132,7 +9132,7 @@
         <v>2.69</v>
       </c>
       <c r="U54">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="V54">
         <v>1.35</v>
@@ -9147,16 +9147,16 @@
         <v>1.33</v>
       </c>
       <c r="Z54">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="AA54">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AB54">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="AC54">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AD54">
         <v>1.22</v>
@@ -9274,64 +9274,64 @@
         </is>
       </c>
       <c r="N55">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="O55">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="P55">
+        <v>3.05</v>
+      </c>
+      <c r="Q55">
+        <v>2.5</v>
+      </c>
+      <c r="R55">
+        <v>2.2</v>
+      </c>
+      <c r="S55">
+        <v>1.36</v>
+      </c>
+      <c r="T55">
         <v>3</v>
       </c>
-      <c r="Q55">
-        <v>0</v>
-      </c>
-      <c r="R55">
-        <v>0</v>
-      </c>
-      <c r="S55">
-        <v>0</v>
-      </c>
-      <c r="T55">
-        <v>0</v>
-      </c>
       <c r="U55">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V55">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W55">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y55">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z55">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA55">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB55">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC55">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD55">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE55">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF55">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG55">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AH55" t="inlineStr">
         <is>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK55">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="O56">
         <v>3.3</v>
       </c>
       <c r="P56">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="Q56">
         <v>2.9</v>
@@ -9458,7 +9458,7 @@
         <v>2.89</v>
       </c>
       <c r="U56">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="V56">
         <v>1.4</v>
@@ -9600,64 +9600,64 @@
         </is>
       </c>
       <c r="N57">
-        <v>4.75</v>
+        <v>5.4</v>
       </c>
       <c r="O57">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="P57">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="Q57">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="R57">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S57">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T57">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U57">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="V57">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W57">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X57">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y57">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z57">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA57">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB57">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AC57">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD57">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE57">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF57">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG57">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK57">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P58">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9802,10 +9802,10 @@
         <v>0</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AC58">
         <v>0</v>
@@ -9926,7 +9926,7 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="O59">
         <v>3.3</v>
@@ -9938,19 +9938,19 @@
         <v>2.8</v>
       </c>
       <c r="R59">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="S59">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T59">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="U59">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="V59">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W59">
         <v>1.06</v>
@@ -9962,7 +9962,7 @@
         <v>1.22</v>
       </c>
       <c r="Z59">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="AA59">
         <v>1.75</v>
@@ -9971,19 +9971,19 @@
         <v>1.99</v>
       </c>
       <c r="AC59">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AD59">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AE59">
         <v>1.14</v>
       </c>
       <c r="AF59">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG59">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="P60">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="Q60">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R60">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S60">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="U60">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="V60">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X60">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y60">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z60">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA60">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB60">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC60">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AD60">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE60">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF60">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG60">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10159,10 +10159,10 @@
         </is>
       </c>
       <c r="AJ60">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK60">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10255,61 +10255,61 @@
         <v>3.25</v>
       </c>
       <c r="O61">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P61">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="Q61">
         <v>3.75</v>
       </c>
       <c r="R61">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="S61">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="T61">
-        <v>3.52</v>
+        <v>3.8</v>
       </c>
       <c r="U61">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="V61">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W61">
         <v>1.13</v>
       </c>
       <c r="X61">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y61">
         <v>1.14</v>
       </c>
       <c r="Z61">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="AA61">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AB61">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="AC61">
-        <v>2.24</v>
+        <v>2.43</v>
       </c>
       <c r="AD61">
-        <v>1.63</v>
+        <v>1.54</v>
       </c>
       <c r="AE61">
         <v>1.22</v>
       </c>
       <c r="AF61">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AG61">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10415,16 +10415,16 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="O62">
         <v>3.5</v>
       </c>
       <c r="P62">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="Q62">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="R62">
         <v>2.47</v>
@@ -10436,13 +10436,13 @@
         <v>3.28</v>
       </c>
       <c r="U62">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="V62">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="W62">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X62">
         <v>1.01</v>
@@ -10463,7 +10463,7 @@
         <v>2.3</v>
       </c>
       <c r="AD62">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AE62">
         <v>1.22</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK62">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL62">
         <v>0</v>
@@ -10578,28 +10578,28 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.52</v>
+        <v>3.72</v>
       </c>
       <c r="O63">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="P63">
         <v>1.93</v>
       </c>
       <c r="Q63">
-        <v>3.41</v>
+        <v>4.2</v>
       </c>
       <c r="R63">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="S63">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T63">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U63">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="V63">
         <v>1.5</v>
@@ -10614,22 +10614,22 @@
         <v>1.2</v>
       </c>
       <c r="Z63">
-        <v>4.15</v>
+        <v>4.19</v>
       </c>
       <c r="AA63">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AB63">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AC63">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="AD63">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE63">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AF63">
         <v>1.59</v>
@@ -10648,10 +10648,10 @@
         </is>
       </c>
       <c r="AJ63">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AK63">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AL63">
         <v>0</v>
@@ -10741,58 +10741,58 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="O64">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="P64">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="Q64">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R64">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="S64">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T64">
-        <v>3.6</v>
+        <v>3.68</v>
       </c>
       <c r="U64">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V64">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W64">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X64">
         <v>1.02</v>
       </c>
       <c r="Y64">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Z64">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AA64">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="AB64">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC64">
         <v>2.1</v>
       </c>
       <c r="AD64">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AE64">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AF64">
         <v>1.36</v>
@@ -10811,10 +10811,10 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="AK64">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AL64">
         <v>0</v>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="G65">
@@ -10904,65 +10904,65 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.06</v>
+        <v>2.55</v>
       </c>
       <c r="O65">
-        <v>3.68</v>
+        <v>3.4</v>
       </c>
       <c r="P65">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="Q65">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="R65">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="S65">
+        <v>1.3</v>
+      </c>
+      <c r="T65">
+        <v>3.3</v>
+      </c>
+      <c r="U65">
+        <v>2.58</v>
+      </c>
+      <c r="V65">
+        <v>1.5</v>
+      </c>
+      <c r="W65">
+        <v>1.08</v>
+      </c>
+      <c r="X65">
+        <v>1</v>
+      </c>
+      <c r="Y65">
         <v>1.22</v>
       </c>
-      <c r="T65">
-        <v>3.55</v>
-      </c>
-      <c r="U65">
-        <v>2.15</v>
-      </c>
-      <c r="V65">
-        <v>1.61</v>
-      </c>
-      <c r="W65">
-        <v>1.13</v>
-      </c>
-      <c r="X65">
-        <v>1.01</v>
-      </c>
-      <c r="Y65">
-        <v>1.14</v>
-      </c>
       <c r="Z65">
-        <v>5.06</v>
+        <v>3.9</v>
       </c>
       <c r="AA65">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AB65">
-        <v>2.49</v>
+        <v>2</v>
       </c>
       <c r="AC65">
+        <v>2.88</v>
+      </c>
+      <c r="AD65">
+        <v>1.4</v>
+      </c>
+      <c r="AE65">
+        <v>1.12</v>
+      </c>
+      <c r="AF65">
+        <v>1.57</v>
+      </c>
+      <c r="AG65">
         <v>2.3</v>
       </c>
-      <c r="AD65">
-        <v>1.6</v>
-      </c>
-      <c r="AE65">
-        <v>1.21</v>
-      </c>
-      <c r="AF65">
-        <v>1.44</v>
-      </c>
-      <c r="AG65">
-        <v>2.55</v>
-      </c>
       <c r="AH65" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10974,10 +10974,10 @@
         </is>
       </c>
       <c r="AJ65">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK65">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11035,12 +11035,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G66">
@@ -11067,80 +11067,80 @@
         </is>
       </c>
       <c r="N66">
-        <v>2.57</v>
+        <v>1.93</v>
       </c>
       <c r="O66">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="P66">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="Q66">
-        <v>2.81</v>
+        <v>2.31</v>
       </c>
       <c r="R66">
+        <v>2.5</v>
+      </c>
+      <c r="S66">
+        <v>1.22</v>
+      </c>
+      <c r="T66">
+        <v>3.55</v>
+      </c>
+      <c r="U66">
         <v>2.15</v>
       </c>
-      <c r="S66">
+      <c r="V66">
+        <v>1.63</v>
+      </c>
+      <c r="W66">
+        <v>1.13</v>
+      </c>
+      <c r="X66">
+        <v>1.01</v>
+      </c>
+      <c r="Y66">
+        <v>1.14</v>
+      </c>
+      <c r="Z66">
+        <v>5.13</v>
+      </c>
+      <c r="AA66">
+        <v>1.5</v>
+      </c>
+      <c r="AB66">
+        <v>2.51</v>
+      </c>
+      <c r="AC66">
+        <v>2.3</v>
+      </c>
+      <c r="AD66">
+        <v>1.61</v>
+      </c>
+      <c r="AE66">
+        <v>1.21</v>
+      </c>
+      <c r="AF66">
+        <v>1.44</v>
+      </c>
+      <c r="AG66">
+        <v>2.55</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ66">
         <v>1.3</v>
       </c>
-      <c r="T66">
-        <v>3.3</v>
-      </c>
-      <c r="U66">
-        <v>2.57</v>
-      </c>
-      <c r="V66">
-        <v>1.5</v>
-      </c>
-      <c r="W66">
-        <v>1.08</v>
-      </c>
-      <c r="X66">
-        <v>1</v>
-      </c>
-      <c r="Y66">
-        <v>1.22</v>
-      </c>
-      <c r="Z66">
-        <v>4</v>
-      </c>
-      <c r="AA66">
-        <v>1.72</v>
-      </c>
-      <c r="AB66">
-        <v>2.05</v>
-      </c>
-      <c r="AC66">
-        <v>2.8</v>
-      </c>
-      <c r="AD66">
-        <v>1.4</v>
-      </c>
-      <c r="AE66">
-        <v>1.12</v>
-      </c>
-      <c r="AF66">
-        <v>1.57</v>
-      </c>
-      <c r="AG66">
-        <v>2.3</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ66">
-        <v>1.28</v>
-      </c>
       <c r="AK66">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AL66">
         <v>0</v>
@@ -11236,13 +11236,13 @@
         <v>4</v>
       </c>
       <c r="P67">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="Q67">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="R67">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="S67">
         <v>1.29</v>
@@ -11251,22 +11251,22 @@
         <v>3.3</v>
       </c>
       <c r="U67">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="V67">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W67">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X67">
         <v>1.01</v>
       </c>
       <c r="Y67">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z67">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AA67">
         <v>1.67</v>
@@ -11278,10 +11278,10 @@
         <v>2.63</v>
       </c>
       <c r="AD67">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE67">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF67">
         <v>1.7</v>
@@ -11393,64 +11393,64 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O68">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P68">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q68">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="R68">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S68">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T68">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U68">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V68">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W68">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X68">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z68">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA68">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB68">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC68">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD68">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE68">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF68">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG68">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK68">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11556,10 +11556,10 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O69">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P69">
         <v>5</v>
@@ -11626,7 +11626,7 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AK69">
         <v>2.2</v>
@@ -11719,28 +11719,28 @@
         </is>
       </c>
       <c r="N70">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O70">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="P70">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Q70">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="R70">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="S70">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T70">
         <v>2.75</v>
       </c>
       <c r="U70">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="V70">
         <v>1.36</v>
@@ -11749,25 +11749,25 @@
         <v>1.07</v>
       </c>
       <c r="X70">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y70">
         <v>1.28</v>
       </c>
       <c r="Z70">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA70">
         <v>2.01</v>
       </c>
       <c r="AB70">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC70">
         <v>3.8</v>
       </c>
       <c r="AD70">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AE70">
         <v>1.05</v>
@@ -11776,7 +11776,7 @@
         <v>1.8</v>
       </c>
       <c r="AG70">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="AK70">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -11885,49 +11885,49 @@
         <v>2.25</v>
       </c>
       <c r="O71">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="P71">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="Q71">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R71">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="S71">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T71">
         <v>3.25</v>
       </c>
       <c r="U71">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="V71">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W71">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X71">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y71">
         <v>1.22</v>
       </c>
       <c r="Z71">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AA71">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AB71">
         <v>1.95</v>
       </c>
       <c r="AC71">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AD71">
         <v>1.36</v>
@@ -11936,7 +11936,7 @@
         <v>1.13</v>
       </c>
       <c r="AF71">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG71">
         <v>2.15</v>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AK71">
         <v>1.51</v>
@@ -12045,19 +12045,19 @@
         </is>
       </c>
       <c r="N72">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="P72">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Q72">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="R72">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S72">
         <v>1.29</v>
@@ -12066,7 +12066,7 @@
         <v>3.3</v>
       </c>
       <c r="U72">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="V72">
         <v>1.47</v>
@@ -12078,16 +12078,16 @@
         <v>1.04</v>
       </c>
       <c r="Y72">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z72">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="AA72">
         <v>1.78</v>
       </c>
       <c r="AB72">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC72">
         <v>2.75</v>
@@ -12115,7 +12115,7 @@
         </is>
       </c>
       <c r="AJ72">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AK72">
         <v>1.1</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="O73">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P73">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="Q73">
         <v>3.04</v>
@@ -12223,7 +12223,7 @@
         <v>2.1</v>
       </c>
       <c r="S73">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T73">
         <v>2.77</v>
@@ -12232,40 +12232,40 @@
         <v>2.63</v>
       </c>
       <c r="V73">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W73">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X73">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y73">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z73">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AA73">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB73">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AC73">
         <v>2.92</v>
       </c>
       <c r="AD73">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE73">
         <v>1.08</v>
       </c>
       <c r="AF73">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="AG73">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12278,10 +12278,10 @@
         </is>
       </c>
       <c r="AJ73">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AK73">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12537,25 +12537,25 @@
         <v>2.35</v>
       </c>
       <c r="O75">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P75">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="Q75">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R75">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S75">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T75">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="U75">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="V75">
         <v>1.46</v>
@@ -12564,31 +12564,31 @@
         <v>1.11</v>
       </c>
       <c r="X75">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z75">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AA75">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB75">
         <v>1.98</v>
       </c>
       <c r="AC75">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="AD75">
         <v>1.36</v>
       </c>
       <c r="AE75">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AF75">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AG75">
         <v>2.25</v>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="AJ75">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK75">
         <v>1.53</v>
@@ -12709,7 +12709,7 @@
         <v>2.45</v>
       </c>
       <c r="R76">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="S76">
         <v>1.29</v>
@@ -12721,40 +12721,40 @@
         <v>2.45</v>
       </c>
       <c r="V76">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W76">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X76">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y76">
         <v>1.22</v>
       </c>
       <c r="Z76">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AA76">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AB76">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC76">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD76">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE76">
         <v>1.11</v>
       </c>
       <c r="AF76">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AG76">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH76" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,64 +12860,64 @@
         </is>
       </c>
       <c r="N77">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="O77">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P77">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q77">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R77">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S77">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T77">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U77">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="V77">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W77">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X77">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y77">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z77">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA77">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB77">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC77">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD77">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE77">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF77">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG77">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AK77">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -13023,13 +13023,13 @@
         </is>
       </c>
       <c r="N78">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O78">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="P78">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q78">
         <v>3.8</v>
@@ -13038,19 +13038,19 @@
         <v>2.2</v>
       </c>
       <c r="S78">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="T78">
-        <v>2.32</v>
+        <v>3.15</v>
       </c>
       <c r="U78">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="V78">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W78">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X78">
         <v>1.02</v>
@@ -13062,25 +13062,25 @@
         <v>3.58</v>
       </c>
       <c r="AA78">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB78">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AC78">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="AD78">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE78">
         <v>1.12</v>
       </c>
       <c r="AF78">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG78">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13096,7 +13096,7 @@
         <v>1.73</v>
       </c>
       <c r="AK78">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13189,7 +13189,7 @@
         <v>1.8</v>
       </c>
       <c r="O79">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P79">
         <v>3.6</v>
@@ -13204,16 +13204,16 @@
         <v>1.29</v>
       </c>
       <c r="T79">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="U79">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="V79">
         <v>1.39</v>
       </c>
       <c r="W79">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X79">
         <v>1.04</v>
@@ -13222,22 +13222,22 @@
         <v>1.22</v>
       </c>
       <c r="Z79">
-        <v>3.95</v>
+        <v>3</v>
       </c>
       <c r="AA79">
         <v>1.72</v>
       </c>
       <c r="AB79">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC79">
         <v>2.74</v>
       </c>
       <c r="AD79">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE79">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF79">
         <v>1.67</v>
@@ -13256,7 +13256,7 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK79">
         <v>1.81</v>
@@ -13349,31 +13349,31 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="O80">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="P80">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Q80">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="R80">
-        <v>2.36</v>
+        <v>2.6</v>
       </c>
       <c r="S80">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T80">
-        <v>3.75</v>
+        <v>3.66</v>
       </c>
       <c r="U80">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V80">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="W80">
         <v>1.15</v>
@@ -13385,10 +13385,10 @@
         <v>1.13</v>
       </c>
       <c r="Z80">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AA80">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AB80">
         <v>2.5</v>
@@ -13400,13 +13400,13 @@
         <v>1.6</v>
       </c>
       <c r="AE80">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF80">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG80">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13419,10 +13419,10 @@
         </is>
       </c>
       <c r="AJ80">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK80">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="O84">
         <v>3.2</v>
       </c>
       <c r="P84">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="Q84">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R84">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S84">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T84">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U84">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V84">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W84">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X84">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y84">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z84">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA84">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB84">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="AC84">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD84">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE84">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF84">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG84">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AK84">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14176,13 +14176,13 @@
         <v>3.3</v>
       </c>
       <c r="R85">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S85">
         <v>1.29</v>
       </c>
       <c r="T85">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U85">
         <v>2.3</v>
@@ -14203,7 +14203,7 @@
         <v>3.85</v>
       </c>
       <c r="AA85">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AB85">
         <v>2.14</v>
@@ -14218,7 +14218,7 @@
         <v>1.13</v>
       </c>
       <c r="AF85">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG85">
         <v>2.25</v>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AK85">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14327,25 +14327,25 @@
         </is>
       </c>
       <c r="N86">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="O86">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P86">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q86">
-        <v>7.06</v>
+        <v>6.73</v>
       </c>
       <c r="R86">
-        <v>2.18</v>
+        <v>2.58</v>
       </c>
       <c r="S86">
         <v>1.3</v>
       </c>
       <c r="T86">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U86">
         <v>2.4</v>
@@ -14354,37 +14354,37 @@
         <v>1.5</v>
       </c>
       <c r="W86">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X86">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y86">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z86">
         <v>3.95</v>
       </c>
       <c r="AA86">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB86">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AC86">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AD86">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AE86">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF86">
         <v>1.75</v>
       </c>
       <c r="AG86">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="AH86" t="inlineStr">
         <is>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK86">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14499,7 +14499,7 @@
         <v>2.9</v>
       </c>
       <c r="Q87">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R87">
         <v>2.25</v>
@@ -14511,16 +14511,16 @@
         <v>3</v>
       </c>
       <c r="U87">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="V87">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W87">
         <v>1.06</v>
       </c>
       <c r="X87">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y87">
         <v>1.22</v>
@@ -14532,22 +14532,22 @@
         <v>1.8</v>
       </c>
       <c r="AB87">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="AC87">
         <v>3.1</v>
       </c>
       <c r="AD87">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE87">
         <v>1.13</v>
       </c>
       <c r="AF87">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG87">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK87">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="O88">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="P88">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14692,10 +14692,10 @@
         <v>0</v>
       </c>
       <c r="AA88">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB88">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC88">
         <v>0</v>
@@ -14819,16 +14819,16 @@
         <v>3.2</v>
       </c>
       <c r="O89">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P89">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="Q89">
-        <v>4.14</v>
+        <v>4.28</v>
       </c>
       <c r="R89">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S89">
         <v>1.4</v>
@@ -14837,43 +14837,43 @@
         <v>2.75</v>
       </c>
       <c r="U89">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="V89">
         <v>1.3</v>
       </c>
       <c r="W89">
+        <v>1.04</v>
+      </c>
+      <c r="X89">
         <v>1.05</v>
-      </c>
-      <c r="X89">
-        <v>1.06</v>
       </c>
       <c r="Y89">
         <v>1.36</v>
       </c>
       <c r="Z89">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AA89">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AB89">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC89">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AD89">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE89">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF89">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AG89">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AH89" t="inlineStr">
         <is>
@@ -14886,10 +14886,10 @@
         </is>
       </c>
       <c r="AJ89">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AK89">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -14979,10 +14979,10 @@
         </is>
       </c>
       <c r="N90">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="O90">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="P90">
         <v>15.35</v>
@@ -14997,13 +14997,13 @@
         <v>1.25</v>
       </c>
       <c r="T90">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="U90">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="V90">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W90">
         <v>1.15</v>
@@ -15012,7 +15012,7 @@
         <v>1.02</v>
       </c>
       <c r="Y90">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z90">
         <v>5</v>
@@ -15021,7 +15021,7 @@
         <v>1.64</v>
       </c>
       <c r="AB90">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="AC90">
         <v>2.31</v>
@@ -15030,13 +15030,13 @@
         <v>1.52</v>
       </c>
       <c r="AE90">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF90">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="AG90">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH90" t="inlineStr">
         <is>
@@ -15049,10 +15049,10 @@
         </is>
       </c>
       <c r="AJ90">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AK90">
-        <v>5.1</v>
+        <v>5.05</v>
       </c>
       <c r="AL90">
         <v>0</v>
@@ -15468,64 +15468,64 @@
         </is>
       </c>
       <c r="N93">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="O93">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="P93">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q93">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="R93">
         <v>2.2</v>
       </c>
       <c r="S93">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T93">
-        <v>2.77</v>
+        <v>2.85</v>
       </c>
       <c r="U93">
-        <v>2.53</v>
+        <v>2.47</v>
       </c>
       <c r="V93">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W93">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X93">
         <v>1.05</v>
       </c>
       <c r="Y93">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z93">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA93">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB93">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AC93">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD93">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE93">
         <v>1.11</v>
       </c>
       <c r="AF93">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AG93">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="AH93" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         </is>
       </c>
       <c r="AJ93">
-        <v>1.59</v>
+        <v>1.26</v>
       </c>
       <c r="AK93">
         <v>1.36</v>
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="O94">
         <v>3.4</v>
@@ -15640,7 +15640,7 @@
         <v>3.5</v>
       </c>
       <c r="Q94">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R94">
         <v>2.15</v>
@@ -15652,43 +15652,43 @@
         <v>2.8</v>
       </c>
       <c r="U94">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="V94">
         <v>1.39</v>
       </c>
       <c r="W94">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X94">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y94">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z94">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AA94">
         <v>2</v>
       </c>
       <c r="AB94">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="AC94">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD94">
         <v>1.29</v>
       </c>
       <c r="AE94">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF94">
         <v>1.76</v>
       </c>
       <c r="AG94">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AH94" t="inlineStr">
         <is>
@@ -15762,12 +15762,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Scafatese</t>
         </is>
       </c>
       <c r="G95">
@@ -15794,25 +15794,25 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.16</v>
+        <v>2.27</v>
       </c>
       <c r="O95">
         <v>3</v>
       </c>
       <c r="P95">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="Q95">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="R95">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S95">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T95">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="U95">
         <v>2.92</v>
@@ -15821,22 +15821,22 @@
         <v>1.32</v>
       </c>
       <c r="W95">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X95">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y95">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="Z95">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA95">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="AB95">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="AC95">
         <v>3.5</v>
@@ -15848,10 +15848,10 @@
         <v>1.04</v>
       </c>
       <c r="AF95">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AG95">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK95">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15925,12 +15925,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Bari 1908</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Scafatese</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G96">
@@ -15957,80 +15957,80 @@
         </is>
       </c>
       <c r="N96">
+        <v>1.35</v>
+      </c>
+      <c r="O96">
+        <v>4.33</v>
+      </c>
+      <c r="P96">
+        <v>7</v>
+      </c>
+      <c r="Q96">
+        <v>1.82</v>
+      </c>
+      <c r="R96">
         <v>2.27</v>
       </c>
-      <c r="O96">
+      <c r="S96">
+        <v>1.35</v>
+      </c>
+      <c r="T96">
+        <v>2.7</v>
+      </c>
+      <c r="U96">
+        <v>2.75</v>
+      </c>
+      <c r="V96">
+        <v>1.36</v>
+      </c>
+      <c r="W96">
+        <v>1.04</v>
+      </c>
+      <c r="X96">
+        <v>1.01</v>
+      </c>
+      <c r="Y96">
+        <v>1.25</v>
+      </c>
+      <c r="Z96">
+        <v>3.28</v>
+      </c>
+      <c r="AA96">
+        <v>1.87</v>
+      </c>
+      <c r="AB96">
+        <v>1.82</v>
+      </c>
+      <c r="AC96">
+        <v>3.14</v>
+      </c>
+      <c r="AD96">
+        <v>1.27</v>
+      </c>
+      <c r="AE96">
+        <v>1.07</v>
+      </c>
+      <c r="AF96">
+        <v>2.24</v>
+      </c>
+      <c r="AG96">
+        <v>1.55</v>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ96">
+        <v>1.14</v>
+      </c>
+      <c r="AK96">
         <v>3</v>
-      </c>
-      <c r="P96">
-        <v>3.15</v>
-      </c>
-      <c r="Q96">
-        <v>2.87</v>
-      </c>
-      <c r="R96">
-        <v>2.07</v>
-      </c>
-      <c r="S96">
-        <v>0</v>
-      </c>
-      <c r="T96">
-        <v>0</v>
-      </c>
-      <c r="U96">
-        <v>2.82</v>
-      </c>
-      <c r="V96">
-        <v>1.34</v>
-      </c>
-      <c r="W96">
-        <v>1.07</v>
-      </c>
-      <c r="X96">
-        <v>0</v>
-      </c>
-      <c r="Y96">
-        <v>1.31</v>
-      </c>
-      <c r="Z96">
-        <v>2.97</v>
-      </c>
-      <c r="AA96">
-        <v>2.04</v>
-      </c>
-      <c r="AB96">
-        <v>1.69</v>
-      </c>
-      <c r="AC96">
-        <v>3.4</v>
-      </c>
-      <c r="AD96">
-        <v>1.26</v>
-      </c>
-      <c r="AE96">
-        <v>0</v>
-      </c>
-      <c r="AF96">
-        <v>1.79</v>
-      </c>
-      <c r="AG96">
-        <v>1.98</v>
-      </c>
-      <c r="AH96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ96">
-        <v>0</v>
-      </c>
-      <c r="AK96">
-        <v>0</v>
       </c>
       <c r="AL96">
         <v>0</v>
@@ -16088,12 +16088,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Bari 1908</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G97">
@@ -16120,43 +16120,43 @@
         </is>
       </c>
       <c r="N97">
-        <v>1.39</v>
+        <v>2.5</v>
       </c>
       <c r="O97">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="P97">
-        <v>6.76</v>
+        <v>2.62</v>
       </c>
       <c r="Q97">
-        <v>1.88</v>
+        <v>2.9</v>
       </c>
       <c r="R97">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="S97">
         <v>1.33</v>
       </c>
       <c r="T97">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U97">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="V97">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="W97">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X97">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y97">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="Z97">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="AA97">
         <v>1.91</v>
@@ -16165,19 +16165,19 @@
         <v>1.8</v>
       </c>
       <c r="AC97">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="AD97">
         <v>1.3</v>
       </c>
       <c r="AE97">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF97">
-        <v>2.27</v>
+        <v>1.65</v>
       </c>
       <c r="AG97">
-        <v>1.58</v>
+        <v>2.05</v>
       </c>
       <c r="AH97" t="inlineStr">
         <is>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.14</v>
+        <v>1.33</v>
       </c>
       <c r="AK97">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16609,25 +16609,25 @@
         </is>
       </c>
       <c r="N100">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="O100">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="P100">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="Q100">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R100">
         <v>2.03</v>
       </c>
       <c r="S100">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T100">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="U100">
         <v>3.1</v>
@@ -16651,13 +16651,13 @@
         <v>2.1</v>
       </c>
       <c r="AB100">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AC100">
         <v>3.8</v>
       </c>
       <c r="AD100">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AE100">
         <v>1.02</v>
@@ -16679,7 +16679,7 @@
         </is>
       </c>
       <c r="AJ100">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AK100">
         <v>1.8</v>
@@ -16772,64 +16772,64 @@
         </is>
       </c>
       <c r="N101">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="O101">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P101">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q101">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R101">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S101">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T101">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="U101">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="V101">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W101">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X101">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y101">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z101">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AA101">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AB101">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC101">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AD101">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE101">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF101">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG101">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AH101" t="inlineStr">
         <is>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="AJ101">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK101">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL101">
         <v>0</v>
@@ -17098,19 +17098,19 @@
         </is>
       </c>
       <c r="N103">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="O103">
         <v>7</v>
       </c>
       <c r="P103">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="Q103">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="R103">
-        <v>3.25</v>
+        <v>3.04</v>
       </c>
       <c r="S103">
         <v>1.17</v>
@@ -17119,43 +17119,43 @@
         <v>4.4</v>
       </c>
       <c r="U103">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="V103">
         <v>1.77</v>
       </c>
       <c r="W103">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X103">
         <v>1.01</v>
       </c>
       <c r="Y103">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z103">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="AA103">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AB103">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AC103">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AD103">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AE103">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AF103">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG103">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AH103" t="inlineStr">
         <is>
@@ -17168,10 +17168,10 @@
         </is>
       </c>
       <c r="AJ103">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK103">
-        <v>4.95</v>
+        <v>3.8</v>
       </c>
       <c r="AL103">
         <v>0</v>
@@ -17587,34 +17587,34 @@
         </is>
       </c>
       <c r="N106">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="O106">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P106">
         <v>3</v>
       </c>
       <c r="Q106">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="R106">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="S106">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T106">
-        <v>2.75</v>
+        <v>2.48</v>
       </c>
       <c r="U106">
         <v>2.8</v>
       </c>
       <c r="V106">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W106">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X106">
         <v>1.03</v>
@@ -17623,19 +17623,19 @@
         <v>1.3</v>
       </c>
       <c r="Z106">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AA106">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB106">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AC106">
-        <v>3.86</v>
+        <v>3.76</v>
       </c>
       <c r="AD106">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AE106">
         <v>1.03</v>
@@ -17657,10 +17657,10 @@
         </is>
       </c>
       <c r="AJ106">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AK106">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL106">
         <v>0</v>
@@ -17762,22 +17762,22 @@
         <v>4.75</v>
       </c>
       <c r="R107">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="S107">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="T107">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="U107">
-        <v>3.03</v>
+        <v>2.75</v>
       </c>
       <c r="V107">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W107">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X107">
         <v>1</v>
@@ -17801,7 +17801,7 @@
         <v>1.28</v>
       </c>
       <c r="AE107">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF107">
         <v>1.89</v>
@@ -17820,7 +17820,7 @@
         </is>
       </c>
       <c r="AJ107">
-        <v>1.2</v>
+        <v>2.12</v>
       </c>
       <c r="AK107">
         <v>1.14</v>
@@ -18402,13 +18402,13 @@
         </is>
       </c>
       <c r="N111">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O111">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="P111">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q111">
         <v>0</v>
@@ -18565,16 +18565,16 @@
         </is>
       </c>
       <c r="N112">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="O112">
         <v>3.2</v>
       </c>
       <c r="P112">
-        <v>3.8</v>
+        <v>3.97</v>
       </c>
       <c r="Q112">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="R112">
         <v>2.08</v>
@@ -18586,16 +18586,16 @@
         <v>2.75</v>
       </c>
       <c r="U112">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V112">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W112">
         <v>1.05</v>
       </c>
       <c r="X112">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y112">
         <v>1.33</v>
@@ -18604,25 +18604,25 @@
         <v>3.1</v>
       </c>
       <c r="AA112">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AB112">
         <v>1.74</v>
       </c>
       <c r="AC112">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="AD112">
         <v>1.22</v>
       </c>
       <c r="AE112">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AF112">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="AG112">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
@@ -18731,16 +18731,16 @@
         <v>1.46</v>
       </c>
       <c r="O113">
-        <v>4.33</v>
+        <v>4.35</v>
       </c>
       <c r="P113">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="Q113">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="R113">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="S113">
         <v>1.2</v>
@@ -18749,37 +18749,37 @@
         <v>4</v>
       </c>
       <c r="U113">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="V113">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="W113">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X113">
         <v>1.02</v>
       </c>
       <c r="Y113">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z113">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA113">
         <v>1.36</v>
       </c>
       <c r="AB113">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AC113">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AD113">
         <v>1.7</v>
       </c>
       <c r="AE113">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AF113">
         <v>1.51</v>
@@ -18798,10 +18798,10 @@
         </is>
       </c>
       <c r="AJ113">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AK113">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="AL113">
         <v>0</v>
@@ -18900,22 +18900,22 @@
         <v>3.45</v>
       </c>
       <c r="Q114">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="R114">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S114">
         <v>1.29</v>
       </c>
       <c r="T114">
-        <v>2.99</v>
+        <v>3.04</v>
       </c>
       <c r="U114">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="V114">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W114">
         <v>1.08</v>
@@ -18924,31 +18924,31 @@
         <v>1.04</v>
       </c>
       <c r="Y114">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z114">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="AA114">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB114">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AC114">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AD114">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE114">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF114">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AG114">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK114">
         <v>1.6</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -3572,10 +3572,10 @@
         <v>8.5</v>
       </c>
       <c r="O20">
-        <v>6.21</v>
+        <v>6.5</v>
       </c>
       <c r="P20">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Q20">
         <v>7</v>
@@ -3584,16 +3584,16 @@
         <v>2.84</v>
       </c>
       <c r="S20">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="T20">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="U20">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="V20">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="W20">
         <v>1.22</v>
@@ -3602,25 +3602,25 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="Z20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA20">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AB20">
         <v>3.4</v>
       </c>
       <c r="AC20">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AD20">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="AE20">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AF20">
         <v>1.59</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.71</v>
+        <v>2.75</v>
       </c>
       <c r="O26">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="P26">
-        <v>3.5</v>
+        <v>2.21</v>
       </c>
       <c r="Q26">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="R26">
         <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T26">
-        <v>2.97</v>
+        <v>3.09</v>
       </c>
       <c r="U26">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="V26">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="W26">
         <v>1.11</v>
@@ -4580,31 +4580,31 @@
         <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z26">
-        <v>3.6</v>
+        <v>3.76</v>
       </c>
       <c r="AA26">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AB26">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AC26">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="AD26">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE26">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG26">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AK26">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,31 +4710,31 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="O27">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P27">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="Q27">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S27">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="T27">
-        <v>3.08</v>
+        <v>2.97</v>
       </c>
       <c r="U27">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W27">
         <v>1.11</v>
@@ -4743,47 +4743,47 @@
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="AA27">
+        <v>1.77</v>
+      </c>
+      <c r="AB27">
+        <v>2</v>
+      </c>
+      <c r="AC27">
+        <v>2.95</v>
+      </c>
+      <c r="AD27">
+        <v>1.34</v>
+      </c>
+      <c r="AE27">
+        <v>1.13</v>
+      </c>
+      <c r="AF27">
+        <v>1.65</v>
+      </c>
+      <c r="AG27">
+        <v>2.07</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ27">
+        <v>1.21</v>
+      </c>
+      <c r="AK27">
         <v>1.75</v>
-      </c>
-      <c r="AB27">
-        <v>1.98</v>
-      </c>
-      <c r="AC27">
-        <v>2.7</v>
-      </c>
-      <c r="AD27">
-        <v>1.36</v>
-      </c>
-      <c r="AE27">
-        <v>1.11</v>
-      </c>
-      <c r="AF27">
-        <v>1.67</v>
-      </c>
-      <c r="AG27">
-        <v>2.05</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ27">
-        <v>1.19</v>
-      </c>
-      <c r="AK27">
-        <v>2.05</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,31 +5036,31 @@
         </is>
       </c>
       <c r="N29">
-        <v>2.75</v>
+        <v>1.61</v>
       </c>
       <c r="O29">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="P29">
-        <v>2.21</v>
+        <v>4.2</v>
       </c>
       <c r="Q29">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="R29">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S29">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T29">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="U29">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="V29">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W29">
         <v>1.11</v>
@@ -5069,31 +5069,31 @@
         <v>1.03</v>
       </c>
       <c r="Y29">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z29">
-        <v>3.76</v>
+        <v>4.2</v>
       </c>
       <c r="AA29">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB29">
-        <v>2.04</v>
+        <v>1.98</v>
       </c>
       <c r="AC29">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AD29">
         <v>1.36</v>
       </c>
       <c r="AE29">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF29">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AG29">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="AK29">
-        <v>1.4</v>
+        <v>2.05</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -8296,13 +8296,13 @@
         </is>
       </c>
       <c r="N49">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="O49">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="P49">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -8459,34 +8459,34 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="O50">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="P50">
-        <v>4.05</v>
+        <v>4.75</v>
       </c>
       <c r="Q50">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="R50">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="S50">
         <v>1.18</v>
       </c>
       <c r="T50">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="U50">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="V50">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="W50">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="X50">
         <v>1.01</v>
@@ -8498,22 +8498,22 @@
         <v>6.5</v>
       </c>
       <c r="AA50">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AB50">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="AC50">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AD50">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AE50">
         <v>1.28</v>
       </c>
       <c r="AF50">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AG50">
         <v>2.5</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AK50">
         <v>2.1</v>
@@ -8622,13 +8622,13 @@
         </is>
       </c>
       <c r="N51">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="O51">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="P51">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="Q51">
         <v>4.33</v>
@@ -8637,7 +8637,7 @@
         <v>1.91</v>
       </c>
       <c r="S51">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="T51">
         <v>2.38</v>
@@ -8655,19 +8655,19 @@
         <v>1.1</v>
       </c>
       <c r="Y51">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z51">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AA51">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="AB51">
         <v>1.44</v>
       </c>
       <c r="AC51">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="AD51">
         <v>1.15</v>
@@ -8676,10 +8676,10 @@
         <v>1.04</v>
       </c>
       <c r="AF51">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG51">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="AJ51">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AK51">
         <v>1.22</v>
@@ -12371,31 +12371,31 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.76</v>
+        <v>2.95</v>
       </c>
       <c r="O74">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="P74">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="Q74">
         <v>3.4</v>
       </c>
       <c r="R74">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="S74">
         <v>1.62</v>
       </c>
       <c r="T74">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="U74">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="V74">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W74">
         <v>1.03</v>
@@ -12410,7 +12410,7 @@
         <v>2.3</v>
       </c>
       <c r="AA74">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="AB74">
         <v>1.31</v>
@@ -12428,7 +12428,7 @@
         <v>2.18</v>
       </c>
       <c r="AG74">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,7 +12441,7 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AK74">
         <v>1.33</v>
@@ -13512,22 +13512,22 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="O81">
-        <v>3.2</v>
+        <v>3.32</v>
       </c>
       <c r="P81">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="Q81">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R81">
         <v>2.14</v>
       </c>
       <c r="S81">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T81">
         <v>2.9</v>
@@ -13539,7 +13539,7 @@
         <v>1.34</v>
       </c>
       <c r="W81">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X81">
         <v>1.05</v>
@@ -13548,19 +13548,19 @@
         <v>1.37</v>
       </c>
       <c r="Z81">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="AA81">
-        <v>2.06</v>
+        <v>2.13</v>
       </c>
       <c r="AB81">
         <v>1.69</v>
       </c>
       <c r="AC81">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AD81">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE81">
         <v>1.08</v>
@@ -13582,10 +13582,10 @@
         </is>
       </c>
       <c r="AJ81">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AK81">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="AL81">
         <v>0</v>
@@ -13675,10 +13675,10 @@
         </is>
       </c>
       <c r="N82">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O82">
-        <v>3.5</v>
+        <v>3.74</v>
       </c>
       <c r="P82">
         <v>1.68</v>
@@ -13690,7 +13690,7 @@
         <v>2.2</v>
       </c>
       <c r="S82">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T82">
         <v>2.9</v>
@@ -13711,7 +13711,7 @@
         <v>1.28</v>
       </c>
       <c r="Z82">
-        <v>3.43</v>
+        <v>3.44</v>
       </c>
       <c r="AA82">
         <v>1.85</v>
@@ -13726,7 +13726,7 @@
         <v>1.29</v>
       </c>
       <c r="AE82">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF82">
         <v>1.79</v>
@@ -13748,7 +13748,7 @@
         <v>1.25</v>
       </c>
       <c r="AK82">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AL82">
         <v>0</v>
@@ -13844,25 +13844,25 @@
         <v>3.7</v>
       </c>
       <c r="P83">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Q83">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="R83">
-        <v>2.29</v>
+        <v>2.34</v>
       </c>
       <c r="S83">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="T83">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U83">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="V83">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="W83">
         <v>1.13</v>
@@ -13874,13 +13874,13 @@
         <v>1.13</v>
       </c>
       <c r="Z83">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA83">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="AB83">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="AC83">
         <v>2.5</v>
@@ -13889,7 +13889,7 @@
         <v>1.49</v>
       </c>
       <c r="AE83">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AF83">
         <v>1.55</v>
@@ -13911,7 +13911,7 @@
         <v>1.21</v>
       </c>
       <c r="AK83">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AL83">
         <v>0</v>
@@ -13969,12 +13969,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G84">
@@ -14001,64 +14001,64 @@
         </is>
       </c>
       <c r="N84">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="O84">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P84">
-        <v>2.5</v>
+        <v>1.93</v>
       </c>
       <c r="Q84">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R84">
         <v>2.3</v>
       </c>
       <c r="S84">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T84">
-        <v>2.91</v>
+        <v>3.12</v>
       </c>
       <c r="U84">
+        <v>2.3</v>
+      </c>
+      <c r="V84">
+        <v>1.55</v>
+      </c>
+      <c r="W84">
+        <v>1.12</v>
+      </c>
+      <c r="X84">
+        <v>1.01</v>
+      </c>
+      <c r="Y84">
+        <v>1.19</v>
+      </c>
+      <c r="Z84">
+        <v>3.85</v>
+      </c>
+      <c r="AA84">
+        <v>1.64</v>
+      </c>
+      <c r="AB84">
+        <v>2.14</v>
+      </c>
+      <c r="AC84">
         <v>2.63</v>
       </c>
-      <c r="V84">
-        <v>1.44</v>
-      </c>
-      <c r="W84">
-        <v>1.06</v>
-      </c>
-      <c r="X84">
-        <v>1.03</v>
-      </c>
-      <c r="Y84">
-        <v>1.18</v>
-      </c>
-      <c r="Z84">
-        <v>3.5</v>
-      </c>
-      <c r="AA84">
-        <v>1.74</v>
-      </c>
-      <c r="AB84">
-        <v>2.1</v>
-      </c>
-      <c r="AC84">
-        <v>2.8</v>
-      </c>
       <c r="AD84">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AE84">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF84">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AG84">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AH84" t="inlineStr">
         <is>
@@ -14071,10 +14071,10 @@
         </is>
       </c>
       <c r="AJ84">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="AK84">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AL84">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="O85">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="P85">
-        <v>1.93</v>
+        <v>1.48</v>
       </c>
       <c r="Q85">
+        <v>6.73</v>
+      </c>
+      <c r="R85">
+        <v>2.58</v>
+      </c>
+      <c r="S85">
+        <v>1.3</v>
+      </c>
+      <c r="T85">
         <v>3.3</v>
       </c>
-      <c r="R85">
-        <v>2.3</v>
-      </c>
-      <c r="S85">
-        <v>1.29</v>
-      </c>
-      <c r="T85">
-        <v>3.12</v>
-      </c>
       <c r="U85">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="V85">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W85">
         <v>1.12</v>
       </c>
       <c r="X85">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
+        <v>1.2</v>
+      </c>
+      <c r="Z85">
+        <v>3.95</v>
+      </c>
+      <c r="AA85">
+        <v>1.73</v>
+      </c>
+      <c r="AB85">
+        <v>2.15</v>
+      </c>
+      <c r="AC85">
+        <v>2.7</v>
+      </c>
+      <c r="AD85">
+        <v>1.44</v>
+      </c>
+      <c r="AE85">
         <v>1.19</v>
       </c>
-      <c r="Z85">
-        <v>3.85</v>
-      </c>
-      <c r="AA85">
-        <v>1.64</v>
-      </c>
-      <c r="AB85">
-        <v>2.14</v>
-      </c>
-      <c r="AC85">
-        <v>2.63</v>
-      </c>
-      <c r="AD85">
-        <v>1.47</v>
-      </c>
-      <c r="AE85">
-        <v>1.13</v>
-      </c>
       <c r="AF85">
-        <v>1.54</v>
+        <v>1.75</v>
       </c>
       <c r="AG85">
-        <v>2.25</v>
+        <v>1.97</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.22</v>
+        <v>2.5</v>
       </c>
       <c r="AK85">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,65 +14327,65 @@
         </is>
       </c>
       <c r="N86">
-        <v>5.25</v>
+        <v>2.5</v>
       </c>
       <c r="O86">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="P86">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q86">
-        <v>6.73</v>
+        <v>3.2</v>
       </c>
       <c r="R86">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="S86">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T86">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="U86">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V86">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W86">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z86">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA86">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB86">
+        <v>2.1</v>
+      </c>
+      <c r="AC86">
+        <v>2.8</v>
+      </c>
+      <c r="AD86">
+        <v>1.41</v>
+      </c>
+      <c r="AE86">
+        <v>1.1</v>
+      </c>
+      <c r="AF86">
+        <v>1.56</v>
+      </c>
+      <c r="AG86">
         <v>2.15</v>
       </c>
-      <c r="AC86">
-        <v>2.7</v>
-      </c>
-      <c r="AD86">
-        <v>1.44</v>
-      </c>
-      <c r="AE86">
-        <v>1.19</v>
-      </c>
-      <c r="AF86">
-        <v>1.75</v>
-      </c>
-      <c r="AG86">
-        <v>1.97</v>
-      </c>
       <c r="AH86" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>2.5</v>
+        <v>1.43</v>
       </c>
       <c r="AK86">
-        <v>1.09</v>
+        <v>1.39</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -15154,7 +15154,7 @@
         <v>2.45</v>
       </c>
       <c r="R91">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S91">
         <v>1.34</v>
@@ -15178,7 +15178,7 @@
         <v>1.25</v>
       </c>
       <c r="Z91">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="AA91">
         <v>1.85</v>
@@ -15212,10 +15212,10 @@
         </is>
       </c>
       <c r="AJ91">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK91">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15311,13 +15311,13 @@
         <v>3.4</v>
       </c>
       <c r="P92">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="Q92">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R92">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S92">
         <v>1.33</v>
@@ -15338,7 +15338,7 @@
         <v>1.04</v>
       </c>
       <c r="Y92">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z92">
         <v>3.9</v>
@@ -15347,22 +15347,22 @@
         <v>1.72</v>
       </c>
       <c r="AB92">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC92">
         <v>2.63</v>
       </c>
       <c r="AD92">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AE92">
         <v>1.17</v>
       </c>
       <c r="AF92">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG92">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AH92" t="inlineStr">
         <is>
@@ -15375,10 +15375,10 @@
         </is>
       </c>
       <c r="AJ92">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="AK92">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="N94">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="O94">
         <v>3.4</v>
@@ -15655,13 +15655,13 @@
         <v>2.8</v>
       </c>
       <c r="V94">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W94">
         <v>1.08</v>
       </c>
       <c r="X94">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y94">
         <v>1.29</v>
@@ -15670,13 +15670,13 @@
         <v>3.5</v>
       </c>
       <c r="AA94">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB94">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AC94">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD94">
         <v>1.29</v>
@@ -16935,43 +16935,43 @@
         </is>
       </c>
       <c r="N102">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="O102">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P102">
         <v>4.5</v>
       </c>
       <c r="Q102">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R102">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S102">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="T102">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="U102">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V102">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W102">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X102">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Y102">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z102">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA102">
         <v>2.87</v>
@@ -16980,19 +16980,19 @@
         <v>1.4</v>
       </c>
       <c r="AC102">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD102">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AE102">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF102">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG102">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AH102" t="inlineStr">
         <is>
@@ -17005,10 +17005,10 @@
         </is>
       </c>
       <c r="AJ102">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AK102">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL102">
         <v>0</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="O25">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P25">
-        <v>3</v>
+        <v>2.21</v>
       </c>
       <c r="Q25">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R25">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S25">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
-        <v>3.28</v>
+        <v>3.09</v>
       </c>
       <c r="U25">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V25">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="W25">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X25">
         <v>1.03</v>
       </c>
       <c r="Y25">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="Z25">
-        <v>4.3</v>
+        <v>3.76</v>
       </c>
       <c r="AA25">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AB25">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AC25">
-        <v>2.52</v>
+        <v>2.85</v>
       </c>
       <c r="AD25">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE25">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AF25">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="AG25">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.21</v>
+        <v>1.53</v>
       </c>
       <c r="AK25">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,31 +4547,31 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.75</v>
+        <v>1.71</v>
       </c>
       <c r="O26">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="P26">
-        <v>2.21</v>
+        <v>3.5</v>
       </c>
       <c r="Q26">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="R26">
         <v>2.25</v>
       </c>
       <c r="S26">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T26">
-        <v>3.09</v>
+        <v>2.97</v>
       </c>
       <c r="U26">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V26">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W26">
         <v>1.11</v>
@@ -4580,31 +4580,31 @@
         <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="Z26">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="AA26">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AB26">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AC26">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="AD26">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE26">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AG26">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.53</v>
+        <v>1.21</v>
       </c>
       <c r="AK26">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="O27">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P27">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q27">
+        <v>2.5</v>
+      </c>
+      <c r="R27">
+        <v>2.22</v>
+      </c>
+      <c r="S27">
+        <v>1.28</v>
+      </c>
+      <c r="T27">
+        <v>3.28</v>
+      </c>
+      <c r="U27">
         <v>2.38</v>
       </c>
-      <c r="R27">
-        <v>2.25</v>
-      </c>
-      <c r="S27">
-        <v>1.32</v>
-      </c>
-      <c r="T27">
-        <v>2.97</v>
-      </c>
-      <c r="U27">
-        <v>2.63</v>
-      </c>
       <c r="V27">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="W27">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X27">
         <v>1.03</v>
       </c>
       <c r="Y27">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="Z27">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="AA27">
-        <v>1.77</v>
+        <v>1.62</v>
       </c>
       <c r="AB27">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC27">
-        <v>2.95</v>
+        <v>2.52</v>
       </c>
       <c r="AD27">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF27">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AG27">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4783,7 +4783,7 @@
         <v>1.21</v>
       </c>
       <c r="AK27">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,80 +7644,80 @@
         </is>
       </c>
       <c r="N45">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O45">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P45">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="Q45">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R45">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S45">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T45">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="U45">
-        <v>2.17</v>
+        <v>2.47</v>
       </c>
       <c r="V45">
-        <v>1.64</v>
+        <v>1.52</v>
       </c>
       <c r="W45">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X45">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y45">
+        <v>1.18</v>
+      </c>
+      <c r="Z45">
+        <v>4.4</v>
+      </c>
+      <c r="AA45">
+        <v>1.62</v>
+      </c>
+      <c r="AB45">
+        <v>2.16</v>
+      </c>
+      <c r="AC45">
+        <v>2.52</v>
+      </c>
+      <c r="AD45">
+        <v>1.44</v>
+      </c>
+      <c r="AE45">
         <v>1.14</v>
       </c>
-      <c r="Z45">
-        <v>5.5</v>
-      </c>
-      <c r="AA45">
-        <v>1.45</v>
-      </c>
-      <c r="AB45">
-        <v>2.41</v>
-      </c>
-      <c r="AC45">
-        <v>2.1</v>
-      </c>
-      <c r="AD45">
-        <v>1.65</v>
-      </c>
-      <c r="AE45">
+      <c r="AF45">
+        <v>1.55</v>
+      </c>
+      <c r="AG45">
+        <v>2.23</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ45">
         <v>1.25</v>
       </c>
-      <c r="AF45">
-        <v>1.4</v>
-      </c>
-      <c r="AG45">
-        <v>2.7</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ45">
-        <v>1.22</v>
-      </c>
       <c r="AK45">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,64 +7807,64 @@
         </is>
       </c>
       <c r="N46">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O46">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P46">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="Q46">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="R46">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S46">
+        <v>1.28</v>
+      </c>
+      <c r="T46">
+        <v>3.7</v>
+      </c>
+      <c r="U46">
+        <v>2.17</v>
+      </c>
+      <c r="V46">
+        <v>1.64</v>
+      </c>
+      <c r="W46">
+        <v>1.13</v>
+      </c>
+      <c r="X46">
+        <v>1.02</v>
+      </c>
+      <c r="Y46">
+        <v>1.14</v>
+      </c>
+      <c r="Z46">
+        <v>5.5</v>
+      </c>
+      <c r="AA46">
+        <v>1.45</v>
+      </c>
+      <c r="AB46">
+        <v>2.41</v>
+      </c>
+      <c r="AC46">
+        <v>2.1</v>
+      </c>
+      <c r="AD46">
+        <v>1.65</v>
+      </c>
+      <c r="AE46">
         <v>1.25</v>
       </c>
-      <c r="T46">
-        <v>3.3</v>
-      </c>
-      <c r="U46">
-        <v>2.47</v>
-      </c>
-      <c r="V46">
-        <v>1.52</v>
-      </c>
-      <c r="W46">
-        <v>1.12</v>
-      </c>
-      <c r="X46">
-        <v>1.01</v>
-      </c>
-      <c r="Y46">
-        <v>1.18</v>
-      </c>
-      <c r="Z46">
-        <v>4.4</v>
-      </c>
-      <c r="AA46">
-        <v>1.62</v>
-      </c>
-      <c r="AB46">
-        <v>2.16</v>
-      </c>
-      <c r="AC46">
-        <v>2.52</v>
-      </c>
-      <c r="AD46">
-        <v>1.44</v>
-      </c>
-      <c r="AE46">
-        <v>1.14</v>
-      </c>
       <c r="AF46">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG46">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="AH46" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         </is>
       </c>
       <c r="AJ46">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK46">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>5.25</v>
+        <v>2.15</v>
       </c>
       <c r="O85">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="P85">
-        <v>1.48</v>
+        <v>2.9</v>
       </c>
       <c r="Q85">
-        <v>6.73</v>
+        <v>2.7</v>
       </c>
       <c r="R85">
-        <v>2.58</v>
+        <v>2.25</v>
       </c>
       <c r="S85">
         <v>1.3</v>
       </c>
       <c r="T85">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U85">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="V85">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W85">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X85">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y85">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z85">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AA85">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB85">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AC85">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AD85">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AE85">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF85">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AG85">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK85">
-        <v>1.09</v>
+        <v>1.58</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,80 +14327,80 @@
         </is>
       </c>
       <c r="N86">
+        <v>5.25</v>
+      </c>
+      <c r="O86">
+        <v>4.1</v>
+      </c>
+      <c r="P86">
+        <v>1.48</v>
+      </c>
+      <c r="Q86">
+        <v>6.73</v>
+      </c>
+      <c r="R86">
+        <v>2.58</v>
+      </c>
+      <c r="S86">
+        <v>1.3</v>
+      </c>
+      <c r="T86">
+        <v>3.3</v>
+      </c>
+      <c r="U86">
+        <v>2.4</v>
+      </c>
+      <c r="V86">
+        <v>1.5</v>
+      </c>
+      <c r="W86">
+        <v>1.12</v>
+      </c>
+      <c r="X86">
+        <v>1.02</v>
+      </c>
+      <c r="Y86">
+        <v>1.2</v>
+      </c>
+      <c r="Z86">
+        <v>3.95</v>
+      </c>
+      <c r="AA86">
+        <v>1.73</v>
+      </c>
+      <c r="AB86">
+        <v>2.15</v>
+      </c>
+      <c r="AC86">
+        <v>2.7</v>
+      </c>
+      <c r="AD86">
+        <v>1.44</v>
+      </c>
+      <c r="AE86">
+        <v>1.19</v>
+      </c>
+      <c r="AF86">
+        <v>1.75</v>
+      </c>
+      <c r="AG86">
+        <v>1.97</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ86">
         <v>2.5</v>
       </c>
-      <c r="O86">
-        <v>3.2</v>
-      </c>
-      <c r="P86">
-        <v>2.5</v>
-      </c>
-      <c r="Q86">
-        <v>3.2</v>
-      </c>
-      <c r="R86">
-        <v>2.3</v>
-      </c>
-      <c r="S86">
-        <v>1.33</v>
-      </c>
-      <c r="T86">
-        <v>2.91</v>
-      </c>
-      <c r="U86">
-        <v>2.63</v>
-      </c>
-      <c r="V86">
-        <v>1.44</v>
-      </c>
-      <c r="W86">
-        <v>1.06</v>
-      </c>
-      <c r="X86">
-        <v>1.03</v>
-      </c>
-      <c r="Y86">
-        <v>1.18</v>
-      </c>
-      <c r="Z86">
-        <v>3.5</v>
-      </c>
-      <c r="AA86">
-        <v>1.74</v>
-      </c>
-      <c r="AB86">
-        <v>2.1</v>
-      </c>
-      <c r="AC86">
-        <v>2.8</v>
-      </c>
-      <c r="AD86">
-        <v>1.41</v>
-      </c>
-      <c r="AE86">
-        <v>1.1</v>
-      </c>
-      <c r="AF86">
-        <v>1.56</v>
-      </c>
-      <c r="AG86">
-        <v>2.15</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ86">
-        <v>1.43</v>
-      </c>
       <c r="AK86">
-        <v>1.39</v>
+        <v>1.09</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,31 +14490,31 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="O87">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P87">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="Q87">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="R87">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S87">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T87">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="U87">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="V87">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W87">
         <v>1.06</v>
@@ -14523,31 +14523,31 @@
         <v>1.03</v>
       </c>
       <c r="Y87">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z87">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA87">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AB87">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AC87">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD87">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE87">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF87">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AG87">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH87" t="inlineStr">
         <is>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AK87">
-        <v>1.58</v>
+        <v>1.39</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -18903,34 +18903,34 @@
         <v>2.7</v>
       </c>
       <c r="R114">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S114">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T114">
-        <v>3.04</v>
+        <v>2.99</v>
       </c>
       <c r="U114">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="V114">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W114">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X114">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y114">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z114">
         <v>3.6</v>
       </c>
       <c r="AA114">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AB114">
         <v>1.98</v>
@@ -18942,13 +18942,13 @@
         <v>1.37</v>
       </c>
       <c r="AE114">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF114">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AG114">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AH114" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         </is>
       </c>
       <c r="AJ114">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="AK114">
         <v>1.6</v>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="O6">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="P6">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="O8">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="P8">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="Q8">
         <v>2.8</v>
@@ -1628,13 +1628,13 @@
         <v>2.02</v>
       </c>
       <c r="S8">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="T8">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="U8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="V8">
         <v>1.25</v>
@@ -1649,22 +1649,22 @@
         <v>1.44</v>
       </c>
       <c r="Z8">
-        <v>2.53</v>
+        <v>2.42</v>
       </c>
       <c r="AA8">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="AB8">
         <v>1.53</v>
       </c>
       <c r="AC8">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AD8">
         <v>1.13</v>
       </c>
       <c r="AE8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF8">
         <v>2.1</v>
@@ -1686,7 +1686,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O9">
         <v>4.35</v>
       </c>
       <c r="P9">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q9">
         <v>4.75</v>
@@ -1794,7 +1794,7 @@
         <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.75</v>
+        <v>3.42</v>
       </c>
       <c r="U9">
         <v>2.24</v>
@@ -1803,7 +1803,7 @@
         <v>1.57</v>
       </c>
       <c r="W9">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1815,13 +1815,13 @@
         <v>5.5</v>
       </c>
       <c r="AA9">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AB9">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AC9">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AD9">
         <v>1.55</v>
@@ -1830,10 +1830,10 @@
         <v>1.17</v>
       </c>
       <c r="AF9">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AG9">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.15</v>
+        <v>2.3</v>
       </c>
       <c r="AK9">
         <v>1.17</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB10">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -3080,31 +3080,31 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.45</v>
+        <v>1.8</v>
       </c>
       <c r="O17">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>5.98</v>
+        <v>3.55</v>
       </c>
       <c r="Q17">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="R17">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T17">
+        <v>2.69</v>
+      </c>
+      <c r="U17">
         <v>2.88</v>
       </c>
-      <c r="U17">
-        <v>2.71</v>
-      </c>
       <c r="V17">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
         <v>1.07</v>
@@ -3113,31 +3113,31 @@
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z17">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AA17">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="AB17">
         <v>1.85</v>
       </c>
       <c r="AC17">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="AD17">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AE17">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="AF17">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>2.55</v>
+        <v>1.73</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,43 +3243,43 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q18">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="R18">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T18">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="U18">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="V18">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Z18">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="AA18">
         <v>1.93</v>
@@ -3291,16 +3291,16 @@
         <v>3.6</v>
       </c>
       <c r="AD18">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE18">
         <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AK18">
         <v>1.47</v>
@@ -3569,16 +3569,16 @@
         </is>
       </c>
       <c r="N20">
-        <v>8.5</v>
+        <v>8.75</v>
       </c>
       <c r="O20">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="P20">
         <v>1.28</v>
       </c>
       <c r="Q20">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="R20">
         <v>2.84</v>
@@ -3602,16 +3602,16 @@
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="Z20">
         <v>7</v>
       </c>
       <c r="AA20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB20">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AC20">
         <v>1.78</v>
@@ -3620,7 +3620,7 @@
         <v>1.97</v>
       </c>
       <c r="AE20">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AF20">
         <v>1.59</v>
@@ -4233,7 +4233,7 @@
         <v>1.73</v>
       </c>
       <c r="R24">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="S24">
         <v>1.2</v>
@@ -4242,10 +4242,10 @@
         <v>4.2</v>
       </c>
       <c r="U24">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V24">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="W24">
         <v>1.2</v>
@@ -4254,31 +4254,31 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Z24">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA24">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AB24">
-        <v>2.66</v>
+        <v>2.78</v>
       </c>
       <c r="AC24">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="AD24">
         <v>1.73</v>
       </c>
       <c r="AE24">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AF24">
         <v>1.57</v>
       </c>
       <c r="AG24">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Vysočina Jihlava</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Táborsko</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,64 +4384,64 @@
         </is>
       </c>
       <c r="N25">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="O25">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="P25">
-        <v>2.21</v>
+        <v>2.85</v>
       </c>
       <c r="Q25">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="R25">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="T25">
-        <v>3.09</v>
+        <v>2.9</v>
       </c>
       <c r="U25">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="V25">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="W25">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y25">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="Z25">
-        <v>3.76</v>
+        <v>3.14</v>
       </c>
       <c r="AA25">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="AB25">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="AC25">
-        <v>2.85</v>
+        <v>3.14</v>
       </c>
       <c r="AD25">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AE25">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="AF25">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AG25">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="AH25" t="inlineStr">
         <is>
@@ -4454,10 +4454,10 @@
         </is>
       </c>
       <c r="AJ25">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="AK25">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AL25">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kladno</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="O26">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="P26">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Q26">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="R26">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T26">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="U26">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="V26">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="W26">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X26">
         <v>1.03</v>
       </c>
       <c r="Y26">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="Z26">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AA26">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AB26">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AC26">
-        <v>2.95</v>
+        <v>2.6</v>
       </c>
       <c r="AD26">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AE26">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF26">
-        <v>1.65</v>
+        <v>1.52</v>
       </c>
       <c r="AG26">
-        <v>2.07</v>
+        <v>2.25</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AK26">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Kladno</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,65 +4710,65 @@
         </is>
       </c>
       <c r="N27">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="O27">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P27">
+        <v>2.86</v>
+      </c>
+      <c r="Q27">
+        <v>2.38</v>
+      </c>
+      <c r="R27">
+        <v>2.25</v>
+      </c>
+      <c r="S27">
+        <v>1.34</v>
+      </c>
+      <c r="T27">
         <v>3</v>
       </c>
-      <c r="Q27">
-        <v>2.5</v>
-      </c>
-      <c r="R27">
-        <v>2.22</v>
-      </c>
-      <c r="S27">
-        <v>1.28</v>
-      </c>
-      <c r="T27">
-        <v>3.28</v>
-      </c>
       <c r="U27">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="V27">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="W27">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y27">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="Z27">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="AA27">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AB27">
+        <v>2.01</v>
+      </c>
+      <c r="AC27">
+        <v>2.95</v>
+      </c>
+      <c r="AD27">
+        <v>1.35</v>
+      </c>
+      <c r="AE27">
+        <v>1.14</v>
+      </c>
+      <c r="AF27">
+        <v>1.65</v>
+      </c>
+      <c r="AG27">
         <v>2.15</v>
       </c>
-      <c r="AC27">
-        <v>2.52</v>
-      </c>
-      <c r="AD27">
-        <v>1.41</v>
-      </c>
-      <c r="AE27">
-        <v>1.18</v>
-      </c>
-      <c r="AF27">
-        <v>1.52</v>
-      </c>
-      <c r="AG27">
-        <v>2.25</v>
-      </c>
       <c r="AH27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="AK27">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Vysočina Jihlava</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Táborsko</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,64 +4873,64 @@
         </is>
       </c>
       <c r="N28">
-        <v>2.2</v>
+        <v>1.65</v>
       </c>
       <c r="O28">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="P28">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="Q28">
-        <v>2.95</v>
+        <v>2.25</v>
       </c>
       <c r="R28">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="T28">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="U28">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="V28">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="X28">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y28">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z28">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="AA28">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AB28">
-        <v>1.78</v>
+        <v>2.07</v>
       </c>
       <c r="AC28">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="AD28">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AE28">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AF28">
         <v>1.7</v>
       </c>
       <c r="AG28">
-        <v>1.96</v>
+        <v>2.01</v>
       </c>
       <c r="AH28" t="inlineStr">
         <is>
@@ -4943,10 +4943,10 @@
         </is>
       </c>
       <c r="AJ28">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK28">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="G29">
@@ -5036,64 +5036,64 @@
         </is>
       </c>
       <c r="N29">
-        <v>1.61</v>
+        <v>2.75</v>
       </c>
       <c r="O29">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P29">
-        <v>4.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q29">
+        <v>3.1</v>
+      </c>
+      <c r="R29">
         <v>2.15</v>
       </c>
-      <c r="R29">
-        <v>2.3</v>
-      </c>
       <c r="S29">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T29">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="U29">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W29">
         <v>1.11</v>
       </c>
       <c r="X29">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y29">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z29">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="AA29">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB29">
         <v>1.98</v>
       </c>
       <c r="AC29">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="AD29">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE29">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF29">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="AG29">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="AJ29">
-        <v>1.19</v>
+        <v>1.53</v>
       </c>
       <c r="AK29">
-        <v>2.05</v>
+        <v>1.4</v>
       </c>
       <c r="AL29">
         <v>0</v>
@@ -5199,64 +5199,64 @@
         </is>
       </c>
       <c r="N30">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="O30">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P30">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="AA30">
         <v>1.7</v>
       </c>
       <c r="AB30">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL30">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         </is>
       </c>
       <c r="N36">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="O36">
         <v>3.45</v>
       </c>
       <c r="P36">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="Q36">
         <v>3</v>
@@ -6192,28 +6192,28 @@
         <v>2.45</v>
       </c>
       <c r="S36">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="T36">
         <v>3.75</v>
       </c>
       <c r="U36">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="V36">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="W36">
         <v>1.14</v>
       </c>
       <c r="X36">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y36">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z36">
-        <v>4.85</v>
+        <v>5</v>
       </c>
       <c r="AA36">
         <v>1.53</v>
@@ -6225,32 +6225,32 @@
         <v>2.3</v>
       </c>
       <c r="AD36">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AE36">
+        <v>1.21</v>
+      </c>
+      <c r="AF36">
+        <v>1.45</v>
+      </c>
+      <c r="AG36">
+        <v>2.5</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ36">
         <v>1.22</v>
       </c>
-      <c r="AF36">
-        <v>1.43</v>
-      </c>
-      <c r="AG36">
-        <v>2.59</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ36">
-        <v>1.2</v>
-      </c>
       <c r="AK36">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL36">
         <v>0</v>
@@ -6343,16 +6343,16 @@
         <v>3</v>
       </c>
       <c r="O37">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="P37">
         <v>1.95</v>
       </c>
       <c r="Q37">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="R37">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S37">
         <v>1.3</v>
@@ -6376,7 +6376,7 @@
         <v>1.2</v>
       </c>
       <c r="Z37">
-        <v>4.34</v>
+        <v>4.39</v>
       </c>
       <c r="AA37">
         <v>1.7</v>
@@ -6385,16 +6385,16 @@
         <v>2.1</v>
       </c>
       <c r="AC37">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AD37">
         <v>1.42</v>
       </c>
       <c r="AE37">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF37">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG37">
         <v>2.25</v>
@@ -6413,7 +6413,7 @@
         <v>1.28</v>
       </c>
       <c r="AK37">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL37">
         <v>0</v>
@@ -6503,28 +6503,28 @@
         </is>
       </c>
       <c r="N38">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="O38">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P38">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="Q38">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="R38">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="S38">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="T38">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="U38">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="V38">
         <v>1.33</v>
@@ -6533,13 +6533,13 @@
         <v>1.03</v>
       </c>
       <c r="X38">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y38">
         <v>1.4</v>
       </c>
       <c r="Z38">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AA38">
         <v>2.38</v>
@@ -6548,19 +6548,19 @@
         <v>1.57</v>
       </c>
       <c r="AC38">
-        <v>4.37</v>
+        <v>4.08</v>
       </c>
       <c r="AD38">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE38">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF38">
         <v>2.3</v>
       </c>
       <c r="AG38">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
@@ -6573,10 +6573,10 @@
         </is>
       </c>
       <c r="AJ38">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AK38">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AL38">
         <v>0</v>
@@ -6669,13 +6669,13 @@
         <v>3.96</v>
       </c>
       <c r="O39">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="P39">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Q39">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="R39">
         <v>1.85</v>
@@ -6720,10 +6720,10 @@
         <v>1.03</v>
       </c>
       <c r="AF39">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AG39">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6736,10 +6736,10 @@
         </is>
       </c>
       <c r="AJ39">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AK39">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AL39">
         <v>0</v>
@@ -7612,12 +7612,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Neuchâtel Xamax</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Étoile Carouge</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G45">
@@ -7644,64 +7644,64 @@
         </is>
       </c>
       <c r="N45">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O45">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P45">
         <v>1.95</v>
       </c>
       <c r="Q45">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="R45">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="S45">
+        <v>1.2</v>
+      </c>
+      <c r="T45">
+        <v>3.7</v>
+      </c>
+      <c r="U45">
+        <v>2.17</v>
+      </c>
+      <c r="V45">
+        <v>1.65</v>
+      </c>
+      <c r="W45">
+        <v>1.13</v>
+      </c>
+      <c r="X45">
+        <v>1.02</v>
+      </c>
+      <c r="Y45">
+        <v>1.14</v>
+      </c>
+      <c r="Z45">
+        <v>5.5</v>
+      </c>
+      <c r="AA45">
+        <v>1.44</v>
+      </c>
+      <c r="AB45">
+        <v>2.6</v>
+      </c>
+      <c r="AC45">
+        <v>2.1</v>
+      </c>
+      <c r="AD45">
+        <v>1.65</v>
+      </c>
+      <c r="AE45">
         <v>1.25</v>
       </c>
-      <c r="T45">
-        <v>3.3</v>
-      </c>
-      <c r="U45">
-        <v>2.47</v>
-      </c>
-      <c r="V45">
-        <v>1.52</v>
-      </c>
-      <c r="W45">
-        <v>1.12</v>
-      </c>
-      <c r="X45">
-        <v>1.01</v>
-      </c>
-      <c r="Y45">
-        <v>1.18</v>
-      </c>
-      <c r="Z45">
-        <v>4.4</v>
-      </c>
-      <c r="AA45">
-        <v>1.62</v>
-      </c>
-      <c r="AB45">
-        <v>2.16</v>
-      </c>
-      <c r="AC45">
-        <v>2.52</v>
-      </c>
-      <c r="AD45">
-        <v>1.44</v>
-      </c>
-      <c r="AE45">
-        <v>1.14</v>
-      </c>
       <c r="AF45">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="AG45">
-        <v>2.23</v>
+        <v>2.75</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="AJ45">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK45">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AL45">
         <v>0</v>
@@ -7775,12 +7775,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Neuchâtel Xamax</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Étoile Carouge</t>
         </is>
       </c>
       <c r="G46">
@@ -7807,80 +7807,80 @@
         </is>
       </c>
       <c r="N46">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O46">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P46">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="Q46">
-        <v>3.4</v>
+        <v>3.42</v>
       </c>
       <c r="R46">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S46">
         <v>1.28</v>
       </c>
       <c r="T46">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="U46">
-        <v>2.17</v>
+        <v>2.48</v>
       </c>
       <c r="V46">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="W46">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="X46">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y46">
+        <v>1.18</v>
+      </c>
+      <c r="Z46">
+        <v>4.33</v>
+      </c>
+      <c r="AA46">
+        <v>1.65</v>
+      </c>
+      <c r="AB46">
+        <v>2.11</v>
+      </c>
+      <c r="AC46">
+        <v>2.56</v>
+      </c>
+      <c r="AD46">
+        <v>1.44</v>
+      </c>
+      <c r="AE46">
         <v>1.14</v>
       </c>
-      <c r="Z46">
-        <v>5.5</v>
-      </c>
-      <c r="AA46">
-        <v>1.45</v>
-      </c>
-      <c r="AB46">
-        <v>2.41</v>
-      </c>
-      <c r="AC46">
-        <v>2.1</v>
-      </c>
-      <c r="AD46">
-        <v>1.65</v>
-      </c>
-      <c r="AE46">
+      <c r="AF46">
+        <v>1.55</v>
+      </c>
+      <c r="AG46">
+        <v>2.25</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ46">
         <v>1.25</v>
       </c>
-      <c r="AF46">
-        <v>1.4</v>
-      </c>
-      <c r="AG46">
-        <v>2.7</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ46">
-        <v>1.22</v>
-      </c>
       <c r="AK46">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL46">
         <v>0</v>
@@ -7988,25 +7988,25 @@
         <v>1.4</v>
       </c>
       <c r="T47">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="U47">
-        <v>3.05</v>
+        <v>2.9</v>
       </c>
       <c r="V47">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W47">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X47">
         <v>1.06</v>
       </c>
       <c r="Y47">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z47">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AA47">
         <v>2.09</v>
@@ -8015,13 +8015,13 @@
         <v>1.67</v>
       </c>
       <c r="AC47">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD47">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE47">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="AF47">
         <v>1.84</v>
@@ -8043,7 +8043,7 @@
         <v>1.3</v>
       </c>
       <c r="AK47">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AL47">
         <v>0</v>
@@ -8296,65 +8296,65 @@
         </is>
       </c>
       <c r="N49">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="O49">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="P49">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="Q49">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R49">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S49">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T49">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U49">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="V49">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W49">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X49">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y49">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z49">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA49">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB49">
+        <v>2.15</v>
+      </c>
+      <c r="AC49">
+        <v>2.46</v>
+      </c>
+      <c r="AD49">
+        <v>1.48</v>
+      </c>
+      <c r="AE49">
+        <v>1.17</v>
+      </c>
+      <c r="AF49">
+        <v>1.57</v>
+      </c>
+      <c r="AG49">
         <v>2.2</v>
       </c>
-      <c r="AC49">
-        <v>0</v>
-      </c>
-      <c r="AD49">
-        <v>0</v>
-      </c>
-      <c r="AE49">
-        <v>0</v>
-      </c>
-      <c r="AF49">
-        <v>0</v>
-      </c>
-      <c r="AG49">
-        <v>0</v>
-      </c>
       <c r="AH49" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8366,10 +8366,10 @@
         </is>
       </c>
       <c r="AJ49">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK49">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AL49">
         <v>0</v>
@@ -8459,19 +8459,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="O50">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="P50">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="Q50">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="R50">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="S50">
         <v>1.18</v>
@@ -8480,7 +8480,7 @@
         <v>3.95</v>
       </c>
       <c r="U50">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="V50">
         <v>1.75</v>
@@ -8501,16 +8501,16 @@
         <v>1.4</v>
       </c>
       <c r="AB50">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AC50">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AD50">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AE50">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AF50">
         <v>1.45</v>
@@ -8529,10 +8529,10 @@
         </is>
       </c>
       <c r="AJ50">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AK50">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="AL50">
         <v>0</v>
@@ -10089,64 +10089,64 @@
         </is>
       </c>
       <c r="N60">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="O60">
-        <v>2.85</v>
+        <v>3.05</v>
       </c>
       <c r="P60">
-        <v>3.8</v>
+        <v>3.96</v>
       </c>
       <c r="Q60">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R60">
         <v>1.95</v>
       </c>
       <c r="S60">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="T60">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="U60">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="V60">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W60">
+        <v>1.05</v>
+      </c>
+      <c r="X60">
         <v>1.02</v>
       </c>
-      <c r="X60">
-        <v>1.06</v>
-      </c>
       <c r="Y60">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="Z60">
-        <v>2.6</v>
+        <v>2.73</v>
       </c>
       <c r="AA60">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="AB60">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AC60">
-        <v>5.05</v>
+        <v>4.25</v>
       </c>
       <c r="AD60">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE60">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF60">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="AG60">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AH60" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>1.17</v>
       </c>
       <c r="AK60">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="AL60">
         <v>0</v>
@@ -10252,43 +10252,43 @@
         </is>
       </c>
       <c r="N61">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="O61">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P61">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="Q61">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="R61">
         <v>2.48</v>
       </c>
       <c r="S61">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="T61">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U61">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="V61">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="W61">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X61">
         <v>1.01</v>
       </c>
       <c r="Y61">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z61">
-        <v>4.65</v>
+        <v>4.6</v>
       </c>
       <c r="AA61">
         <v>1.55</v>
@@ -10300,16 +10300,16 @@
         <v>2.43</v>
       </c>
       <c r="AD61">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AE61">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AF61">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AG61">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="AH61" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>1.96</v>
       </c>
       <c r="AK61">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AL61">
         <v>0</v>
@@ -10415,19 +10415,19 @@
         </is>
       </c>
       <c r="N62">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="O62">
         <v>3.5</v>
       </c>
       <c r="P62">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="Q62">
         <v>2.5</v>
       </c>
       <c r="R62">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="S62">
         <v>1.25</v>
@@ -10445,7 +10445,7 @@
         <v>1.13</v>
       </c>
       <c r="X62">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y62">
         <v>1.14</v>
@@ -10454,25 +10454,25 @@
         <v>4.65</v>
       </c>
       <c r="AA62">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB62">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AC62">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="AD62">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AE62">
         <v>1.22</v>
       </c>
       <c r="AF62">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AG62">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AH62" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         </is>
       </c>
       <c r="AJ62">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK62">
         <v>1.67</v>
@@ -10578,22 +10578,22 @@
         </is>
       </c>
       <c r="N63">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="O63">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P63">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="Q63">
         <v>4.2</v>
       </c>
       <c r="R63">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="S63">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T63">
         <v>3.1</v>
@@ -10614,16 +10614,16 @@
         <v>1.2</v>
       </c>
       <c r="Z63">
-        <v>4.19</v>
+        <v>4.27</v>
       </c>
       <c r="AA63">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AB63">
         <v>2.11</v>
       </c>
       <c r="AC63">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="AD63">
         <v>1.39</v>
@@ -10632,10 +10632,10 @@
         <v>1.16</v>
       </c>
       <c r="AF63">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AG63">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AH63" t="inlineStr">
         <is>
@@ -10741,22 +10741,22 @@
         </is>
       </c>
       <c r="N64">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="O64">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P64">
         <v>2.36</v>
       </c>
       <c r="Q64">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="R64">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S64">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T64">
         <v>3.68</v>
@@ -10765,7 +10765,7 @@
         <v>2.01</v>
       </c>
       <c r="V64">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="W64">
         <v>1.14</v>
@@ -10783,7 +10783,7 @@
         <v>1.38</v>
       </c>
       <c r="AB64">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC64">
         <v>2.1</v>
@@ -10792,7 +10792,7 @@
         <v>1.72</v>
       </c>
       <c r="AE64">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AF64">
         <v>1.36</v>
@@ -10811,7 +10811,7 @@
         </is>
       </c>
       <c r="AJ64">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="AK64">
         <v>1.53</v>
@@ -10904,31 +10904,31 @@
         </is>
       </c>
       <c r="N65">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="O65">
         <v>3.4</v>
       </c>
       <c r="P65">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="Q65">
-        <v>2.9</v>
+        <v>3.16</v>
       </c>
       <c r="R65">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="S65">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T65">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="U65">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="V65">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W65">
         <v>1.08</v>
@@ -10946,7 +10946,7 @@
         <v>1.75</v>
       </c>
       <c r="AB65">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AC65">
         <v>2.88</v>
@@ -10977,7 +10977,7 @@
         <v>1.28</v>
       </c>
       <c r="AK65">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AL65">
         <v>0</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="N66">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="O66">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P66">
         <v>2.88</v>
@@ -11082,7 +11082,7 @@
         <v>2.5</v>
       </c>
       <c r="S66">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="T66">
         <v>3.55</v>
@@ -11091,25 +11091,25 @@
         <v>2.15</v>
       </c>
       <c r="V66">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W66">
         <v>1.13</v>
       </c>
       <c r="X66">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y66">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z66">
-        <v>5.13</v>
+        <v>5.19</v>
       </c>
       <c r="AA66">
         <v>1.5</v>
       </c>
       <c r="AB66">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="AC66">
         <v>2.3</v>
@@ -11393,7 +11393,7 @@
         </is>
       </c>
       <c r="N68">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O68">
         <v>3.5</v>
@@ -11402,40 +11402,40 @@
         <v>2.15</v>
       </c>
       <c r="Q68">
-        <v>3.09</v>
+        <v>3.15</v>
       </c>
       <c r="R68">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="S68">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T68">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U68">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="V68">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W68">
         <v>1.11</v>
       </c>
       <c r="X68">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y68">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="Z68">
-        <v>5.1</v>
+        <v>5.25</v>
       </c>
       <c r="AA68">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AB68">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="AC68">
         <v>2.3</v>
@@ -11444,13 +11444,13 @@
         <v>1.57</v>
       </c>
       <c r="AE68">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AF68">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AG68">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="AH68" t="inlineStr">
         <is>
@@ -11463,10 +11463,10 @@
         </is>
       </c>
       <c r="AJ68">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="AK68">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AL68">
         <v>0</v>
@@ -11722,16 +11722,16 @@
         <v>2.6</v>
       </c>
       <c r="O70">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="P70">
         <v>2.6</v>
       </c>
       <c r="Q70">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R70">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S70">
         <v>1.4</v>
@@ -11743,7 +11743,7 @@
         <v>2.9</v>
       </c>
       <c r="V70">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="W70">
         <v>1.07</v>
@@ -11755,28 +11755,28 @@
         <v>1.28</v>
       </c>
       <c r="Z70">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="AA70">
         <v>2.01</v>
       </c>
       <c r="AB70">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AC70">
         <v>3.8</v>
       </c>
       <c r="AD70">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE70">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF70">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG70">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH70" t="inlineStr">
         <is>
@@ -11789,10 +11789,10 @@
         </is>
       </c>
       <c r="AJ70">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AK70">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AL70">
         <v>0</v>
@@ -14132,12 +14132,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G85">
@@ -14164,64 +14164,64 @@
         </is>
       </c>
       <c r="N85">
-        <v>2.15</v>
+        <v>5.25</v>
       </c>
       <c r="O85">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="P85">
-        <v>2.9</v>
+        <v>1.48</v>
       </c>
       <c r="Q85">
-        <v>2.7</v>
+        <v>6.73</v>
       </c>
       <c r="R85">
-        <v>2.25</v>
+        <v>2.58</v>
       </c>
       <c r="S85">
         <v>1.3</v>
       </c>
       <c r="T85">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="U85">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="V85">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W85">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X85">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y85">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z85">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AA85">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AB85">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AC85">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AD85">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AE85">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF85">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AG85">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="AH85" t="inlineStr">
         <is>
@@ -14234,10 +14234,10 @@
         </is>
       </c>
       <c r="AJ85">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="AK85">
-        <v>1.58</v>
+        <v>1.09</v>
       </c>
       <c r="AL85">
         <v>0</v>
@@ -14295,12 +14295,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="G86">
@@ -14327,65 +14327,65 @@
         </is>
       </c>
       <c r="N86">
-        <v>5.25</v>
+        <v>2.5</v>
       </c>
       <c r="O86">
-        <v>4.1</v>
+        <v>3.2</v>
       </c>
       <c r="P86">
-        <v>1.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q86">
-        <v>6.73</v>
+        <v>3.2</v>
       </c>
       <c r="R86">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="S86">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T86">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="U86">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V86">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W86">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X86">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y86">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z86">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA86">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AB86">
+        <v>2.1</v>
+      </c>
+      <c r="AC86">
+        <v>2.8</v>
+      </c>
+      <c r="AD86">
+        <v>1.41</v>
+      </c>
+      <c r="AE86">
+        <v>1.1</v>
+      </c>
+      <c r="AF86">
+        <v>1.56</v>
+      </c>
+      <c r="AG86">
         <v>2.15</v>
       </c>
-      <c r="AC86">
-        <v>2.7</v>
-      </c>
-      <c r="AD86">
-        <v>1.44</v>
-      </c>
-      <c r="AE86">
-        <v>1.19</v>
-      </c>
-      <c r="AF86">
-        <v>1.75</v>
-      </c>
-      <c r="AG86">
-        <v>1.97</v>
-      </c>
       <c r="AH86" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14397,10 +14397,10 @@
         </is>
       </c>
       <c r="AJ86">
-        <v>2.5</v>
+        <v>1.43</v>
       </c>
       <c r="AK86">
-        <v>1.09</v>
+        <v>1.39</v>
       </c>
       <c r="AL86">
         <v>0</v>
@@ -14458,12 +14458,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G87">
@@ -14490,31 +14490,31 @@
         </is>
       </c>
       <c r="N87">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="O87">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P87">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="Q87">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="R87">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S87">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T87">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="U87">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V87">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W87">
         <v>1.06</v>
@@ -14523,32 +14523,32 @@
         <v>1.03</v>
       </c>
       <c r="Y87">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z87">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA87">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AB87">
+        <v>1.93</v>
+      </c>
+      <c r="AC87">
+        <v>3.1</v>
+      </c>
+      <c r="AD87">
+        <v>1.36</v>
+      </c>
+      <c r="AE87">
+        <v>1.13</v>
+      </c>
+      <c r="AF87">
+        <v>1.62</v>
+      </c>
+      <c r="AG87">
         <v>2.1</v>
       </c>
-      <c r="AC87">
-        <v>2.8</v>
-      </c>
-      <c r="AD87">
-        <v>1.41</v>
-      </c>
-      <c r="AE87">
-        <v>1.1</v>
-      </c>
-      <c r="AF87">
-        <v>1.56</v>
-      </c>
-      <c r="AG87">
-        <v>2.15</v>
-      </c>
       <c r="AH87" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14560,10 +14560,10 @@
         </is>
       </c>
       <c r="AJ87">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AK87">
-        <v>1.39</v>
+        <v>1.58</v>
       </c>
       <c r="AL87">
         <v>0</v>
@@ -14653,13 +14653,13 @@
         </is>
       </c>
       <c r="N88">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="O88">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="P88">
-        <v>4.04</v>
+        <v>4.1</v>
       </c>
       <c r="Q88">
         <v>0</v>
@@ -14825,10 +14825,10 @@
         <v>2.11</v>
       </c>
       <c r="Q89">
-        <v>4.28</v>
+        <v>4</v>
       </c>
       <c r="R89">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="S89">
         <v>1.4</v>
@@ -14846,28 +14846,28 @@
         <v>1.04</v>
       </c>
       <c r="X89">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y89">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="Z89">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AA89">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AB89">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC89">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AD89">
         <v>1.19</v>
       </c>
       <c r="AE89">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF89">
         <v>1.84</v>
@@ -14889,7 +14889,7 @@
         <v>1.29</v>
       </c>
       <c r="AK89">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AL89">
         <v>0</v>
@@ -15110,12 +15110,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="G91">
@@ -15138,84 +15138,84 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N91">
-        <v>1.75</v>
+        <v>2.89</v>
       </c>
       <c r="O91">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P91">
-        <v>4</v>
+        <v>2.2</v>
       </c>
       <c r="Q91">
-        <v>2.45</v>
+        <v>3.4</v>
       </c>
       <c r="R91">
+        <v>2.15</v>
+      </c>
+      <c r="S91">
+        <v>1.33</v>
+      </c>
+      <c r="T91">
+        <v>3.04</v>
+      </c>
+      <c r="U91">
+        <v>2.5</v>
+      </c>
+      <c r="V91">
+        <v>1.47</v>
+      </c>
+      <c r="W91">
+        <v>1.11</v>
+      </c>
+      <c r="X91">
+        <v>1.04</v>
+      </c>
+      <c r="Y91">
+        <v>1.18</v>
+      </c>
+      <c r="Z91">
+        <v>3.9</v>
+      </c>
+      <c r="AA91">
+        <v>1.72</v>
+      </c>
+      <c r="AB91">
         <v>2.1</v>
       </c>
-      <c r="S91">
-        <v>1.34</v>
-      </c>
-      <c r="T91">
-        <v>2.77</v>
-      </c>
-      <c r="U91">
-        <v>2.77</v>
-      </c>
-      <c r="V91">
-        <v>1.43</v>
-      </c>
-      <c r="W91">
-        <v>1.04</v>
-      </c>
-      <c r="X91">
-        <v>1</v>
-      </c>
-      <c r="Y91">
-        <v>1.25</v>
-      </c>
-      <c r="Z91">
-        <v>3.5</v>
-      </c>
-      <c r="AA91">
-        <v>1.85</v>
-      </c>
-      <c r="AB91">
-        <v>1.89</v>
-      </c>
       <c r="AC91">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="AD91">
+        <v>1.44</v>
+      </c>
+      <c r="AE91">
+        <v>1.17</v>
+      </c>
+      <c r="AF91">
+        <v>1.53</v>
+      </c>
+      <c r="AG91">
+        <v>2.3</v>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ91">
+        <v>1.54</v>
+      </c>
+      <c r="AK91">
         <v>1.36</v>
-      </c>
-      <c r="AE91">
-        <v>1.08</v>
-      </c>
-      <c r="AF91">
-        <v>1.79</v>
-      </c>
-      <c r="AG91">
-        <v>1.75</v>
-      </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ91">
-        <v>1.18</v>
-      </c>
-      <c r="AK91">
-        <v>1.91</v>
       </c>
       <c r="AL91">
         <v>0</v>
@@ -15273,12 +15273,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G92">
@@ -15301,84 +15301,84 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N92">
-        <v>2.89</v>
+        <v>1.75</v>
       </c>
       <c r="O92">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P92">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="Q92">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="R92">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S92">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="T92">
-        <v>3.04</v>
+        <v>2.77</v>
       </c>
       <c r="U92">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="V92">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W92">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X92">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y92">
+        <v>1.25</v>
+      </c>
+      <c r="Z92">
+        <v>3.5</v>
+      </c>
+      <c r="AA92">
+        <v>1.85</v>
+      </c>
+      <c r="AB92">
+        <v>1.89</v>
+      </c>
+      <c r="AC92">
+        <v>3.08</v>
+      </c>
+      <c r="AD92">
+        <v>1.36</v>
+      </c>
+      <c r="AE92">
+        <v>1.08</v>
+      </c>
+      <c r="AF92">
+        <v>1.79</v>
+      </c>
+      <c r="AG92">
+        <v>1.75</v>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ92">
         <v>1.18</v>
       </c>
-      <c r="Z92">
-        <v>3.9</v>
-      </c>
-      <c r="AA92">
-        <v>1.72</v>
-      </c>
-      <c r="AB92">
-        <v>2.1</v>
-      </c>
-      <c r="AC92">
-        <v>2.63</v>
-      </c>
-      <c r="AD92">
-        <v>1.44</v>
-      </c>
-      <c r="AE92">
-        <v>1.17</v>
-      </c>
-      <c r="AF92">
-        <v>1.53</v>
-      </c>
-      <c r="AG92">
-        <v>2.3</v>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ92">
-        <v>1.54</v>
-      </c>
       <c r="AK92">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AL92">
         <v>0</v>
@@ -15794,64 +15794,64 @@
         </is>
       </c>
       <c r="N95">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="O95">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P95">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="Q95">
+        <v>2.75</v>
+      </c>
+      <c r="R95">
+        <v>2.03</v>
+      </c>
+      <c r="S95">
+        <v>1.44</v>
+      </c>
+      <c r="T95">
+        <v>2.53</v>
+      </c>
+      <c r="U95">
         <v>2.88</v>
       </c>
-      <c r="R95">
-        <v>2.02</v>
-      </c>
-      <c r="S95">
-        <v>1.45</v>
-      </c>
-      <c r="T95">
-        <v>2.49</v>
-      </c>
-      <c r="U95">
-        <v>2.92</v>
-      </c>
       <c r="V95">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W95">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X95">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y95">
         <v>1.31</v>
       </c>
       <c r="Z95">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA95">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AB95">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AC95">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AD95">
         <v>1.22</v>
       </c>
       <c r="AE95">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF95">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG95">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH95" t="inlineStr">
         <is>
@@ -15864,10 +15864,10 @@
         </is>
       </c>
       <c r="AJ95">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK95">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AL95">
         <v>0</v>
@@ -15960,25 +15960,25 @@
         <v>1.35</v>
       </c>
       <c r="O96">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="P96">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Q96">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="R96">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="S96">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T96">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U96">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="V96">
         <v>1.36</v>
@@ -15990,25 +15990,25 @@
         <v>1.01</v>
       </c>
       <c r="Y96">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z96">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="AA96">
-        <v>1.87</v>
+        <v>2.05</v>
       </c>
       <c r="AB96">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AC96">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="AD96">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AE96">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF96">
         <v>2.24</v>
@@ -16027,7 +16027,7 @@
         </is>
       </c>
       <c r="AJ96">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="AK96">
         <v>3</v>
@@ -16120,13 +16120,13 @@
         </is>
       </c>
       <c r="N97">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="O97">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="P97">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="Q97">
         <v>2.9</v>
@@ -16135,7 +16135,7 @@
         <v>2.1</v>
       </c>
       <c r="S97">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T97">
         <v>2.9</v>
@@ -16150,28 +16150,28 @@
         <v>1.06</v>
       </c>
       <c r="X97">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y97">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z97">
-        <v>3.14</v>
+        <v>3.28</v>
       </c>
       <c r="AA97">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AB97">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC97">
-        <v>3.1</v>
+        <v>2.97</v>
       </c>
       <c r="AD97">
         <v>1.3</v>
       </c>
       <c r="AE97">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF97">
         <v>1.65</v>
@@ -16190,10 +16190,10 @@
         </is>
       </c>
       <c r="AJ97">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK97">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL97">
         <v>0</v>
@@ -16286,7 +16286,7 @@
         <v>2.7</v>
       </c>
       <c r="O98">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="P98">
         <v>2.7</v>
@@ -16295,7 +16295,7 @@
         <v>3.6</v>
       </c>
       <c r="R98">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="S98">
         <v>1.5</v>
@@ -16313,7 +16313,7 @@
         <v>1.04</v>
       </c>
       <c r="X98">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y98">
         <v>1.47</v>
@@ -16322,10 +16322,10 @@
         <v>2.63</v>
       </c>
       <c r="AA98">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="AB98">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AC98">
         <v>5</v>
@@ -16334,7 +16334,7 @@
         <v>1.17</v>
       </c>
       <c r="AE98">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF98">
         <v>2.01</v>
@@ -16353,10 +16353,10 @@
         </is>
       </c>
       <c r="AJ98">
+        <v>1.3</v>
+      </c>
+      <c r="AK98">
         <v>1.35</v>
-      </c>
-      <c r="AK98">
-        <v>1.36</v>
       </c>
       <c r="AL98">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         </is>
       </c>
       <c r="N99">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O99">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="P99">
         <v>8.5</v>
@@ -16458,25 +16458,25 @@
         <v>1.77</v>
       </c>
       <c r="R99">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S99">
         <v>1.33</v>
       </c>
       <c r="T99">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U99">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="V99">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W99">
         <v>1.1</v>
       </c>
       <c r="X99">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y99">
         <v>1.25</v>
@@ -16485,25 +16485,25 @@
         <v>3.8</v>
       </c>
       <c r="AA99">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AB99">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AC99">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AD99">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AE99">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF99">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AG99">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AH99" t="inlineStr">
         <is>

--- a/jogos_2026-08-21.xlsx
+++ b/jogos_2026-08-21.xlsx
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.7</v>
+        <v>3.79</v>
       </c>
       <c r="O2">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="P2">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="Q2">
-        <v>4.2</v>
+        <v>4.43</v>
       </c>
       <c r="R2">
         <v>2.25</v>
@@ -653,10 +653,10 @@
         <v>1.29</v>
       </c>
       <c r="T2">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="U2">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="V2">
         <v>1.49</v>
@@ -665,7 +665,7 @@
         <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
         <v>1.16</v>
@@ -680,19 +680,19 @@
         <v>2.06</v>
       </c>
       <c r="AC2">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AD2">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="AE2">
         <v>1.12</v>
       </c>
       <c r="AF2">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="AG2">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="O3">
-        <v>3.7</v>
+        <v>3.96</v>
       </c>
       <c r="P3">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="Q3">
         <v>2.12</v>
@@ -822,13 +822,13 @@
         <v>2.5</v>
       </c>
       <c r="V3">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W3">
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y3">
         <v>1.25</v>
@@ -840,22 +840,22 @@
         <v>1.78</v>
       </c>
       <c r="AB3">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AC3">
         <v>2.8</v>
       </c>
       <c r="AD3">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE3">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF3">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AG3">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,19 +961,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="O4">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="P4">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>1.91</v>
       </c>
       <c r="R4">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="S4">
         <v>1.35</v>
@@ -982,10 +982,10 @@
         <v>3</v>
       </c>
       <c r="U4">
-        <v>2.69</v>
+        <v>2.77</v>
       </c>
       <c r="V4">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W4">
         <v>1.07</v>
@@ -1006,7 +1006,7 @@
         <v>1.9</v>
       </c>
       <c r="AC4">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="AD4">
         <v>1.33</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>4.26</v>
+        <v>4.6</v>
       </c>
       <c r="O5">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="P5">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q5">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="R5">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="U5">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z5">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="AA5">
         <v>1.8</v>
       </c>
       <c r="AB5">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AC5">
         <v>2.97</v>
       </c>
       <c r="AD5">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AG5">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1450,49 +1450,49 @@
         </is>
       </c>
       <c r="N7">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="O7">
-        <v>3.4</v>
+        <v>3.48</v>
       </c>
       <c r="P7">
-        <v>4.65</v>
+        <v>4.68</v>
       </c>
       <c r="Q7">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R7">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="S7">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T7">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U7">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="V7">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W7">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X7">
         <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z7">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="AA7">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB7">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC7">
         <v>3.5</v>
@@ -1507,7 +1507,7 @@
         <v>1.85</v>
       </c>
       <c r="AG7">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AK7">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -2102,49 +2102,49 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="O11">
-        <v>5.25</v>
+        <v>5.1</v>
       </c>
       <c r="P11">
-        <v>10</v>
+        <v>7.3</v>
       </c>
       <c r="Q11">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="R11">
+        <v>2.65</v>
+      </c>
+      <c r="S11">
+        <v>1.28</v>
+      </c>
+      <c r="T11">
+        <v>3.14</v>
+      </c>
+      <c r="U11">
         <v>2.39</v>
       </c>
-      <c r="S11">
-        <v>1.25</v>
-      </c>
-      <c r="T11">
-        <v>3.25</v>
-      </c>
-      <c r="U11">
-        <v>2.44</v>
-      </c>
       <c r="V11">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="W11">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
         <v>4.34</v>
       </c>
       <c r="AA11">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB11">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AC11">
         <v>2.61</v>
@@ -2153,7 +2153,7 @@
         <v>1.45</v>
       </c>
       <c r="AE11">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
         <v>2</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK11">
         <v>3.6</v>
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="O12">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="P12">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="Q12">
-        <v>4.28</v>
+        <v>3.3</v>
       </c>
       <c r="R12">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="S12">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.7</v>
+        <v>3.14</v>
       </c>
       <c r="U12">
         <v>2.25</v>
       </c>
       <c r="V12">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W12">
         <v>1.11</v>
@@ -2301,28 +2301,28 @@
         <v>1.13</v>
       </c>
       <c r="Z12">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AA12">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AB12">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="AC12">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="AD12">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AE12">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF12">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AG12">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.75</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="O13">
         <v>3.75</v>
@@ -2437,10 +2437,10 @@
         <v>4.2</v>
       </c>
       <c r="Q13">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>2.41</v>
       </c>
       <c r="S13">
         <v>1.25</v>
@@ -2455,53 +2455,53 @@
         <v>1.57</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X13">
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Z13">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA13">
         <v>1.6</v>
       </c>
       <c r="AB13">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AC13">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="AD13">
         <v>1.47</v>
       </c>
       <c r="AE13">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF13">
         <v>1.6</v>
       </c>
       <c r="AG13">
+        <v>1.88</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.17</v>
+      </c>
+      <c r="AK13">
         <v>2.15</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.16</v>
-      </c>
-      <c r="AK13">
-        <v>2.13</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,55 +2591,55 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="O14">
         <v>3.75</v>
       </c>
       <c r="P14">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="Q14">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="R14">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="S14">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.28</v>
+        <v>3.13</v>
       </c>
       <c r="U14">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="V14">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="W14">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="X14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="Z14">
-        <v>4.33</v>
+        <v>3.9</v>
       </c>
       <c r="AA14">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AB14">
-        <v>2.2</v>
+        <v>1.96</v>
       </c>
       <c r="AC14">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="AD14">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
         <v>1.15</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
         <v>2.07</v>
@@ -2763,10 +2763,10 @@
         <v>2.8</v>
       </c>
       <c r="Q15">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="R15">
-        <v>2.02</v>
+        <v>2.21</v>
       </c>
       <c r="S15">
         <v>1.35</v>
@@ -2799,16 +2799,16 @@
         <v>1.85</v>
       </c>
       <c r="AC15">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="AD15">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AE15">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AG15">
         <v>2.05</v>
@@ -2917,16 +2917,16 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="O16">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="P16">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q16">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="R16">
         <v>2.45</v>
@@ -2938,10 +2938,10 @@
         <v>4</v>
       </c>
       <c r="U16">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="V16">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="W16">
         <v>1.2</v>
@@ -2950,10 +2950,10 @@
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>6.4</v>
+        <v>6.69</v>
       </c>
       <c r="AA16">
         <v>1.4</v>
@@ -2962,19 +2962,19 @@
         <v>2.75</v>
       </c>
       <c r="AC16">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AD16">
         <v>1.73</v>
       </c>
       <c r="AE16">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF16">
         <v>1.4</v>
       </c>
       <c r="AG16">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3080,34 +3080,34 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="O17">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P17">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="Q17">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
         <v>1.36</v>
       </c>
       <c r="T17">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="U17">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
         <v>1.03</v>
@@ -3116,28 +3116,28 @@
         <v>1.3</v>
       </c>
       <c r="Z17">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AA17">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AB17">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC17">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AD17">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
         <v>1.05</v>
       </c>
       <c r="AF17">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG17">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3243,34 +3243,34 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q18">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S18">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T18">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="U18">
-        <v>2.86</v>
+        <v>2.77</v>
       </c>
       <c r="V18">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="W18">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X18">
         <v>1.02</v>
@@ -3282,25 +3282,25 @@
         <v>3.14</v>
       </c>
       <c r="AA18">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AB18">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AC18">
         <v>3.6</v>
       </c>
       <c r="AD18">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AE18">
         <v>1.06</v>
       </c>
       <c r="AF18">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AG18">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
         <v>1.47</v>
@@ -3415,10 +3415,10 @@
         <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="R19">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="S19">
         <v>1.31</v>
@@ -3433,7 +3433,7 @@
         <v>1.45</v>
       </c>
       <c r="W19">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X19">
         <v>1.01</v>
@@ -3445,7 +3445,7 @@
         <v>3.68</v>
       </c>
       <c r="AA19">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AB19">
         <v>1.99</v>
@@ -3460,7 +3460,7 @@
         <v>1.11</v>
       </c>
       <c r="AF19">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG19">
         <v>2.15</v>
@@ -3479,7 +3479,7 @@
         <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="O21">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>41</v>
+        <v>14.61</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="S21">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="T21">
-        <v>4.75</v>
+        <v>5.1</v>
       </c>
       <c r="U21">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V21">
         <v>1.95</v>
       </c>
       <c r="W21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="X21">
         <v>0</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AF21">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AG21">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,46 +3895,46 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="O22">
         <v>3.35</v>
       </c>
       <c r="P22">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q22">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="R22">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="S22">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T22">
         <v>2.92</v>
       </c>
       <c r="U22">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="V22">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W22">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y22">
         <v>1.25</v>
       </c>
       <c r="Z22">
-        <v>3.35</v>
+        <v>3.58</v>
       </c>
       <c r="AA22">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB22">
         <v>1.82</v>
@@ -3949,7 +3949,7 @@
         <v>1.08</v>
       </c>
       <c r="AF22">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AG22">
         <v>2.06</v>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.23</v>
+        <v>1.57</v>
       </c>
       <c r="AK22">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4061,7 +4061,7 @@
         <v>1.15</v>
       </c>
       <c r="O23">
-        <v>7.65</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>11</v>
@@ -4070,13 +4070,13 @@
         <v>1.44</v>
       </c>
       <c r="R23">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="S23">
         <v>1.17</v>
       </c>
       <c r="T23">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="U23">
         <v>1.83</v>
@@ -4085,31 +4085,31 @@
         <v>1.83</v>
       </c>
       <c r="W23">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X23">
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z23">
-        <v>6.55</v>
+        <v>6.25</v>
       </c>
       <c r="AA23">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB23">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AC23">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AD23">
         <v>1.85</v>
       </c>
       <c r="AE23">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AF23">
         <v>1.78</v>
@@ -4131,7 +4131,7 @@
         <v>1.03</v>
       </c>
       <c r="AK23">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Opava</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Třinec</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,80 +4547,80 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="O26">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="P26">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="Q26">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="R26">
         <v>2.3</v>
       </c>
       <c r="S26">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="T26">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U26">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="V26">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X26">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y26">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z26">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AA26">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AB26">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="AC26">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AD26">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AE26">
+        <v>1.14</v>
+      </c>
+      <c r="AF26">
+        <v>1.7</v>
+      </c>
+      <c r="AG26">
+        <v>2.01</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ26">
         <v>1.18</v>
       </c>
-      <c r="AF26">
-        <v>1.52</v>
-      </c>
-      <c r="AG26">
-        <v>2.25</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ26">
-        <v>1.22</v>
-      </c>
       <c r="AK26">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Opava</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Třinec</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="G28">
@@ -4873,80 +4873,80 @@
         </is>
       </c>
       <c r="N28">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="O28">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="P28">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="Q28">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="R28">
         <v>2.3</v>
       </c>
       <c r="S28">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="T28">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U28">
-        <v>2.53</v>
+        <v>2.3</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W28">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X28">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y28">
+        <v>1.19</v>
+      </c>
+      <c r="Z28">
+        <v>3.75</v>
+      </c>
+      <c r="AA28">
+        <v>1.66</v>
+      </c>
+      <c r="AB28">
+        <v>2.15</v>
+      </c>
+      <c r="AC28">
+        <v>2.6</v>
+      </c>
+      <c r="AD28">
+        <v>1.42</v>
+      </c>
+      <c r="AE28">
+        <v>1.18</v>
+      </c>
+      <c r="AF28">
+        <v>1.52</v>
+      </c>
+      <c r="AG28">
+        <v>2.25</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ28">
         <v>1.22</v>
       </c>
-      <c r="Z28">
-        <v>4.2</v>
-      </c>
-      <c r="AA28">
-        <v>1.74</v>
-      </c>
-      <c r="AB28">
-        <v>2.07</v>
-      </c>
-      <c r="AC28">
-        <v>2.88</v>
-      </c>
-      <c r="AD28">
-        <v>1.4</v>
-      </c>
-      <c r="AE28">
-        <v>1.14</v>
-      </c>
-      <c r="AF28">
-        <v>1.7</v>
-      </c>
-      <c r="AG28">
-        <v>2.01</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>1.18</v>
-      </c>
       <c r="AK28">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AL28">
         <v>0</v>
@@ -5365,52 +5365,52 @@
         <v>1.85</v>
       </c>
       <c r="O31">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="P31">
-        <v>3.28</v>
+        <v>3.75</v>
       </c>
       <c r="Q31">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="R31">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="S31">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T31">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="U31">
         <v>3.1</v>
       </c>
       <c r="V31">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W31">
         <v>1.03</v>
       </c>
       <c r="X31">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y31">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="Z31">
         <v>2.74</v>
       </c>
       <c r="AA31">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="AB31">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="AC31">
-        <v>3.72</v>
+        <v>3.99</v>
       </c>
       <c r="AD31">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE31">
         <v>1.03</v>
@@ -5432,10 +5432,10 @@
         </is>
       </c>
       <c r="AJ31">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK31">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="AL31">
         <v>0</v>
@@ -5528,7 +5528,7 @@
         <v>1.65</v>
       </c>
       <c r="O32">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P32">
         <v>4.4</v>
@@ -5564,10 +5564,10 @@
         <v>0</v>
       </c>
       <c r="AA32">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AB32">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AC32">
         <v>0</v>
@@ -5691,10 +5691,10 @@
         <v>3.2</v>
       </c>
       <c r="O33">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="P33">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="Q33">
         <v>3.6</v>
@@ -5703,40 +5703,40 @@
         <v>2.2</v>
       </c>
       <c r="S33">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="T33">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U33">
-        <v>2.69</v>
+        <v>2.62</v>
       </c>
       <c r="V33">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X33">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y33">
         <v>1.25</v>
       </c>
       <c r="Z33">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA33">
+        <v>1.85</v>
+      </c>
+      <c r="AB33">
         <v>1.87</v>
-      </c>
-      <c r="AB33">
-        <v>1.9</v>
       </c>
       <c r="AC33">
         <v>3.25</v>
       </c>
       <c r="AD33">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE33">
         <v>1.1</v>
@@ -5745,7 +5745,7 @@
         <v>1.73</v>
       </c>
       <c r="AG33">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="AJ33">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AK33">
         <v>1.3</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="O34">
-        <v>4.05</v>
+        <v>3.8</v>
       </c>
       <c r="P34">
-        <v>3.76</v>
+        <v>3.27</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB34">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="AC34">
         <v>0</v>
@@ -6014,28 +6014,28 @@
         </is>
       </c>
       <c r="N35">
-        <v>1.85</v>
+        <v>1.93</v>
       </c>
       <c r="O35">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P35">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q35">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="R35">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="S35">
         <v>1.3</v>
       </c>
       <c r="T35">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="U35">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="V35">
         <v>1.48</v>
@@ -6044,34 +6044,34 @@
         <v>1.11</v>
       </c>
       <c r="X35">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y35">
         <v>1.18</v>
       </c>
       <c r="Z35">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AA35">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB35">
         <v>2.1</v>
       </c>
       <c r="AC35">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="AD35">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE35">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF35">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG35">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="AH35" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="AJ35">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="AK35">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="AL35">
         <v>0</v>
@@ -6829,16 +6829,16 @@
         </is>
       </c>
       <c r="N40">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="O40">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P40">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="Q40">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="R40">
         <v>2.15</v>
@@ -6850,13 +6850,13 @@
         <v>2.85</v>
       </c>
       <c r="U40">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="V40">
         <v>1.4</v>
       </c>
       <c r="W40">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X40">
         <v>1.05</v>
@@ -6868,22 +6868,22 @@
         <v>3.4</v>
       </c>
       <c r="AA40">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AB40">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AC40">
-        <v>3.08</v>
+        <v>3.14</v>
       </c>
       <c r="AD40">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AE40">
         <v>1.1</v>
       </c>
       <c r="AF40">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="AG40">
         <v>1.95</v>
@@ -6899,10 +6899,10 @@
         </is>
       </c>
       <c r="AJ40">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AK40">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AL40">
         <v>0</v>
@@ -6992,34 +6992,34 @@
         </is>
       </c>
       <c r="N41">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="O41">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="P41">
-        <v>3.72</v>
+        <v>6</v>
       </c>
       <c r="Q41">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="R41">
+        <v>2.3</v>
+      </c>
+      <c r="S41">
+        <v>1.29</v>
+      </c>
+      <c r="T41">
+        <v>3.3</v>
+      </c>
+      <c r="U41">
         <v>2.38</v>
       </c>
-      <c r="S41">
-        <v>1.25</v>
-      </c>
-      <c r="T41">
-        <v>3.6</v>
-      </c>
-      <c r="U41">
-        <v>2.25</v>
-      </c>
       <c r="V41">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W41">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X41">
         <v>1.01</v>
@@ -7028,28 +7028,28 @@
         <v>1.14</v>
       </c>
       <c r="Z41">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AA41">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AB41">
-        <v>2.35</v>
+        <v>2.21</v>
       </c>
       <c r="AC41">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AD41">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE41">
         <v>1.16</v>
       </c>
       <c r="AF41">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AG41">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AH41" t="inlineStr">
         <is>
@@ -7062,10 +7062,10 @@
         </is>
       </c>
       <c r="AJ41">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AK41">
-        <v>2.21</v>
+        <v>3</v>
       </c>
       <c r="AL41">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         </is>
       </c>
       <c r="N42">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="O42">
         <v>3.7</v>
@@ -7167,7 +7167,7 @@
         <v>2.3</v>
       </c>
       <c r="R42">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S42">
         <v>1.21</v>
@@ -7176,7 +7176,7 @@
         <v>3.75</v>
       </c>
       <c r="U42">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V42">
         <v>1.73</v>
@@ -7194,13 +7194,13 @@
         <v>6.5</v>
       </c>
       <c r="AA42">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AB42">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AC42">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AD42">
         <v>1.8</v>
@@ -7209,7 +7209,7 @@
         <v>1.3</v>
       </c>
       <c r="AF42">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AG42">
         <v>2.8</v>
@@ -7228,7 +7228,7 @@
         <v>1.3</v>
       </c>
       <c r="AK42">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AL42">
         <v>0</v>
@@ -7318,16 +7318,16 @@
         </is>
       </c>
       <c r="N43">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="O43">
         <v>3.28</v>
       </c>
       <c r="P43">
-        <v>3.51</v>
+        <v>3.42</v>
       </c>
       <c r="Q43">
-        <v>2.62</v>
+        <v>2.45</v>
       </c>
       <c r="R43">
         <v>2.2</v>
@@ -7342,7 +7342,7 @@
         <v>2.85</v>
       </c>
       <c r="V43">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="W43">
         <v>1.1</v>
@@ -7357,7 +7357,7 @@
         <v>3.3</v>
       </c>
       <c r="AA43">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AB43">
         <v>1.88</v>
@@ -7366,7 +7366,7 @@
         <v>3.4</v>
       </c>
       <c r="AD43">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE43">
         <v>1.05</v>
@@ -7481,25 +7481,25 @@
         </is>
       </c>
       <c r="N44">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="O44">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P44">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="Q44">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="R44">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="S44">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="T44">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="U44">
         <v>2.4</v>
@@ -7508,13 +7508,13 @@
         <v>1.48</v>
       </c>
       <c r="W44">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X44">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y44">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z44">
         <v>3.8</v>
@@ -7523,19 +7523,19 @@
         <v>1.7</v>
       </c>
       <c r="AB44">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="AC44">
         <v>2.75</v>
       </c>
       <c r="AD44">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AE44">
         <v>1.13</v>
       </c>
       <c r="AF44">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AG44">
         <v>2.15</v>
@@ -7554,7 +7554,7 @@
         <v>1.22</v>
       </c>
       <c r="AK44">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AL44">
         <v>0</v>
@@ -8136,16 +8136,16 @@
         <v>1.2</v>
       </c>
       <c r="O48">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="P48">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q48">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="R48">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S48">
         <v>1.38</v>
@@ -8160,13 +8160,13 @@
         <v>1.38</v>
       </c>
       <c r="W48">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X48">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y48">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z48">
         <v>3.2</v>
@@ -8181,16 +8181,16 @@
         <v>3.45</v>
       </c>
       <c r="AD48">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AE48">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF48">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AG48">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
@@ -8628,7 +8628,7 @@
         <v>3</v>
       </c>
       <c r="P51">
-        <v>2.01</v>
+        <v>2.07</v>
       </c>
       <c r="Q51">
         <v>4.33</v>
@@ -8637,28 +8637,28 @@
         <v>1.91</v>
       </c>
       <c r="S51">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="T51">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="U51">
         <v>3.75</v>
       </c>
       <c r="V51">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W51">
         <v>1.03</v>
       </c>
       <c r="X51">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y51">
         <v>1.53</v>
       </c>
       <c r="Z51">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AA51">
         <v>2.5</v>
@@ -8670,16 +8670,16 @@
         <v>5</v>
       </c>
       <c r="AD51">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE51">
         <v>1.04</v>
       </c>
       <c r="AF51">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
       <c r="AG51">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AH51" t="inlineStr">
         <is>
@@ -8785,7 +8785,7 @@
         </is>
       </c>
       <c r="N52">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O52">
         <v>3</v>
@@ -8800,19 +8800,19 @@
         <v>1.94</v>
       </c>
       <c r="S52">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T52">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="U52">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="V52">
         <v>1.34</v>
       </c>
       <c r="W52">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X52">
         <v>1.03</v>
@@ -8824,10 +8824,10 @@
         <v>2.88</v>
       </c>
       <c r="AA52">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="AB52">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AC52">
         <v>3.62</v>
@@ -8836,10 +8836,10 @@
         <v>1.2</v>
       </c>
       <c r="AE52">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF52">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AG52">
         <v>1.88</v>
@@ -8948,25 +8948,25 @@
         </is>
       </c>
       <c r="N53">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O53">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P53">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="Q53">
-        <v>3.31</v>
+        <v>3.37</v>
       </c>
       <c r="R53">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="S53">
         <v>1.4</v>
       </c>
       <c r="T53">
-        <v>2.75</v>
+        <v>2.58</v>
       </c>
       <c r="U53">
         <v>3</v>
@@ -8978,7 +8978,7 @@
         <v>1.07</v>
       </c>
       <c r="X53">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y53">
         <v>1.35</v>
@@ -8990,7 +8990,7 @@
         <v>2.05</v>
       </c>
       <c r="AB53">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AC53">
         <v>3.3</v>
@@ -9018,10 +9018,10 @@
         </is>
       </c>
       <c r="AJ53">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AK53">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL53">
         <v>0</v>
@@ -9111,13 +9111,13 @@
         </is>
       </c>
       <c r="N54">
-        <v>2.86</v>
+        <v>2.47</v>
       </c>
       <c r="O54">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P54">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q54">
         <v>3.35</v>
@@ -9126,43 +9126,43 @@
         <v>2.05</v>
       </c>
       <c r="S54">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="T54">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="U54">
-        <v>2.94</v>
+        <v>3.02</v>
       </c>
       <c r="V54">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W54">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X54">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y54">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z54">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="AA54">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="AB54">
         <v>1.67</v>
       </c>
       <c r="AC54">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AD54">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE54">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF54">
         <v>1.85</v>
@@ -9274,55 +9274,55 @@
         </is>
       </c>
       <c r="N55">
+        <v>2.15</v>
+      </c>
+      <c r="O55">
+        <v>3.2</v>
+      </c>
+      <c r="P55">
+        <v>3.15</v>
+      </c>
+      <c r="Q55">
+        <v>2.75</v>
+      </c>
+      <c r="R55">
         <v>2.1</v>
       </c>
-      <c r="O55">
-        <v>3.25</v>
-      </c>
-      <c r="P55">
-        <v>3.05</v>
-      </c>
-      <c r="Q55">
-        <v>2.5</v>
-      </c>
-      <c r="R55">
-        <v>2.2</v>
-      </c>
       <c r="S55">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="T55">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="U55">
         <v>2.55</v>
       </c>
       <c r="V55">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="W55">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X55">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y55">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z55">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="AA55">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="AB55">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC55">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AD55">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AE55">
         <v>1.12</v>
@@ -9344,10 +9344,10 @@
         </is>
       </c>
       <c r="AJ55">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK55">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AL55">
         <v>0</v>
@@ -9437,13 +9437,13 @@
         </is>
       </c>
       <c r="N56">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="O56">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P56">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q56">
         <v>2.9</v>
@@ -9458,7 +9458,7 @@
         <v>2.89</v>
       </c>
       <c r="U56">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="V56">
         <v>1.4</v>
@@ -9470,7 +9470,7 @@
         <v>1.04</v>
       </c>
       <c r="Y56">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z56">
         <v>3.5</v>
@@ -9482,7 +9482,7 @@
         <v>1.85</v>
       </c>
       <c r="AC56">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AD56">
         <v>1.33</v>
@@ -9491,10 +9491,10 @@
         <v>1.07</v>
       </c>
       <c r="AF56">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AG56">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AH56" t="inlineStr">
         <is>
@@ -9510,7 +9510,7 @@
         <v>1.4</v>
       </c>
       <c r="AK56">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AL56">
         <v>0</v>
@@ -9600,19 +9600,19 @@
         </is>
       </c>
       <c r="N57">
-        <v>5.4</v>
+        <v>7.35</v>
       </c>
       <c r="O57">
-        <v>4.15</v>
+        <v>4.4</v>
       </c>
       <c r="P57">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="Q57">
-        <v>5.5</v>
+        <v>4.82</v>
       </c>
       <c r="R57">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="S57">
         <v>1.29</v>
@@ -9621,43 +9621,43 @@
         <v>3.5</v>
       </c>
       <c r="U57">
-        <v>2.36</v>
+        <v>2.47</v>
       </c>
       <c r="V57">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W57">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X57">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y57">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z57">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA57">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AB57">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AC57">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="AD57">
         <v>1.44</v>
       </c>
       <c r="AE57">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF57">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AG57">
-        <v>2.04</v>
+        <v>1.81</v>
       </c>
       <c r="AH57" t="inlineStr">
         <is>
@@ -9670,10 +9670,10 @@
         </is>
       </c>
       <c r="AJ57">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AK57">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="AL57">
         <v>0</v>
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="N58">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="O58">
-        <v>3.54</v>
+        <v>3.35</v>
       </c>
       <c r="P58">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="Q58">
         <v>0</v>
@@ -9926,13 +9926,13 @@
         </is>
       </c>
       <c r="N59">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O59">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="P59">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="Q59">
         <v>2.8</v>
@@ -9947,10 +9947,10 @@
         <v>3.12</v>
       </c>
       <c r="U59">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="V59">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W59">
         <v>1.06</v>
@@ -9959,19 +9959,19 @@
         <v>1.04</v>
       </c>
       <c r="Y59">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z59">
-        <v>3.98</v>
+        <v>4.03</v>
       </c>
       <c r="AA59">
         <v>1.75</v>
       </c>
       <c r="AB59">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AC59">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="AD59">
         <v>1.39</v>
@@ -9983,7 +9983,7 @@
         <v>1.6</v>
       </c>
       <c r="AG59">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="AH59" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>1.4</v>
       </c>
       <c r="AK59">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AL59">
         <v>0</v>
@@ -11233,40 +11233,40 @@
         <v>1.5</v>
       </c>
       <c r="O67">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="P67">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Q67">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="R67">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="S67">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T67">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U67">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="V67">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W67">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X67">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y67">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="Z67">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="AA67">
         <v>1.67</v>
@@ -11278,16 +11278,16 @@
         <v>2.63</v>
       </c>
       <c r="AD67">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE67">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF67">
         <v>1.7</v>
       </c>
       <c r="AG67">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH67" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>1.16</v>
       </c>
       <c r="AK67">
-        <v>2.38</v>
+        <v>2.29</v>
       </c>
       <c r="AL67">
         <v>0</v>
@@ -11556,7 +11556,7 @@
         </is>
       </c>
       <c r="N69">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="O69">
         <v>3.7</v>
@@ -11568,13 +11568,13 @@
         <v>2.1</v>
       </c>
       <c r="R69">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="S69">
         <v>1.36</v>
       </c>
       <c r="T69">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="U69">
         <v>2.9</v>
@@ -11589,13 +11589,13 @@
         <v>1.05</v>
       </c>
       <c r="Y69">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Z69">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AA69">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB69">
         <v>1.7</v>
@@ -11607,13 +11607,13 @@
         <v>1.27</v>
       </c>
       <c r="AE69">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF69">
         <v>1.95</v>
       </c>
       <c r="AG69">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AH69" t="inlineStr">
         <is>
@@ -11626,10 +11626,10 @@
         </is>
       </c>
       <c r="AJ69">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AK69">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AL69">
         <v>0</v>
@@ -11888,22 +11888,22 @@
         <v>3.65</v>
       </c>
       <c r="P71">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="Q71">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="R71">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="S71">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T71">
         <v>3.25</v>
       </c>
       <c r="U71">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="V71">
         <v>1.43</v>
@@ -11927,16 +11927,16 @@
         <v>1.95</v>
       </c>
       <c r="AC71">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="AD71">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE71">
         <v>1.13</v>
       </c>
       <c r="AF71">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG71">
         <v>2.15</v>
@@ -11952,7 +11952,7 @@
         </is>
       </c>
       <c r="AJ71">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AK71">
         <v>1.51</v>
@@ -12045,25 +12045,25 @@
         </is>
       </c>
       <c r="N72">
-        <v>7.5</v>
+        <v>6.77</v>
       </c>
       <c r="O72">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="P72">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Q72">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="R72">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="S72">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T72">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U72">
         <v>2.56</v>
@@ -12072,10 +12072,10 @@
         <v>1.47</v>
       </c>
       <c r="W72">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X72">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y72">
         <v>1.2</v>
@@ -12208,13 +12208,13 @@
         </is>
       </c>
       <c r="N73">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="O73">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="P73">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="Q73">
         <v>3.04</v>
@@ -12223,34 +12223,34 @@
         <v>2.1</v>
       </c>
       <c r="S73">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T73">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="U73">
-        <v>2.63</v>
+        <v>2.56</v>
       </c>
       <c r="V73">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W73">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X73">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y73">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z73">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AA73">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB73">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AC73">
         <v>2.92</v>
@@ -12262,10 +12262,10 @@
         <v>1.08</v>
       </c>
       <c r="AF73">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AG73">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AH73" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>1.25</v>
       </c>
       <c r="AK73">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL73">
         <v>0</v>
@@ -12371,31 +12371,31 @@
         </is>
       </c>
       <c r="N74">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="O74">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P74">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="Q74">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R74">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S74">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="T74">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="U74">
         <v>4</v>
       </c>
       <c r="V74">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W74">
         <v>1.03</v>
@@ -12410,10 +12410,10 @@
         <v>2.3</v>
       </c>
       <c r="AA74">
-        <v>3.15</v>
+        <v>3.02</v>
       </c>
       <c r="AB74">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AC74">
         <v>6.5</v>
@@ -12428,7 +12428,7 @@
         <v>2.18</v>
       </c>
       <c r="AG74">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH74" t="inlineStr">
         <is>
@@ -12441,10 +12441,10 @@
         </is>
       </c>
       <c r="AJ74">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK74">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AL74">
         <v>0</v>
@@ -12534,40 +12534,40 @@
         </is>
       </c>
       <c r="N75">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="O75">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P75">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="Q75">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="R75">
         <v>2.2</v>
       </c>
       <c r="S75">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T75">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U75">
-        <v>2.45</v>
+        <v>2.64</v>
       </c>
       <c r="V75">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W75">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X75">
         <v>1.03</v>
       </c>
       <c r="Y75">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z75">
         <v>4.2</v>
@@ -12576,7 +12576,7 @@
         <v>1.75</v>
       </c>
       <c r="AB75">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AC75">
         <v>2.88</v>
@@ -12591,7 +12591,7 @@
         <v>1.57</v>
       </c>
       <c r="AG75">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AH75" t="inlineStr">
         <is>
@@ -12697,25 +12697,25 @@
         </is>
       </c>
       <c r="N76">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="O76">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P76">
         <v>3.2</v>
       </c>
       <c r="Q76">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="R76">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S76">
         <v>1.29</v>
       </c>
       <c r="T76">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U76">
         <v>2.45</v>
@@ -12727,28 +12727,28 @@
         <v>1.11</v>
       </c>
       <c r="X76">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y76">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z76">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA76">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AB76">
         <v>2</v>
       </c>
       <c r="AC76">
-        <v>2.74</v>
+        <v>3.02</v>
       </c>
       <c r="AD76">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AE76">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF76">
         <v>1.64</v>
@@ -12770,7 +12770,7 @@
         <v>1.25</v>
       </c>
       <c r="AK76">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL76">
         <v>0</v>
@@ -12860,55 +12860,55 @@
         </is>
       </c>
       <c r="N77">
-        <v>3.21</v>
+        <v>3.1</v>
       </c>
       <c r="O77">
         <v>3.3</v>
       </c>
       <c r="P77">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="Q77">
-        <v>4.15</v>
+        <v>3.86</v>
       </c>
       <c r="R77">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="S77">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="T77">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="U77">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="V77">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="W77">
         <v>1.05</v>
       </c>
       <c r="X77">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y77">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="Z77">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AA77">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AB77">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AC77">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="AD77">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AE77">
         <v>1.07</v>
@@ -12917,7 +12917,7 @@
         <v>1.7</v>
       </c>
       <c r="AG77">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="AH77" t="inlineStr">
         <is>
@@ -12930,10 +12930,10 @@
         </is>
       </c>
       <c r="AJ77">
-        <v>1.71</v>
+        <v>1.29</v>
       </c>
       <c r="AK77">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AL77">
         <v>0</v>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G78">
@@ -13023,64 +13023,64 @@
         </is>
       </c>
       <c r="N78">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="O78">
+        <v>3.55</v>
+      </c>
+      <c r="P78">
         <v>3.5</v>
       </c>
-      <c r="P78">
-        <v>1.95</v>
-      </c>
       <c r="Q78">
-        <v>3.8</v>
+        <v>2.33</v>
       </c>
       <c r="R78">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="S78">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="T78">
-        <v>3.15</v>
+        <v>2.5</v>
       </c>
       <c r="U78">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="V78">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W78">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X78">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y78">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z78">
-        <v>3.58</v>
+        <v>3</v>
       </c>
       <c r="AA78">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="AB78">
-        <v>1.94</v>
+        <v>2.07</v>
       </c>
       <c r="AC78">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AD78">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE78">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AF78">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AG78">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="AH78" t="inlineStr">
         <is>
@@ -13093,10 +13093,10 @@
         </is>
       </c>
       <c r="AJ78">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="AK78">
-        <v>1.23</v>
+        <v>1.83</v>
       </c>
       <c r="AL78">
         <v>0</v>
@@ -13154,12 +13154,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G79">
@@ -13186,64 +13186,64 @@
         </is>
       </c>
       <c r="N79">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="O79">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="P79">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="Q79">
-        <v>2.33</v>
+        <v>3.8</v>
       </c>
       <c r="R79">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S79">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="T79">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U79">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="V79">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="W79">
         <v>1.1</v>
       </c>
       <c r="X79">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y79">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z79">
-        <v>3</v>
+        <v>3.58</v>
       </c>
       <c r="AA79">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AB79">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC79">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="AD79">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE79">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AF79">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AG79">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="AH79" t="inlineStr">
         <is>
@@ -13256,10 +13256,10 @@
         </is>
       </c>
       <c r="AJ79">
-        <v>1.22</v>
+        <v>1.73</v>
       </c>
       <c r="AK79">
-        <v>1.81</v>
+        <v>1.2</v>
       </c>
       <c r="AL79">
         <v>0</v>
@@ -13349,10 +13349,10 @@
         </is>
       </c>
       <c r="N80">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O80">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="P80">
         <v>4.4</v>
@@ -13370,13 +13370,13 @@
         <v>3.66</v>
       </c>
       <c r="U80">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="V80">
         <v>1.62</v>
       </c>
       <c r="W80">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X80">
         <v>1.01</v>
@@ -13385,10 +13385,10 @@
         <v>1.13</v>
       </c>
       <c r="Z80">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA80">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="AB80">
         <v>2.5</v>
@@ -13397,16 +13397,16 @@
         <v>2.31</v>
       </c>
       <c r="AD80">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AE80">
         <v>1.23</v>
       </c>
       <c r="AF80">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG80">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="AH80" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         <v>1.2</v>
       </c>
       <c r="AK80">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AL80">
         <v>0</v>
@@ -13512,19 +13512,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="O81">
-        <v>3.32</v>
+        <v>3.4</v>
       </c>
       <c r="P81">
-        <v>3.36</v>
+        <v>3.3</v>
       </c>
       <c r="Q81">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="R81">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="S81">
         <v>1.44</v>
@@ -13539,7 +13539,7 @@
         <v>1.34</v>
       </c>
       <c r="W81">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X81">
         <v>1.05</v>
@@ -13548,16 +13548,16 @@
         <v>1.37</v>
       </c>
       <c r="Z81">
-        <v>3.08</v>
+        <v>3.33</v>
 